--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7C6EDD-2F1B-4044-AE9F-EA12EF81776F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7430" yWindow="5040" windowWidth="28800" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,6 +94,23 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -112,7 +129,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -135,13 +152,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -150,6 +182,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -429,21 +479,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.75" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" customWidth="1"/>
+    <col min="11" max="11" width="15.08203125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -465,15 +515,15 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,14 +542,14 @@
       <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -524,10 +574,127 @@
       <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I5" s="4"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="5"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I8" s="4"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="7"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="K12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="K13" s="6"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I14" s="4"/>
+      <c r="K14" s="6"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="K15" s="6"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="K16" s="6"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="K22" s="6"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="K23" s="6"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="K24" s="6"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="8"/>
+      <c r="K25" s="6"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="K26" s="6"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="K27" s="6"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="K28" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7C6EDD-2F1B-4044-AE9F-EA12EF81776F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C70ACB8-E08F-412C-AD44-6DAFDC9745C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7430" yWindow="5040" windowWidth="28800" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1900" windowWidth="40520" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -77,6 +90,114 @@
   </si>
   <si>
     <t>注释</t>
+  </si>
+  <si>
+    <t>DialogueType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通角色对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>旁白</t>
+  </si>
+  <si>
+    <t>内心独白</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 系统提示</t>
+  </si>
+  <si>
+    <t>过场动画对话</t>
+  </si>
+  <si>
+    <t>剧情推进对话</t>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Narration</t>
+  </si>
+  <si>
+    <t>InnerMonologue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SystemNotification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cutscene</t>
+  </si>
+  <si>
+    <t>StoryDialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日常对话(点击角色直接触发)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支线对话（点击角色直接触发）</t>
+  </si>
+  <si>
+    <t>DailyConversation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SideQuestDialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DlgPriorityType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PrevSpriteHandleType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑色遮罩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遮罩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MASK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OVERRIDE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同时展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -115,7 +236,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,8 +249,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -167,13 +300,108 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -189,9 +417,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -201,7 +426,94 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -488,9 +800,9 @@
     <col min="6" max="6" width="9.33203125" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="38.6640625" customWidth="1"/>
-    <col min="9" max="9" width="10.75" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" customWidth="1"/>
     <col min="10" max="10" width="12.08203125" customWidth="1"/>
-    <col min="11" max="11" width="15.08203125" style="7" customWidth="1"/>
+    <col min="11" max="11" width="55.25" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -515,13 +827,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -580,121 +892,301 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="K4" s="6"/>
+      <c r="B4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="33">
+        <v>1</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="I5" s="4"/>
-      <c r="K5" s="6"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="34">
+        <v>2</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="K6" s="6"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="34">
+        <v>3</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="K7" s="6"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="34">
+        <v>4</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="I8" s="4"/>
-      <c r="K8" s="6"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="34">
+        <v>5</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="K9" s="6"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="22">
+        <v>6</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="K10" s="6"/>
+      <c r="B10" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="11">
+        <v>1</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C11" s="7"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="K11" s="6"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="19">
+        <v>2</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="K12" s="6"/>
+      <c r="B12" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="26">
+        <v>1</v>
+      </c>
+      <c r="K12" s="35" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="K13" s="6"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="23">
+        <v>2</v>
+      </c>
+      <c r="K13" s="36" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="I14" s="4"/>
-      <c r="K14" s="6"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" s="31">
+        <v>3</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="K15" s="6"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="K16" s="6"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="K17" s="6"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="K19" s="6"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="K20" s="6"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="K21" s="6"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="K22" s="6"/>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="K23" s="6"/>
+      <c r="K23" s="5"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="K24" s="6"/>
+      <c r="K24" s="5"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="8"/>
-      <c r="K25" s="6"/>
+      <c r="B25" s="7"/>
+      <c r="K25" s="5"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="K26" s="6"/>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="K27" s="6"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="K28" s="6"/>
+      <c r="K28" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C70ACB8-E08F-412C-AD44-6DAFDC9745C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1989E0-CB56-472C-A733-2CB11EA82940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1900" windowWidth="40520" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="27010" windowHeight="10250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -197,6 +197,33 @@
   </si>
   <si>
     <t>同时展示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShopUpdateType</t>
+  </si>
+  <si>
+    <t>Day</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Week</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每周</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每天刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每周刷新</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -236,7 +263,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,6 +285,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,7 +434,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -498,22 +531,31 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -827,13 +869,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -910,7 +952,7 @@
       <c r="I4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="32">
         <v>1</v>
       </c>
       <c r="K4" s="12" t="s">
@@ -930,7 +972,7 @@
       <c r="I5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="33">
         <v>2</v>
       </c>
       <c r="K5" s="16" t="s">
@@ -950,7 +992,7 @@
       <c r="I6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="33">
         <v>3</v>
       </c>
       <c r="K6" s="16" t="s">
@@ -970,7 +1012,7 @@
       <c r="I7" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="33">
         <v>4</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -990,7 +1032,7 @@
       <c r="I8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="33">
         <v>5</v>
       </c>
       <c r="K8" s="16" t="s">
@@ -1081,7 +1123,7 @@
       <c r="J12" s="26">
         <v>1</v>
       </c>
-      <c r="K12" s="35" t="s">
+      <c r="K12" s="34" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1101,7 +1143,7 @@
       <c r="J13" s="23">
         <v>2</v>
       </c>
-      <c r="K13" s="36" t="s">
+      <c r="K13" s="35" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1121,19 +1163,55 @@
       <c r="J14" s="31">
         <v>3</v>
       </c>
-      <c r="K14" s="37" t="s">
+      <c r="K14" s="36" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="K15" s="5"/>
+      <c r="B15" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" s="40">
+        <v>0</v>
+      </c>
+      <c r="K15" s="40" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="K16" s="5"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="J16" s="40">
+        <v>1</v>
+      </c>
+      <c r="K16" s="40" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H17" s="4"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1989E0-CB56-472C-A733-2CB11EA82940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103C0595-E4D3-40E6-809D-8D8081074849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="27010" windowHeight="10250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="25740" windowHeight="10250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
   <si>
     <t>##var</t>
   </si>
@@ -224,6 +224,88 @@
   </si>
   <si>
     <t>每周刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropertyType</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>GameGold</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>游戏币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行动值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>通用游戏货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏玩法货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strength</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionPointsValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UICanvasLayer</t>
+  </si>
+  <si>
+    <t>UIDown</t>
+  </si>
+  <si>
+    <t>UIPanel</t>
+  </si>
+  <si>
+    <t>UIPop</t>
+  </si>
+  <si>
+    <t>UITop</t>
+  </si>
+  <si>
+    <t>中层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIParentLayer</t>
+  </si>
+  <si>
+    <t>最底层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹窗层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顶层</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIDialogue</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -263,7 +345,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,6 +373,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,128 +534,134 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -836,15 +942,17 @@
   <dimension ref="A1:L28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="5" width="14.08203125" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="38.6640625" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" customWidth="1"/>
-    <col min="11" max="11" width="55.25" style="6" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="19" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="2" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="55.25" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -869,13 +977,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -896,7 +1004,7 @@
       <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="L2" s="1" t="s">
@@ -910,7 +1018,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="28" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -928,242 +1036,242 @@
       <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="9" t="b">
+      <c r="C4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="D4" s="10" t="b">
+      <c r="D4" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="11" t="s">
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="14">
         <v>1</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="I5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="15">
         <v>2</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="13"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="15" t="s">
+      <c r="B6" s="30"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="15">
         <v>3</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="13"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15" t="s">
+      <c r="B7" s="30"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="15">
         <v>4</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="13"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="15" t="s">
+      <c r="B8" s="30"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="15">
         <v>5</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="17"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="19" t="s">
+      <c r="B9" s="31"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="9">
         <v>6</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="K9" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="9" t="b">
+      <c r="C10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="D10" s="10" t="b">
+      <c r="D10" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="11" t="s">
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="3">
         <v>1</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="17"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="19" t="s">
+      <c r="B11" s="31"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="7">
         <v>2</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="26" t="s">
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="26" t="s">
+      <c r="I12" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="12">
         <v>1</v>
       </c>
-      <c r="K12" s="34" t="s">
+      <c r="K12" s="16" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="27"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="23" t="s">
+      <c r="B13" s="34"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="10">
         <v>2</v>
       </c>
-      <c r="K13" s="35" t="s">
+      <c r="K13" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="29"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="31" t="s">
+      <c r="B14" s="36"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="13">
         <v>3</v>
       </c>
-      <c r="K14" s="36" t="s">
+      <c r="K14" s="18" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1171,7 +1279,7 @@
       <c r="B15" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="39" t="b">
+      <c r="C15" s="19" t="b">
         <v>0</v>
       </c>
       <c r="D15" s="38" t="b">
@@ -1180,16 +1288,16 @@
       <c r="E15" s="38"/>
       <c r="F15" s="38"/>
       <c r="G15" s="38"/>
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="40" t="s">
+      <c r="I15" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="J15" s="40">
+      <c r="J15" s="19">
         <v>0</v>
       </c>
-      <c r="K15" s="40" t="s">
+      <c r="K15" s="19" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1200,71 +1308,268 @@
       <c r="E16" s="38"/>
       <c r="F16" s="38"/>
       <c r="G16" s="38"/>
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="I16" s="40" t="s">
+      <c r="I16" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="40">
+      <c r="J16" s="19">
         <v>1</v>
       </c>
-      <c r="K16" s="40" t="s">
+      <c r="K16" s="19" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="K17" s="5"/>
+      <c r="B17" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="20">
+        <v>1</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="K18" s="5"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="20">
+        <v>2</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="K19" s="5"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="39"/>
+      <c r="H19" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="20">
+        <v>3</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="K20" s="5"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" s="20">
+        <v>4</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="K21" s="5"/>
+      <c r="B21" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="23">
+        <v>0</v>
+      </c>
+      <c r="K21" s="23" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="K22" s="5"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="23">
+        <v>1</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="K23" s="5"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="J23" s="23">
+        <v>2</v>
+      </c>
+      <c r="K23" s="22" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="K24" s="5"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I24" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" s="23">
+        <v>3</v>
+      </c>
+      <c r="K24" s="22" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="7"/>
-      <c r="K25" s="5"/>
+      <c r="B25" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="J25" s="26">
+        <v>0</v>
+      </c>
+      <c r="K25" s="26" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="K26" s="5"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J26" s="26">
+        <v>1</v>
+      </c>
+      <c r="K26" s="26" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="K27" s="5"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J27" s="26">
+        <v>2</v>
+      </c>
+      <c r="K27" s="27" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="K28" s="5"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="J28" s="26">
+        <v>3</v>
+      </c>
+      <c r="K28" s="27" t="s">
+        <v>76</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103C0595-E4D3-40E6-809D-8D8081074849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920D8CA7-F74A-4F1B-BBFE-D06CBC68C859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="25740" windowHeight="10250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="2900" windowWidth="31800" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -306,6 +306,45 @@
   </si>
   <si>
     <t>UIDialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LlustrationDirection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Left</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crent</t>
+  </si>
+  <si>
+    <t>Right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>适配左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>适配中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>适配右</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -345,7 +384,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -391,6 +430,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -534,7 +579,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -598,22 +643,13 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -662,6 +698,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -939,7 +990,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -977,13 +1028,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1018,7 +1069,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="25" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1042,7 +1093,7 @@
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="26" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="3" t="b">
@@ -1068,7 +1119,7 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B5" s="30"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
@@ -1088,7 +1139,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B6" s="30"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
@@ -1108,7 +1159,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B7" s="30"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -1128,7 +1179,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B8" s="30"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
@@ -1148,7 +1199,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B9" s="31"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
@@ -1168,7 +1219,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="29" t="s">
         <v>38</v>
       </c>
       <c r="C10" s="3" t="b">
@@ -1194,7 +1245,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B11" s="31"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
@@ -1217,11 +1268,11 @@
       <c r="B12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="12" t="s">
         <v>44</v>
       </c>
@@ -1236,12 +1287,12 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B13" s="34"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
       <c r="H13" s="10" t="s">
         <v>45</v>
       </c>
@@ -1256,12 +1307,12 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B14" s="36"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="13" t="s">
         <v>46</v>
       </c>
@@ -1276,18 +1327,18 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="35" t="s">
         <v>48</v>
       </c>
       <c r="C15" s="19" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="38" t="b">
+      <c r="D15" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
       <c r="H15" s="19" t="s">
         <v>49</v>
       </c>
@@ -1302,12 +1353,12 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="19" t="s">
         <v>50</v>
       </c>
@@ -1322,18 +1373,18 @@
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="40" t="b">
+      <c r="C17" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="D17" s="41" t="b">
+      <c r="D17" s="38" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
       <c r="H17" s="20" t="s">
         <v>56</v>
       </c>
@@ -1348,12 +1399,12 @@
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
       <c r="H18" s="20" t="s">
         <v>57</v>
       </c>
@@ -1368,12 +1419,12 @@
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
       <c r="H19" s="20" t="s">
         <v>65</v>
       </c>
@@ -1388,12 +1439,12 @@
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
       <c r="H20" s="20" t="s">
         <v>66</v>
       </c>
@@ -1408,167 +1459,241 @@
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="22" t="s">
+      <c r="C21" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="I21" s="23" t="s">
+      <c r="I21" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="21">
         <v>0</v>
       </c>
-      <c r="K21" s="23" t="s">
+      <c r="K21" s="21" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="22" t="s">
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I22" s="23" t="s">
+      <c r="I22" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="J22" s="23">
+      <c r="J22" s="21">
         <v>1</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="K22" s="21" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="22" t="s">
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="39"/>
+      <c r="H23" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="I23" s="22" t="s">
+      <c r="I23" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="J23" s="23">
+      <c r="J23" s="21">
         <v>2</v>
       </c>
-      <c r="K23" s="22" t="s">
+      <c r="K23" s="21" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="22" t="s">
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="I24" s="22" t="s">
+      <c r="I24" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="J24" s="23">
+      <c r="J24" s="21">
         <v>3</v>
       </c>
-      <c r="K24" s="22" t="s">
+      <c r="K24" s="21" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25" t="s">
+      <c r="C25" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="I25" s="26" t="s">
+      <c r="I25" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="J25" s="26">
+      <c r="J25" s="24">
         <v>0</v>
       </c>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="24" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="27" t="s">
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="I26" s="26" t="s">
+      <c r="I26" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="J26" s="26">
+      <c r="J26" s="24">
         <v>1</v>
       </c>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="24" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25" t="s">
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="I27" s="27" t="s">
+      <c r="I27" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="J27" s="26">
+      <c r="J27" s="24">
         <v>2</v>
       </c>
-      <c r="K27" s="27" t="s">
+      <c r="K27" s="24" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25" t="s">
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="I28" s="27" t="s">
+      <c r="I28" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="J28" s="26">
+      <c r="J28" s="24">
         <v>3</v>
       </c>
-      <c r="K28" s="27" t="s">
+      <c r="K28" s="24" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="I29" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="J29" s="44">
+        <v>1</v>
+      </c>
+      <c r="K29" s="41" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="I30" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="J30" s="44">
+        <v>2</v>
+      </c>
+      <c r="K30" s="41" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="I31" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="J31" s="44">
+        <v>3</v>
+      </c>
+      <c r="K31" s="41" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920D8CA7-F74A-4F1B-BBFE-D06CBC68C859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7FDBD8-77F2-495A-9AD6-3FA07FFB52BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="2900" windowWidth="31800" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="2570" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="180">
   <si>
     <t>##var</t>
   </si>
@@ -345,6 +345,341 @@
   </si>
   <si>
     <t>适配右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FunctionGrpup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1=对话（如果有对话，每日第一次对话增加好感，读取通用配置）</t>
+  </si>
+  <si>
+    <t>2=好感</t>
+  </si>
+  <si>
+    <t>3=送礼</t>
+  </si>
+  <si>
+    <t>4=厨房</t>
+  </si>
+  <si>
+    <t>5=娃娃机</t>
+  </si>
+  <si>
+    <t>18=酒吧</t>
+  </si>
+  <si>
+    <t>Dialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爆点游戏</t>
+  </si>
+  <si>
+    <t>女巫毒药</t>
+  </si>
+  <si>
+    <t>展会</t>
+  </si>
+  <si>
+    <t>催稿</t>
+  </si>
+  <si>
+    <t>超市</t>
+  </si>
+  <si>
+    <t>果蔬店</t>
+  </si>
+  <si>
+    <t>布料店</t>
+  </si>
+  <si>
+    <t>情趣用品店</t>
+  </si>
+  <si>
+    <t>钓鱼</t>
+  </si>
+  <si>
+    <t>摄影</t>
+  </si>
+  <si>
+    <t>咖啡店</t>
+  </si>
+  <si>
+    <t>Goodwill</t>
+  </si>
+  <si>
+    <t>好感</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GiftGiving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>送礼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kitchen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厨房</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClawMachine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>娃娃机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExplosiveGames</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6=爆点游戏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WitchsPoison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7=女巫毒药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8=展会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exhibition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Manuscript</t>
+  </si>
+  <si>
+    <t>9=催稿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Supermarket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10=超市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11=果蔬店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FabricStore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FruitShop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12=布料店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13=情趣用品店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SexToyStore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fishing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14=钓鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15=鱼饵购买</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FishingBaitShop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼饵店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16=摄影</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Photography</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17=咖啡店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoffeeShop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒吧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Node</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无任何功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Morning</t>
+  </si>
+  <si>
+    <t>Noon</t>
+  </si>
+  <si>
+    <t>Evening</t>
+  </si>
+  <si>
+    <t>Midnight</t>
+  </si>
+  <si>
+    <t>ShowRuleTimeType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>早上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中午</t>
+  </si>
+  <si>
+    <t>傍晚</t>
+  </si>
+  <si>
+    <t>半夜</t>
+  </si>
+  <si>
+    <t>中午时间段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄昏时间段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜晚时间段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShowRuleWeekType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>周一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>周二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>周三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>周四</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>周五</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周六</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>周日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>All</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全部时间段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DialogueEndActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FunctionGroup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能面板</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -384,7 +719,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,6 +771,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,7 +932,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -700,19 +1053,52 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -990,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1028,13 +1414,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1631,70 +2017,770 @@
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="42" t="b">
+      <c r="C29" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="D29" s="43" t="b">
+      <c r="D29" s="42" t="b">
         <v>1</v>
       </c>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="41" t="s">
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="I29" s="41" t="s">
+      <c r="I29" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="J29" s="44">
+      <c r="J29" s="43">
         <v>1</v>
       </c>
-      <c r="K29" s="41" t="s">
+      <c r="K29" s="40" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44" t="s">
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="I30" s="41" t="s">
+      <c r="I30" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="J30" s="44">
+      <c r="J30" s="43">
         <v>2</v>
       </c>
-      <c r="K30" s="41" t="s">
+      <c r="K30" s="40" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="41" t="s">
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="I31" s="41" t="s">
+      <c r="I31" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="J31" s="44">
+      <c r="J31" s="43">
         <v>3</v>
       </c>
-      <c r="K31" s="41" t="s">
+      <c r="K31" s="40" t="s">
         <v>87</v>
       </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B32" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="45" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="I32" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="J32" s="47">
+        <v>0</v>
+      </c>
+      <c r="K32" s="48" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="I33" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="J33" s="47">
+        <v>1</v>
+      </c>
+      <c r="K33" s="48" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="I34" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="J34" s="47">
+        <v>2</v>
+      </c>
+      <c r="K34" s="48" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="47"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
+      <c r="G35" s="47"/>
+      <c r="H35" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="I35" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="J35" s="47">
+        <v>4</v>
+      </c>
+      <c r="K35" s="48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" s="47"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="I36" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="J36" s="47">
+        <v>8</v>
+      </c>
+      <c r="K36" s="48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="I37" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="J37" s="47">
+        <v>16</v>
+      </c>
+      <c r="K37" s="48" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="I38" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="J38" s="47">
+        <v>32</v>
+      </c>
+      <c r="K38" s="48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39" s="47"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="I39" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="J39" s="47">
+        <v>64</v>
+      </c>
+      <c r="K39" s="48" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B40" s="47"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
+      <c r="G40" s="47"/>
+      <c r="H40" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="I40" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="J40" s="47">
+        <v>128</v>
+      </c>
+      <c r="K40" s="48" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="47"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="I41" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="J41" s="47">
+        <v>256</v>
+      </c>
+      <c r="K41" s="48" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B42" s="47"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="47"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="I42" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="J42" s="47">
+        <v>512</v>
+      </c>
+      <c r="K42" s="48" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="47"/>
+      <c r="C43" s="47"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="I43" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="J43" s="47">
+        <v>1024</v>
+      </c>
+      <c r="K43" s="48" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="I44" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="J44" s="47">
+        <v>2048</v>
+      </c>
+      <c r="K44" s="48" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="47"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="I45" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="J45" s="47">
+        <v>4096</v>
+      </c>
+      <c r="K45" s="48" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="47"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+      <c r="H46" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="I46" s="47" t="s">
+        <v>105</v>
+      </c>
+      <c r="J46" s="47">
+        <v>8192</v>
+      </c>
+      <c r="K46" s="48" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47" s="47"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="I47" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="J47" s="47">
+        <v>16384</v>
+      </c>
+      <c r="K47" s="48" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B48" s="47"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="I48" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="J48" s="47">
+        <v>32768</v>
+      </c>
+      <c r="K48" s="48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="I49" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="J49" s="47">
+        <v>65535</v>
+      </c>
+      <c r="K49" s="48" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="47"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="I50" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="J50" s="47">
+        <v>131072</v>
+      </c>
+      <c r="K50" s="48" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B51" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" s="45" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
+      <c r="G51" s="50"/>
+      <c r="H51" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="I51" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="J51" s="47">
+        <v>1</v>
+      </c>
+      <c r="K51" s="49" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B52" s="50"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50"/>
+      <c r="H52" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="I52" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="J52" s="47">
+        <v>2</v>
+      </c>
+      <c r="K52" s="49" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B53" s="50"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="50"/>
+      <c r="E53" s="50"/>
+      <c r="F53" s="50"/>
+      <c r="G53" s="50"/>
+      <c r="H53" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="I53" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="J53" s="47">
+        <v>4</v>
+      </c>
+      <c r="K53" s="49" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B54" s="50"/>
+      <c r="C54" s="50"/>
+      <c r="D54" s="50"/>
+      <c r="E54" s="50"/>
+      <c r="F54" s="50"/>
+      <c r="G54" s="50"/>
+      <c r="H54" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="I54" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="J54" s="47">
+        <v>8</v>
+      </c>
+      <c r="K54" s="49" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B55" s="50"/>
+      <c r="C55" s="50"/>
+      <c r="D55" s="50"/>
+      <c r="E55" s="50"/>
+      <c r="F55" s="50"/>
+      <c r="G55" s="50"/>
+      <c r="H55" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I55" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="J55" s="47">
+        <v>15</v>
+      </c>
+      <c r="K55" s="49" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" s="52" t="b">
+        <v>1</v>
+      </c>
+      <c r="D56" s="53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="I56" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="J56" s="54">
+        <v>1</v>
+      </c>
+      <c r="K56" s="51" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B57" s="54"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="J57" s="54">
+        <v>2</v>
+      </c>
+      <c r="K57" s="51" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B58" s="54"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="54"/>
+      <c r="H58" s="54" t="s">
+        <v>163</v>
+      </c>
+      <c r="I58" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="J58" s="54">
+        <v>4</v>
+      </c>
+      <c r="K58" s="51" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B59" s="54"/>
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="I59" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="J59" s="54">
+        <v>8</v>
+      </c>
+      <c r="K59" s="51" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B60" s="54"/>
+      <c r="C60" s="54"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="54"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="54"/>
+      <c r="H60" s="54" t="s">
+        <v>167</v>
+      </c>
+      <c r="I60" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="J60" s="54">
+        <v>16</v>
+      </c>
+      <c r="K60" s="51" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B61" s="54"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="54"/>
+      <c r="H61" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="I61" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="J61" s="54">
+        <v>32</v>
+      </c>
+      <c r="K61" s="51" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B62" s="54"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="54" t="s">
+        <v>169</v>
+      </c>
+      <c r="I62" s="51" t="s">
+        <v>172</v>
+      </c>
+      <c r="J62" s="54">
+        <v>64</v>
+      </c>
+      <c r="K62" s="51" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B63" s="54"/>
+      <c r="C63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="I63" s="51" t="s">
+        <v>174</v>
+      </c>
+      <c r="J63" s="54">
+        <v>127</v>
+      </c>
+      <c r="K63" s="51" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B64" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="C64" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D64" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I64" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="J64" s="36">
+        <v>0</v>
+      </c>
+      <c r="K64" s="36"/>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="I65" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="J65" s="36">
+        <v>1</v>
+      </c>
+      <c r="K65" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1702,6 +2788,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7FDBD8-77F2-495A-9AD6-3FA07FFB52BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F931B859-A300-443F-B156-AE265142D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="2570" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3200" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -348,10 +348,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FunctionGrpup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1=对话（如果有对话，每日第一次对话增加好感，读取通用配置）</t>
   </si>
   <si>
@@ -450,10 +446,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WitchsPoison</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>7=女巫毒药</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -681,6 +673,13 @@
   <si>
     <t>功能面板</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WitchPoison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FunctionGroup</t>
   </si>
 </sst>
 </file>
@@ -2084,7 +2083,7 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="44" t="s">
-        <v>88</v>
+        <v>179</v>
       </c>
       <c r="C32" s="45" t="b">
         <v>1</v>
@@ -2096,16 +2095,16 @@
       <c r="F32" s="47"/>
       <c r="G32" s="47"/>
       <c r="H32" s="44" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I32" s="44" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J32" s="47">
         <v>0</v>
       </c>
       <c r="K32" s="48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.3">
@@ -2116,16 +2115,16 @@
       <c r="F33" s="47"/>
       <c r="G33" s="47"/>
       <c r="H33" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="I33" s="44" t="s">
         <v>95</v>
-      </c>
-      <c r="I33" s="44" t="s">
-        <v>96</v>
       </c>
       <c r="J33" s="47">
         <v>1</v>
       </c>
       <c r="K33" s="48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.3">
@@ -2136,16 +2135,16 @@
       <c r="F34" s="47"/>
       <c r="G34" s="47"/>
       <c r="H34" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="I34" s="44" t="s">
         <v>108</v>
-      </c>
-      <c r="I34" s="44" t="s">
-        <v>109</v>
       </c>
       <c r="J34" s="47">
         <v>2</v>
       </c>
       <c r="K34" s="48" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.3">
@@ -2156,16 +2155,16 @@
       <c r="F35" s="47"/>
       <c r="G35" s="47"/>
       <c r="H35" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="I35" s="44" t="s">
         <v>110</v>
-      </c>
-      <c r="I35" s="44" t="s">
-        <v>111</v>
       </c>
       <c r="J35" s="47">
         <v>4</v>
       </c>
       <c r="K35" s="48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.3">
@@ -2176,16 +2175,16 @@
       <c r="F36" s="47"/>
       <c r="G36" s="47"/>
       <c r="H36" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="I36" s="44" t="s">
         <v>112</v>
-      </c>
-      <c r="I36" s="44" t="s">
-        <v>113</v>
       </c>
       <c r="J36" s="47">
         <v>8</v>
       </c>
       <c r="K36" s="48" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.3">
@@ -2196,16 +2195,16 @@
       <c r="F37" s="47"/>
       <c r="G37" s="47"/>
       <c r="H37" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="I37" s="44" t="s">
         <v>114</v>
-      </c>
-      <c r="I37" s="44" t="s">
-        <v>115</v>
       </c>
       <c r="J37" s="47">
         <v>16</v>
       </c>
       <c r="K37" s="48" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.3">
@@ -2216,16 +2215,16 @@
       <c r="F38" s="47"/>
       <c r="G38" s="47"/>
       <c r="H38" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I38" s="47" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J38" s="47">
         <v>32</v>
       </c>
       <c r="K38" s="48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.3">
@@ -2236,16 +2235,16 @@
       <c r="F39" s="47"/>
       <c r="G39" s="47"/>
       <c r="H39" s="44" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="I39" s="47" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J39" s="47">
         <v>64</v>
       </c>
       <c r="K39" s="48" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.3">
@@ -2256,16 +2255,16 @@
       <c r="F40" s="47"/>
       <c r="G40" s="47"/>
       <c r="H40" s="44" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I40" s="47" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J40" s="47">
         <v>128</v>
       </c>
       <c r="K40" s="48" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.3">
@@ -2276,16 +2275,16 @@
       <c r="F41" s="47"/>
       <c r="G41" s="47"/>
       <c r="H41" s="47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I41" s="47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J41" s="47">
         <v>256</v>
       </c>
       <c r="K41" s="48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.3">
@@ -2296,16 +2295,16 @@
       <c r="F42" s="47"/>
       <c r="G42" s="47"/>
       <c r="H42" s="44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I42" s="47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J42" s="47">
         <v>512</v>
       </c>
       <c r="K42" s="48" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.3">
@@ -2316,16 +2315,16 @@
       <c r="F43" s="47"/>
       <c r="G43" s="47"/>
       <c r="H43" s="44" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I43" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J43" s="47">
         <v>1024</v>
       </c>
       <c r="K43" s="48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.3">
@@ -2336,16 +2335,16 @@
       <c r="F44" s="47"/>
       <c r="G44" s="47"/>
       <c r="H44" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I44" s="47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J44" s="47">
         <v>2048</v>
       </c>
       <c r="K44" s="48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.3">
@@ -2356,16 +2355,16 @@
       <c r="F45" s="47"/>
       <c r="G45" s="47"/>
       <c r="H45" s="44" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I45" s="47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J45" s="47">
         <v>4096</v>
       </c>
       <c r="K45" s="48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.3">
@@ -2376,16 +2375,16 @@
       <c r="F46" s="47"/>
       <c r="G46" s="47"/>
       <c r="H46" s="44" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I46" s="47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J46" s="47">
         <v>8192</v>
       </c>
       <c r="K46" s="48" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.3">
@@ -2396,16 +2395,16 @@
       <c r="F47" s="47"/>
       <c r="G47" s="47"/>
       <c r="H47" s="44" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I47" s="44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J47" s="47">
         <v>16384</v>
       </c>
       <c r="K47" s="48" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.3">
@@ -2416,16 +2415,16 @@
       <c r="F48" s="47"/>
       <c r="G48" s="47"/>
       <c r="H48" s="44" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I48" s="47" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J48" s="47">
         <v>32768</v>
       </c>
       <c r="K48" s="48" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.3">
@@ -2436,16 +2435,16 @@
       <c r="F49" s="47"/>
       <c r="G49" s="47"/>
       <c r="H49" s="44" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I49" s="47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J49" s="47">
         <v>65535</v>
       </c>
       <c r="K49" s="48" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.3">
@@ -2456,21 +2455,21 @@
       <c r="F50" s="47"/>
       <c r="G50" s="47"/>
       <c r="H50" s="44" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I50" s="44" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J50" s="47">
         <v>131072</v>
       </c>
       <c r="K50" s="48" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="49" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C51" s="45" t="b">
         <v>1</v>
@@ -2482,16 +2481,16 @@
       <c r="F51" s="50"/>
       <c r="G51" s="50"/>
       <c r="H51" s="50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I51" s="49" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J51" s="47">
         <v>1</v>
       </c>
       <c r="K51" s="49" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.3">
@@ -2502,16 +2501,16 @@
       <c r="F52" s="50"/>
       <c r="G52" s="50"/>
       <c r="H52" s="50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I52" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J52" s="47">
         <v>2</v>
       </c>
       <c r="K52" s="49" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
@@ -2522,16 +2521,16 @@
       <c r="F53" s="50"/>
       <c r="G53" s="50"/>
       <c r="H53" s="50" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I53" s="50" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J53" s="47">
         <v>4</v>
       </c>
       <c r="K53" s="49" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
@@ -2542,16 +2541,16 @@
       <c r="F54" s="50"/>
       <c r="G54" s="50"/>
       <c r="H54" s="50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I54" s="50" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J54" s="47">
         <v>8</v>
       </c>
       <c r="K54" s="49" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.3">
@@ -2562,21 +2561,21 @@
       <c r="F55" s="50"/>
       <c r="G55" s="50"/>
       <c r="H55" s="49" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I55" s="49" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J55" s="47">
         <v>15</v>
       </c>
       <c r="K55" s="49" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" s="51" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C56" s="52" t="b">
         <v>1</v>
@@ -2588,16 +2587,16 @@
       <c r="F56" s="54"/>
       <c r="G56" s="54"/>
       <c r="H56" s="54" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I56" s="51" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J56" s="54">
         <v>1</v>
       </c>
       <c r="K56" s="51" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.3">
@@ -2608,16 +2607,16 @@
       <c r="F57" s="54"/>
       <c r="G57" s="54"/>
       <c r="H57" s="54" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I57" s="51" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J57" s="54">
         <v>2</v>
       </c>
       <c r="K57" s="51" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.3">
@@ -2628,16 +2627,16 @@
       <c r="F58" s="54"/>
       <c r="G58" s="54"/>
       <c r="H58" s="54" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I58" s="51" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="J58" s="54">
         <v>4</v>
       </c>
       <c r="K58" s="51" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.3">
@@ -2648,16 +2647,16 @@
       <c r="F59" s="54"/>
       <c r="G59" s="54"/>
       <c r="H59" s="54" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I59" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J59" s="54">
         <v>8</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.3">
@@ -2668,16 +2667,16 @@
       <c r="F60" s="54"/>
       <c r="G60" s="54"/>
       <c r="H60" s="54" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I60" s="51" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J60" s="54">
         <v>16</v>
       </c>
       <c r="K60" s="51" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.3">
@@ -2688,16 +2687,16 @@
       <c r="F61" s="54"/>
       <c r="G61" s="54"/>
       <c r="H61" s="54" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I61" s="51" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J61" s="54">
         <v>32</v>
       </c>
       <c r="K61" s="51" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.3">
@@ -2708,16 +2707,16 @@
       <c r="F62" s="54"/>
       <c r="G62" s="54"/>
       <c r="H62" s="54" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I62" s="51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="J62" s="54">
         <v>64</v>
       </c>
       <c r="K62" s="51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.3">
@@ -2728,21 +2727,21 @@
       <c r="F63" s="54"/>
       <c r="G63" s="54"/>
       <c r="H63" s="51" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I63" s="51" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J63" s="54">
         <v>127</v>
       </c>
       <c r="K63" s="51" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C64" s="37" t="b">
         <v>0</v>
@@ -2754,10 +2753,10 @@
       <c r="F64" s="36"/>
       <c r="G64" s="36"/>
       <c r="H64" s="20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J64" s="36">
         <v>0</v>
@@ -2772,10 +2771,10 @@
       <c r="F65" s="36"/>
       <c r="G65" s="36"/>
       <c r="H65" s="20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="J65" s="36">
         <v>1</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F931B859-A300-443F-B156-AE265142D2B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74E8439-3BED-438C-87F8-E1F539CF5C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3200" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3420" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="187">
   <si>
     <t>##var</t>
   </si>
@@ -680,6 +680,32 @@
   </si>
   <si>
     <t>FunctionGroup</t>
+  </si>
+  <si>
+    <t>PermanentSceneType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Special</t>
+  </si>
+  <si>
+    <t>常驻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认就存在的场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据条件出现的场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -718,7 +744,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -791,8 +817,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -925,13 +957,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF1F2329"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF1F2329"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F2329"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1098,6 +1145,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1375,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -2781,6 +2843,52 @@
       </c>
       <c r="K65" s="36"/>
     </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B66" s="56" t="s">
+        <v>180</v>
+      </c>
+      <c r="C66" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="D66" s="58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="59"/>
+      <c r="F66" s="59"/>
+      <c r="G66" s="59"/>
+      <c r="H66" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="I66" s="60" t="s">
+        <v>183</v>
+      </c>
+      <c r="J66" s="59">
+        <v>0</v>
+      </c>
+      <c r="K66" s="60" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B67" s="59"/>
+      <c r="C67" s="59"/>
+      <c r="D67" s="59"/>
+      <c r="E67" s="59"/>
+      <c r="F67" s="59"/>
+      <c r="G67" s="59"/>
+      <c r="H67" s="59" t="s">
+        <v>182</v>
+      </c>
+      <c r="I67" s="60" t="s">
+        <v>184</v>
+      </c>
+      <c r="J67" s="59">
+        <v>1</v>
+      </c>
+      <c r="K67" s="60" t="s">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74E8439-3BED-438C-87F8-E1F539CF5C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF73C1A-8550-4329-9B07-822E45C177D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3420" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1520" windowWidth="38610" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1144,22 +1144,22 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1437,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1475,13 +1475,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2844,50 +2844,54 @@
       <c r="K65" s="36"/>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B66" s="56" t="s">
+      <c r="B66" s="55" t="s">
         <v>180</v>
       </c>
-      <c r="C66" s="57" t="b">
+      <c r="C66" s="56" t="b">
         <v>0</v>
       </c>
-      <c r="D66" s="58" t="b">
+      <c r="D66" s="57" t="b">
         <v>1</v>
       </c>
-      <c r="E66" s="59"/>
-      <c r="F66" s="59"/>
-      <c r="G66" s="59"/>
-      <c r="H66" s="59" t="s">
+      <c r="E66" s="58"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="58"/>
+      <c r="H66" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="I66" s="60" t="s">
+      <c r="I66" s="59" t="s">
         <v>183</v>
       </c>
-      <c r="J66" s="59">
+      <c r="J66" s="58">
         <v>0</v>
       </c>
-      <c r="K66" s="60" t="s">
+      <c r="K66" s="59" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B67" s="59"/>
-      <c r="C67" s="59"/>
-      <c r="D67" s="59"/>
-      <c r="E67" s="59"/>
-      <c r="F67" s="59"/>
-      <c r="G67" s="59"/>
-      <c r="H67" s="59" t="s">
+      <c r="B67" s="58"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="58"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="I67" s="60" t="s">
+      <c r="I67" s="59" t="s">
         <v>184</v>
       </c>
-      <c r="J67" s="59">
+      <c r="J67" s="58">
         <v>1</v>
       </c>
-      <c r="K67" s="60" t="s">
+      <c r="K67" s="59" t="s">
         <v>186</v>
       </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C68" s="56"/>
+      <c r="D68" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F105087-3A3C-464B-9459-FF3231178676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="7690" yWindow="3270" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="186">
   <si>
     <t>##var</t>
   </si>
@@ -228,12 +234,6 @@
   </si>
   <si>
     <t>行动值</t>
-  </si>
-  <si>
-    <t>基本生产量</t>
-  </si>
-  <si>
-    <t>基础良品率</t>
   </si>
   <si>
     <t>UICanvasLayer</t>
@@ -596,14 +596,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,162 +609,21 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -779,19 +632,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799951170384838"/>
+        <fgColor theme="9" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -809,7 +662,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -821,25 +674,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -849,194 +702,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1184,255 +851,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1613,62 +1038,21 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1926,29 +1310,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L68"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="14.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1970,15 +1354,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2004,7 +1388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2034,7 +1418,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
@@ -2060,7 +1444,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" s="8"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -2080,7 +1464,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -2100,7 +1484,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -2120,7 +1504,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -2140,7 +1524,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" s="12"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -2160,7 +1544,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
         <v>32</v>
       </c>
@@ -2186,7 +1570,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" s="12"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -2206,7 +1590,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" s="17" t="s">
         <v>39</v>
       </c>
@@ -2228,7 +1612,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
       <c r="D13" s="22"/>
@@ -2248,7 +1632,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="25"/>
       <c r="C14" s="26"/>
       <c r="D14" s="26"/>
@@ -2268,7 +1652,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" s="29" t="s">
         <v>48</v>
       </c>
@@ -2294,7 +1678,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B16" s="29"/>
       <c r="C16" s="29"/>
       <c r="D16" s="29"/>
@@ -2314,7 +1698,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="31" t="s">
         <v>55</v>
       </c>
@@ -2340,7 +1724,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="2:11">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="31"/>
@@ -2360,7 +1744,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
       <c r="D19" s="31"/>
@@ -2380,7 +1764,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="2:11">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
       <c r="D20" s="31"/>
@@ -2400,73 +1784,73 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="34" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="I21" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="34">
-        <v>5</v>
-      </c>
-      <c r="K21" s="34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11">
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="34" t="s">
+      <c r="C21" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="I22" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="J22" s="34">
-        <v>6</v>
-      </c>
-      <c r="K22" s="34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11">
-      <c r="B23" s="35" t="s">
+      <c r="I21" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="32" t="b">
+      <c r="J21" s="36">
         <v>0</v>
       </c>
-      <c r="D23" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="K21" s="36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="36" t="s">
+        <v>70</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="J22" s="36">
+        <v>1</v>
+      </c>
+      <c r="K22" s="36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
       <c r="E23" s="35"/>
       <c r="F23" s="35"/>
       <c r="G23" s="35"/>
       <c r="H23" s="36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J23" s="36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" s="36" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="35"/>
       <c r="C24" s="35"/>
       <c r="D24" s="35"/>
@@ -2474,68 +1858,68 @@
       <c r="F24" s="35"/>
       <c r="G24" s="35"/>
       <c r="H24" s="36" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J24" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24" s="36" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="J25" s="36">
-        <v>2</v>
-      </c>
-      <c r="K25" s="36" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="36" t="s">
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="37" t="s">
         <v>76</v>
       </c>
-      <c r="I26" s="36" t="s">
+      <c r="C25" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="I25" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="J25" s="39">
+        <v>0</v>
+      </c>
+      <c r="K25" s="39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="J26" s="36">
-        <v>3</v>
-      </c>
-      <c r="K26" s="36" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="I26" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="39">
+        <v>1</v>
+      </c>
+      <c r="K26" s="39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
       <c r="E27" s="38"/>
       <c r="F27" s="38"/>
       <c r="G27" s="38"/>
@@ -2543,168 +1927,168 @@
         <v>72</v>
       </c>
       <c r="I27" s="39" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J27" s="39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" s="39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="38"/>
       <c r="C28" s="38"/>
       <c r="D28" s="38"/>
       <c r="E28" s="38"/>
       <c r="F28" s="38"/>
       <c r="G28" s="38"/>
-      <c r="H28" s="39" t="s">
+      <c r="H28" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="J28" s="39">
+        <v>3</v>
+      </c>
+      <c r="K28" s="39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" s="42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="I28" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="J28" s="39">
-        <v>1</v>
-      </c>
-      <c r="K28" s="39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11">
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="I29" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="J29" s="39">
+      <c r="I29" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="J29" s="43">
+        <v>1</v>
+      </c>
+      <c r="K29" s="40" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="I30" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="J30" s="43">
         <v>2</v>
       </c>
-      <c r="K29" s="39" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="J30" s="39">
-        <v>3</v>
-      </c>
-      <c r="K30" s="39" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="42" t="b">
-        <v>1</v>
-      </c>
+      <c r="K30" s="40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
       <c r="E31" s="43"/>
       <c r="F31" s="43"/>
       <c r="G31" s="43"/>
       <c r="H31" s="40" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I31" s="40" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J31" s="43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" s="40" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="J32" s="43">
-        <v>2</v>
-      </c>
-      <c r="K32" s="40" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="I33" s="40" t="s">
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B32" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="J33" s="43">
-        <v>3</v>
-      </c>
-      <c r="K33" s="40" t="s">
+      <c r="C32" s="45" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="44" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="44" t="s">
+      <c r="I32" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="C34" s="45" t="b">
-        <v>1</v>
-      </c>
-      <c r="D34" s="46" t="b">
-        <v>1</v>
-      </c>
+      <c r="J32" s="47">
+        <v>0</v>
+      </c>
+      <c r="K32" s="48" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="J33" s="47">
+        <v>1</v>
+      </c>
+      <c r="K33" s="48" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
       <c r="E34" s="47"/>
       <c r="F34" s="47"/>
       <c r="G34" s="47"/>
-      <c r="H34" s="44" t="s">
-        <v>91</v>
+      <c r="H34" s="47" t="s">
+        <v>95</v>
       </c>
       <c r="I34" s="44" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="J34" s="47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K34" s="48" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="47"/>
       <c r="C35" s="47"/>
       <c r="D35" s="47"/>
@@ -2712,39 +2096,39 @@
       <c r="F35" s="47"/>
       <c r="G35" s="47"/>
       <c r="H35" s="44" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I35" s="44" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J35" s="47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" s="48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="47"/>
       <c r="C36" s="47"/>
       <c r="D36" s="47"/>
       <c r="E36" s="47"/>
       <c r="F36" s="47"/>
       <c r="G36" s="47"/>
-      <c r="H36" s="47" t="s">
-        <v>97</v>
+      <c r="H36" s="44" t="s">
+        <v>101</v>
       </c>
       <c r="I36" s="44" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J36" s="47">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K36" s="48" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="47"/>
       <c r="C37" s="47"/>
       <c r="D37" s="47"/>
@@ -2752,19 +2136,19 @@
       <c r="F37" s="47"/>
       <c r="G37" s="47"/>
       <c r="H37" s="44" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I37" s="44" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J37" s="47">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K37" s="48" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="47"/>
       <c r="C38" s="47"/>
       <c r="D38" s="47"/>
@@ -2772,19 +2156,19 @@
       <c r="F38" s="47"/>
       <c r="G38" s="47"/>
       <c r="H38" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="I38" s="44" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="I38" s="47" t="s">
+        <v>108</v>
       </c>
       <c r="J38" s="47">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K38" s="48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="47"/>
       <c r="C39" s="47"/>
       <c r="D39" s="47"/>
@@ -2792,19 +2176,19 @@
       <c r="F39" s="47"/>
       <c r="G39" s="47"/>
       <c r="H39" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="I39" s="44" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="I39" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="J39" s="47">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="K39" s="48" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40" s="47"/>
       <c r="C40" s="47"/>
       <c r="D40" s="47"/>
@@ -2812,39 +2196,39 @@
       <c r="F40" s="47"/>
       <c r="G40" s="47"/>
       <c r="H40" s="44" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I40" s="47" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="J40" s="47">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="K40" s="48" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="47"/>
       <c r="C41" s="47"/>
       <c r="D41" s="47"/>
       <c r="E41" s="47"/>
       <c r="F41" s="47"/>
       <c r="G41" s="47"/>
-      <c r="H41" s="44" t="s">
-        <v>112</v>
+      <c r="H41" s="47" t="s">
+        <v>116</v>
       </c>
       <c r="I41" s="47" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J41" s="47">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="K41" s="48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="47"/>
       <c r="C42" s="47"/>
       <c r="D42" s="47"/>
@@ -2852,39 +2236,39 @@
       <c r="F42" s="47"/>
       <c r="G42" s="47"/>
       <c r="H42" s="44" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I42" s="47" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J42" s="47">
-        <v>128</v>
+        <v>512</v>
       </c>
       <c r="K42" s="48" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="47"/>
       <c r="C43" s="47"/>
       <c r="D43" s="47"/>
       <c r="E43" s="47"/>
       <c r="F43" s="47"/>
       <c r="G43" s="47"/>
-      <c r="H43" s="47" t="s">
-        <v>118</v>
+      <c r="H43" s="44" t="s">
+        <v>122</v>
       </c>
       <c r="I43" s="47" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J43" s="47">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="K43" s="48" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="47"/>
       <c r="C44" s="47"/>
       <c r="D44" s="47"/>
@@ -2892,19 +2276,19 @@
       <c r="F44" s="47"/>
       <c r="G44" s="47"/>
       <c r="H44" s="44" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I44" s="47" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J44" s="47">
-        <v>512</v>
+        <v>2048</v>
       </c>
       <c r="K44" s="48" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="47"/>
       <c r="C45" s="47"/>
       <c r="D45" s="47"/>
@@ -2912,19 +2296,19 @@
       <c r="F45" s="47"/>
       <c r="G45" s="47"/>
       <c r="H45" s="44" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I45" s="47" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="J45" s="47">
-        <v>1024</v>
+        <v>4096</v>
       </c>
       <c r="K45" s="48" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="47"/>
       <c r="C46" s="47"/>
       <c r="D46" s="47"/>
@@ -2932,19 +2316,19 @@
       <c r="F46" s="47"/>
       <c r="G46" s="47"/>
       <c r="H46" s="44" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I46" s="47" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J46" s="47">
-        <v>2048</v>
+        <v>8192</v>
       </c>
       <c r="K46" s="48" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="47"/>
       <c r="C47" s="47"/>
       <c r="D47" s="47"/>
@@ -2952,19 +2336,19 @@
       <c r="F47" s="47"/>
       <c r="G47" s="47"/>
       <c r="H47" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="I47" s="47" t="s">
-        <v>131</v>
+        <v>134</v>
+      </c>
+      <c r="I47" s="44" t="s">
+        <v>135</v>
       </c>
       <c r="J47" s="47">
-        <v>4096</v>
+        <v>16384</v>
       </c>
       <c r="K47" s="48" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="47"/>
       <c r="C48" s="47"/>
       <c r="D48" s="47"/>
@@ -2972,19 +2356,19 @@
       <c r="F48" s="47"/>
       <c r="G48" s="47"/>
       <c r="H48" s="44" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="I48" s="47" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="J48" s="47">
-        <v>8192</v>
+        <v>32768</v>
       </c>
       <c r="K48" s="48" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="47"/>
       <c r="C49" s="47"/>
       <c r="D49" s="47"/>
@@ -2992,19 +2376,19 @@
       <c r="F49" s="47"/>
       <c r="G49" s="47"/>
       <c r="H49" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="I49" s="44" t="s">
-        <v>137</v>
+        <v>140</v>
+      </c>
+      <c r="I49" s="47" t="s">
+        <v>141</v>
       </c>
       <c r="J49" s="47">
-        <v>16384</v>
+        <v>65535</v>
       </c>
       <c r="K49" s="48" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="47"/>
       <c r="C50" s="47"/>
       <c r="D50" s="47"/>
@@ -3012,85 +2396,85 @@
       <c r="F50" s="47"/>
       <c r="G50" s="47"/>
       <c r="H50" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="I50" s="47" t="s">
-        <v>140</v>
+        <v>143</v>
+      </c>
+      <c r="I50" s="44" t="s">
+        <v>144</v>
       </c>
       <c r="J50" s="47">
-        <v>32768</v>
+        <v>131072</v>
       </c>
       <c r="K50" s="48" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
-      <c r="B51" s="47"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="I51" s="47" t="s">
-        <v>143</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B51" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" s="45" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
+      <c r="G51" s="50"/>
+      <c r="H51" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="I51" s="49" t="s">
+        <v>148</v>
       </c>
       <c r="J51" s="47">
-        <v>65535</v>
-      </c>
-      <c r="K51" s="48" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="B52" s="47"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="I52" s="44" t="s">
-        <v>146</v>
+        <v>1</v>
+      </c>
+      <c r="K51" s="49" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B52" s="50"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50"/>
+      <c r="H52" s="50" t="s">
+        <v>149</v>
+      </c>
+      <c r="I52" s="50" t="s">
+        <v>150</v>
       </c>
       <c r="J52" s="47">
-        <v>131072</v>
-      </c>
-      <c r="K52" s="48" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
-      <c r="B53" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="C53" s="45" t="b">
-        <v>1</v>
-      </c>
-      <c r="D53" s="46" t="b">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K52" s="49" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B53" s="50"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="50"/>
       <c r="E53" s="50"/>
       <c r="F53" s="50"/>
       <c r="G53" s="50"/>
       <c r="H53" s="50" t="s">
-        <v>149</v>
-      </c>
-      <c r="I53" s="49" t="s">
-        <v>150</v>
+        <v>152</v>
+      </c>
+      <c r="I53" s="50" t="s">
+        <v>153</v>
       </c>
       <c r="J53" s="47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K53" s="49" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="50"/>
       <c r="C54" s="50"/>
       <c r="D54" s="50"/>
@@ -3098,105 +2482,105 @@
       <c r="F54" s="50"/>
       <c r="G54" s="50"/>
       <c r="H54" s="50" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I54" s="50" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J54" s="47">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K54" s="49" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" s="50"/>
       <c r="C55" s="50"/>
       <c r="D55" s="50"/>
       <c r="E55" s="50"/>
       <c r="F55" s="50"/>
       <c r="G55" s="50"/>
-      <c r="H55" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="I55" s="50" t="s">
-        <v>155</v>
+      <c r="H55" s="49" t="s">
+        <v>158</v>
+      </c>
+      <c r="I55" s="49" t="s">
+        <v>159</v>
       </c>
       <c r="J55" s="47">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K55" s="49" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="B56" s="50"/>
-      <c r="C56" s="50"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="I56" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="J56" s="47">
-        <v>8</v>
-      </c>
-      <c r="K56" s="49" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="50"/>
-      <c r="C57" s="50"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="50"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="49" t="s">
         <v>160</v>
       </c>
-      <c r="I57" s="49" t="s">
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="J57" s="47">
-        <v>15</v>
-      </c>
-      <c r="K57" s="49" t="s">
+      <c r="C56" s="52" t="b">
+        <v>1</v>
+      </c>
+      <c r="D56" s="53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="54" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="51" t="s">
+      <c r="I56" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="C58" s="52" t="b">
-        <v>1</v>
-      </c>
-      <c r="D58" s="53" t="b">
-        <v>1</v>
-      </c>
+      <c r="J56" s="54">
+        <v>1</v>
+      </c>
+      <c r="K56" s="51" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B57" s="54"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="54"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="54"/>
+      <c r="H57" s="54" t="s">
+        <v>164</v>
+      </c>
+      <c r="I57" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="J57" s="54">
+        <v>2</v>
+      </c>
+      <c r="K57" s="51" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B58" s="54"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
       <c r="E58" s="54"/>
       <c r="F58" s="54"/>
       <c r="G58" s="54"/>
       <c r="H58" s="54" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I58" s="51" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J58" s="54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K58" s="51" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="54"/>
       <c r="C59" s="54"/>
       <c r="D59" s="54"/>
@@ -3204,19 +2588,19 @@
       <c r="F59" s="54"/>
       <c r="G59" s="54"/>
       <c r="H59" s="54" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I59" s="51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J59" s="54">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K59" s="51" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" s="54"/>
       <c r="C60" s="54"/>
       <c r="D60" s="54"/>
@@ -3224,19 +2608,19 @@
       <c r="F60" s="54"/>
       <c r="G60" s="54"/>
       <c r="H60" s="54" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I60" s="51" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J60" s="54">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K60" s="51" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="54"/>
       <c r="C61" s="54"/>
       <c r="D61" s="54"/>
@@ -3244,19 +2628,19 @@
       <c r="F61" s="54"/>
       <c r="G61" s="54"/>
       <c r="H61" s="54" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I61" s="51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J61" s="54">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K61" s="51" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62" s="54"/>
       <c r="C62" s="54"/>
       <c r="D62" s="54"/>
@@ -3264,176 +2648,136 @@
       <c r="F62" s="54"/>
       <c r="G62" s="54"/>
       <c r="H62" s="54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I62" s="51" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J62" s="54">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="K62" s="51" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63" s="54"/>
       <c r="C63" s="54"/>
       <c r="D63" s="54"/>
       <c r="E63" s="54"/>
       <c r="F63" s="54"/>
       <c r="G63" s="54"/>
-      <c r="H63" s="54" t="s">
-        <v>174</v>
+      <c r="H63" s="51" t="s">
+        <v>158</v>
       </c>
       <c r="I63" s="51" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="J63" s="54">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="K63" s="51" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="54"/>
-      <c r="C64" s="54"/>
-      <c r="D64" s="54"/>
-      <c r="E64" s="54"/>
-      <c r="F64" s="54"/>
-      <c r="G64" s="54"/>
-      <c r="H64" s="54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B64" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="I64" s="51" t="s">
+      <c r="C64" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D64" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="I64" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="J64" s="54">
-        <v>64</v>
-      </c>
-      <c r="K64" s="51" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="54"/>
-      <c r="C65" s="54"/>
-      <c r="D65" s="54"/>
-      <c r="E65" s="54"/>
-      <c r="F65" s="54"/>
-      <c r="G65" s="54"/>
-      <c r="H65" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="I65" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="J65" s="54">
-        <v>127</v>
-      </c>
-      <c r="K65" s="51" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="34" t="s">
+      <c r="J64" s="31">
+        <v>0</v>
+      </c>
+      <c r="K64" s="31"/>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B65" s="31"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31"/>
+      <c r="H65" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="I65" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="C66" s="32" t="b">
+      <c r="J65" s="31">
+        <v>1</v>
+      </c>
+      <c r="K65" s="31"/>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B66" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="C66" s="56" t="b">
         <v>0</v>
       </c>
-      <c r="D66" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="I66" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="J66" s="31">
+      <c r="D66" s="57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="58"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="58"/>
+      <c r="H66" s="58" t="s">
+        <v>180</v>
+      </c>
+      <c r="I66" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="J66" s="58">
         <v>0</v>
       </c>
-      <c r="K66" s="31"/>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="I67" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="J67" s="31">
-        <v>1</v>
-      </c>
-      <c r="K67" s="31"/>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="C68" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="D68" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58" t="s">
+      <c r="K66" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="I68" s="59" t="s">
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B67" s="58"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="58"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="J68" s="58">
-        <v>0</v>
-      </c>
-      <c r="K68" s="59" t="s">
+      <c r="I67" s="59" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="58"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58" t="s">
+      <c r="J67" s="58">
+        <v>1</v>
+      </c>
+      <c r="K67" s="59" t="s">
         <v>185</v>
       </c>
-      <c r="I69" s="59" t="s">
-        <v>186</v>
-      </c>
-      <c r="J69" s="58">
-        <v>1</v>
-      </c>
-      <c r="K69" s="59" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
-      <c r="C70" s="56"/>
-      <c r="D70" s="57"/>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C68" s="56"/>
+      <c r="D68" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="202">
   <si>
     <t>##var</t>
   </si>
@@ -230,9 +230,15 @@
     <t>行动值</t>
   </si>
   <si>
+    <t>BasicProductionVolume</t>
+  </si>
+  <si>
     <t>基本生产量</t>
   </si>
   <si>
+    <t>BasicGoodProductRate</t>
+  </si>
+  <si>
     <t>基础良品率</t>
   </si>
   <si>
@@ -471,6 +477,42 @@
   </si>
   <si>
     <t>18=酒吧</t>
+  </si>
+  <si>
+    <t>PhotoShop</t>
+  </si>
+  <si>
+    <t>摄影店</t>
+  </si>
+  <si>
+    <t>19=摄影商店</t>
+  </si>
+  <si>
+    <t>GoToTheCasino</t>
+  </si>
+  <si>
+    <t>去赌场</t>
+  </si>
+  <si>
+    <t>20=去赌场</t>
+  </si>
+  <si>
+    <t>GameCurrencyStore</t>
+  </si>
+  <si>
+    <t>游戏币商店</t>
+  </si>
+  <si>
+    <t>21=游戏币商店</t>
+  </si>
+  <si>
+    <t>BePassionate</t>
+  </si>
+  <si>
+    <t>激情一下</t>
+  </si>
+  <si>
+    <t>22=激情一下</t>
   </si>
   <si>
     <t>ShowRuleTimeType</t>
@@ -603,7 +645,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -614,16 +656,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -770,7 +804,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -833,6 +867,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -893,19 +933,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -935,18 +963,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -977,19 +993,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1001,37 +1005,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1302,316 +1282,259 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1666,6 +1589,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00C6E0B4"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1932,113 +1860,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:L74"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="19" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.8333333333333" style="2" customWidth="1"/>
+    <col min="4" max="5" width="14.0833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.33333333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="38.6666666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22.3333333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="55.25" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="2"/>
+      <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="5" t="b">
+      <c r="C4" s="6" t="b">
         <v>0</v>
       </c>
       <c r="D4" s="6" t="b">
@@ -2047,7 +1975,7 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="7" t="s">
@@ -2067,16 +1995,16 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="10" t="s">
         <v>23</v>
       </c>
       <c r="J5" s="9">
         <v>2</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="10" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2087,16 +2015,16 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>25</v>
       </c>
       <c r="J6" s="9">
         <v>3</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="10" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2107,16 +2035,16 @@
       <c r="E7" s="9"/>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="10" t="s">
         <v>27</v>
       </c>
       <c r="J7" s="9">
         <v>4</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="K7" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2127,44 +2055,44 @@
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="10" t="s">
         <v>29</v>
       </c>
       <c r="J8" s="9">
         <v>5</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="10" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="B9" s="12"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="14" t="s">
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <v>6</v>
       </c>
-      <c r="K9" s="15" t="s">
+      <c r="K9" s="13" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="5" t="b">
+      <c r="C10" s="6" t="b">
         <v>0</v>
       </c>
       <c r="D10" s="6" t="b">
@@ -2173,13 +2101,13 @@
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="6">
         <v>1</v>
       </c>
       <c r="K10" s="7" t="s">
@@ -2187,1246 +2115,1347 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14" t="s">
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="12">
         <v>2</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="K11" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="19" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="16">
         <v>1</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="K12" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="B13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="23" t="s">
+      <c r="B13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="19">
         <v>2</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="27" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="27" t="s">
+      <c r="I14" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="22">
         <v>3</v>
       </c>
-      <c r="K14" s="28" t="s">
+      <c r="K14" s="23" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="30" t="b">
+      <c r="C15" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="29" t="b">
+      <c r="D15" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="30" t="s">
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="30" t="s">
+      <c r="I15" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="30">
+      <c r="J15" s="24">
         <v>0</v>
       </c>
-      <c r="K15" s="30" t="s">
+      <c r="K15" s="24" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="30" t="s">
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="30" t="s">
+      <c r="I16" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="30">
+      <c r="J16" s="24">
         <v>1</v>
       </c>
-      <c r="K16" s="30" t="s">
+      <c r="K16" s="24" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="17" spans="2:11">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="32" t="b">
+      <c r="C17" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D17" s="33" t="b">
+      <c r="D17" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="34" t="s">
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="34" t="s">
+      <c r="I17" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J17" s="25">
         <v>1</v>
       </c>
-      <c r="K17" s="34" t="s">
+      <c r="K17" s="25" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="2:11">
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="34" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="I18" s="34" t="s">
+      <c r="I18" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="34">
+      <c r="J18" s="25">
         <v>2</v>
       </c>
-      <c r="K18" s="34" t="s">
+      <c r="K18" s="25" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="34" t="s">
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="I19" s="34" t="s">
+      <c r="I19" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="25">
         <v>3</v>
       </c>
-      <c r="K19" s="34" t="s">
+      <c r="K19" s="25" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="34" t="s">
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="J20" s="34">
+      <c r="J20" s="25">
         <v>4</v>
       </c>
-      <c r="K20" s="34" t="s">
+      <c r="K20" s="25" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="34" t="s">
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="I21" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="J21" s="34">
+      <c r="I21" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="25">
         <v>5</v>
       </c>
-      <c r="K21" s="34" t="s">
-        <v>67</v>
+      <c r="K21" s="25" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:11">
-      <c r="B22" s="31"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I22" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="J22" s="34">
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" s="25">
         <v>6</v>
       </c>
-      <c r="K22" s="34" t="s">
-        <v>68</v>
+      <c r="K22" s="25" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="2:11">
-      <c r="B23" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="32" t="b">
+      <c r="B23" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D23" s="33" t="b">
+      <c r="D23" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23" s="36">
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="I23" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="J23" s="27">
         <v>0</v>
       </c>
-      <c r="K23" s="36" t="s">
-        <v>71</v>
+      <c r="K23" s="27" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="I24" s="36" t="s">
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="J24" s="27">
+        <v>1</v>
+      </c>
+      <c r="K24" s="27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="I25" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25" s="27">
+        <v>2</v>
+      </c>
+      <c r="K25" s="27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="J26" s="27">
+        <v>3</v>
+      </c>
+      <c r="K26" s="27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="I27" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="J24" s="36">
+      <c r="J27" s="29">
+        <v>0</v>
+      </c>
+      <c r="K27" s="29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="J28" s="29">
         <v>1</v>
       </c>
-      <c r="K24" s="36" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="I25" s="36" t="s">
+      <c r="K28" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="J25" s="36">
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="J29" s="29">
         <v>2</v>
       </c>
-      <c r="K25" s="36" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="I26" s="36" t="s">
+      <c r="K29" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="J26" s="36">
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="J30" s="29">
         <v>3</v>
       </c>
-      <c r="K26" s="36" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="32" t="b">
+      <c r="K30" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="D27" s="33" t="b">
+      <c r="D31" s="31" t="b">
         <v>1</v>
       </c>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="I27" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="J27" s="39">
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="I31" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="J31" s="30">
+        <v>1</v>
+      </c>
+      <c r="K31" s="30" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="I32" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="J32" s="30">
+        <v>2</v>
+      </c>
+      <c r="K32" s="30" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="I33" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="J33" s="30">
+        <v>3</v>
+      </c>
+      <c r="K33" s="30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="I34" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="J34" s="32">
         <v>0</v>
       </c>
-      <c r="K27" s="39" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39" t="s">
-        <v>79</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="J28" s="39">
+      <c r="K34" s="32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="J35" s="32">
         <v>1</v>
       </c>
-      <c r="K28" s="39" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11">
-      <c r="B29" s="38"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="I29" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="J29" s="39">
+      <c r="K35" s="32" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="I36" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="J36" s="32">
+        <f t="shared" ref="J36:J56" si="0">J35*2</f>
         <v>2</v>
       </c>
-      <c r="K29" s="39" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="J30" s="39">
-        <v>3</v>
-      </c>
-      <c r="K30" s="39" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="41" t="b">
+      <c r="K36" s="32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="I37" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="J37" s="32">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="K37" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="I38" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="J38" s="32">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K38" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="I39" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="J39" s="32">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="K39" s="32" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="I40" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="J40" s="32">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="K40" s="32" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="I41" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="J41" s="32">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="K41" s="32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="I42" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="J42" s="32">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="K42" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="I43" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="J43" s="32">
+        <f t="shared" si="0"/>
+        <v>256</v>
+      </c>
+      <c r="K43" s="32" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11">
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="I44" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="J44" s="32">
+        <f t="shared" si="0"/>
+        <v>512</v>
+      </c>
+      <c r="K44" s="32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11">
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="I45" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="J45" s="32">
+        <f t="shared" si="0"/>
+        <v>1024</v>
+      </c>
+      <c r="K45" s="32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="I46" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="J46" s="32">
+        <f t="shared" si="0"/>
+        <v>2048</v>
+      </c>
+      <c r="K46" s="32" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="I47" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="J47" s="32">
+        <f t="shared" si="0"/>
+        <v>4096</v>
+      </c>
+      <c r="K47" s="32" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11">
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="I48" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="J48" s="32">
+        <f t="shared" si="0"/>
+        <v>8192</v>
+      </c>
+      <c r="K48" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11">
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="I49" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="J49" s="32">
+        <f t="shared" si="0"/>
+        <v>16384</v>
+      </c>
+      <c r="K49" s="32" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="I50" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="J50" s="32">
+        <f t="shared" si="0"/>
+        <v>32768</v>
+      </c>
+      <c r="K50" s="32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="I51" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="J51" s="32">
+        <f t="shared" si="0"/>
+        <v>65536</v>
+      </c>
+      <c r="K51" s="32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="I52" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="J52" s="32">
+        <f t="shared" si="0"/>
+        <v>131072</v>
+      </c>
+      <c r="K52" s="32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="I53" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="J53" s="32">
+        <f t="shared" si="0"/>
+        <v>262144</v>
+      </c>
+      <c r="K53" s="32" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="2:11">
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="I54" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="J54" s="34">
+        <f t="shared" si="0"/>
+        <v>524288</v>
+      </c>
+      <c r="K54" s="34" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="2:11">
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="I55" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="J55" s="34">
+        <f t="shared" si="0"/>
+        <v>1048576</v>
+      </c>
+      <c r="K55" s="34" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="2:11">
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="I56" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="J56" s="34">
+        <f t="shared" si="0"/>
+        <v>2097152</v>
+      </c>
+      <c r="K56" s="34" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
+      <c r="B57" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="C57" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D57" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="I57" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="J57" s="32">
+        <v>1</v>
+      </c>
+      <c r="K57" s="35" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" s="35"/>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="I58" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="J58" s="32">
+        <v>2</v>
+      </c>
+      <c r="K58" s="35" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="I59" s="35" t="s">
+        <v>169</v>
+      </c>
+      <c r="J59" s="32">
+        <v>4</v>
+      </c>
+      <c r="K59" s="35" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="I60" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="J60" s="32">
+        <v>8</v>
+      </c>
+      <c r="K60" s="35" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="I61" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="J61" s="32">
+        <v>15</v>
+      </c>
+      <c r="K61" s="35" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
+      <c r="B62" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="C62" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="D62" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="36"/>
+      <c r="F62" s="36"/>
+      <c r="G62" s="36"/>
+      <c r="H62" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="I62" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="J62" s="36">
+        <v>1</v>
+      </c>
+      <c r="K62" s="36" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="36"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="36"/>
+      <c r="H63" s="36" t="s">
+        <v>180</v>
+      </c>
+      <c r="I63" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="J63" s="36">
+        <v>2</v>
+      </c>
+      <c r="K63" s="36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="I64" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="J64" s="36">
+        <v>4</v>
+      </c>
+      <c r="K64" s="36" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="I65" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="J65" s="36">
+        <v>8</v>
+      </c>
+      <c r="K65" s="36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="36"/>
+      <c r="H66" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="I66" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="J66" s="36">
+        <v>16</v>
+      </c>
+      <c r="K66" s="36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" s="36"/>
+      <c r="C67" s="36"/>
+      <c r="D67" s="36"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="36"/>
+      <c r="G67" s="36"/>
+      <c r="H67" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="I67" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="J67" s="36">
+        <v>32</v>
+      </c>
+      <c r="K67" s="36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="I68" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="J68" s="36">
+        <v>64</v>
+      </c>
+      <c r="K68" s="36" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11">
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="I69" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="J69" s="36">
+        <v>127</v>
+      </c>
+      <c r="K69" s="36" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="B70" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="C70" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D31" s="42" t="b">
+      <c r="D70" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="I31" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="J31" s="43">
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="I70" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="J70" s="25">
+        <v>0</v>
+      </c>
+      <c r="K70" s="25"/>
+    </row>
+    <row r="71" spans="2:11">
+      <c r="B71" s="25"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
+      <c r="H71" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="I71" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="J71" s="25">
         <v>1</v>
       </c>
-      <c r="K31" s="40" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="J32" s="43">
-        <v>2</v>
-      </c>
-      <c r="K32" s="40" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="I33" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="J33" s="43">
-        <v>3</v>
-      </c>
-      <c r="K33" s="40" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="45" t="b">
+      <c r="K71" s="25"/>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="B72" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D72" s="39" t="b">
         <v>1</v>
       </c>
-      <c r="D34" s="46" t="b">
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="I72" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="J72" s="40">
+        <v>0</v>
+      </c>
+      <c r="K72" s="40" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
+      <c r="B73" s="40"/>
+      <c r="C73" s="40"/>
+      <c r="D73" s="40"/>
+      <c r="E73" s="40"/>
+      <c r="F73" s="40"/>
+      <c r="G73" s="40"/>
+      <c r="H73" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="I73" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="J73" s="40">
         <v>1</v>
       </c>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="I34" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="J34" s="47">
-        <v>0</v>
-      </c>
-      <c r="K34" s="48" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="I35" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="J35" s="47">
-        <v>1</v>
-      </c>
-      <c r="K35" s="48" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
-      <c r="G36" s="47"/>
-      <c r="H36" s="47" t="s">
-        <v>97</v>
-      </c>
-      <c r="I36" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="J36" s="47">
-        <v>2</v>
-      </c>
-      <c r="K36" s="48" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="B37" s="47"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
-      <c r="H37" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="I37" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="J37" s="47">
-        <v>4</v>
-      </c>
-      <c r="K37" s="48" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="47"/>
-      <c r="H38" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="I38" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="J38" s="47">
-        <v>8</v>
-      </c>
-      <c r="K38" s="48" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="47"/>
-      <c r="C39" s="47"/>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="I39" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="J39" s="47">
-        <v>16</v>
-      </c>
-      <c r="K39" s="48" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="B40" s="47"/>
-      <c r="C40" s="47"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="I40" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="J40" s="47">
-        <v>32</v>
-      </c>
-      <c r="K40" s="48" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11">
-      <c r="B41" s="47"/>
-      <c r="C41" s="47"/>
-      <c r="D41" s="47"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="47"/>
-      <c r="G41" s="47"/>
-      <c r="H41" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="I41" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="J41" s="47">
-        <v>64</v>
-      </c>
-      <c r="K41" s="48" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="B42" s="47"/>
-      <c r="C42" s="47"/>
-      <c r="D42" s="47"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="47"/>
-      <c r="G42" s="47"/>
-      <c r="H42" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="I42" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="J42" s="47">
-        <v>128</v>
-      </c>
-      <c r="K42" s="48" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
-      <c r="B43" s="47"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="I43" s="47" t="s">
-        <v>119</v>
-      </c>
-      <c r="J43" s="47">
-        <v>256</v>
-      </c>
-      <c r="K43" s="48" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
-      <c r="B44" s="47"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="47"/>
-      <c r="E44" s="47"/>
-      <c r="F44" s="47"/>
-      <c r="G44" s="47"/>
-      <c r="H44" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="I44" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="J44" s="47">
-        <v>512</v>
-      </c>
-      <c r="K44" s="48" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11">
-      <c r="B45" s="47"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="I45" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="J45" s="47">
-        <v>1024</v>
-      </c>
-      <c r="K45" s="48" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
-      <c r="B46" s="47"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="47"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="47"/>
-      <c r="G46" s="47"/>
-      <c r="H46" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="I46" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="J46" s="47">
-        <v>2048</v>
-      </c>
-      <c r="K46" s="48" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11">
-      <c r="B47" s="47"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="44" t="s">
-        <v>130</v>
-      </c>
-      <c r="I47" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="J47" s="47">
-        <v>4096</v>
-      </c>
-      <c r="K47" s="48" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="B48" s="47"/>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="I48" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="J48" s="47">
-        <v>8192</v>
-      </c>
-      <c r="K48" s="48" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11">
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="I49" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="J49" s="47">
-        <v>16384</v>
-      </c>
-      <c r="K49" s="48" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11">
-      <c r="B50" s="47"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="47"/>
-      <c r="F50" s="47"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="I50" s="47" t="s">
-        <v>140</v>
-      </c>
-      <c r="J50" s="47">
-        <v>32768</v>
-      </c>
-      <c r="K50" s="48" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
-      <c r="B51" s="47"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
-      <c r="F51" s="47"/>
-      <c r="G51" s="47"/>
-      <c r="H51" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="I51" s="47" t="s">
-        <v>143</v>
-      </c>
-      <c r="J51" s="47">
-        <v>65535</v>
-      </c>
-      <c r="K51" s="48" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="B52" s="47"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="47"/>
-      <c r="F52" s="47"/>
-      <c r="G52" s="47"/>
-      <c r="H52" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="I52" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="J52" s="47">
-        <v>131072</v>
-      </c>
-      <c r="K52" s="48" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
-      <c r="B53" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="C53" s="45" t="b">
-        <v>1</v>
-      </c>
-      <c r="D53" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="50"/>
-      <c r="F53" s="50"/>
-      <c r="G53" s="50"/>
-      <c r="H53" s="50" t="s">
-        <v>149</v>
-      </c>
-      <c r="I53" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="J53" s="47">
-        <v>1</v>
-      </c>
-      <c r="K53" s="49" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
-      <c r="B54" s="50"/>
-      <c r="C54" s="50"/>
-      <c r="D54" s="50"/>
-      <c r="E54" s="50"/>
-      <c r="F54" s="50"/>
-      <c r="G54" s="50"/>
-      <c r="H54" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="I54" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="J54" s="47">
-        <v>2</v>
-      </c>
-      <c r="K54" s="49" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="B55" s="50"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="50"/>
-      <c r="E55" s="50"/>
-      <c r="F55" s="50"/>
-      <c r="G55" s="50"/>
-      <c r="H55" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="I55" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="J55" s="47">
-        <v>4</v>
-      </c>
-      <c r="K55" s="49" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="B56" s="50"/>
-      <c r="C56" s="50"/>
-      <c r="D56" s="50"/>
-      <c r="E56" s="50"/>
-      <c r="F56" s="50"/>
-      <c r="G56" s="50"/>
-      <c r="H56" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="I56" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="J56" s="47">
-        <v>8</v>
-      </c>
-      <c r="K56" s="49" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="50"/>
-      <c r="C57" s="50"/>
-      <c r="D57" s="50"/>
-      <c r="E57" s="50"/>
-      <c r="F57" s="50"/>
-      <c r="G57" s="50"/>
-      <c r="H57" s="49" t="s">
-        <v>160</v>
-      </c>
-      <c r="I57" s="49" t="s">
-        <v>161</v>
-      </c>
-      <c r="J57" s="47">
-        <v>15</v>
-      </c>
-      <c r="K57" s="49" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="C58" s="52" t="b">
-        <v>1</v>
-      </c>
-      <c r="D58" s="53" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="54"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
-      <c r="H58" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="I58" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="J58" s="54">
-        <v>1</v>
-      </c>
-      <c r="K58" s="51" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="B59" s="54"/>
-      <c r="C59" s="54"/>
-      <c r="D59" s="54"/>
-      <c r="E59" s="54"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="54"/>
-      <c r="H59" s="54" t="s">
-        <v>166</v>
-      </c>
-      <c r="I59" s="51" t="s">
-        <v>167</v>
-      </c>
-      <c r="J59" s="54">
-        <v>2</v>
-      </c>
-      <c r="K59" s="51" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54"/>
-      <c r="F60" s="54"/>
-      <c r="G60" s="54"/>
-      <c r="H60" s="54" t="s">
-        <v>168</v>
-      </c>
-      <c r="I60" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="J60" s="54">
-        <v>4</v>
-      </c>
-      <c r="K60" s="51" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="54"/>
-      <c r="C61" s="54"/>
-      <c r="D61" s="54"/>
-      <c r="E61" s="54"/>
-      <c r="F61" s="54"/>
-      <c r="G61" s="54"/>
-      <c r="H61" s="54" t="s">
-        <v>170</v>
-      </c>
-      <c r="I61" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="J61" s="54">
-        <v>8</v>
-      </c>
-      <c r="K61" s="51" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="54"/>
-      <c r="C62" s="54"/>
-      <c r="D62" s="54"/>
-      <c r="E62" s="54"/>
-      <c r="F62" s="54"/>
-      <c r="G62" s="54"/>
-      <c r="H62" s="54" t="s">
-        <v>172</v>
-      </c>
-      <c r="I62" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="J62" s="54">
-        <v>16</v>
-      </c>
-      <c r="K62" s="51" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="54"/>
-      <c r="C63" s="54"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="54"/>
-      <c r="F63" s="54"/>
-      <c r="G63" s="54"/>
-      <c r="H63" s="54" t="s">
-        <v>174</v>
-      </c>
-      <c r="I63" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="J63" s="54">
-        <v>32</v>
-      </c>
-      <c r="K63" s="51" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="54"/>
-      <c r="C64" s="54"/>
-      <c r="D64" s="54"/>
-      <c r="E64" s="54"/>
-      <c r="F64" s="54"/>
-      <c r="G64" s="54"/>
-      <c r="H64" s="54" t="s">
-        <v>176</v>
-      </c>
-      <c r="I64" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="J64" s="54">
-        <v>64</v>
-      </c>
-      <c r="K64" s="51" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="54"/>
-      <c r="C65" s="54"/>
-      <c r="D65" s="54"/>
-      <c r="E65" s="54"/>
-      <c r="F65" s="54"/>
-      <c r="G65" s="54"/>
-      <c r="H65" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="I65" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="J65" s="54">
-        <v>127</v>
-      </c>
-      <c r="K65" s="51" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="C66" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="D66" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="I66" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="J66" s="31">
-        <v>0</v>
-      </c>
-      <c r="K66" s="31"/>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="I67" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="J67" s="31">
-        <v>1</v>
-      </c>
-      <c r="K67" s="31"/>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="55" t="s">
-        <v>181</v>
-      </c>
-      <c r="C68" s="56" t="b">
-        <v>0</v>
-      </c>
-      <c r="D68" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="I68" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="J68" s="58">
-        <v>0</v>
-      </c>
-      <c r="K68" s="59" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="58"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58" t="s">
-        <v>185</v>
-      </c>
-      <c r="I69" s="59" t="s">
-        <v>186</v>
-      </c>
-      <c r="J69" s="58">
-        <v>1</v>
-      </c>
-      <c r="K69" s="59" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
-      <c r="C70" s="56"/>
-      <c r="D70" s="57"/>
+      <c r="K73" s="40" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391C0D39-0FE6-491D-BBCC-D0D46C2565C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="0" yWindow="1140" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -638,14 +644,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,154 +657,18 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -813,19 +677,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799951170384838"/>
+        <fgColor theme="9" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -843,7 +707,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -855,13 +719,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -873,13 +737,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -889,134 +753,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1164,251 +902,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1416,9 +912,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1536,67 +1029,26 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00C6E0B4"/>
+      <color rgb="FFC6E0B4"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1854,1615 +1306,1612 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L74"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L73"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="19" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" style="2" customWidth="1"/>
-    <col min="4" max="5" width="14.0833333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="38.6666666666667" style="2" customWidth="1"/>
-    <col min="9" max="9" width="22.3333333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="55.25" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="3" t="s">
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="B4" s="5" t="s">
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="b">
+      <c r="C4" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D4" s="6" t="b">
+      <c r="D4" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>2</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>3</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="B7" s="8"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="7"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>4</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="7"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>5</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="11">
         <v>6</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="B10" s="14" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="6" t="b">
+      <c r="C10" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D10" s="6" t="b">
+      <c r="D10" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6" t="s">
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>1</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <v>2</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
-      <c r="B12" s="15" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B12" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16" t="s">
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="15">
         <v>1</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="K12" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
-      <c r="B13" s="18"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B13" s="17"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="18">
         <v>2</v>
       </c>
-      <c r="K13" s="20" t="s">
+      <c r="K13" s="19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
-      <c r="B14" s="21"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="21">
         <v>3</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="K14" s="22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
-      <c r="B15" s="24" t="s">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B15" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="24" t="b">
+      <c r="C15" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="24" t="b">
+      <c r="D15" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24" t="s">
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="24" t="s">
+      <c r="I15" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="23">
         <v>0</v>
       </c>
-      <c r="K15" s="24" t="s">
+      <c r="K15" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I16" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="24">
+      <c r="J16" s="23">
         <v>1</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="23" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
-      <c r="B17" s="25" t="s">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="26" t="b">
+      <c r="C17" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D17" s="26" t="b">
+      <c r="D17" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25" t="s">
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="24">
         <v>1</v>
       </c>
-      <c r="K17" s="25" t="s">
+      <c r="K17" s="24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="2:11">
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25" t="s">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="I18" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="24">
         <v>2</v>
       </c>
-      <c r="K18" s="25" t="s">
+      <c r="K18" s="24" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25" t="s">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="I19" s="25" t="s">
+      <c r="I19" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="24">
         <v>3</v>
       </c>
-      <c r="K19" s="25" t="s">
+      <c r="K19" s="24" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="2:11">
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25" t="s">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="I20" s="25" t="s">
+      <c r="I20" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="24">
         <v>4</v>
       </c>
-      <c r="K20" s="25" t="s">
+      <c r="K20" s="24" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="I21" s="25" t="s">
+      <c r="I21" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="24">
         <v>5</v>
       </c>
-      <c r="K21" s="25" t="s">
+      <c r="K21" s="24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="2:11">
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25" t="s">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="I22" s="25" t="s">
+      <c r="I22" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="24">
         <v>6</v>
       </c>
-      <c r="K22" s="25" t="s">
+      <c r="K22" s="24" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="2:11">
-      <c r="B23" s="27" t="s">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="26" t="b">
+      <c r="C23" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D23" s="26" t="b">
+      <c r="D23" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27" t="s">
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="I23" s="27" t="s">
+      <c r="I23" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="26">
         <v>0</v>
       </c>
-      <c r="K23" s="27" t="s">
+      <c r="K23" s="26" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="2:11">
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27" t="s">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="27" t="s">
+      <c r="I24" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="J24" s="27">
+      <c r="J24" s="26">
         <v>1</v>
       </c>
-      <c r="K24" s="27" t="s">
+      <c r="K24" s="26" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27" t="s">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="I25" s="27" t="s">
+      <c r="I25" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="J25" s="27">
+      <c r="J25" s="26">
         <v>2</v>
       </c>
-      <c r="K25" s="27" t="s">
+      <c r="K25" s="26" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27" t="s">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="I26" s="27" t="s">
+      <c r="I26" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="J26" s="27">
+      <c r="J26" s="26">
         <v>3</v>
       </c>
-      <c r="K26" s="27" t="s">
+      <c r="K26" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="28" t="s">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="26" t="b">
+      <c r="C27" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D27" s="26" t="b">
+      <c r="D27" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29" t="s">
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="I27" s="29" t="s">
+      <c r="I27" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="28">
         <v>0</v>
       </c>
-      <c r="K27" s="29" t="s">
+      <c r="K27" s="28" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29" t="s">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="I28" s="29" t="s">
+      <c r="I28" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="28">
         <v>1</v>
       </c>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="2:11">
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29" t="s">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="I29" s="29" t="s">
+      <c r="I29" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="J29" s="29">
+      <c r="J29" s="28">
         <v>2</v>
       </c>
-      <c r="K29" s="29" t="s">
+      <c r="K29" s="28" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29" t="s">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="I30" s="29" t="s">
+      <c r="I30" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="28">
         <v>3</v>
       </c>
-      <c r="K30" s="29" t="s">
+      <c r="K30" s="28" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="30" t="s">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C31" s="31" t="b">
+      <c r="C31" s="30" t="b">
         <v>0</v>
       </c>
-      <c r="D31" s="31" t="b">
+      <c r="D31" s="30" t="b">
         <v>1</v>
       </c>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30" t="s">
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="I31" s="30" t="s">
+      <c r="I31" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J31" s="29">
         <v>1</v>
       </c>
-      <c r="K31" s="30" t="s">
+      <c r="K31" s="29" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30" t="s">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="I32" s="30" t="s">
+      <c r="I32" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="J32" s="30">
+      <c r="J32" s="29">
         <v>2</v>
       </c>
-      <c r="K32" s="30" t="s">
+      <c r="K32" s="29" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30" t="s">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="I33" s="30" t="s">
+      <c r="I33" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J33" s="30">
+      <c r="J33" s="29">
         <v>3</v>
       </c>
-      <c r="K33" s="30" t="s">
+      <c r="K33" s="29" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="32" t="s">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="33" t="b">
+      <c r="C34" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="D34" s="33" t="b">
+      <c r="D34" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32" t="s">
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="I34" s="32" t="s">
+      <c r="I34" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="J34" s="32">
+      <c r="J34" s="31">
         <v>0</v>
       </c>
-      <c r="K34" s="32" t="s">
+      <c r="K34" s="31" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32" t="s">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="I35" s="32" t="s">
+      <c r="I35" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="J35" s="32">
+      <c r="J35" s="31">
         <v>1</v>
       </c>
-      <c r="K35" s="32" t="s">
+      <c r="K35" s="31" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32" t="s">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="I36" s="32" t="s">
+      <c r="I36" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="J36" s="32">
+      <c r="J36" s="31">
         <f t="shared" ref="J36:J56" si="0">J35*2</f>
         <v>2</v>
       </c>
-      <c r="K36" s="32" t="s">
+      <c r="K36" s="31" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="2:11">
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32" t="s">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="I37" s="32" t="s">
+      <c r="I37" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="J37" s="32">
+      <c r="J37" s="31">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K37" s="32" t="s">
+      <c r="K37" s="31" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32" t="s">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="I38" s="32" t="s">
+      <c r="I38" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="31">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K38" s="32" t="s">
+      <c r="K38" s="31" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32" t="s">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="I39" s="32" t="s">
+      <c r="I39" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="31">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="K39" s="32" t="s">
+      <c r="K39" s="31" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="2:11">
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32" t="s">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="I40" s="32" t="s">
+      <c r="I40" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="J40" s="32">
+      <c r="J40" s="31">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="K40" s="32" t="s">
+      <c r="K40" s="31" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="2:11">
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32" t="s">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="I41" s="32" t="s">
+      <c r="I41" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="31">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="K41" s="32" t="s">
+      <c r="K41" s="31" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="2:11">
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32" t="s">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="I42" s="32" t="s">
+      <c r="I42" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="31">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="K42" s="32" t="s">
+      <c r="K42" s="31" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="2:11">
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32" t="s">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="I43" s="32" t="s">
+      <c r="I43" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="J43" s="32">
+      <c r="J43" s="31">
         <f t="shared" si="0"/>
         <v>256</v>
       </c>
-      <c r="K43" s="32" t="s">
+      <c r="K43" s="31" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="2:11">
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32" t="s">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B44" s="31"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="I44" s="32" t="s">
+      <c r="I44" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="31">
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
-      <c r="K44" s="32" t="s">
+      <c r="K44" s="31" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="2:11">
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32" t="s">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="I45" s="32" t="s">
+      <c r="I45" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="31">
         <f t="shared" si="0"/>
         <v>1024</v>
       </c>
-      <c r="K45" s="32" t="s">
+      <c r="K45" s="31" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="2:11">
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32" t="s">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="I46" s="32" t="s">
+      <c r="I46" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="J46" s="32">
+      <c r="J46" s="31">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
-      <c r="K46" s="32" t="s">
+      <c r="K46" s="31" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="2:11">
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32" t="s">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="I47" s="32" t="s">
+      <c r="I47" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="J47" s="32">
+      <c r="J47" s="31">
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
-      <c r="K47" s="32" t="s">
+      <c r="K47" s="31" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="2:11">
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32" t="s">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="I48" s="32" t="s">
+      <c r="I48" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="J48" s="32">
+      <c r="J48" s="31">
         <f t="shared" si="0"/>
         <v>8192</v>
       </c>
-      <c r="K48" s="32" t="s">
+      <c r="K48" s="31" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="2:11">
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32" t="s">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="I49" s="32" t="s">
+      <c r="I49" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="J49" s="32">
+      <c r="J49" s="31">
         <f t="shared" si="0"/>
         <v>16384</v>
       </c>
-      <c r="K49" s="32" t="s">
+      <c r="K49" s="31" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="2:11">
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32" t="s">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="31"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="I50" s="32" t="s">
+      <c r="I50" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="J50" s="32">
+      <c r="J50" s="31">
         <f t="shared" si="0"/>
         <v>32768</v>
       </c>
-      <c r="K50" s="32" t="s">
+      <c r="K50" s="31" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="2:11">
-      <c r="B51" s="32"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32" t="s">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="I51" s="32" t="s">
+      <c r="I51" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="J51" s="32">
+      <c r="J51" s="31">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
-      <c r="K51" s="32" t="s">
+      <c r="K51" s="31" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="2:11">
-      <c r="B52" s="32"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32" t="s">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="I52" s="32" t="s">
+      <c r="I52" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="J52" s="32">
+      <c r="J52" s="31">
         <f t="shared" si="0"/>
         <v>131072</v>
       </c>
-      <c r="K52" s="32" t="s">
+      <c r="K52" s="31" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="2:11">
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32" t="s">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="I53" s="32" t="s">
+      <c r="I53" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="J53" s="32">
+      <c r="J53" s="31">
         <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K53" s="32" t="s">
+      <c r="K53" s="31" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" spans="2:11">
-      <c r="B54" s="34"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="34" t="s">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B54" s="33"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="I54" s="34" t="s">
+      <c r="I54" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="J54" s="34">
+      <c r="J54" s="33">
         <f t="shared" si="0"/>
         <v>524288</v>
       </c>
-      <c r="K54" s="34" t="s">
+      <c r="K54" s="33" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" spans="2:11">
-      <c r="B55" s="34"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34" t="s">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="I55" s="34" t="s">
+      <c r="I55" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="J55" s="34">
+      <c r="J55" s="33">
         <f t="shared" si="0"/>
         <v>1048576</v>
       </c>
-      <c r="K55" s="34" t="s">
+      <c r="K55" s="33" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" spans="2:11">
-      <c r="B56" s="34"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="34" t="s">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="I56" s="34" t="s">
+      <c r="I56" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="J56" s="34">
+      <c r="J56" s="33">
         <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
-      <c r="K56" s="34" t="s">
+      <c r="K56" s="33" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="35" t="s">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B57" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="C57" s="33" t="b">
+      <c r="C57" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="D57" s="33" t="b">
+      <c r="D57" s="32" t="b">
         <v>1</v>
       </c>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35" t="s">
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="I57" s="35" t="s">
+      <c r="I57" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="31">
         <v>1</v>
       </c>
-      <c r="K57" s="35" t="s">
+      <c r="K57" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="35"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="35"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35" t="s">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B58" s="34"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="I58" s="35" t="s">
+      <c r="I58" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="J58" s="32">
+      <c r="J58" s="31">
         <v>2</v>
       </c>
-      <c r="K58" s="35" t="s">
+      <c r="K58" s="34" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="59" spans="2:11">
-      <c r="B59" s="35"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35" t="s">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="I59" s="35" t="s">
+      <c r="I59" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="J59" s="32">
+      <c r="J59" s="31">
         <v>4</v>
       </c>
-      <c r="K59" s="35" t="s">
+      <c r="K59" s="34" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="60" spans="2:11">
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35" t="s">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="I60" s="35" t="s">
+      <c r="I60" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="J60" s="32">
+      <c r="J60" s="31">
         <v>8</v>
       </c>
-      <c r="K60" s="35" t="s">
+      <c r="K60" s="34" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35" t="s">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="I61" s="35" t="s">
+      <c r="I61" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="J61" s="32">
+      <c r="J61" s="31">
         <v>15</v>
       </c>
-      <c r="K61" s="35" t="s">
+      <c r="K61" s="34" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="36" t="s">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B62" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="C62" s="37" t="b">
+      <c r="C62" s="36" t="b">
         <v>1</v>
       </c>
-      <c r="D62" s="37" t="b">
+      <c r="D62" s="36" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="36"/>
-      <c r="F62" s="36"/>
-      <c r="G62" s="36"/>
-      <c r="H62" s="36" t="s">
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="I62" s="36" t="s">
+      <c r="I62" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="J62" s="36">
+      <c r="J62" s="35">
         <v>1</v>
       </c>
-      <c r="K62" s="36" t="s">
+      <c r="K62" s="35" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="36"/>
-      <c r="C63" s="36"/>
-      <c r="D63" s="36"/>
-      <c r="E63" s="36"/>
-      <c r="F63" s="36"/>
-      <c r="G63" s="36"/>
-      <c r="H63" s="36" t="s">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B63" s="35"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="I63" s="36" t="s">
+      <c r="I63" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="J63" s="36">
+      <c r="J63" s="35">
         <v>2</v>
       </c>
-      <c r="K63" s="36" t="s">
+      <c r="K63" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="36"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="36"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-      <c r="G64" s="36"/>
-      <c r="H64" s="36" t="s">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B64" s="35"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="I64" s="36" t="s">
+      <c r="I64" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="J64" s="36">
+      <c r="J64" s="35">
         <v>4</v>
       </c>
-      <c r="K64" s="36" t="s">
+      <c r="K64" s="35" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="36"/>
-      <c r="C65" s="36"/>
-      <c r="D65" s="36"/>
-      <c r="E65" s="36"/>
-      <c r="F65" s="36"/>
-      <c r="G65" s="36"/>
-      <c r="H65" s="36" t="s">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B65" s="35"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="I65" s="36" t="s">
+      <c r="I65" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="J65" s="36">
+      <c r="J65" s="35">
         <v>8</v>
       </c>
-      <c r="K65" s="36" t="s">
+      <c r="K65" s="35" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-      <c r="G66" s="36"/>
-      <c r="H66" s="36" t="s">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B66" s="35"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="I66" s="36" t="s">
+      <c r="I66" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="J66" s="36">
+      <c r="J66" s="35">
         <v>16</v>
       </c>
-      <c r="K66" s="36" t="s">
+      <c r="K66" s="35" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="36"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
-      <c r="E67" s="36"/>
-      <c r="F67" s="36"/>
-      <c r="G67" s="36"/>
-      <c r="H67" s="36" t="s">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B67" s="35"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="35"/>
+      <c r="E67" s="35"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="I67" s="36" t="s">
+      <c r="I67" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="J67" s="36">
+      <c r="J67" s="35">
         <v>32</v>
       </c>
-      <c r="K67" s="36" t="s">
+      <c r="K67" s="35" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36" t="s">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="I68" s="36" t="s">
+      <c r="I68" s="35" t="s">
         <v>191</v>
       </c>
-      <c r="J68" s="36">
+      <c r="J68" s="35">
         <v>64</v>
       </c>
-      <c r="K68" s="36" t="s">
+      <c r="K68" s="35" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="69" spans="2:11">
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36" t="s">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B69" s="35"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="35" t="s">
         <v>174</v>
       </c>
-      <c r="I69" s="36" t="s">
+      <c r="I69" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="J69" s="36">
+      <c r="J69" s="35">
         <v>127</v>
       </c>
-      <c r="K69" s="36" t="s">
+      <c r="K69" s="35" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="70" spans="2:11">
-      <c r="B70" s="25" t="s">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B70" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="C70" s="26" t="b">
+      <c r="C70" s="25" t="b">
         <v>0</v>
       </c>
-      <c r="D70" s="26" t="b">
+      <c r="D70" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
-      <c r="H70" s="25" t="s">
+      <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
+      <c r="H70" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="I70" s="25" t="s">
+      <c r="I70" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="J70" s="25">
+      <c r="J70" s="24">
         <v>0</v>
       </c>
-      <c r="K70" s="25"/>
-    </row>
-    <row r="71" spans="2:11">
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25" t="s">
+      <c r="K70" s="24"/>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="24"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="I71" s="25" t="s">
+      <c r="I71" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="J71" s="25">
+      <c r="J71" s="24">
         <v>1</v>
       </c>
-      <c r="K71" s="25"/>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="38" t="s">
+      <c r="K71" s="24"/>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B72" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="C72" s="39" t="b">
+      <c r="C72" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="D72" s="39" t="b">
+      <c r="D72" s="38" t="b">
         <v>1</v>
       </c>
-      <c r="E72" s="40"/>
-      <c r="F72" s="40"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="40" t="s">
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="I72" s="40" t="s">
+      <c r="I72" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="J72" s="40">
+      <c r="J72" s="39">
         <v>0</v>
       </c>
-      <c r="K72" s="40" t="s">
+      <c r="K72" s="39" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="73" spans="2:11">
-      <c r="B73" s="40"/>
-      <c r="C73" s="40"/>
-      <c r="D73" s="40"/>
-      <c r="E73" s="40"/>
-      <c r="F73" s="40"/>
-      <c r="G73" s="40"/>
-      <c r="H73" s="40" t="s">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="I73" s="40" t="s">
+      <c r="I73" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="J73" s="40">
+      <c r="J73" s="39">
         <v>1</v>
       </c>
-      <c r="K73" s="40" t="s">
+      <c r="K73" s="39" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391C0D39-0FE6-491D-BBCC-D0D46C2565C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1140" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="203">
   <si>
     <t>##var</t>
   </si>
@@ -200,6 +194,12 @@
     <t>每周刷新</t>
   </si>
   <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>永久</t>
+  </si>
+  <si>
     <t>PropertyType</t>
   </si>
   <si>
@@ -621,9 +621,6 @@
   </si>
   <si>
     <t>PermanentSceneType</t>
-  </si>
-  <si>
-    <t>Permanent</t>
   </si>
   <si>
     <t>常驻</t>
@@ -644,8 +641,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,18 +660,160 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -677,19 +822,235 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79992065187536243"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.799920651875362"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACB9CA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399945066682943"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399945066682943"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,60 +1062,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E0B4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -902,13 +1251,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -978,77 +1569,145 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFC6E0B4"/>
+      <color rgb="00C6E0B4"/>
+      <color rgb="0070AD47"/>
+      <color rgb="00ACB9CA"/>
+      <color rgb="004472C4"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1306,30 +1965,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L74"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.0833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1351,15 +2010,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1385,7 +2044,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1415,7 +2074,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
@@ -1441,7 +2100,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1461,7 +2120,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -1481,7 +2140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -1501,7 +2160,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -1521,7 +2180,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -1541,7 +2200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="B10" s="13" t="s">
         <v>32</v>
       </c>
@@ -1567,7 +2226,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -1587,7 +2246,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="B12" s="14" t="s">
         <v>39</v>
       </c>
@@ -1609,7 +2268,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="B13" s="17"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -1629,7 +2288,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12">
       <c r="B14" s="20"/>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -1649,1269 +2308,1289 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12">
       <c r="B15" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="23" t="b">
+      <c r="C15" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="23" t="b">
+      <c r="D15" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
       <c r="H15" s="23" t="s">
         <v>49</v>
       </c>
       <c r="I15" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="23">
-        <v>0</v>
+      <c r="J15" s="24">
+        <v>1</v>
       </c>
       <c r="K15" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
+    <row r="16" spans="1:12">
+      <c r="B16" s="24"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
       <c r="H16" s="23" t="s">
         <v>52</v>
       </c>
       <c r="I16" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="23">
-        <v>1</v>
+      <c r="J16" s="24">
+        <v>2</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="25" t="b">
-        <v>1</v>
-      </c>
+    <row r="17" spans="2:11">
+      <c r="B17" s="24"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="24" t="s">
+      <c r="J17" s="24">
+        <v>0</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J17" s="24">
+      <c r="C18" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="K17" s="24" t="s">
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="25" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24" t="s">
+      <c r="I18" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="J18" s="26">
+        <v>1</v>
+      </c>
+      <c r="K18" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="J18" s="24">
+    </row>
+    <row r="19" spans="2:11">
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="26">
         <v>2</v>
       </c>
-      <c r="K18" s="24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="24" t="s">
+      <c r="K19" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="J19" s="24">
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" s="27"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="J20" s="27">
         <v>3</v>
       </c>
-      <c r="K19" s="24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="I20" s="24" t="s">
+      <c r="K20" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="J20" s="24">
+    </row>
+    <row r="21" spans="2:11">
+      <c r="B21" s="28"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I21" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" s="27">
         <v>4</v>
       </c>
-      <c r="K20" s="24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="24" t="s">
+      <c r="K21" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="24">
+    </row>
+    <row r="22" spans="2:11">
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="J22" s="27">
         <v>5</v>
       </c>
-      <c r="K21" s="24" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="24" t="s">
+      <c r="K22" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="24">
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="I23" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="J23" s="27">
         <v>6</v>
       </c>
-      <c r="K22" s="24" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B23" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="25" t="b">
+      <c r="K23" s="27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="30" t="b">
         <v>0</v>
       </c>
-      <c r="D23" s="25" t="b">
+      <c r="D24" s="30" t="b">
         <v>1</v>
       </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23" s="26">
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="J24" s="29">
         <v>0</v>
       </c>
-      <c r="K23" s="26" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="I24" s="26" t="s">
+      <c r="K24" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="J24" s="26">
+    </row>
+    <row r="25" spans="2:11">
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="J25" s="29">
         <v>1</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="K25" s="29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="31"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="J26" s="29">
+        <v>2</v>
+      </c>
+      <c r="K26" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29" t="s">
+        <v>80</v>
+      </c>
+      <c r="I27" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="29">
+        <v>3</v>
+      </c>
+      <c r="K27" s="29" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="I28" s="34" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="I25" s="26" t="s">
+      <c r="J28" s="34">
+        <v>0</v>
+      </c>
+      <c r="K28" s="34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29" s="35"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="J25" s="26">
+      <c r="J29" s="34">
+        <v>1</v>
+      </c>
+      <c r="K29" s="34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="J30" s="34">
         <v>2</v>
       </c>
-      <c r="K25" s="26" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="26" t="s">
+      <c r="K30" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="J26" s="26">
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="I31" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J31" s="34">
         <v>3</v>
       </c>
-      <c r="K26" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B27" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="25" t="b">
+      <c r="K31" s="34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="D27" s="25" t="b">
+      <c r="D32" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="I27" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="J27" s="28">
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="I32" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="J32" s="36">
+        <v>1</v>
+      </c>
+      <c r="K32" s="36" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="B33" s="36"/>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="I33" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="J33" s="36">
+        <v>2</v>
+      </c>
+      <c r="K33" s="36" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="I34" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="J34" s="36">
+        <v>3</v>
+      </c>
+      <c r="K34" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" s="38">
         <v>0</v>
       </c>
-      <c r="K27" s="28" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="I28" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="J28" s="28">
+      <c r="K35" s="38" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="J36" s="38">
         <v>1</v>
       </c>
-      <c r="K28" s="28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="I29" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="J29" s="28">
+      <c r="K36" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37" s="38"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="I37" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="J37" s="38">
+        <f t="shared" ref="J37:J57" si="0">J36*2</f>
         <v>2</v>
       </c>
-      <c r="K29" s="28" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="I30" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="J30" s="28">
-        <v>3</v>
-      </c>
-      <c r="K30" s="28" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B31" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" s="30" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" s="30" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="I31" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="J31" s="29">
-        <v>1</v>
-      </c>
-      <c r="K31" s="29" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="I32" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="J32" s="29">
-        <v>2</v>
-      </c>
-      <c r="K32" s="29" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="I33" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="J33" s="29">
-        <v>3</v>
-      </c>
-      <c r="K33" s="29" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="D34" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="I34" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="J34" s="31">
-        <v>0</v>
-      </c>
-      <c r="K34" s="31" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="I35" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="J35" s="31">
-        <v>1</v>
-      </c>
-      <c r="K35" s="31" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="I36" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="J36" s="31">
-        <f t="shared" ref="J36:J56" si="0">J35*2</f>
-        <v>2</v>
-      </c>
-      <c r="K36" s="31" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="I37" s="31" t="s">
+      <c r="K37" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="J37" s="31">
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="J38" s="38">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K37" s="31" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B38" s="31"/>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="I38" s="31" t="s">
+      <c r="K38" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="J38" s="31">
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="I39" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="J39" s="38">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K38" s="31" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="I39" s="31" t="s">
+      <c r="K39" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="J39" s="31">
+    </row>
+    <row r="40" spans="2:11">
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="I40" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="J40" s="38">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="K39" s="31" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="I40" s="31" t="s">
+      <c r="K40" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="J40" s="31">
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41" s="38"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="I41" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="J41" s="38">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="K40" s="31" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="I41" s="31" t="s">
+      <c r="K41" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="J41" s="31">
+    </row>
+    <row r="42" spans="2:11">
+      <c r="B42" s="38"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="I42" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="J42" s="38">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="K41" s="31" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="I42" s="31" t="s">
+      <c r="K42" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="J42" s="31">
+    </row>
+    <row r="43" spans="2:11">
+      <c r="B43" s="38"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="I43" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="J43" s="38">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="K42" s="31" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="I43" s="31" t="s">
+      <c r="K43" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="J43" s="31">
+    </row>
+    <row r="44" spans="2:11">
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="I44" s="38" t="s">
+        <v>123</v>
+      </c>
+      <c r="J44" s="38">
         <f t="shared" si="0"/>
         <v>256</v>
       </c>
-      <c r="K43" s="31" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B44" s="31"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="I44" s="31" t="s">
+      <c r="K44" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="J44" s="31">
+    </row>
+    <row r="45" spans="2:11">
+      <c r="B45" s="38"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
+      <c r="E45" s="38"/>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38" t="s">
+        <v>125</v>
+      </c>
+      <c r="I45" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="J45" s="38">
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
-      <c r="K44" s="31" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="I45" s="31" t="s">
+      <c r="K45" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="J45" s="31">
+    </row>
+    <row r="46" spans="2:11">
+      <c r="B46" s="38"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="I46" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="J46" s="38">
         <f t="shared" si="0"/>
         <v>1024</v>
       </c>
-      <c r="K45" s="31" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B46" s="31"/>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="I46" s="31" t="s">
+      <c r="K46" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="J46" s="31">
+    </row>
+    <row r="47" spans="2:11">
+      <c r="B47" s="38"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38"/>
+      <c r="H47" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="I47" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="J47" s="38">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
-      <c r="K46" s="31" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B47" s="31"/>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="I47" s="31" t="s">
+      <c r="K47" s="38" t="s">
         <v>133</v>
       </c>
-      <c r="J47" s="31">
+    </row>
+    <row r="48" spans="2:11">
+      <c r="B48" s="38"/>
+      <c r="C48" s="38"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="I48" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J48" s="38">
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
-      <c r="K47" s="31" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="31"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="I48" s="31" t="s">
+      <c r="K48" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="J48" s="31">
+    </row>
+    <row r="49" spans="2:11">
+      <c r="B49" s="38"/>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="38"/>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38" t="s">
+        <v>137</v>
+      </c>
+      <c r="I49" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="J49" s="38">
         <f t="shared" si="0"/>
         <v>8192</v>
       </c>
-      <c r="K48" s="31" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B49" s="31"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="I49" s="31" t="s">
+      <c r="K49" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="J49" s="31">
+    </row>
+    <row r="50" spans="2:11">
+      <c r="B50" s="38"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="I50" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="J50" s="38">
         <f t="shared" si="0"/>
         <v>16384</v>
       </c>
-      <c r="K49" s="31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B50" s="31"/>
-      <c r="C50" s="31"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="I50" s="31" t="s">
+      <c r="K50" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="J50" s="31">
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="38"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="38"/>
+      <c r="H51" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="I51" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="J51" s="38">
         <f t="shared" si="0"/>
         <v>32768</v>
       </c>
-      <c r="K50" s="31" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B51" s="31"/>
-      <c r="C51" s="31"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="I51" s="31" t="s">
+      <c r="K51" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="J51" s="31">
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="I52" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="J52" s="38">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
-      <c r="K51" s="31" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B52" s="31"/>
-      <c r="C52" s="31"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="I52" s="31" t="s">
+      <c r="K52" s="38" t="s">
         <v>148</v>
       </c>
-      <c r="J52" s="31">
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="38"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I53" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="J53" s="38">
         <f t="shared" si="0"/>
         <v>131072</v>
       </c>
-      <c r="K52" s="31" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B53" s="31"/>
-      <c r="C53" s="31"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="I53" s="31" t="s">
+      <c r="K53" s="38" t="s">
         <v>151</v>
       </c>
-      <c r="J53" s="31">
+    </row>
+    <row r="54" spans="2:11">
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="I54" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="J54" s="38">
         <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K53" s="31" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="I54" s="33" t="s">
+      <c r="K54" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="J54" s="33">
+    </row>
+    <row r="55" spans="2:11">
+      <c r="B55" s="40"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="I55" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="J55" s="40">
         <f t="shared" si="0"/>
         <v>524288</v>
       </c>
-      <c r="K54" s="33" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B55" s="33"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
-      <c r="H55" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="I55" s="33" t="s">
+      <c r="K55" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="J55" s="33">
+    </row>
+    <row r="56" spans="2:11">
+      <c r="B56" s="40"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="40"/>
+      <c r="H56" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="I56" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="J56" s="40">
         <f t="shared" si="0"/>
         <v>1048576</v>
       </c>
-      <c r="K55" s="33" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B56" s="33"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="33"/>
-      <c r="G56" s="33"/>
-      <c r="H56" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="I56" s="33" t="s">
+      <c r="K56" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="J56" s="33">
+    </row>
+    <row r="57" spans="2:11">
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="J57" s="40">
         <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
-      <c r="K56" s="33" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B57" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="32" t="b">
+      <c r="K57" s="40" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" s="39" t="b">
         <v>1</v>
       </c>
-      <c r="D57" s="32" t="b">
+      <c r="D58" s="39" t="b">
         <v>1</v>
       </c>
-      <c r="E57" s="34"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="I57" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="J57" s="31">
+      <c r="E58" s="41"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="41" t="s">
+        <v>165</v>
+      </c>
+      <c r="I58" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="J58" s="38">
         <v>1</v>
       </c>
-      <c r="K57" s="34" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B58" s="34"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="I58" s="34" t="s">
+      <c r="K58" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="J58" s="31">
+    </row>
+    <row r="59" spans="2:11">
+      <c r="B59" s="41"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="I59" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="J59" s="38">
         <v>2</v>
       </c>
-      <c r="K58" s="34" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B59" s="34"/>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="34"/>
-      <c r="H59" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="I59" s="34" t="s">
+      <c r="K59" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="J59" s="31">
+    </row>
+    <row r="60" spans="2:11">
+      <c r="B60" s="41"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="41"/>
+      <c r="E60" s="41"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="41"/>
+      <c r="H60" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="I60" s="41" t="s">
+        <v>171</v>
+      </c>
+      <c r="J60" s="38">
         <v>4</v>
       </c>
-      <c r="K59" s="34" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B60" s="34"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="I60" s="34" t="s">
+      <c r="K60" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="J60" s="31">
+    </row>
+    <row r="61" spans="2:11">
+      <c r="B61" s="41"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="41"/>
+      <c r="E61" s="41"/>
+      <c r="F61" s="41"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="I61" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="J61" s="38">
         <v>8</v>
       </c>
-      <c r="K60" s="34" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B61" s="34"/>
-      <c r="C61" s="34"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="34"/>
-      <c r="H61" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="I61" s="34" t="s">
+      <c r="K61" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="J61" s="31">
+    </row>
+    <row r="62" spans="2:11">
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="I62" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="J62" s="38">
         <v>15</v>
       </c>
-      <c r="K61" s="34" t="s">
+      <c r="K62" s="41" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" s="43" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" s="43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42" t="s">
+        <v>180</v>
+      </c>
+      <c r="I63" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="J63" s="42">
+        <v>1</v>
+      </c>
+      <c r="K63" s="42" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="B64" s="42"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="I64" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="J64" s="42">
+        <v>2</v>
+      </c>
+      <c r="K64" s="42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" s="42"/>
+      <c r="C65" s="42"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="I65" s="42" t="s">
+        <v>185</v>
+      </c>
+      <c r="J65" s="42">
+        <v>4</v>
+      </c>
+      <c r="K65" s="42" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" s="42"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42" t="s">
+        <v>186</v>
+      </c>
+      <c r="I66" s="42" t="s">
+        <v>187</v>
+      </c>
+      <c r="J66" s="42">
+        <v>8</v>
+      </c>
+      <c r="K66" s="42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="I67" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="J67" s="42">
+        <v>16</v>
+      </c>
+      <c r="K67" s="42" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" s="42"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="I68" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="J68" s="42">
+        <v>32</v>
+      </c>
+      <c r="K68" s="42" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11">
+      <c r="B69" s="42"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="I69" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="J69" s="42">
+        <v>64</v>
+      </c>
+      <c r="K69" s="42" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="B70" s="42"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B62" s="35" t="s">
+      <c r="I70" s="42" t="s">
         <v>177</v>
       </c>
-      <c r="C62" s="36" t="b">
+      <c r="J70" s="42">
+        <v>127</v>
+      </c>
+      <c r="K70" s="42" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
+      <c r="B71" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C71" s="44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" s="44" t="b">
         <v>1</v>
       </c>
-      <c r="D62" s="36" t="b">
+      <c r="E71" s="27"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="27"/>
+      <c r="H71" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="I71" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="J71" s="27">
+        <v>0</v>
+      </c>
+      <c r="K71" s="27"/>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="B72" s="27"/>
+      <c r="C72" s="27"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="I72" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="J72" s="27">
         <v>1</v>
       </c>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="I62" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="J62" s="35">
+      <c r="K72" s="27"/>
+    </row>
+    <row r="73" spans="2:11">
+      <c r="B73" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C73" s="46" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" s="46" t="b">
         <v>1</v>
       </c>
-      <c r="K62" s="35" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B63" s="35"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="I63" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="J63" s="35">
-        <v>2</v>
-      </c>
-      <c r="K63" s="35" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B64" s="35"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="I64" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="J64" s="35">
-        <v>4</v>
-      </c>
-      <c r="K64" s="35" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B65" s="35"/>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="I65" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="J65" s="35">
-        <v>8</v>
-      </c>
-      <c r="K65" s="35" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B66" s="35"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="I66" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="J66" s="35">
-        <v>16</v>
-      </c>
-      <c r="K66" s="35" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B67" s="35"/>
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="I67" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="J67" s="35">
-        <v>32</v>
-      </c>
-      <c r="K67" s="35" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B68" s="35"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="I68" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="J68" s="35">
-        <v>64</v>
-      </c>
-      <c r="K68" s="35" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B69" s="35"/>
-      <c r="C69" s="35"/>
-      <c r="D69" s="35"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="35"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="I69" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="J69" s="35">
-        <v>127</v>
-      </c>
-      <c r="K69" s="35" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B70" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="C70" s="25" t="b">
+      <c r="E73" s="47"/>
+      <c r="F73" s="47"/>
+      <c r="G73" s="47"/>
+      <c r="H73" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="I73" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="J73" s="47">
         <v>0</v>
       </c>
-      <c r="D70" s="25" t="b">
+      <c r="K73" s="47" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" s="47"/>
+      <c r="C74" s="47"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="47"/>
+      <c r="F74" s="47"/>
+      <c r="G74" s="47"/>
+      <c r="H74" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="I74" s="47" t="s">
+        <v>201</v>
+      </c>
+      <c r="J74" s="47">
         <v>1</v>
       </c>
-      <c r="E70" s="24"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="24"/>
-      <c r="H70" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="I70" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="J70" s="24">
-        <v>0</v>
-      </c>
-      <c r="K70" s="24"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="24"/>
-      <c r="H71" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="I71" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="J71" s="24">
-        <v>1</v>
-      </c>
-      <c r="K71" s="24"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B72" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="C72" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="D72" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39"/>
-      <c r="H72" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="I72" s="39" t="s">
-        <v>197</v>
-      </c>
-      <c r="J72" s="39">
-        <v>0</v>
-      </c>
-      <c r="K72" s="39" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B73" s="39"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39"/>
-      <c r="H73" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="I73" s="39" t="s">
-        <v>200</v>
-      </c>
-      <c r="J73" s="39">
-        <v>1</v>
-      </c>
-      <c r="K73" s="39" t="s">
-        <v>201</v>
+      <c r="K74" s="47" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192D3658-1D17-443A-918C-BB5DCD598F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="0" yWindow="1030" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="222">
   <si>
     <t>##var</t>
   </si>
@@ -569,86 +575,153 @@
     <t>ShowRuleWeekType</t>
   </si>
   <si>
+    <t>周一</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>周二</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>周三</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>周四</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>周五</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>周六</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>周日</t>
+  </si>
+  <si>
+    <t>DialogueEndActionType</t>
+  </si>
+  <si>
+    <t>无操作</t>
+  </si>
+  <si>
+    <t>功能面板</t>
+  </si>
+  <si>
+    <t>PermanentSceneType</t>
+  </si>
+  <si>
+    <t>常驻</t>
+  </si>
+  <si>
+    <t>默认就存在的场景</t>
+  </si>
+  <si>
+    <t>Special</t>
+  </si>
+  <si>
+    <t>条件</t>
+  </si>
+  <si>
+    <t>根据条件出现的场景</t>
+  </si>
+  <si>
+    <t>UnlockConditionsType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prop</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Character</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>无解锁条件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有解锁条件</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家属性</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家物品</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Monday</t>
-  </si>
-  <si>
-    <t>周一</t>
-  </si>
-  <si>
-    <t>Tuesday</t>
-  </si>
-  <si>
-    <t>周二</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
-  </si>
-  <si>
-    <t>周三</t>
-  </si>
-  <si>
-    <t>Thursday</t>
-  </si>
-  <si>
-    <t>周四</t>
-  </si>
-  <si>
-    <t>Friday</t>
-  </si>
-  <si>
-    <t>周五</t>
-  </si>
-  <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>周六</t>
-  </si>
-  <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>周日</t>
-  </si>
-  <si>
-    <t>DialogueEndActionType</t>
-  </si>
-  <si>
-    <t>无操作</t>
-  </si>
-  <si>
-    <t>功能面板</t>
-  </si>
-  <si>
-    <t>PermanentSceneType</t>
-  </si>
-  <si>
-    <t>常驻</t>
-  </si>
-  <si>
-    <t>默认就存在的场景</t>
-  </si>
-  <si>
-    <t>Special</t>
-  </si>
-  <si>
-    <t>条件</t>
-  </si>
-  <si>
-    <t>根据条件出现的场景</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterPropType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Feeling </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Goodwill </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>心情值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>好感值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -660,160 +733,33 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="49">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -822,19 +768,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799920651875362"/>
+        <fgColor theme="9" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -858,7 +804,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -882,13 +828,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399945066682943"/>
+        <fgColor theme="5" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -900,13 +846,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399945066682943"/>
+        <fgColor theme="9" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -916,194 +862,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1251,255 +1011,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1572,15 +1090,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1644,70 +1156,38 @@
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00C6E0B4"/>
-      <color rgb="0070AD47"/>
-      <color rgb="00ACB9CA"/>
-      <color rgb="004472C4"/>
+      <color rgb="FFC6E0B4"/>
+      <color rgb="FF70AD47"/>
+      <color rgb="FFACB9CA"/>
+      <color rgb="FF4472C4"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1965,30 +1445,30 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L74"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L81"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.0833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2010,15 +1490,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2044,7 +1524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2074,7 +1554,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
@@ -2100,7 +1580,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2120,7 +1600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -2140,7 +1620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -2160,7 +1640,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -2180,7 +1660,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -2200,7 +1680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
         <v>32</v>
       </c>
@@ -2226,7 +1706,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -2246,7 +1726,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B12" s="14" t="s">
         <v>39</v>
       </c>
@@ -2268,7 +1748,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B13" s="17"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -2288,7 +1768,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B14" s="20"/>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -2308,1289 +1788,1432 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B15" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="24" t="b">
+      <c r="C15" s="23" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="24" t="b">
+      <c r="D15" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
       <c r="H15" s="23" t="s">
         <v>49</v>
       </c>
       <c r="I15" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="23">
         <v>1</v>
       </c>
       <c r="K15" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
       <c r="H16" s="23" t="s">
         <v>52</v>
       </c>
       <c r="I16" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="24">
+      <c r="J16" s="23">
         <v>2</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:11">
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
       <c r="H17" s="23" t="s">
         <v>55</v>
       </c>
       <c r="I17" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="J17" s="24">
+      <c r="J17" s="23">
         <v>0</v>
       </c>
       <c r="K17" s="23" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="2:11">
-      <c r="B18" s="25" t="s">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="26" t="b">
+      <c r="C18" s="24" t="b">
         <v>0</v>
       </c>
-      <c r="D18" s="26" t="b">
+      <c r="D18" s="24" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="25" t="s">
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="I18" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="J18" s="26">
+      <c r="J18" s="24">
         <v>1</v>
       </c>
-      <c r="K18" s="25" t="s">
+      <c r="K18" s="24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
-      <c r="B19" s="26"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="25" t="s">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="25" t="s">
+      <c r="I19" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="24">
         <v>2</v>
       </c>
-      <c r="K19" s="25" t="s">
+      <c r="K19" s="24" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="2:11">
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27" t="s">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="I20" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="25">
         <v>3</v>
       </c>
-      <c r="K20" s="27" t="s">
+      <c r="K20" s="25" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:11">
-      <c r="B21" s="28"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="26"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="I21" s="27" t="s">
+      <c r="I21" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="27">
+      <c r="J21" s="25">
         <v>4</v>
       </c>
-      <c r="K21" s="27" t="s">
+      <c r="K21" s="25" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="2:11">
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27" t="s">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="I22" s="27" t="s">
+      <c r="I22" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="27">
+      <c r="J22" s="25">
         <v>5</v>
       </c>
-      <c r="K22" s="27" t="s">
+      <c r="K22" s="25" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="2:11">
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27" t="s">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="25"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="I23" s="27" t="s">
+      <c r="I23" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="25">
         <v>6</v>
       </c>
-      <c r="K23" s="27" t="s">
+      <c r="K23" s="25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="2:11">
-      <c r="B24" s="29" t="s">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="30" t="b">
+      <c r="C24" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="D24" s="30" t="b">
+      <c r="D24" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29" t="s">
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="29" t="s">
+      <c r="I24" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="27">
         <v>0</v>
       </c>
-      <c r="K24" s="29" t="s">
+      <c r="K24" s="27" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="29"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29" t="s">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="I25" s="29" t="s">
+      <c r="I25" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="27">
         <v>1</v>
       </c>
-      <c r="K25" s="29" t="s">
+      <c r="K25" s="27" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="31"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29" t="s">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B26" s="29"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="I26" s="29" t="s">
+      <c r="I26" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="J26" s="29">
+      <c r="J26" s="27">
         <v>2</v>
       </c>
-      <c r="K26" s="29" t="s">
+      <c r="K26" s="27" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29" t="s">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="29" t="s">
+      <c r="I27" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="27">
         <v>3</v>
       </c>
-      <c r="K27" s="29" t="s">
+      <c r="K27" s="27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="32" t="s">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B28" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="33" t="b">
+      <c r="C28" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="33" t="b">
+      <c r="D28" s="31" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34" t="s">
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="I28" s="34" t="s">
+      <c r="I28" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="J28" s="34">
+      <c r="J28" s="32">
         <v>0</v>
       </c>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="32" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="2:11">
-      <c r="B29" s="35"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34" t="s">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="33"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="I29" s="34" t="s">
+      <c r="I29" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="J29" s="34">
+      <c r="J29" s="32">
         <v>1</v>
       </c>
-      <c r="K29" s="34" t="s">
+      <c r="K29" s="32" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34" t="s">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="32"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="I30" s="34" t="s">
+      <c r="I30" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="32">
         <v>2</v>
       </c>
-      <c r="K30" s="34" t="s">
+      <c r="K30" s="32" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34" t="s">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="I31" s="34" t="s">
+      <c r="I31" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="32">
         <v>3</v>
       </c>
-      <c r="K31" s="34" t="s">
+      <c r="K31" s="32" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="36" t="s">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B32" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="37" t="b">
+      <c r="C32" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="D32" s="37" t="b">
+      <c r="D32" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36" t="s">
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="I32" s="36" t="s">
+      <c r="I32" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="J32" s="36">
+      <c r="J32" s="34">
         <v>1</v>
       </c>
-      <c r="K32" s="36" t="s">
+      <c r="K32" s="34" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36" t="s">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="I33" s="36" t="s">
+      <c r="I33" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="34">
         <v>2</v>
       </c>
-      <c r="K33" s="36" t="s">
+      <c r="K33" s="34" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36" t="s">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I34" s="36" t="s">
+      <c r="I34" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="J34" s="36">
+      <c r="J34" s="34">
         <v>3</v>
       </c>
-      <c r="K34" s="36" t="s">
+      <c r="K34" s="34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="38" t="s">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="39" t="b">
+      <c r="C35" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="D35" s="39" t="b">
+      <c r="D35" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="H35" s="38" t="s">
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="I35" s="38" t="s">
+      <c r="I35" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="J35" s="38">
+      <c r="J35" s="36">
         <v>0</v>
       </c>
-      <c r="K35" s="38" t="s">
+      <c r="K35" s="36" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38" t="s">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="I36" s="38" t="s">
+      <c r="I36" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="J36" s="38">
+      <c r="J36" s="36">
         <v>1</v>
       </c>
-      <c r="K36" s="38" t="s">
+      <c r="K36" s="36" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:11">
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38" t="s">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
+      <c r="G37" s="36"/>
+      <c r="H37" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="I37" s="38" t="s">
+      <c r="I37" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="J37" s="38">
+      <c r="J37" s="36">
         <f t="shared" ref="J37:J57" si="0">J36*2</f>
         <v>2</v>
       </c>
-      <c r="K37" s="38" t="s">
+      <c r="K37" s="36" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38" t="s">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="I38" s="38" t="s">
+      <c r="I38" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="J38" s="38">
+      <c r="J38" s="36">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K38" s="38" t="s">
+      <c r="K38" s="36" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38" t="s">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="I39" s="38" t="s">
+      <c r="I39" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="J39" s="38">
+      <c r="J39" s="36">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K39" s="38" t="s">
+      <c r="K39" s="36" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="40" spans="2:11">
-      <c r="B40" s="38"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="38" t="s">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B40" s="36"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="I40" s="38" t="s">
+      <c r="I40" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="J40" s="38">
+      <c r="J40" s="36">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="K40" s="38" t="s">
+      <c r="K40" s="36" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="2:11">
-      <c r="B41" s="38"/>
-      <c r="C41" s="38"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="38"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="38" t="s">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="I41" s="38" t="s">
+      <c r="I41" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="J41" s="38">
+      <c r="J41" s="36">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="K41" s="38" t="s">
+      <c r="K41" s="36" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="2:11">
-      <c r="B42" s="38"/>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38" t="s">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B42" s="36"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="I42" s="38" t="s">
+      <c r="I42" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="J42" s="38">
+      <c r="J42" s="36">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="K42" s="38" t="s">
+      <c r="K42" s="36" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="2:11">
-      <c r="B43" s="38"/>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38" t="s">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="36"/>
+      <c r="C43" s="36"/>
+      <c r="D43" s="36"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="H43" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="I43" s="38" t="s">
+      <c r="I43" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="J43" s="38">
+      <c r="J43" s="36">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="K43" s="38" t="s">
+      <c r="K43" s="36" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="2:11">
-      <c r="B44" s="38"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="38"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="38" t="s">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B44" s="36"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="I44" s="38" t="s">
+      <c r="I44" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="J44" s="38">
+      <c r="J44" s="36">
         <f t="shared" si="0"/>
         <v>256</v>
       </c>
-      <c r="K44" s="38" t="s">
+      <c r="K44" s="36" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="2:11">
-      <c r="B45" s="38"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="38"/>
-      <c r="H45" s="38" t="s">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="36"/>
+      <c r="C45" s="36"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="H45" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="I45" s="38" t="s">
+      <c r="I45" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="J45" s="38">
+      <c r="J45" s="36">
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
-      <c r="K45" s="38" t="s">
+      <c r="K45" s="36" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="2:11">
-      <c r="B46" s="38"/>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38" t="s">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="36"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="I46" s="38" t="s">
+      <c r="I46" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="J46" s="38">
+      <c r="J46" s="36">
         <f t="shared" si="0"/>
         <v>1024</v>
       </c>
-      <c r="K46" s="38" t="s">
+      <c r="K46" s="36" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="47" spans="2:11">
-      <c r="B47" s="38"/>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38"/>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38" t="s">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="I47" s="38" t="s">
+      <c r="I47" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="J47" s="38">
+      <c r="J47" s="36">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
-      <c r="K47" s="38" t="s">
+      <c r="K47" s="36" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="48" spans="2:11">
-      <c r="B48" s="38"/>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38" t="s">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="I48" s="38" t="s">
+      <c r="I48" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="J48" s="38">
+      <c r="J48" s="36">
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
-      <c r="K48" s="38" t="s">
+      <c r="K48" s="36" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="2:11">
-      <c r="B49" s="38"/>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38" t="s">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B49" s="36"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="36"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
+      <c r="H49" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="I49" s="38" t="s">
+      <c r="I49" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="J49" s="38">
+      <c r="J49" s="36">
         <f t="shared" si="0"/>
         <v>8192</v>
       </c>
-      <c r="K49" s="38" t="s">
+      <c r="K49" s="36" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="50" spans="2:11">
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38" t="s">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="I50" s="38" t="s">
+      <c r="I50" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="J50" s="38">
+      <c r="J50" s="36">
         <f t="shared" si="0"/>
         <v>16384</v>
       </c>
-      <c r="K50" s="38" t="s">
+      <c r="K50" s="36" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="51" spans="2:11">
-      <c r="B51" s="38"/>
-      <c r="C51" s="38"/>
-      <c r="D51" s="38"/>
-      <c r="E51" s="38"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="38"/>
-      <c r="H51" s="38" t="s">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B51" s="36"/>
+      <c r="C51" s="36"/>
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="36"/>
+      <c r="H51" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="I51" s="38" t="s">
+      <c r="I51" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="J51" s="38">
+      <c r="J51" s="36">
         <f t="shared" si="0"/>
         <v>32768</v>
       </c>
-      <c r="K51" s="38" t="s">
+      <c r="K51" s="36" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="52" spans="2:11">
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38" t="s">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="I52" s="38" t="s">
+      <c r="I52" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="J52" s="38">
+      <c r="J52" s="36">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
-      <c r="K52" s="38" t="s">
+      <c r="K52" s="36" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="53" spans="2:11">
-      <c r="B53" s="38"/>
-      <c r="C53" s="38"/>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38"/>
-      <c r="H53" s="38" t="s">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B53" s="36"/>
+      <c r="C53" s="36"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="I53" s="38" t="s">
+      <c r="I53" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="J53" s="38">
+      <c r="J53" s="36">
         <f t="shared" si="0"/>
         <v>131072</v>
       </c>
-      <c r="K53" s="38" t="s">
+      <c r="K53" s="36" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="2:11">
-      <c r="B54" s="38"/>
-      <c r="C54" s="38"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38" t="s">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B54" s="36"/>
+      <c r="C54" s="36"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="H54" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="I54" s="38" t="s">
+      <c r="I54" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="J54" s="38">
+      <c r="J54" s="36">
         <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K54" s="38" t="s">
+      <c r="K54" s="36" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="55" spans="2:11">
-      <c r="B55" s="40"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40" t="s">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B55" s="38"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="I55" s="40" t="s">
+      <c r="I55" s="38" t="s">
         <v>156</v>
       </c>
-      <c r="J55" s="40">
+      <c r="J55" s="38">
         <f t="shared" si="0"/>
         <v>524288</v>
       </c>
-      <c r="K55" s="40" t="s">
+      <c r="K55" s="38" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="56" spans="2:11">
-      <c r="B56" s="40"/>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40" t="s">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="I56" s="40" t="s">
+      <c r="I56" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="J56" s="40">
+      <c r="J56" s="38">
         <f t="shared" si="0"/>
         <v>1048576</v>
       </c>
-      <c r="K56" s="40" t="s">
+      <c r="K56" s="38" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="40"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="40" t="s">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B57" s="38"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38"/>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="I57" s="40" t="s">
+      <c r="I57" s="38" t="s">
         <v>162</v>
       </c>
-      <c r="J57" s="40">
+      <c r="J57" s="38">
         <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
-      <c r="K57" s="40" t="s">
+      <c r="K57" s="38" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="41" t="s">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B58" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="C58" s="39" t="b">
+      <c r="C58" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="D58" s="39" t="b">
+      <c r="D58" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="41" t="s">
+      <c r="E58" s="39"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="I58" s="41" t="s">
+      <c r="I58" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="J58" s="38">
+      <c r="J58" s="36">
         <v>1</v>
       </c>
-      <c r="K58" s="41" t="s">
+      <c r="K58" s="39" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="59" spans="2:11">
-      <c r="B59" s="41"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="41" t="s">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="I59" s="41" t="s">
+      <c r="I59" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="J59" s="38">
+      <c r="J59" s="36">
         <v>2</v>
       </c>
-      <c r="K59" s="41" t="s">
+      <c r="K59" s="39" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="60" spans="2:11">
-      <c r="B60" s="41"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
-      <c r="G60" s="41"/>
-      <c r="H60" s="41" t="s">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B60" s="39"/>
+      <c r="C60" s="39"/>
+      <c r="D60" s="39"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="39"/>
+      <c r="G60" s="39"/>
+      <c r="H60" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="I60" s="41" t="s">
+      <c r="I60" s="39" t="s">
         <v>171</v>
       </c>
-      <c r="J60" s="38">
+      <c r="J60" s="36">
         <v>4</v>
       </c>
-      <c r="K60" s="41" t="s">
+      <c r="K60" s="39" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="41"/>
-      <c r="C61" s="41"/>
-      <c r="D61" s="41"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="41"/>
-      <c r="G61" s="41"/>
-      <c r="H61" s="41" t="s">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B61" s="39"/>
+      <c r="C61" s="39"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39" t="s">
         <v>173</v>
       </c>
-      <c r="I61" s="41" t="s">
+      <c r="I61" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="J61" s="38">
+      <c r="J61" s="36">
         <v>8</v>
       </c>
-      <c r="K61" s="41" t="s">
+      <c r="K61" s="39" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="41"/>
-      <c r="C62" s="41"/>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="41"/>
-      <c r="G62" s="41"/>
-      <c r="H62" s="41" t="s">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B62" s="39"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="I62" s="41" t="s">
+      <c r="I62" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="J62" s="38">
+      <c r="J62" s="36">
         <v>15</v>
       </c>
-      <c r="K62" s="41" t="s">
+      <c r="K62" s="39" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="42" t="s">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B63" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="C63" s="43" t="b">
+      <c r="C63" s="41" t="b">
         <v>1</v>
       </c>
-      <c r="D63" s="43" t="b">
+      <c r="D63" s="41" t="b">
         <v>1</v>
       </c>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="42"/>
-      <c r="H63" s="42" t="s">
+      <c r="E63" s="40"/>
+      <c r="F63" s="40"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="I63" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="I63" s="42" t="s">
+      <c r="J63" s="40">
+        <v>1</v>
+      </c>
+      <c r="K63" s="40" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="40"/>
+      <c r="H64" s="40" t="s">
         <v>181</v>
       </c>
-      <c r="J63" s="42">
+      <c r="I64" s="40" t="s">
+        <v>182</v>
+      </c>
+      <c r="J64" s="40">
+        <v>2</v>
+      </c>
+      <c r="K64" s="40" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="I65" s="40" t="s">
+        <v>184</v>
+      </c>
+      <c r="J65" s="40">
+        <v>4</v>
+      </c>
+      <c r="K65" s="40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="I66" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="J66" s="40">
+        <v>8</v>
+      </c>
+      <c r="K66" s="40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B67" s="40"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="40"/>
+      <c r="G67" s="40"/>
+      <c r="H67" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="I67" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="J67" s="40">
+        <v>16</v>
+      </c>
+      <c r="K67" s="40" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B68" s="40"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="I68" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="J68" s="40">
+        <v>32</v>
+      </c>
+      <c r="K68" s="40" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B69" s="40"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="40"/>
+      <c r="G69" s="40"/>
+      <c r="H69" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="I69" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="J69" s="40">
+        <v>64</v>
+      </c>
+      <c r="K69" s="40" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B70" s="40"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="40"/>
+      <c r="H70" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="I70" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="J70" s="40">
+        <v>127</v>
+      </c>
+      <c r="K70" s="40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B71" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="C71" s="42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" s="42" t="b">
         <v>1</v>
       </c>
-      <c r="K63" s="42" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="42"/>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="I64" s="42" t="s">
-        <v>183</v>
-      </c>
-      <c r="J64" s="42">
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
+      <c r="H71" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="I71" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="J71" s="25">
+        <v>0</v>
+      </c>
+      <c r="K71" s="25"/>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="I72" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J72" s="25">
+        <v>1</v>
+      </c>
+      <c r="K72" s="25"/>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B73" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="C73" s="44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="45"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="45"/>
+      <c r="H73" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="I73" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="J73" s="45">
+        <v>0</v>
+      </c>
+      <c r="K73" s="45" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B74" s="45"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="45"/>
+      <c r="H74" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="I74" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="J74" s="45">
+        <v>1</v>
+      </c>
+      <c r="K74" s="45" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B75" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="C75" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
+      <c r="H75" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="I75" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="J75" s="40">
+        <v>1</v>
+      </c>
+      <c r="K75" s="27" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B76" s="27"/>
+      <c r="C76" s="27"/>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="27"/>
+      <c r="H76" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="I76" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="J76" s="40">
         <v>2</v>
       </c>
-      <c r="K64" s="42" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="42"/>
-      <c r="C65" s="42"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="42"/>
-      <c r="G65" s="42"/>
-      <c r="H65" s="42" t="s">
-        <v>184</v>
-      </c>
-      <c r="I65" s="42" t="s">
-        <v>185</v>
-      </c>
-      <c r="J65" s="42">
+      <c r="K76" s="27" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B77" s="27"/>
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="27"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="I77" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="J77" s="40">
         <v>4</v>
       </c>
-      <c r="K65" s="42" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="42"/>
-      <c r="C66" s="42"/>
-      <c r="D66" s="42"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="42"/>
-      <c r="G66" s="42"/>
-      <c r="H66" s="42" t="s">
-        <v>186</v>
-      </c>
-      <c r="I66" s="42" t="s">
-        <v>187</v>
-      </c>
-      <c r="J66" s="42">
+      <c r="K77" s="27" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B78" s="27"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="I78" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="J78" s="40">
         <v>8</v>
       </c>
-      <c r="K66" s="42" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="42"/>
-      <c r="C67" s="42"/>
-      <c r="D67" s="42"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="42"/>
-      <c r="G67" s="42"/>
-      <c r="H67" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="I67" s="42" t="s">
-        <v>189</v>
-      </c>
-      <c r="J67" s="42">
+      <c r="K78" s="27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B79" s="27"/>
+      <c r="C79" s="27"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="I79" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="J79" s="40">
         <v>16</v>
       </c>
-      <c r="K67" s="42" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="42"/>
-      <c r="C68" s="42"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="42" t="s">
-        <v>190</v>
-      </c>
-      <c r="I68" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="J68" s="42">
-        <v>32</v>
-      </c>
-      <c r="K68" s="42" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69" s="42"/>
-      <c r="C69" s="42"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="42"/>
-      <c r="H69" s="42" t="s">
-        <v>192</v>
-      </c>
-      <c r="I69" s="42" t="s">
-        <v>193</v>
-      </c>
-      <c r="J69" s="42">
-        <v>64</v>
-      </c>
-      <c r="K69" s="42" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
-      <c r="B70" s="42"/>
-      <c r="C70" s="42"/>
-      <c r="D70" s="42"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="42" t="s">
-        <v>176</v>
-      </c>
-      <c r="I70" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="J70" s="42">
-        <v>127</v>
-      </c>
-      <c r="K70" s="42" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11">
-      <c r="B71" s="27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C71" s="44" t="b">
+      <c r="K79" s="27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B80" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="C80" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="D71" s="44" t="b">
+      <c r="D80" s="44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="J80" s="1">
         <v>1</v>
       </c>
-      <c r="E71" s="27"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="I71" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="J71" s="27">
-        <v>0</v>
-      </c>
-      <c r="K71" s="27"/>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="I72" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="J72" s="27">
-        <v>1</v>
-      </c>
-      <c r="K72" s="27"/>
-    </row>
-    <row r="73" spans="2:11">
-      <c r="B73" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="C73" s="46" t="b">
-        <v>0</v>
-      </c>
-      <c r="D73" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="47"/>
-      <c r="F73" s="47"/>
-      <c r="G73" s="47"/>
-      <c r="H73" s="47" t="s">
-        <v>55</v>
-      </c>
-      <c r="I73" s="47" t="s">
-        <v>198</v>
-      </c>
-      <c r="J73" s="47">
-        <v>0</v>
-      </c>
-      <c r="K73" s="47" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="B74" s="47"/>
-      <c r="C74" s="47"/>
-      <c r="D74" s="47"/>
-      <c r="E74" s="47"/>
-      <c r="F74" s="47"/>
-      <c r="G74" s="47"/>
-      <c r="H74" s="47" t="s">
-        <v>200</v>
-      </c>
-      <c r="I74" s="47" t="s">
-        <v>201</v>
-      </c>
-      <c r="J74" s="47">
-        <v>1</v>
-      </c>
-      <c r="K74" s="47" t="s">
-        <v>202</v>
+      <c r="K80" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="81" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="H81" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J81" s="1">
+        <v>2</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192D3658-1D17-443A-918C-BB5DCD598F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08924512-C0DD-44CF-8850-8D221FEBD804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1030" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-8180" yWindow="7670" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="236">
   <si>
     <t>##var</t>
   </si>
@@ -714,6 +714,57 @@
   </si>
   <si>
     <t>None</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelectMode</t>
+  </si>
+  <si>
+    <t>All</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomOne</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机一个</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>全部</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机全部</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RefreshType</t>
+  </si>
+  <si>
+    <t>TimeSlot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day </t>
+  </si>
+  <si>
+    <t>EveryEnter</t>
+  </si>
+  <si>
+    <t>时间段</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>每天</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -721,7 +772,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -758,8 +809,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -859,6 +916,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1017,7 +1080,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1162,11 +1225,23 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1451,8 +1526,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L81"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L87"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
@@ -1468,7 +1543,7 @@
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1490,15 +1565,15 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1524,7 +1599,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="99" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1554,7 +1629,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
@@ -1580,7 +1655,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1600,7 +1675,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -1620,7 +1695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -1640,7 +1715,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -1660,7 +1735,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -1680,7 +1755,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="B10" s="13" t="s">
         <v>32</v>
       </c>
@@ -1706,7 +1781,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -1726,7 +1801,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="B12" s="14" t="s">
         <v>39</v>
       </c>
@@ -1748,7 +1823,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="B13" s="17"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -1768,7 +1843,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12">
       <c r="B14" s="20"/>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -1788,7 +1863,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12">
       <c r="B15" s="23" t="s">
         <v>48</v>
       </c>
@@ -1814,7 +1889,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12">
       <c r="B16" s="23"/>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
@@ -1834,7 +1909,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11">
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
@@ -1854,7 +1929,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11">
       <c r="B18" s="24" t="s">
         <v>57</v>
       </c>
@@ -1880,7 +1955,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11">
       <c r="B19" s="24"/>
       <c r="C19" s="24"/>
       <c r="D19" s="24"/>
@@ -1900,7 +1975,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11">
       <c r="B20" s="25"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
@@ -1920,7 +1995,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11">
       <c r="B21" s="26"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
@@ -1940,7 +2015,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11">
       <c r="B22" s="25"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
@@ -1960,7 +2035,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11">
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
@@ -1980,7 +2055,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11">
       <c r="B24" s="27" t="s">
         <v>73</v>
       </c>
@@ -2006,7 +2081,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11">
       <c r="B25" s="27"/>
       <c r="C25" s="27"/>
       <c r="D25" s="27"/>
@@ -2026,7 +2101,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11">
       <c r="B26" s="29"/>
       <c r="C26" s="27"/>
       <c r="D26" s="27"/>
@@ -2046,7 +2121,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11">
       <c r="B27" s="27"/>
       <c r="C27" s="27"/>
       <c r="D27" s="27"/>
@@ -2066,7 +2141,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11">
       <c r="B28" s="30" t="s">
         <v>82</v>
       </c>
@@ -2092,7 +2167,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11">
       <c r="B29" s="33"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
@@ -2112,7 +2187,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11">
       <c r="B30" s="32"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
@@ -2132,7 +2207,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11">
       <c r="B31" s="32"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
@@ -2152,7 +2227,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11">
       <c r="B32" s="34" t="s">
         <v>84</v>
       </c>
@@ -2178,7 +2253,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11">
       <c r="B33" s="34"/>
       <c r="C33" s="34"/>
       <c r="D33" s="34"/>
@@ -2198,7 +2273,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11">
       <c r="B34" s="34"/>
       <c r="C34" s="34"/>
       <c r="D34" s="34"/>
@@ -2218,7 +2293,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11">
       <c r="B35" s="36" t="s">
         <v>94</v>
       </c>
@@ -2244,7 +2319,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11">
       <c r="B36" s="36"/>
       <c r="C36" s="36"/>
       <c r="D36" s="36"/>
@@ -2264,7 +2339,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11">
       <c r="B37" s="36"/>
       <c r="C37" s="36"/>
       <c r="D37" s="36"/>
@@ -2285,7 +2360,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11">
       <c r="B38" s="36"/>
       <c r="C38" s="36"/>
       <c r="D38" s="36"/>
@@ -2306,7 +2381,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11">
       <c r="B39" s="36"/>
       <c r="C39" s="36"/>
       <c r="D39" s="36"/>
@@ -2327,7 +2402,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11">
       <c r="B40" s="36"/>
       <c r="C40" s="36"/>
       <c r="D40" s="36"/>
@@ -2348,7 +2423,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11">
       <c r="B41" s="36"/>
       <c r="C41" s="36"/>
       <c r="D41" s="36"/>
@@ -2369,7 +2444,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11">
       <c r="B42" s="36"/>
       <c r="C42" s="36"/>
       <c r="D42" s="36"/>
@@ -2390,7 +2465,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11">
       <c r="B43" s="36"/>
       <c r="C43" s="36"/>
       <c r="D43" s="36"/>
@@ -2411,7 +2486,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11">
       <c r="B44" s="36"/>
       <c r="C44" s="36"/>
       <c r="D44" s="36"/>
@@ -2432,7 +2507,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11">
       <c r="B45" s="36"/>
       <c r="C45" s="36"/>
       <c r="D45" s="36"/>
@@ -2453,7 +2528,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11">
       <c r="B46" s="36"/>
       <c r="C46" s="36"/>
       <c r="D46" s="36"/>
@@ -2474,7 +2549,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11">
       <c r="B47" s="36"/>
       <c r="C47" s="36"/>
       <c r="D47" s="36"/>
@@ -2495,7 +2570,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11">
       <c r="B48" s="36"/>
       <c r="C48" s="36"/>
       <c r="D48" s="36"/>
@@ -2516,7 +2591,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:11">
       <c r="B49" s="36"/>
       <c r="C49" s="36"/>
       <c r="D49" s="36"/>
@@ -2537,7 +2612,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:11">
       <c r="B50" s="36"/>
       <c r="C50" s="36"/>
       <c r="D50" s="36"/>
@@ -2558,7 +2633,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:11">
       <c r="B51" s="36"/>
       <c r="C51" s="36"/>
       <c r="D51" s="36"/>
@@ -2579,7 +2654,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:11">
       <c r="B52" s="36"/>
       <c r="C52" s="36"/>
       <c r="D52" s="36"/>
@@ -2600,7 +2675,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:11">
       <c r="B53" s="36"/>
       <c r="C53" s="36"/>
       <c r="D53" s="36"/>
@@ -2621,7 +2696,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:11">
       <c r="B54" s="36"/>
       <c r="C54" s="36"/>
       <c r="D54" s="36"/>
@@ -2642,7 +2717,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:11">
       <c r="B55" s="38"/>
       <c r="C55" s="38"/>
       <c r="D55" s="38"/>
@@ -2663,7 +2738,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:11">
       <c r="B56" s="38"/>
       <c r="C56" s="38"/>
       <c r="D56" s="38"/>
@@ -2684,7 +2759,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:11">
       <c r="B57" s="38"/>
       <c r="C57" s="38"/>
       <c r="D57" s="38"/>
@@ -2705,7 +2780,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:11">
       <c r="B58" s="39" t="s">
         <v>164</v>
       </c>
@@ -2731,7 +2806,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:11">
       <c r="B59" s="39"/>
       <c r="C59" s="39"/>
       <c r="D59" s="39"/>
@@ -2751,7 +2826,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:11">
       <c r="B60" s="39"/>
       <c r="C60" s="39"/>
       <c r="D60" s="39"/>
@@ -2771,7 +2846,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:11">
       <c r="B61" s="39"/>
       <c r="C61" s="39"/>
       <c r="D61" s="39"/>
@@ -2791,7 +2866,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:11">
       <c r="B62" s="39"/>
       <c r="C62" s="39"/>
       <c r="D62" s="39"/>
@@ -2811,7 +2886,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:11">
       <c r="B63" s="40" t="s">
         <v>179</v>
       </c>
@@ -2837,7 +2912,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:11">
       <c r="B64" s="40"/>
       <c r="C64" s="40"/>
       <c r="D64" s="40"/>
@@ -2857,7 +2932,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:11">
       <c r="B65" s="40"/>
       <c r="C65" s="40"/>
       <c r="D65" s="40"/>
@@ -2877,7 +2952,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:11">
       <c r="B66" s="40"/>
       <c r="C66" s="40"/>
       <c r="D66" s="40"/>
@@ -2897,7 +2972,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:11">
       <c r="B67" s="40"/>
       <c r="C67" s="40"/>
       <c r="D67" s="40"/>
@@ -2917,7 +2992,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:11">
       <c r="B68" s="40"/>
       <c r="C68" s="40"/>
       <c r="D68" s="40"/>
@@ -2937,7 +3012,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:11">
       <c r="B69" s="40"/>
       <c r="C69" s="40"/>
       <c r="D69" s="40"/>
@@ -2957,7 +3032,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:11">
       <c r="B70" s="40"/>
       <c r="C70" s="40"/>
       <c r="D70" s="40"/>
@@ -2977,7 +3052,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:11">
       <c r="B71" s="25" t="s">
         <v>193</v>
       </c>
@@ -3001,7 +3076,7 @@
       </c>
       <c r="K71" s="25"/>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:11">
       <c r="B72" s="25"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
@@ -3019,7 +3094,7 @@
       </c>
       <c r="K72" s="25"/>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:11">
       <c r="B73" s="43" t="s">
         <v>196</v>
       </c>
@@ -3045,7 +3120,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:11">
       <c r="B74" s="45"/>
       <c r="C74" s="45"/>
       <c r="D74" s="45"/>
@@ -3065,7 +3140,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:11">
       <c r="B75" s="47" t="s">
         <v>202</v>
       </c>
@@ -3091,7 +3166,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:11">
       <c r="B76" s="27"/>
       <c r="C76" s="27"/>
       <c r="D76" s="27"/>
@@ -3111,7 +3186,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:11">
       <c r="B77" s="27"/>
       <c r="C77" s="27"/>
       <c r="D77" s="27"/>
@@ -3131,7 +3206,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:11">
       <c r="B78" s="27"/>
       <c r="C78" s="27"/>
       <c r="D78" s="27"/>
@@ -3151,7 +3226,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:11">
       <c r="B79" s="27"/>
       <c r="C79" s="27"/>
       <c r="D79" s="27"/>
@@ -3171,41 +3246,182 @@
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B80" s="48" t="s">
+    <row r="80" spans="2:11">
+      <c r="B80" s="50" t="s">
         <v>216</v>
       </c>
       <c r="C80" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="D80" s="44" t="b">
+      <c r="D80" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="I80" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="J80" s="45">
+        <v>1</v>
+      </c>
+      <c r="K80" s="45" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" s="45"/>
+      <c r="C81" s="45"/>
+      <c r="D81" s="45"/>
+      <c r="E81" s="45"/>
+      <c r="F81" s="45"/>
+      <c r="G81" s="45"/>
+      <c r="H81" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="I81" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="J81" s="45">
+        <v>2</v>
+      </c>
+      <c r="K81" s="45" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="C82" s="46" t="b">
         <v>0</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="I80" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="J80" s="1">
-        <v>1</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="81" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H81" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="J81" s="1">
+      <c r="D82" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="49" t="s">
+        <v>223</v>
+      </c>
+      <c r="I82" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="J82" s="27">
+        <v>1</v>
+      </c>
+      <c r="K82" s="27" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="27"/>
+      <c r="C83" s="27"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="49" t="s">
+        <v>224</v>
+      </c>
+      <c r="I83" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="J83" s="27">
         <v>2</v>
       </c>
-      <c r="K81" s="1" t="s">
-        <v>220</v>
+      <c r="K83" s="27" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" s="27"/>
+      <c r="C84" s="27"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="49" t="s">
+        <v>225</v>
+      </c>
+      <c r="I84" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="J84" s="27">
+        <v>3</v>
+      </c>
+      <c r="K84" s="27" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" s="51" t="s">
+        <v>229</v>
+      </c>
+      <c r="C85" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" s="52" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="51"/>
+      <c r="F85" s="51"/>
+      <c r="G85" s="51"/>
+      <c r="H85" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="I85" s="51" t="s">
+        <v>233</v>
+      </c>
+      <c r="J85" s="51">
+        <v>1</v>
+      </c>
+      <c r="K85" s="51" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="51"/>
+      <c r="C86" s="51"/>
+      <c r="D86" s="51"/>
+      <c r="E86" s="51"/>
+      <c r="F86" s="51"/>
+      <c r="G86" s="51"/>
+      <c r="H86" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="I86" s="51" t="s">
+        <v>234</v>
+      </c>
+      <c r="J86" s="51">
+        <v>2</v>
+      </c>
+      <c r="K86" s="51" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" s="51"/>
+      <c r="C87" s="51"/>
+      <c r="D87" s="51"/>
+      <c r="E87" s="51"/>
+      <c r="F87" s="51"/>
+      <c r="G87" s="51"/>
+      <c r="H87" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="I87" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="J87" s="51">
+        <v>3</v>
+      </c>
+      <c r="K87" s="51" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08924512-C0DD-44CF-8850-8D221FEBD804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24544CB4-7FF1-4629-8DD0-AD68A4EA4F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8180" yWindow="7670" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="240">
   <si>
     <t>##var</t>
   </si>
@@ -765,6 +765,22 @@
   </si>
   <si>
     <t>每次</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HeartCoins</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱心币</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClawMachineValue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>娃娃机游戏次数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1225,9 +1241,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1242,6 +1255,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1526,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1565,13 +1581,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="48" t="s">
+      <c r="H1" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="48"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -2056,69 +2072,69 @@
       </c>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="I24" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="J24" s="25">
+        <v>7</v>
+      </c>
+      <c r="K24" s="25" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="I25" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="J25" s="25">
+        <v>8</v>
+      </c>
+      <c r="K25" s="25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="28" t="b">
+      <c r="C26" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="D24" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="I24" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="J24" s="27">
-        <v>0</v>
-      </c>
-      <c r="K24" s="27" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11">
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="I25" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="J25" s="27">
-        <v>1</v>
-      </c>
-      <c r="K25" s="27" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11">
-      <c r="B26" s="29"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
+      <c r="D26" s="28" t="b">
+        <v>1</v>
+      </c>
       <c r="E26" s="27"/>
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
       <c r="H26" s="27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I26" s="27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J26" s="27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -2129,235 +2145,234 @@
       <c r="F27" s="27"/>
       <c r="G27" s="27"/>
       <c r="H27" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="J27" s="27">
+        <v>1</v>
+      </c>
+      <c r="K27" s="27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="29"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="J28" s="27">
+        <v>2</v>
+      </c>
+      <c r="K28" s="27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="27" t="s">
+      <c r="I29" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="J27" s="27">
+      <c r="J29" s="27">
         <v>3</v>
       </c>
-      <c r="K27" s="27" t="s">
+      <c r="K29" s="27" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="30" t="s">
+    <row r="30" spans="2:11">
+      <c r="B30" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="31" t="b">
+      <c r="C30" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="I28" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="J28" s="32">
-        <v>0</v>
-      </c>
-      <c r="K28" s="32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11">
-      <c r="B29" s="33"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="J29" s="32">
-        <v>1</v>
-      </c>
-      <c r="K29" s="32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
+      <c r="D30" s="31" t="b">
+        <v>1</v>
+      </c>
       <c r="E30" s="32"/>
       <c r="F30" s="32"/>
       <c r="G30" s="32"/>
       <c r="H30" s="32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I30" s="32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J30" s="32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" s="32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="32"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="E31" s="32"/>
       <c r="F31" s="32"/>
       <c r="G31" s="32"/>
       <c r="H31" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="I31" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="J31" s="32">
+        <v>1</v>
+      </c>
+      <c r="K31" s="32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="I32" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="J32" s="32">
+        <v>2</v>
+      </c>
+      <c r="K32" s="32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="B33" s="32"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="I31" s="32" t="s">
+      <c r="I33" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="J31" s="32">
+      <c r="J33" s="32">
         <v>3</v>
       </c>
-      <c r="K31" s="32" t="s">
+      <c r="K33" s="32" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="34" t="s">
+    <row r="34" spans="2:11">
+      <c r="B34" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="35" t="b">
+      <c r="C34" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="D32" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="I32" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="J32" s="34">
-        <v>1</v>
-      </c>
-      <c r="K32" s="34" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="I33" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="J33" s="34">
-        <v>2</v>
-      </c>
-      <c r="K33" s="34" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
+      <c r="D34" s="35" t="b">
+        <v>1</v>
+      </c>
       <c r="E34" s="34"/>
       <c r="F34" s="34"/>
       <c r="G34" s="34"/>
       <c r="H34" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="I34" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="J34" s="34">
+        <v>1</v>
+      </c>
+      <c r="K34" s="34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="I35" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="J35" s="34">
+        <v>2</v>
+      </c>
+      <c r="K35" s="34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I34" s="34" t="s">
+      <c r="I36" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="J34" s="34">
+      <c r="J36" s="34">
         <v>3</v>
       </c>
-      <c r="K34" s="34" t="s">
+      <c r="K36" s="34" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="36" t="s">
+    <row r="37" spans="2:11">
+      <c r="B37" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="D35" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="I35" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="J35" s="36">
-        <v>0</v>
-      </c>
-      <c r="K35" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="36"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="I36" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="J36" s="36">
-        <v>1</v>
-      </c>
-      <c r="K36" s="36" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
+      <c r="C37" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" s="37" t="b">
+        <v>1</v>
+      </c>
       <c r="E37" s="36"/>
       <c r="F37" s="36"/>
       <c r="G37" s="36"/>
       <c r="H37" s="36" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="I37" s="36" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J37" s="36">
-        <f t="shared" ref="J37:J57" si="0">J36*2</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" s="36" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="2:11">
@@ -2368,17 +2383,16 @@
       <c r="F38" s="36"/>
       <c r="G38" s="36"/>
       <c r="H38" s="36" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="I38" s="36" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="J38" s="36">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K38" s="36" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="2:11">
@@ -2389,17 +2403,17 @@
       <c r="F39" s="36"/>
       <c r="G39" s="36"/>
       <c r="H39" s="36" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I39" s="36" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="J39" s="36">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f t="shared" ref="J39:J59" si="0">J38*2</f>
+        <v>2</v>
       </c>
       <c r="K39" s="36" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -2410,17 +2424,17 @@
       <c r="F40" s="36"/>
       <c r="G40" s="36"/>
       <c r="H40" s="36" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J40" s="36">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K40" s="36" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="2:11">
@@ -2431,17 +2445,17 @@
       <c r="F41" s="36"/>
       <c r="G41" s="36"/>
       <c r="H41" s="36" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I41" s="36" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="J41" s="36">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K41" s="36" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="2:11">
@@ -2452,17 +2466,17 @@
       <c r="F42" s="36"/>
       <c r="G42" s="36"/>
       <c r="H42" s="36" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I42" s="36" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J42" s="36">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="K42" s="36" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="2:11">
@@ -2473,17 +2487,17 @@
       <c r="F43" s="36"/>
       <c r="G43" s="36"/>
       <c r="H43" s="36" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I43" s="36" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="J43" s="36">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="K43" s="36" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="2:11">
@@ -2494,17 +2508,17 @@
       <c r="F44" s="36"/>
       <c r="G44" s="36"/>
       <c r="H44" s="36" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="I44" s="36" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="J44" s="36">
         <f t="shared" si="0"/>
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="K44" s="36" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="2:11">
@@ -2515,17 +2529,17 @@
       <c r="F45" s="36"/>
       <c r="G45" s="36"/>
       <c r="H45" s="36" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="I45" s="36" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="J45" s="36">
         <f t="shared" si="0"/>
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="K45" s="36" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="2:11">
@@ -2536,17 +2550,17 @@
       <c r="F46" s="36"/>
       <c r="G46" s="36"/>
       <c r="H46" s="36" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J46" s="36">
         <f t="shared" si="0"/>
-        <v>1024</v>
+        <v>256</v>
       </c>
       <c r="K46" s="36" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="2:11">
@@ -2557,17 +2571,17 @@
       <c r="F47" s="36"/>
       <c r="G47" s="36"/>
       <c r="H47" s="36" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="I47" s="36" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="J47" s="36">
         <f t="shared" si="0"/>
-        <v>2048</v>
+        <v>512</v>
       </c>
       <c r="K47" s="36" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="2:11">
@@ -2578,17 +2592,17 @@
       <c r="F48" s="36"/>
       <c r="G48" s="36"/>
       <c r="H48" s="36" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I48" s="36" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="J48" s="36">
         <f t="shared" si="0"/>
-        <v>4096</v>
+        <v>1024</v>
       </c>
       <c r="K48" s="36" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="2:11">
@@ -2599,38 +2613,38 @@
       <c r="F49" s="36"/>
       <c r="G49" s="36"/>
       <c r="H49" s="36" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="I49" s="36" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="J49" s="36">
         <f t="shared" si="0"/>
-        <v>8192</v>
+        <v>2048</v>
       </c>
       <c r="K49" s="36" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="2:11">
       <c r="B50" s="36"/>
       <c r="C50" s="36"/>
       <c r="D50" s="36"/>
-      <c r="E50" s="38"/>
+      <c r="E50" s="36"/>
       <c r="F50" s="36"/>
       <c r="G50" s="36"/>
       <c r="H50" s="36" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I50" s="36" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="J50" s="36">
         <f t="shared" si="0"/>
-        <v>16384</v>
+        <v>4096</v>
       </c>
       <c r="K50" s="36" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="2:11">
@@ -2641,38 +2655,38 @@
       <c r="F51" s="36"/>
       <c r="G51" s="36"/>
       <c r="H51" s="36" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I51" s="36" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="J51" s="36">
         <f t="shared" si="0"/>
-        <v>32768</v>
+        <v>8192</v>
       </c>
       <c r="K51" s="36" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="2:11">
       <c r="B52" s="36"/>
       <c r="C52" s="36"/>
       <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
+      <c r="E52" s="38"/>
       <c r="F52" s="36"/>
       <c r="G52" s="36"/>
       <c r="H52" s="36" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="I52" s="36" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="J52" s="36">
         <f t="shared" si="0"/>
-        <v>65536</v>
+        <v>16384</v>
       </c>
       <c r="K52" s="36" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="53" spans="2:11">
@@ -2683,17 +2697,17 @@
       <c r="F53" s="36"/>
       <c r="G53" s="36"/>
       <c r="H53" s="36" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="J53" s="36">
         <f t="shared" si="0"/>
-        <v>131072</v>
+        <v>32768</v>
       </c>
       <c r="K53" s="36" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="2:11">
@@ -2704,59 +2718,59 @@
       <c r="F54" s="36"/>
       <c r="G54" s="36"/>
       <c r="H54" s="36" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="I54" s="36" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="J54" s="36">
         <f t="shared" si="0"/>
+        <v>65536</v>
+      </c>
+      <c r="K54" s="36" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11">
+      <c r="B55" s="36"/>
+      <c r="C55" s="36"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="H55" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="I55" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="J55" s="36">
+        <f t="shared" si="0"/>
+        <v>131072</v>
+      </c>
+      <c r="K55" s="36" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11">
+      <c r="B56" s="36"/>
+      <c r="C56" s="36"/>
+      <c r="D56" s="36"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="36"/>
+      <c r="G56" s="36"/>
+      <c r="H56" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="I56" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="J56" s="36">
+        <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K54" s="36" t="s">
+      <c r="K56" s="36" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38"/>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="I55" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="J55" s="38">
-        <f t="shared" si="0"/>
-        <v>524288</v>
-      </c>
-      <c r="K55" s="38" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="B56" s="38"/>
-      <c r="C56" s="38"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="I56" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="J56" s="38">
-        <f t="shared" si="0"/>
-        <v>1048576</v>
-      </c>
-      <c r="K56" s="38" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="57" spans="2:11">
@@ -2767,83 +2781,85 @@
       <c r="F57" s="38"/>
       <c r="G57" s="38"/>
       <c r="H57" s="38" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="I57" s="38" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J57" s="38">
         <f t="shared" si="0"/>
+        <v>524288</v>
+      </c>
+      <c r="K57" s="38" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="I58" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="J58" s="38">
+        <f t="shared" si="0"/>
+        <v>1048576</v>
+      </c>
+      <c r="K58" s="38" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
+      <c r="B59" s="38"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="38"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I59" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="J59" s="38">
+        <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
-      <c r="K57" s="38" t="s">
+      <c r="K59" s="38" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="39" t="s">
+    <row r="60" spans="2:11">
+      <c r="B60" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="C58" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="D58" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="39"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="I58" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="J58" s="36">
-        <v>1</v>
-      </c>
-      <c r="K58" s="39" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="B59" s="39"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="I59" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="J59" s="36">
-        <v>2</v>
-      </c>
-      <c r="K59" s="39" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="B60" s="39"/>
-      <c r="C60" s="39"/>
-      <c r="D60" s="39"/>
+      <c r="C60" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="D60" s="37" t="b">
+        <v>1</v>
+      </c>
       <c r="E60" s="39"/>
       <c r="F60" s="39"/>
       <c r="G60" s="39"/>
       <c r="H60" s="39" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="I60" s="39" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J60" s="36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K60" s="39" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" spans="2:11">
@@ -2854,16 +2870,16 @@
       <c r="F61" s="39"/>
       <c r="G61" s="39"/>
       <c r="H61" s="39" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I61" s="39" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="J61" s="36">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K61" s="39" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="2:11">
@@ -2874,82 +2890,82 @@
       <c r="F62" s="39"/>
       <c r="G62" s="39"/>
       <c r="H62" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="I62" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="J62" s="36">
+        <v>4</v>
+      </c>
+      <c r="K62" s="39" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="39"/>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39"/>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39"/>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="I63" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="J63" s="36">
+        <v>8</v>
+      </c>
+      <c r="K63" s="39" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39" t="s">
         <v>176</v>
       </c>
-      <c r="I62" s="39" t="s">
+      <c r="I64" s="39" t="s">
         <v>177</v>
       </c>
-      <c r="J62" s="36">
+      <c r="J64" s="36">
         <v>15</v>
       </c>
-      <c r="K62" s="39" t="s">
+      <c r="K64" s="39" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="40" t="s">
+    <row r="65" spans="2:11">
+      <c r="B65" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="C63" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="D63" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="40"/>
-      <c r="F63" s="40"/>
-      <c r="G63" s="40"/>
-      <c r="H63" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="I63" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="J63" s="40">
-        <v>1</v>
-      </c>
-      <c r="K63" s="40" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="40"/>
-      <c r="C64" s="40"/>
-      <c r="D64" s="40"/>
-      <c r="E64" s="40"/>
-      <c r="F64" s="40"/>
-      <c r="G64" s="40"/>
-      <c r="H64" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="I64" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="J64" s="40">
-        <v>2</v>
-      </c>
-      <c r="K64" s="40" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="40"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="40"/>
+      <c r="C65" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="D65" s="41" t="b">
+        <v>1</v>
+      </c>
       <c r="E65" s="40"/>
       <c r="F65" s="40"/>
       <c r="G65" s="40"/>
       <c r="H65" s="40" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="I65" s="40" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="J65" s="40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K65" s="40" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="2:11">
@@ -2960,16 +2976,16 @@
       <c r="F66" s="40"/>
       <c r="G66" s="40"/>
       <c r="H66" s="40" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I66" s="40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="J66" s="40">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K66" s="40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="67" spans="2:11">
@@ -2980,16 +2996,16 @@
       <c r="F67" s="40"/>
       <c r="G67" s="40"/>
       <c r="H67" s="40" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I67" s="40" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="J67" s="40">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K67" s="40" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="2:11">
@@ -3000,16 +3016,16 @@
       <c r="F68" s="40"/>
       <c r="G68" s="40"/>
       <c r="H68" s="40" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I68" s="40" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="J68" s="40">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K68" s="40" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" spans="2:11">
@@ -3020,16 +3036,16 @@
       <c r="F69" s="40"/>
       <c r="G69" s="40"/>
       <c r="H69" s="40" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I69" s="40" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J69" s="40">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="K69" s="40" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="2:11">
@@ -3040,170 +3056,170 @@
       <c r="F70" s="40"/>
       <c r="G70" s="40"/>
       <c r="H70" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="I70" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="J70" s="40">
+        <v>32</v>
+      </c>
+      <c r="K70" s="40" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
+      <c r="B71" s="40"/>
+      <c r="C71" s="40"/>
+      <c r="D71" s="40"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="40"/>
+      <c r="H71" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="I71" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="J71" s="40">
+        <v>64</v>
+      </c>
+      <c r="K71" s="40" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="B72" s="40"/>
+      <c r="C72" s="40"/>
+      <c r="D72" s="40"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="40"/>
+      <c r="H72" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="I70" s="40" t="s">
+      <c r="I72" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="J70" s="40">
+      <c r="J72" s="40">
         <v>127</v>
       </c>
-      <c r="K70" s="40" t="s">
+      <c r="K72" s="40" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="2:11">
-      <c r="B71" s="25" t="s">
+    <row r="73" spans="2:11">
+      <c r="B73" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="C71" s="42" t="b">
+      <c r="C73" s="42" t="b">
         <v>0</v>
       </c>
-      <c r="D71" s="42" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25" t="s">
+      <c r="D73" s="42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="I71" s="25" t="s">
+      <c r="I73" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="J71" s="25">
+      <c r="J73" s="25">
         <v>0</v>
       </c>
-      <c r="K71" s="25"/>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="25"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
-      <c r="H72" s="25" t="s">
+      <c r="K73" s="25"/>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="I72" s="25" t="s">
+      <c r="I74" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="J72" s="25">
-        <v>1</v>
-      </c>
-      <c r="K72" s="25"/>
-    </row>
-    <row r="73" spans="2:11">
-      <c r="B73" s="43" t="s">
+      <c r="J74" s="25">
+        <v>1</v>
+      </c>
+      <c r="K74" s="25"/>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="B75" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="C73" s="44" t="b">
+      <c r="C75" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="D73" s="44" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="45"/>
-      <c r="F73" s="45"/>
-      <c r="G73" s="45"/>
-      <c r="H73" s="45" t="s">
+      <c r="D75" s="44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="I73" s="45" t="s">
+      <c r="I75" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="J73" s="45">
+      <c r="J75" s="45">
         <v>0</v>
       </c>
-      <c r="K73" s="45" t="s">
+      <c r="K75" s="45" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="74" spans="2:11">
-      <c r="B74" s="45"/>
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="45"/>
-      <c r="F74" s="45"/>
-      <c r="G74" s="45"/>
-      <c r="H74" s="45" t="s">
+    <row r="76" spans="2:11">
+      <c r="B76" s="45"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="45"/>
+      <c r="H76" s="45" t="s">
         <v>199</v>
       </c>
-      <c r="I74" s="45" t="s">
+      <c r="I76" s="45" t="s">
         <v>200</v>
       </c>
-      <c r="J74" s="45">
-        <v>1</v>
-      </c>
-      <c r="K74" s="45" t="s">
+      <c r="J76" s="45">
+        <v>1</v>
+      </c>
+      <c r="K76" s="45" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="75" spans="2:11">
-      <c r="B75" s="47" t="s">
+    <row r="77" spans="2:11">
+      <c r="B77" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="C75" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="D75" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
-      <c r="H75" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="I75" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="J75" s="40">
-        <v>1</v>
-      </c>
-      <c r="K75" s="27" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="27"/>
-      <c r="H76" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="I76" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="J76" s="40">
-        <v>2</v>
-      </c>
-      <c r="K76" s="27" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
-      <c r="D77" s="27"/>
+      <c r="C77" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="D77" s="46" t="b">
+        <v>1</v>
+      </c>
       <c r="E77" s="27"/>
       <c r="F77" s="27"/>
       <c r="G77" s="27"/>
       <c r="H77" s="27" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="I77" s="27" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J77" s="40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K77" s="27" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="2:11">
@@ -3214,16 +3230,16 @@
       <c r="F78" s="27"/>
       <c r="G78" s="27"/>
       <c r="H78" s="27" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I78" s="27" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="J78" s="40">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K78" s="27" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="2:11">
@@ -3234,193 +3250,233 @@
       <c r="F79" s="27"/>
       <c r="G79" s="27"/>
       <c r="H79" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="I79" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="J79" s="40">
+        <v>4</v>
+      </c>
+      <c r="K79" s="27" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" s="27"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="I80" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="J80" s="40">
+        <v>8</v>
+      </c>
+      <c r="K80" s="27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" s="27"/>
+      <c r="C81" s="27"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="I79" s="27" t="s">
+      <c r="I81" s="27" t="s">
         <v>211</v>
       </c>
-      <c r="J79" s="40">
+      <c r="J81" s="40">
         <v>16</v>
       </c>
-      <c r="K79" s="27" t="s">
+      <c r="K81" s="27" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="80" spans="2:11">
-      <c r="B80" s="50" t="s">
+    <row r="82" spans="2:11">
+      <c r="B82" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="C80" s="44" t="b">
+      <c r="C82" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="D80" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" s="45"/>
-      <c r="F80" s="45"/>
-      <c r="G80" s="45"/>
-      <c r="H80" s="45" t="s">
+      <c r="D82" s="46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="45"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="45"/>
+      <c r="H82" s="45" t="s">
         <v>217</v>
       </c>
-      <c r="I80" s="45" t="s">
+      <c r="I82" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="J80" s="45">
-        <v>1</v>
-      </c>
-      <c r="K80" s="45" t="s">
+      <c r="J82" s="45">
+        <v>1</v>
+      </c>
+      <c r="K82" s="45" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="81" spans="2:11">
-      <c r="B81" s="45"/>
-      <c r="C81" s="45"/>
-      <c r="D81" s="45"/>
-      <c r="E81" s="45"/>
-      <c r="F81" s="45"/>
-      <c r="G81" s="45"/>
-      <c r="H81" s="45" t="s">
+    <row r="83" spans="2:11">
+      <c r="B83" s="45"/>
+      <c r="C83" s="45"/>
+      <c r="D83" s="45"/>
+      <c r="E83" s="45"/>
+      <c r="F83" s="45"/>
+      <c r="G83" s="45"/>
+      <c r="H83" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="I81" s="45" t="s">
+      <c r="I83" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="J81" s="45">
+      <c r="J83" s="45">
         <v>2</v>
       </c>
-      <c r="K81" s="45" t="s">
+      <c r="K83" s="45" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="82" spans="2:11">
-      <c r="B82" s="27" t="s">
+    <row r="84" spans="2:11">
+      <c r="B84" s="27" t="s">
         <v>222</v>
       </c>
-      <c r="C82" s="46" t="b">
+      <c r="C84" s="46" t="b">
         <v>0</v>
       </c>
-      <c r="D82" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" s="27"/>
-      <c r="F82" s="27"/>
-      <c r="G82" s="27"/>
-      <c r="H82" s="49" t="s">
-        <v>223</v>
-      </c>
-      <c r="I82" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="J82" s="27">
-        <v>1</v>
-      </c>
-      <c r="K82" s="27" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
-      <c r="H83" s="49" t="s">
-        <v>224</v>
-      </c>
-      <c r="I83" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="J83" s="27">
-        <v>2</v>
-      </c>
-      <c r="K83" s="27" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84" s="27"/>
-      <c r="C84" s="27"/>
-      <c r="D84" s="27"/>
+      <c r="D84" s="46" t="b">
+        <v>1</v>
+      </c>
       <c r="E84" s="27"/>
       <c r="F84" s="27"/>
       <c r="G84" s="27"/>
-      <c r="H84" s="49" t="s">
+      <c r="H84" s="48" t="s">
+        <v>223</v>
+      </c>
+      <c r="I84" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="J84" s="27">
+        <v>1</v>
+      </c>
+      <c r="K84" s="27" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" s="27"/>
+      <c r="C85" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="I85" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="J85" s="27">
+        <v>2</v>
+      </c>
+      <c r="K85" s="27" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="27"/>
+      <c r="C86" s="27"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
+      <c r="H86" s="48" t="s">
         <v>225</v>
       </c>
-      <c r="I84" s="27" t="s">
+      <c r="I86" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="J84" s="27">
+      <c r="J86" s="27">
         <v>3</v>
       </c>
-      <c r="K84" s="27" t="s">
+      <c r="K86" s="27" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="85" spans="2:11">
-      <c r="B85" s="51" t="s">
+    <row r="87" spans="2:11">
+      <c r="B87" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="C85" s="52" t="b">
+      <c r="C87" s="51" t="b">
         <v>0</v>
       </c>
-      <c r="D85" s="52" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="51"/>
-      <c r="F85" s="51"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="53" t="s">
+      <c r="D87" s="51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="50"/>
+      <c r="F87" s="50"/>
+      <c r="G87" s="50"/>
+      <c r="H87" s="52" t="s">
         <v>230</v>
       </c>
-      <c r="I85" s="51" t="s">
+      <c r="I87" s="50" t="s">
         <v>233</v>
       </c>
-      <c r="J85" s="51">
-        <v>1</v>
-      </c>
-      <c r="K85" s="51" t="s">
+      <c r="J87" s="50">
+        <v>1</v>
+      </c>
+      <c r="K87" s="50" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="51"/>
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="51"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="53" t="s">
+    <row r="88" spans="2:11">
+      <c r="B88" s="50"/>
+      <c r="C88" s="50"/>
+      <c r="D88" s="50"/>
+      <c r="E88" s="50"/>
+      <c r="F88" s="50"/>
+      <c r="G88" s="50"/>
+      <c r="H88" s="52" t="s">
         <v>231</v>
       </c>
-      <c r="I86" s="51" t="s">
+      <c r="I88" s="50" t="s">
         <v>234</v>
       </c>
-      <c r="J86" s="51">
+      <c r="J88" s="50">
         <v>2</v>
       </c>
-      <c r="K86" s="51" t="s">
+      <c r="K88" s="50" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="87" spans="2:11">
-      <c r="B87" s="51"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="51"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="53" t="s">
+    <row r="89" spans="2:11">
+      <c r="B89" s="50"/>
+      <c r="C89" s="50"/>
+      <c r="D89" s="50"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="50"/>
+      <c r="G89" s="50"/>
+      <c r="H89" s="52" t="s">
         <v>232</v>
       </c>
-      <c r="I87" s="51" t="s">
+      <c r="I89" s="50" t="s">
         <v>235</v>
       </c>
-      <c r="J87" s="51">
+      <c r="J89" s="50">
         <v>3</v>
       </c>
-      <c r="K87" s="51" t="s">
+      <c r="K89" s="50" t="s">
         <v>235</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24544CB4-7FF1-4629-8DD0-AD68A4EA4F4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1660" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="240">
   <si>
     <t>##var</t>
   </si>
@@ -254,6 +248,18 @@
     <t>基础良品率</t>
   </si>
   <si>
+    <t>ClawMachineValue</t>
+  </si>
+  <si>
+    <t>娃娃机游戏次数</t>
+  </si>
+  <si>
+    <t>HeartCoins</t>
+  </si>
+  <si>
+    <t>爱心币</t>
+  </si>
+  <si>
     <t>UICanvasLayer</t>
   </si>
   <si>
@@ -527,6 +533,15 @@
     <t>22=激情一下</t>
   </si>
   <si>
+    <t>ActoryProduction</t>
+  </si>
+  <si>
+    <t>工厂制作</t>
+  </si>
+  <si>
+    <t>23=工厂制作</t>
+  </si>
+  <si>
     <t>ShowRuleTimeType</t>
   </si>
   <si>
@@ -575,6 +590,9 @@
     <t>ShowRuleWeekType</t>
   </si>
   <si>
+    <t>Monday</t>
+  </si>
+  <si>
     <t>周一</t>
   </si>
   <si>
@@ -642,106 +660,75 @@
   </si>
   <si>
     <t>UnlockConditionsType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>无解锁条件</t>
+  </si>
+  <si>
+    <t>没有解锁条件</t>
   </si>
   <si>
     <t>Prop</t>
   </si>
   <si>
+    <t>属性</t>
+  </si>
+  <si>
+    <t>玩家属性</t>
+  </si>
+  <si>
     <t>Item</t>
   </si>
   <si>
+    <t>物品</t>
+  </si>
+  <si>
+    <t>玩家物品</t>
+  </si>
+  <si>
     <t>Character</t>
   </si>
   <si>
+    <t>角色</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>无解锁条件</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>物品</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>没有解锁条件</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家属性</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家物品</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Monday</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>CharacterPropType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">Feeling </t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>心情值</t>
   </si>
   <si>
     <t xml:space="preserve">Goodwill </t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>心情值</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>好感值</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SelectMode</t>
   </si>
   <si>
-    <t>All</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>RandomOne</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>随机一个</t>
   </si>
   <si>
     <t>RandomCount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>随机一个</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>全部</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>随机全部</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>RefreshType</t>
@@ -750,45 +737,29 @@
     <t>TimeSlot</t>
   </si>
   <si>
+    <t>时间段</t>
+  </si>
+  <si>
     <t xml:space="preserve">Day </t>
   </si>
   <si>
     <t>EveryEnter</t>
   </si>
   <si>
-    <t>时间段</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>每天</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>每次</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HeartCoins</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱心币</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClawMachineValue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>娃娃机游戏次数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -800,28 +771,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -829,10 +784,154 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -841,19 +940,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79989013336588644"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.799890133365886"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -877,7 +976,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
+        <fgColor theme="3" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -901,13 +1000,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39991454817346722"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.399914548173467"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -919,13 +1018,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39991454817346722"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399914548173467"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -937,12 +1036,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1090,13 +1375,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1166,18 +1693,15 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1233,52 +1757,93 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFC6E0B4"/>
-      <color rgb="FF70AD47"/>
-      <color rgb="FFACB9CA"/>
-      <color rgb="FF4472C4"/>
+      <color rgb="00C6E0B4"/>
+      <color rgb="0070AD47"/>
+      <color rgb="00ACB9CA"/>
+      <color rgb="004472C4"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1536,25 +2101,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L89"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.0833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -1581,13 +2146,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1615,7 +2180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2012,7 +2577,7 @@
       </c>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="26"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
       <c r="E21" s="25"/>
@@ -2079,16 +2644,16 @@
       <c r="F24" s="25"/>
       <c r="G24" s="25"/>
       <c r="H24" s="25" t="s">
-        <v>238</v>
+        <v>73</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>239</v>
+        <v>74</v>
       </c>
       <c r="J24" s="25">
         <v>7</v>
       </c>
       <c r="K24" s="25" t="s">
-        <v>239</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="2:11">
@@ -2099,1393 +2664,1414 @@
       <c r="F25" s="25"/>
       <c r="G25" s="25"/>
       <c r="H25" s="25" t="s">
-        <v>236</v>
+        <v>75</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>237</v>
+        <v>76</v>
       </c>
       <c r="J25" s="25">
         <v>8</v>
       </c>
       <c r="K25" s="25" t="s">
-        <v>237</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="27" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="28" t="b">
+      <c r="B26" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D26" s="28" t="b">
+      <c r="D26" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="I26" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="J26" s="27">
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="J26" s="26">
         <v>0</v>
       </c>
-      <c r="K26" s="27" t="s">
-        <v>75</v>
+      <c r="K26" s="26" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="2:11">
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="I27" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="J27" s="27">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="26">
         <v>1</v>
       </c>
-      <c r="K27" s="27" t="s">
-        <v>77</v>
+      <c r="K27" s="26" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="2:11">
-      <c r="B28" s="29"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="27" t="s">
+      <c r="B28" s="28"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="I28" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="J28" s="26">
+        <v>2</v>
+      </c>
+      <c r="K28" s="26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" s="26">
+        <v>3</v>
+      </c>
+      <c r="K29" s="26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="I30" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="J28" s="27">
+      <c r="J30" s="31">
+        <v>0</v>
+      </c>
+      <c r="K30" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="32"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="I31" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="J31" s="31">
+        <v>1</v>
+      </c>
+      <c r="K31" s="31" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="I32" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="J32" s="31">
         <v>2</v>
       </c>
-      <c r="K28" s="27" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11">
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="I29" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="J29" s="27">
+      <c r="K32" s="31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="I33" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="J33" s="31">
         <v>3</v>
       </c>
-      <c r="K29" s="27" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="31" t="b">
+      <c r="K33" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="34" t="b">
         <v>0</v>
       </c>
-      <c r="D30" s="31" t="b">
+      <c r="D34" s="34" t="b">
         <v>1</v>
       </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>75</v>
-      </c>
-      <c r="J30" s="32">
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="J34" s="33">
+        <v>1</v>
+      </c>
+      <c r="K34" s="33" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" s="33"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="J35" s="33">
+        <v>2</v>
+      </c>
+      <c r="K35" s="33" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="I36" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J36" s="33">
+        <v>3</v>
+      </c>
+      <c r="K36" s="33" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="I37" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="J37" s="35">
         <v>0</v>
       </c>
-      <c r="K30" s="32" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="33"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="I31" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="J31" s="32">
+      <c r="K37" s="35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38" s="35"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="I38" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="J38" s="35">
         <v>1</v>
       </c>
-      <c r="K31" s="32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="I32" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="J32" s="32">
+      <c r="K38" s="35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="I39" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="J39" s="35">
+        <f t="shared" ref="J39:J60" si="0">J38*2</f>
         <v>2</v>
       </c>
-      <c r="K32" s="32" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="I33" s="32" t="s">
-        <v>81</v>
-      </c>
-      <c r="J33" s="32">
-        <v>3</v>
-      </c>
-      <c r="K33" s="32" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="I34" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="J34" s="34">
-        <v>1</v>
-      </c>
-      <c r="K34" s="34" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34" t="s">
-        <v>88</v>
-      </c>
-      <c r="I35" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="J35" s="34">
-        <v>2</v>
-      </c>
-      <c r="K35" s="34" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="I36" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="J36" s="34">
-        <v>3</v>
-      </c>
-      <c r="K36" s="34" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="B37" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="D37" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="I37" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="J37" s="36">
-        <v>0</v>
-      </c>
-      <c r="K37" s="36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="36"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="I38" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="J38" s="36">
-        <v>1</v>
-      </c>
-      <c r="K38" s="36" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="36"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="I39" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="J39" s="36">
-        <f t="shared" ref="J39:J59" si="0">J38*2</f>
-        <v>2</v>
-      </c>
-      <c r="K39" s="36" t="s">
-        <v>103</v>
+      <c r="K39" s="35" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="2:11">
-      <c r="B40" s="36"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="I40" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="J40" s="36">
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="I40" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="J40" s="35">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K40" s="36" t="s">
-        <v>106</v>
+      <c r="K40" s="35" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="2:11">
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="I41" s="36" t="s">
-        <v>108</v>
-      </c>
-      <c r="J41" s="36">
+      <c r="B41" s="35"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="I41" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="J41" s="35">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K41" s="36" t="s">
-        <v>109</v>
+      <c r="K41" s="35" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="2:11">
-      <c r="B42" s="36"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="I42" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="J42" s="36">
+      <c r="B42" s="35"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="I42" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="J42" s="35">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="K42" s="36" t="s">
-        <v>112</v>
+      <c r="K42" s="35" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="2:11">
-      <c r="B43" s="36"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="36"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="I43" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="J43" s="36">
+      <c r="B43" s="35"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="I43" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="J43" s="35">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="K43" s="36" t="s">
-        <v>115</v>
+      <c r="K43" s="35" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="2:11">
-      <c r="B44" s="36"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="I44" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="J44" s="36">
+      <c r="B44" s="35"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="I44" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="J44" s="35">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="K44" s="36" t="s">
-        <v>118</v>
+      <c r="K44" s="35" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="2:11">
-      <c r="B45" s="36"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="36"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="I45" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="J45" s="36">
+      <c r="B45" s="35"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="I45" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="J45" s="35">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="K45" s="36" t="s">
-        <v>121</v>
+      <c r="K45" s="35" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="2:11">
-      <c r="B46" s="36"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="I46" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="J46" s="36">
+      <c r="B46" s="35"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="I46" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="J46" s="35">
         <f t="shared" si="0"/>
         <v>256</v>
       </c>
-      <c r="K46" s="36" t="s">
-        <v>124</v>
+      <c r="K46" s="35" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="2:11">
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="36"/>
-      <c r="F47" s="36"/>
-      <c r="G47" s="36"/>
-      <c r="H47" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="I47" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="J47" s="36">
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="I47" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="J47" s="35">
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
-      <c r="K47" s="36" t="s">
-        <v>127</v>
+      <c r="K47" s="35" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="2:11">
-      <c r="B48" s="36"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="36"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="I48" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="J48" s="36">
+      <c r="B48" s="35"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="I48" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="J48" s="35">
         <f t="shared" si="0"/>
         <v>1024</v>
       </c>
-      <c r="K48" s="36" t="s">
-        <v>130</v>
+      <c r="K48" s="35" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="2:11">
-      <c r="B49" s="36"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
-      <c r="G49" s="36"/>
-      <c r="H49" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="I49" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="J49" s="36">
+      <c r="B49" s="35"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="35"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="I49" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="J49" s="35">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
-      <c r="K49" s="36" t="s">
-        <v>133</v>
+      <c r="K49" s="35" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="2:11">
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="36"/>
-      <c r="H50" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="I50" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="J50" s="36">
+      <c r="B50" s="35"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="I50" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="J50" s="35">
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
-      <c r="K50" s="36" t="s">
-        <v>136</v>
+      <c r="K50" s="35" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="2:11">
-      <c r="B51" s="36"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="36"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="I51" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="J51" s="36">
+      <c r="B51" s="35"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="I51" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="J51" s="35">
         <f t="shared" si="0"/>
         <v>8192</v>
       </c>
-      <c r="K51" s="36" t="s">
-        <v>139</v>
+      <c r="K51" s="35" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="52" spans="2:11">
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="38"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="36"/>
-      <c r="H52" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="I52" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="J52" s="36">
+      <c r="B52" s="35"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="I52" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="J52" s="35">
         <f t="shared" si="0"/>
         <v>16384</v>
       </c>
-      <c r="K52" s="36" t="s">
-        <v>142</v>
+      <c r="K52" s="35" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="2:11">
-      <c r="B53" s="36"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="I53" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="J53" s="36">
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="I53" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="J53" s="35">
         <f t="shared" si="0"/>
         <v>32768</v>
       </c>
-      <c r="K53" s="36" t="s">
-        <v>145</v>
+      <c r="K53" s="35" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="2:11">
-      <c r="B54" s="36"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="36"/>
-      <c r="F54" s="36"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="I54" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="J54" s="36">
+      <c r="B54" s="35"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="I54" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="J54" s="35">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
-      <c r="K54" s="36" t="s">
-        <v>148</v>
+      <c r="K54" s="35" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="2:11">
-      <c r="B55" s="36"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="36"/>
-      <c r="F55" s="36"/>
-      <c r="G55" s="36"/>
-      <c r="H55" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="I55" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="J55" s="36">
+      <c r="B55" s="35"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="I55" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="J55" s="35">
         <f t="shared" si="0"/>
         <v>131072</v>
       </c>
-      <c r="K55" s="36" t="s">
-        <v>151</v>
+      <c r="K55" s="35" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="56" spans="2:11">
-      <c r="B56" s="36"/>
-      <c r="C56" s="36"/>
-      <c r="D56" s="36"/>
-      <c r="E56" s="36"/>
-      <c r="F56" s="36"/>
-      <c r="G56" s="36"/>
-      <c r="H56" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="I56" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="J56" s="36">
+      <c r="B56" s="35"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="I56" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="J56" s="35">
         <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K56" s="36" t="s">
-        <v>154</v>
+      <c r="K56" s="35" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="2:11">
-      <c r="B57" s="38"/>
-      <c r="C57" s="38"/>
-      <c r="D57" s="38"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38" t="s">
-        <v>155</v>
-      </c>
-      <c r="I57" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="J57" s="38">
+      <c r="B57" s="37"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="37"/>
+      <c r="E57" s="37"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
+      <c r="H57" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>160</v>
+      </c>
+      <c r="J57" s="37">
         <f t="shared" si="0"/>
         <v>524288</v>
       </c>
-      <c r="K57" s="38" t="s">
-        <v>157</v>
+      <c r="K57" s="37" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="2:11">
-      <c r="B58" s="38"/>
-      <c r="C58" s="38"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="I58" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="J58" s="38">
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="I58" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="J58" s="37">
         <f t="shared" si="0"/>
         <v>1048576</v>
       </c>
-      <c r="K58" s="38" t="s">
-        <v>160</v>
+      <c r="K58" s="37" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="2:11">
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="I59" s="38" t="s">
-        <v>162</v>
-      </c>
-      <c r="J59" s="38">
+      <c r="B59" s="37"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="I59" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="J59" s="37">
         <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
-      <c r="K59" s="38" t="s">
-        <v>163</v>
+      <c r="K59" s="37" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="60" spans="2:11">
-      <c r="B60" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="C60" s="37" t="b">
+      <c r="B60" s="37"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
+      <c r="H60" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="I60" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="J60" s="37">
+        <f t="shared" si="0"/>
+        <v>4194304</v>
+      </c>
+      <c r="K60" s="37" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
+      <c r="B61" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="C61" s="36" t="b">
         <v>1</v>
       </c>
-      <c r="D60" s="37" t="b">
+      <c r="D61" s="36" t="b">
         <v>1</v>
       </c>
-      <c r="E60" s="39"/>
-      <c r="F60" s="39"/>
-      <c r="G60" s="39"/>
-      <c r="H60" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="I60" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="J60" s="36">
+      <c r="E61" s="38"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="I61" s="38" t="s">
+        <v>173</v>
+      </c>
+      <c r="J61" s="35">
         <v>1</v>
       </c>
-      <c r="K60" s="39" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="39"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="I61" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="J61" s="36">
+      <c r="K61" s="38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="I62" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="J62" s="35">
         <v>2</v>
       </c>
-      <c r="K61" s="39" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="39"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
-      <c r="G62" s="39"/>
-      <c r="H62" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="I62" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="J62" s="36">
+      <c r="K62" s="38" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="38"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="I63" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="J63" s="35">
         <v>4</v>
       </c>
-      <c r="K62" s="39" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="39"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="I63" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="J63" s="36">
+      <c r="K63" s="38" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="I64" s="38" t="s">
+        <v>181</v>
+      </c>
+      <c r="J64" s="35">
         <v>8</v>
       </c>
-      <c r="K63" s="39" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="39"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="39"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="I64" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="J64" s="36">
+      <c r="K64" s="38" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11">
+      <c r="B65" s="38"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="38"/>
+      <c r="E65" s="38"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
+      <c r="H65" s="38" t="s">
+        <v>183</v>
+      </c>
+      <c r="I65" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="J65" s="35">
         <v>15</v>
       </c>
-      <c r="K64" s="39" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="65" spans="2:11">
-      <c r="B65" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="C65" s="41" t="b">
+      <c r="K65" s="38" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="C66" s="40" t="b">
         <v>1</v>
       </c>
-      <c r="D65" s="41" t="b">
+      <c r="D66" s="40" t="b">
         <v>1</v>
       </c>
-      <c r="E65" s="40"/>
-      <c r="F65" s="40"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="I65" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="J65" s="40">
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39"/>
+      <c r="H66" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="I66" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="J66" s="39">
         <v>1</v>
       </c>
-      <c r="K65" s="40" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="40"/>
-      <c r="C66" s="40"/>
-      <c r="D66" s="40"/>
-      <c r="E66" s="40"/>
-      <c r="F66" s="40"/>
-      <c r="G66" s="40"/>
-      <c r="H66" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="I66" s="40" t="s">
-        <v>182</v>
-      </c>
-      <c r="J66" s="40">
+      <c r="K66" s="39" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" s="39"/>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="I67" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="J67" s="39">
         <v>2</v>
       </c>
-      <c r="K66" s="40" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="40"/>
-      <c r="C67" s="40"/>
-      <c r="D67" s="40"/>
-      <c r="E67" s="40"/>
-      <c r="F67" s="40"/>
-      <c r="G67" s="40"/>
-      <c r="H67" s="40" t="s">
+      <c r="K67" s="39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" s="39"/>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="I68" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="J68" s="39">
+        <v>4</v>
+      </c>
+      <c r="K68" s="39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11">
+      <c r="B69" s="39"/>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="I69" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="J69" s="39">
+        <v>8</v>
+      </c>
+      <c r="K69" s="39" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11">
+      <c r="B70" s="39"/>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="I70" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="J70" s="39">
+        <v>16</v>
+      </c>
+      <c r="K70" s="39" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
+      <c r="B71" s="39"/>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="I71" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="J71" s="39">
+        <v>32</v>
+      </c>
+      <c r="K71" s="39" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="B72" s="39"/>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39"/>
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="I72" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="J72" s="39">
+        <v>64</v>
+      </c>
+      <c r="K72" s="39" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
+      <c r="B73" s="39"/>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="I67" s="40" t="s">
+      <c r="I73" s="39" t="s">
         <v>184</v>
       </c>
-      <c r="J67" s="40">
-        <v>4</v>
-      </c>
-      <c r="K67" s="40" t="s">
+      <c r="J73" s="39">
+        <v>127</v>
+      </c>
+      <c r="K73" s="39" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="40"/>
-      <c r="C68" s="40"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="40"/>
-      <c r="F68" s="40"/>
-      <c r="G68" s="40"/>
-      <c r="H68" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="I68" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="J68" s="40">
-        <v>8</v>
-      </c>
-      <c r="K68" s="40" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69" s="40"/>
-      <c r="C69" s="40"/>
-      <c r="D69" s="40"/>
-      <c r="E69" s="40"/>
-      <c r="F69" s="40"/>
-      <c r="G69" s="40"/>
-      <c r="H69" s="40" t="s">
-        <v>187</v>
-      </c>
-      <c r="I69" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="J69" s="40">
-        <v>16</v>
-      </c>
-      <c r="K69" s="40" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11">
-      <c r="B70" s="40"/>
-      <c r="C70" s="40"/>
-      <c r="D70" s="40"/>
-      <c r="E70" s="40"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="40"/>
-      <c r="H70" s="40" t="s">
-        <v>189</v>
-      </c>
-      <c r="I70" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="J70" s="40">
-        <v>32</v>
-      </c>
-      <c r="K70" s="40" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11">
-      <c r="B71" s="40"/>
-      <c r="C71" s="40"/>
-      <c r="D71" s="40"/>
-      <c r="E71" s="40"/>
-      <c r="F71" s="40"/>
-      <c r="G71" s="40"/>
-      <c r="H71" s="40" t="s">
-        <v>191</v>
-      </c>
-      <c r="I71" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="J71" s="40">
-        <v>64</v>
-      </c>
-      <c r="K71" s="40" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="40"/>
-      <c r="C72" s="40"/>
-      <c r="D72" s="40"/>
-      <c r="E72" s="40"/>
-      <c r="F72" s="40"/>
-      <c r="G72" s="40"/>
-      <c r="H72" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="I72" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="J72" s="40">
-        <v>127</v>
-      </c>
-      <c r="K72" s="40" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11">
-      <c r="B73" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="C73" s="42" t="b">
+    <row r="74" spans="2:11">
+      <c r="B74" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="C74" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="D73" s="42" t="b">
+      <c r="D74" s="41" t="b">
         <v>1</v>
       </c>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25"/>
-      <c r="G73" s="25"/>
-      <c r="H73" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="I73" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="J73" s="25">
-        <v>0</v>
-      </c>
-      <c r="K73" s="25"/>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
       <c r="E74" s="25"/>
       <c r="F74" s="25"/>
       <c r="G74" s="25"/>
       <c r="H74" s="25" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I74" s="25" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="J74" s="25">
+        <v>0</v>
+      </c>
+      <c r="K74" s="25"/>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="I75" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="J75" s="25">
         <v>1</v>
       </c>
-      <c r="K74" s="25"/>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="B75" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="C75" s="44" t="b">
+      <c r="K75" s="25"/>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="C76" s="43" t="b">
         <v>0</v>
       </c>
-      <c r="D75" s="44" t="b">
+      <c r="D76" s="43" t="b">
         <v>1</v>
       </c>
-      <c r="E75" s="45"/>
-      <c r="F75" s="45"/>
-      <c r="G75" s="45"/>
-      <c r="H75" s="45" t="s">
+      <c r="E76" s="44"/>
+      <c r="F76" s="44"/>
+      <c r="G76" s="44"/>
+      <c r="H76" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="I75" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="J75" s="45">
+      <c r="I76" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="J76" s="44">
         <v>0</v>
       </c>
-      <c r="K75" s="45" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="45"/>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="45"/>
-      <c r="F76" s="45"/>
-      <c r="G76" s="45"/>
-      <c r="H76" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="I76" s="45" t="s">
-        <v>200</v>
-      </c>
-      <c r="J76" s="45">
+      <c r="K76" s="44" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" s="44"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="44"/>
+      <c r="H77" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="I77" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="J77" s="44">
         <v>1</v>
       </c>
-      <c r="K76" s="45" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77" s="47" t="s">
-        <v>202</v>
-      </c>
-      <c r="C77" s="46" t="b">
+      <c r="K77" s="44" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="C78" s="46" t="b">
         <v>1</v>
       </c>
-      <c r="D77" s="46" t="b">
+      <c r="D78" s="46" t="b">
         <v>1</v>
       </c>
-      <c r="E77" s="27"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="27"/>
-      <c r="H77" s="27" t="s">
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="I78" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="J78" s="39">
+        <v>1</v>
+      </c>
+      <c r="K78" s="26" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="I79" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="J79" s="39">
+        <v>2</v>
+      </c>
+      <c r="K79" s="26" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="I80" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="J80" s="39">
+        <v>4</v>
+      </c>
+      <c r="K80" s="26" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="I81" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="I77" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="J77" s="40">
+      <c r="J81" s="39">
+        <v>8</v>
+      </c>
+      <c r="K81" s="26" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="I82" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="J82" s="39">
+        <v>16</v>
+      </c>
+      <c r="K82" s="26" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="C83" s="43" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" s="46" t="b">
         <v>1</v>
       </c>
-      <c r="K77" s="27" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="I78" s="27" t="s">
-        <v>208</v>
-      </c>
-      <c r="J78" s="40">
+      <c r="E83" s="44"/>
+      <c r="F83" s="44"/>
+      <c r="G83" s="44"/>
+      <c r="H83" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="I83" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="J83" s="44">
+        <v>1</v>
+      </c>
+      <c r="K83" s="44" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="I84" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="J84" s="44">
         <v>2</v>
       </c>
-      <c r="K78" s="27" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="I79" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="J79" s="40">
-        <v>4</v>
-      </c>
-      <c r="K79" s="27" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="I80" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="J80" s="40">
-        <v>8</v>
-      </c>
-      <c r="K80" s="27" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="I81" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="J81" s="40">
-        <v>16</v>
-      </c>
-      <c r="K81" s="27" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="C82" s="44" t="b">
+      <c r="K84" s="44" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C85" s="46" t="b">
         <v>0</v>
       </c>
-      <c r="D82" s="46" t="b">
+      <c r="D85" s="46" t="b">
         <v>1</v>
       </c>
-      <c r="E82" s="45"/>
-      <c r="F82" s="45"/>
-      <c r="G82" s="45"/>
-      <c r="H82" s="45" t="s">
-        <v>217</v>
-      </c>
-      <c r="I82" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="J82" s="45">
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="I85" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="J85" s="26">
         <v>1</v>
       </c>
-      <c r="K82" s="45" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="B83" s="45"/>
-      <c r="C83" s="45"/>
-      <c r="D83" s="45"/>
-      <c r="E83" s="45"/>
-      <c r="F83" s="45"/>
-      <c r="G83" s="45"/>
-      <c r="H83" s="45" t="s">
-        <v>218</v>
-      </c>
-      <c r="I83" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="J83" s="45">
+      <c r="K85" s="26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="I86" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="J86" s="26">
         <v>2</v>
       </c>
-      <c r="K83" s="45" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84" s="27" t="s">
-        <v>222</v>
-      </c>
-      <c r="C84" s="46" t="b">
+      <c r="K86" s="26" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+      <c r="G87" s="26"/>
+      <c r="H87" s="48" t="s">
+        <v>232</v>
+      </c>
+      <c r="I87" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="J87" s="26">
+        <v>3</v>
+      </c>
+      <c r="K87" s="26" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" s="49" t="s">
+        <v>234</v>
+      </c>
+      <c r="C88" s="50" t="b">
         <v>0</v>
       </c>
-      <c r="D84" s="46" t="b">
+      <c r="D88" s="50" t="b">
         <v>1</v>
       </c>
-      <c r="E84" s="27"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="27"/>
-      <c r="H84" s="48" t="s">
-        <v>223</v>
-      </c>
-      <c r="I84" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="J84" s="27">
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
+      <c r="G88" s="49"/>
+      <c r="H88" s="51" t="s">
+        <v>235</v>
+      </c>
+      <c r="I88" s="49" t="s">
+        <v>236</v>
+      </c>
+      <c r="J88" s="49">
         <v>1</v>
       </c>
-      <c r="K84" s="27" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="B85" s="27"/>
-      <c r="C85" s="27"/>
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="27"/>
-      <c r="G85" s="27"/>
-      <c r="H85" s="48" t="s">
-        <v>224</v>
-      </c>
-      <c r="I85" s="27" t="s">
-        <v>226</v>
-      </c>
-      <c r="J85" s="27">
+      <c r="K88" s="49" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" s="49"/>
+      <c r="C89" s="49"/>
+      <c r="D89" s="49"/>
+      <c r="E89" s="49"/>
+      <c r="F89" s="49"/>
+      <c r="G89" s="49"/>
+      <c r="H89" s="51" t="s">
+        <v>237</v>
+      </c>
+      <c r="I89" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="J89" s="49">
         <v>2</v>
       </c>
-      <c r="K85" s="27" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="27"/>
-      <c r="C86" s="27"/>
-      <c r="D86" s="27"/>
-      <c r="E86" s="27"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="27"/>
-      <c r="H86" s="48" t="s">
-        <v>225</v>
-      </c>
-      <c r="I86" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="J86" s="27">
+      <c r="K89" s="49" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" s="49"/>
+      <c r="C90" s="49"/>
+      <c r="D90" s="49"/>
+      <c r="E90" s="49"/>
+      <c r="F90" s="49"/>
+      <c r="G90" s="49"/>
+      <c r="H90" s="51" t="s">
+        <v>238</v>
+      </c>
+      <c r="I90" s="49" t="s">
+        <v>239</v>
+      </c>
+      <c r="J90" s="49">
         <v>3</v>
       </c>
-      <c r="K86" s="27" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="B87" s="50" t="s">
-        <v>229</v>
-      </c>
-      <c r="C87" s="51" t="b">
-        <v>0</v>
-      </c>
-      <c r="D87" s="51" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="50"/>
-      <c r="F87" s="50"/>
-      <c r="G87" s="50"/>
-      <c r="H87" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="I87" s="50" t="s">
-        <v>233</v>
-      </c>
-      <c r="J87" s="50">
-        <v>1</v>
-      </c>
-      <c r="K87" s="50" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11">
-      <c r="B88" s="50"/>
-      <c r="C88" s="50"/>
-      <c r="D88" s="50"/>
-      <c r="E88" s="50"/>
-      <c r="F88" s="50"/>
-      <c r="G88" s="50"/>
-      <c r="H88" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="I88" s="50" t="s">
-        <v>234</v>
-      </c>
-      <c r="J88" s="50">
-        <v>2</v>
-      </c>
-      <c r="K88" s="50" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
-      <c r="B89" s="50"/>
-      <c r="C89" s="50"/>
-      <c r="D89" s="50"/>
-      <c r="E89" s="50"/>
-      <c r="F89" s="50"/>
-      <c r="G89" s="50"/>
-      <c r="H89" s="52" t="s">
-        <v>232</v>
-      </c>
-      <c r="I89" s="50" t="s">
-        <v>235</v>
-      </c>
-      <c r="J89" s="50">
-        <v>3</v>
-      </c>
-      <c r="K89" s="50" t="s">
-        <v>235</v>
+      <c r="K90" s="49" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43600EDD-D57B-4C7C-9399-A1F7D72830DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="-760" yWindow="4470" windowWidth="33700" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="289">
   <si>
     <t>##var</t>
   </si>
@@ -747,19 +753,189 @@
   </si>
   <si>
     <t>每次</t>
+  </si>
+  <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Affection</t>
+  </si>
+  <si>
+    <t>好感道具</t>
+  </si>
+  <si>
+    <t>Inspiration</t>
+  </si>
+  <si>
+    <t>灵感道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stress</t>
+  </si>
+  <si>
+    <t>压力道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina</t>
+  </si>
+  <si>
+    <t>体力道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>剧情道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ingredient</t>
+  </si>
+  <si>
+    <t>食材道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recipe</t>
+  </si>
+  <si>
+    <t>配方道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>食物道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FigureModel</t>
+  </si>
+  <si>
+    <t>手办模型</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Painting</t>
+  </si>
+  <si>
+    <t>绘画道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FactoryProductionMaterials</t>
+  </si>
+  <si>
+    <t>工厂生产材料</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cloth</t>
+  </si>
+  <si>
+    <t>布料</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Merchandise</t>
+  </si>
+  <si>
+    <t>周边货物</t>
+  </si>
+  <si>
+    <t>ShopItem</t>
+  </si>
+  <si>
+    <t>商店道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FishBait</t>
+  </si>
+  <si>
+    <t>鱼饵店</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FishRod</t>
+  </si>
+  <si>
+    <t>鱼竿</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>AdultToy</t>
+  </si>
+  <si>
+    <t>情趣道具</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClawMachineDoll</t>
+  </si>
+  <si>
+    <t>娃娃机</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemQuality</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SSR</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>稀有</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>神器</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>史诗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -771,12 +947,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -784,154 +962,17 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="50">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -940,19 +981,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799890133365886"/>
+        <fgColor theme="9" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -976,7 +1017,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.599993896298105"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,13 +1041,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399914548173467"/>
+        <fgColor theme="5" tint="0.39988402966399123"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1018,13 +1059,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399914548173467"/>
+        <fgColor theme="9" tint="0.39988402966399123"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1036,198 +1077,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1375,255 +1236,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1780,70 +1399,47 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00C6E0B4"/>
-      <color rgb="0070AD47"/>
-      <color rgb="00ACB9CA"/>
-      <color rgb="004472C4"/>
+      <color rgb="FFC6E0B4"/>
+      <color rgb="FF70AD47"/>
+      <color rgb="FFACB9CA"/>
+      <color rgb="FF4472C4"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2101,25 +1697,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L90"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.0833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -2146,13 +1742,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -2180,7 +1776,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -4066,12 +3662,504 @@
         <v>239</v>
       </c>
     </row>
+    <row r="91" spans="2:11">
+      <c r="B91" s="54" t="s">
+        <v>240</v>
+      </c>
+      <c r="C91" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="D91" s="55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="54"/>
+      <c r="F91" s="54"/>
+      <c r="G91" s="54"/>
+      <c r="H91" s="56" t="s">
+        <v>211</v>
+      </c>
+      <c r="I91" s="56" t="s">
+        <v>241</v>
+      </c>
+      <c r="J91" s="54">
+        <v>0</v>
+      </c>
+      <c r="K91" s="56" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="B92" s="54"/>
+      <c r="C92" s="54"/>
+      <c r="D92" s="54"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="54"/>
+      <c r="H92" s="56" t="s">
+        <v>242</v>
+      </c>
+      <c r="I92" s="56" t="s">
+        <v>243</v>
+      </c>
+      <c r="J92" s="54">
+        <v>1</v>
+      </c>
+      <c r="K92" s="56" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" s="54"/>
+      <c r="C93" s="54"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="54"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="56" t="s">
+        <v>244</v>
+      </c>
+      <c r="I93" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="J93" s="54">
+        <v>2</v>
+      </c>
+      <c r="K93" s="56" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="54"/>
+      <c r="C94" s="54"/>
+      <c r="D94" s="54"/>
+      <c r="E94" s="54"/>
+      <c r="F94" s="54"/>
+      <c r="G94" s="54"/>
+      <c r="H94" s="56" t="s">
+        <v>246</v>
+      </c>
+      <c r="I94" s="56" t="s">
+        <v>247</v>
+      </c>
+      <c r="J94" s="54">
+        <v>3</v>
+      </c>
+      <c r="K94" s="56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="B95" s="54"/>
+      <c r="C95" s="54"/>
+      <c r="D95" s="54"/>
+      <c r="E95" s="54"/>
+      <c r="F95" s="54"/>
+      <c r="G95" s="54"/>
+      <c r="H95" s="56" t="s">
+        <v>248</v>
+      </c>
+      <c r="I95" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="J95" s="54">
+        <v>4</v>
+      </c>
+      <c r="K95" s="56" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="B96" s="54"/>
+      <c r="C96" s="54"/>
+      <c r="D96" s="54"/>
+      <c r="E96" s="54"/>
+      <c r="F96" s="54"/>
+      <c r="G96" s="54"/>
+      <c r="H96" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="I96" s="56" t="s">
+        <v>251</v>
+      </c>
+      <c r="J96" s="54">
+        <v>5</v>
+      </c>
+      <c r="K96" s="56" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11">
+      <c r="B97" s="54"/>
+      <c r="C97" s="54"/>
+      <c r="D97" s="54"/>
+      <c r="E97" s="54"/>
+      <c r="F97" s="54"/>
+      <c r="G97" s="54"/>
+      <c r="H97" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="I97" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="J97" s="54">
+        <v>6</v>
+      </c>
+      <c r="K97" s="56" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11">
+      <c r="B98" s="54"/>
+      <c r="C98" s="54"/>
+      <c r="D98" s="54"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="54"/>
+      <c r="H98" s="56" t="s">
+        <v>254</v>
+      </c>
+      <c r="I98" s="56" t="s">
+        <v>255</v>
+      </c>
+      <c r="J98" s="54">
+        <v>7</v>
+      </c>
+      <c r="K98" s="56" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
+      <c r="B99" s="54"/>
+      <c r="C99" s="54"/>
+      <c r="D99" s="54"/>
+      <c r="E99" s="54"/>
+      <c r="F99" s="54"/>
+      <c r="G99" s="54"/>
+      <c r="H99" s="56" t="s">
+        <v>256</v>
+      </c>
+      <c r="I99" s="56" t="s">
+        <v>257</v>
+      </c>
+      <c r="J99" s="54">
+        <v>8</v>
+      </c>
+      <c r="K99" s="56" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11">
+      <c r="B100" s="54"/>
+      <c r="C100" s="54"/>
+      <c r="D100" s="54"/>
+      <c r="E100" s="54"/>
+      <c r="F100" s="54"/>
+      <c r="G100" s="54"/>
+      <c r="H100" s="56" t="s">
+        <v>258</v>
+      </c>
+      <c r="I100" s="56" t="s">
+        <v>259</v>
+      </c>
+      <c r="J100" s="54">
+        <v>9</v>
+      </c>
+      <c r="K100" s="56" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11">
+      <c r="B101" s="54"/>
+      <c r="C101" s="54"/>
+      <c r="D101" s="54"/>
+      <c r="E101" s="54"/>
+      <c r="F101" s="54"/>
+      <c r="G101" s="54"/>
+      <c r="H101" s="56" t="s">
+        <v>260</v>
+      </c>
+      <c r="I101" s="56" t="s">
+        <v>261</v>
+      </c>
+      <c r="J101" s="54">
+        <v>10</v>
+      </c>
+      <c r="K101" s="56" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11">
+      <c r="B102" s="54"/>
+      <c r="C102" s="54"/>
+      <c r="D102" s="54"/>
+      <c r="E102" s="54"/>
+      <c r="F102" s="54"/>
+      <c r="G102" s="54"/>
+      <c r="H102" s="56" t="s">
+        <v>262</v>
+      </c>
+      <c r="I102" s="56" t="s">
+        <v>263</v>
+      </c>
+      <c r="J102" s="54">
+        <v>11</v>
+      </c>
+      <c r="K102" s="56" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="B103" s="54"/>
+      <c r="C103" s="54"/>
+      <c r="D103" s="54"/>
+      <c r="E103" s="54"/>
+      <c r="F103" s="54"/>
+      <c r="G103" s="54"/>
+      <c r="H103" s="56" t="s">
+        <v>264</v>
+      </c>
+      <c r="I103" s="56" t="s">
+        <v>265</v>
+      </c>
+      <c r="J103" s="54">
+        <v>12</v>
+      </c>
+      <c r="K103" s="56" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="B104" s="54"/>
+      <c r="C104" s="54"/>
+      <c r="D104" s="54"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="54"/>
+      <c r="G104" s="54"/>
+      <c r="H104" s="56" t="s">
+        <v>266</v>
+      </c>
+      <c r="I104" s="56" t="s">
+        <v>267</v>
+      </c>
+      <c r="J104" s="54">
+        <v>13</v>
+      </c>
+      <c r="K104" s="56" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11">
+      <c r="B105" s="54"/>
+      <c r="C105" s="54"/>
+      <c r="D105" s="54"/>
+      <c r="E105" s="54"/>
+      <c r="F105" s="54"/>
+      <c r="G105" s="54"/>
+      <c r="H105" s="56" t="s">
+        <v>268</v>
+      </c>
+      <c r="I105" s="56" t="s">
+        <v>269</v>
+      </c>
+      <c r="J105" s="54">
+        <v>14</v>
+      </c>
+      <c r="K105" s="56" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
+      <c r="B106" s="54"/>
+      <c r="C106" s="54"/>
+      <c r="D106" s="54"/>
+      <c r="E106" s="54"/>
+      <c r="F106" s="54"/>
+      <c r="G106" s="54"/>
+      <c r="H106" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="I106" s="56" t="s">
+        <v>271</v>
+      </c>
+      <c r="J106" s="54">
+        <v>15</v>
+      </c>
+      <c r="K106" s="56" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11">
+      <c r="B107" s="54"/>
+      <c r="C107" s="54"/>
+      <c r="D107" s="54"/>
+      <c r="E107" s="54"/>
+      <c r="F107" s="54"/>
+      <c r="G107" s="54"/>
+      <c r="H107" s="56" t="s">
+        <v>272</v>
+      </c>
+      <c r="I107" s="56" t="s">
+        <v>273</v>
+      </c>
+      <c r="J107" s="54">
+        <v>16</v>
+      </c>
+      <c r="K107" s="56" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11">
+      <c r="B108" s="54"/>
+      <c r="C108" s="54"/>
+      <c r="D108" s="54"/>
+      <c r="E108" s="54"/>
+      <c r="F108" s="54"/>
+      <c r="G108" s="54"/>
+      <c r="H108" s="56" t="s">
+        <v>274</v>
+      </c>
+      <c r="I108" s="56" t="s">
+        <v>275</v>
+      </c>
+      <c r="J108" s="54">
+        <v>17</v>
+      </c>
+      <c r="K108" s="56" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11">
+      <c r="B109" s="54"/>
+      <c r="C109" s="54"/>
+      <c r="D109" s="54"/>
+      <c r="E109" s="54"/>
+      <c r="F109" s="54"/>
+      <c r="G109" s="54"/>
+      <c r="H109" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="I109" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="J109" s="54">
+        <v>18</v>
+      </c>
+      <c r="K109" s="56" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11">
+      <c r="B110" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="C110" s="58" t="b">
+        <v>0</v>
+      </c>
+      <c r="D110" s="58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E110" s="53"/>
+      <c r="F110" s="53"/>
+      <c r="G110" s="53"/>
+      <c r="H110" s="57" t="s">
+        <v>279</v>
+      </c>
+      <c r="I110" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="J110" s="53">
+        <v>1</v>
+      </c>
+      <c r="K110" s="53" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11">
+      <c r="B111" s="53"/>
+      <c r="C111" s="53"/>
+      <c r="D111" s="53"/>
+      <c r="E111" s="53"/>
+      <c r="F111" s="53"/>
+      <c r="G111" s="53"/>
+      <c r="H111" s="57" t="s">
+        <v>280</v>
+      </c>
+      <c r="I111" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="J111" s="53">
+        <v>2</v>
+      </c>
+      <c r="K111" s="53" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11">
+      <c r="B112" s="53"/>
+      <c r="C112" s="53"/>
+      <c r="D112" s="53"/>
+      <c r="E112" s="53"/>
+      <c r="F112" s="53"/>
+      <c r="G112" s="53"/>
+      <c r="H112" s="57" t="s">
+        <v>281</v>
+      </c>
+      <c r="I112" s="53" t="s">
+        <v>286</v>
+      </c>
+      <c r="J112" s="53">
+        <v>3</v>
+      </c>
+      <c r="K112" s="53" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="113" spans="2:11">
+      <c r="B113" s="53"/>
+      <c r="C113" s="53"/>
+      <c r="D113" s="53"/>
+      <c r="E113" s="53"/>
+      <c r="F113" s="53"/>
+      <c r="G113" s="53"/>
+      <c r="H113" s="57" t="s">
+        <v>282</v>
+      </c>
+      <c r="I113" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="J113" s="53">
+        <v>4</v>
+      </c>
+      <c r="K113" s="53" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="114" spans="2:11">
+      <c r="B114" s="53"/>
+      <c r="C114" s="53"/>
+      <c r="D114" s="53"/>
+      <c r="E114" s="53"/>
+      <c r="F114" s="53"/>
+      <c r="G114" s="53"/>
+      <c r="H114" s="57" t="s">
+        <v>283</v>
+      </c>
+      <c r="I114" s="53" t="s">
+        <v>288</v>
+      </c>
+      <c r="J114" s="53">
+        <v>5</v>
+      </c>
+      <c r="K114" s="53" t="s">
+        <v>288</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43600EDD-D57B-4C7C-9399-A1F7D72830DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4600DA6-9676-4C30-922E-123B3D4C9EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-760" yWindow="4470" windowWidth="33700" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="2940" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -972,7 +972,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1084,6 +1084,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1399,12 +1405,6 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1414,10 +1414,16 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1742,13 +1748,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="H1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -3663,494 +3669,494 @@
       </c>
     </row>
     <row r="91" spans="2:11">
-      <c r="B91" s="54" t="s">
+      <c r="B91" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="C91" s="55" t="b">
+      <c r="C91" s="53" t="b">
         <v>0</v>
       </c>
-      <c r="D91" s="55" t="b">
+      <c r="D91" s="53" t="b">
         <v>1</v>
       </c>
-      <c r="E91" s="54"/>
-      <c r="F91" s="54"/>
-      <c r="G91" s="54"/>
-      <c r="H91" s="56" t="s">
+      <c r="E91" s="52"/>
+      <c r="F91" s="52"/>
+      <c r="G91" s="52"/>
+      <c r="H91" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="I91" s="56" t="s">
+      <c r="I91" s="54" t="s">
         <v>241</v>
       </c>
-      <c r="J91" s="54">
+      <c r="J91" s="52">
         <v>0</v>
       </c>
-      <c r="K91" s="56" t="s">
+      <c r="K91" s="54" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="92" spans="2:11">
-      <c r="B92" s="54"/>
-      <c r="C92" s="54"/>
-      <c r="D92" s="54"/>
-      <c r="E92" s="54"/>
-      <c r="F92" s="54"/>
-      <c r="G92" s="54"/>
-      <c r="H92" s="56" t="s">
+      <c r="B92" s="52"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="52"/>
+      <c r="E92" s="52"/>
+      <c r="F92" s="52"/>
+      <c r="G92" s="52"/>
+      <c r="H92" s="54" t="s">
         <v>242</v>
       </c>
-      <c r="I92" s="56" t="s">
+      <c r="I92" s="54" t="s">
         <v>243</v>
       </c>
-      <c r="J92" s="54">
+      <c r="J92" s="52">
         <v>1</v>
       </c>
-      <c r="K92" s="56" t="s">
+      <c r="K92" s="54" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="93" spans="2:11">
-      <c r="B93" s="54"/>
-      <c r="C93" s="54"/>
-      <c r="D93" s="54"/>
-      <c r="E93" s="54"/>
-      <c r="F93" s="54"/>
-      <c r="G93" s="54"/>
-      <c r="H93" s="56" t="s">
+      <c r="B93" s="52"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="52"/>
+      <c r="F93" s="52"/>
+      <c r="G93" s="52"/>
+      <c r="H93" s="54" t="s">
         <v>244</v>
       </c>
-      <c r="I93" s="56" t="s">
+      <c r="I93" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="J93" s="54">
+      <c r="J93" s="52">
         <v>2</v>
       </c>
-      <c r="K93" s="56" t="s">
+      <c r="K93" s="54" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="94" spans="2:11">
-      <c r="B94" s="54"/>
-      <c r="C94" s="54"/>
-      <c r="D94" s="54"/>
-      <c r="E94" s="54"/>
-      <c r="F94" s="54"/>
-      <c r="G94" s="54"/>
-      <c r="H94" s="56" t="s">
+      <c r="B94" s="52"/>
+      <c r="C94" s="52"/>
+      <c r="D94" s="52"/>
+      <c r="E94" s="52"/>
+      <c r="F94" s="52"/>
+      <c r="G94" s="52"/>
+      <c r="H94" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="I94" s="56" t="s">
+      <c r="I94" s="54" t="s">
         <v>247</v>
       </c>
-      <c r="J94" s="54">
+      <c r="J94" s="52">
         <v>3</v>
       </c>
-      <c r="K94" s="56" t="s">
+      <c r="K94" s="54" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="95" spans="2:11">
-      <c r="B95" s="54"/>
-      <c r="C95" s="54"/>
-      <c r="D95" s="54"/>
-      <c r="E95" s="54"/>
-      <c r="F95" s="54"/>
-      <c r="G95" s="54"/>
-      <c r="H95" s="56" t="s">
+      <c r="B95" s="52"/>
+      <c r="C95" s="52"/>
+      <c r="D95" s="52"/>
+      <c r="E95" s="52"/>
+      <c r="F95" s="52"/>
+      <c r="G95" s="52"/>
+      <c r="H95" s="54" t="s">
         <v>248</v>
       </c>
-      <c r="I95" s="56" t="s">
+      <c r="I95" s="54" t="s">
         <v>249</v>
       </c>
-      <c r="J95" s="54">
+      <c r="J95" s="52">
         <v>4</v>
       </c>
-      <c r="K95" s="56" t="s">
+      <c r="K95" s="54" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="96" spans="2:11">
-      <c r="B96" s="54"/>
-      <c r="C96" s="54"/>
-      <c r="D96" s="54"/>
-      <c r="E96" s="54"/>
-      <c r="F96" s="54"/>
-      <c r="G96" s="54"/>
-      <c r="H96" s="56" t="s">
+      <c r="B96" s="52"/>
+      <c r="C96" s="52"/>
+      <c r="D96" s="52"/>
+      <c r="E96" s="52"/>
+      <c r="F96" s="52"/>
+      <c r="G96" s="52"/>
+      <c r="H96" s="54" t="s">
         <v>250</v>
       </c>
-      <c r="I96" s="56" t="s">
+      <c r="I96" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="J96" s="54">
+      <c r="J96" s="52">
         <v>5</v>
       </c>
-      <c r="K96" s="56" t="s">
+      <c r="K96" s="54" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="97" spans="2:11">
-      <c r="B97" s="54"/>
-      <c r="C97" s="54"/>
-      <c r="D97" s="54"/>
-      <c r="E97" s="54"/>
-      <c r="F97" s="54"/>
-      <c r="G97" s="54"/>
-      <c r="H97" s="56" t="s">
+      <c r="B97" s="52"/>
+      <c r="C97" s="52"/>
+      <c r="D97" s="52"/>
+      <c r="E97" s="52"/>
+      <c r="F97" s="52"/>
+      <c r="G97" s="52"/>
+      <c r="H97" s="54" t="s">
         <v>252</v>
       </c>
-      <c r="I97" s="56" t="s">
+      <c r="I97" s="54" t="s">
         <v>253</v>
       </c>
-      <c r="J97" s="54">
+      <c r="J97" s="52">
         <v>6</v>
       </c>
-      <c r="K97" s="56" t="s">
+      <c r="K97" s="54" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="98" spans="2:11">
-      <c r="B98" s="54"/>
-      <c r="C98" s="54"/>
-      <c r="D98" s="54"/>
-      <c r="E98" s="54"/>
-      <c r="F98" s="54"/>
-      <c r="G98" s="54"/>
-      <c r="H98" s="56" t="s">
+      <c r="B98" s="52"/>
+      <c r="C98" s="52"/>
+      <c r="D98" s="52"/>
+      <c r="E98" s="52"/>
+      <c r="F98" s="52"/>
+      <c r="G98" s="52"/>
+      <c r="H98" s="54" t="s">
         <v>254</v>
       </c>
-      <c r="I98" s="56" t="s">
+      <c r="I98" s="54" t="s">
         <v>255</v>
       </c>
-      <c r="J98" s="54">
+      <c r="J98" s="52">
         <v>7</v>
       </c>
-      <c r="K98" s="56" t="s">
+      <c r="K98" s="54" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="99" spans="2:11">
-      <c r="B99" s="54"/>
-      <c r="C99" s="54"/>
-      <c r="D99" s="54"/>
-      <c r="E99" s="54"/>
-      <c r="F99" s="54"/>
-      <c r="G99" s="54"/>
-      <c r="H99" s="56" t="s">
+      <c r="B99" s="52"/>
+      <c r="C99" s="52"/>
+      <c r="D99" s="52"/>
+      <c r="E99" s="52"/>
+      <c r="F99" s="52"/>
+      <c r="G99" s="52"/>
+      <c r="H99" s="54" t="s">
         <v>256</v>
       </c>
-      <c r="I99" s="56" t="s">
+      <c r="I99" s="54" t="s">
         <v>257</v>
       </c>
-      <c r="J99" s="54">
+      <c r="J99" s="52">
         <v>8</v>
       </c>
-      <c r="K99" s="56" t="s">
+      <c r="K99" s="54" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="100" spans="2:11">
-      <c r="B100" s="54"/>
-      <c r="C100" s="54"/>
-      <c r="D100" s="54"/>
-      <c r="E100" s="54"/>
-      <c r="F100" s="54"/>
-      <c r="G100" s="54"/>
-      <c r="H100" s="56" t="s">
+      <c r="B100" s="52"/>
+      <c r="C100" s="52"/>
+      <c r="D100" s="52"/>
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
+      <c r="H100" s="54" t="s">
         <v>258</v>
       </c>
-      <c r="I100" s="56" t="s">
+      <c r="I100" s="54" t="s">
         <v>259</v>
       </c>
-      <c r="J100" s="54">
+      <c r="J100" s="52">
         <v>9</v>
       </c>
-      <c r="K100" s="56" t="s">
+      <c r="K100" s="54" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="101" spans="2:11">
-      <c r="B101" s="54"/>
-      <c r="C101" s="54"/>
-      <c r="D101" s="54"/>
-      <c r="E101" s="54"/>
-      <c r="F101" s="54"/>
-      <c r="G101" s="54"/>
-      <c r="H101" s="56" t="s">
+      <c r="B101" s="52"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="52"/>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
+      <c r="H101" s="54" t="s">
         <v>260</v>
       </c>
-      <c r="I101" s="56" t="s">
+      <c r="I101" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="J101" s="54">
+      <c r="J101" s="52">
         <v>10</v>
       </c>
-      <c r="K101" s="56" t="s">
+      <c r="K101" s="54" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="102" spans="2:11">
-      <c r="B102" s="54"/>
-      <c r="C102" s="54"/>
-      <c r="D102" s="54"/>
-      <c r="E102" s="54"/>
-      <c r="F102" s="54"/>
-      <c r="G102" s="54"/>
-      <c r="H102" s="56" t="s">
+      <c r="B102" s="52"/>
+      <c r="C102" s="52"/>
+      <c r="D102" s="52"/>
+      <c r="E102" s="52"/>
+      <c r="F102" s="52"/>
+      <c r="G102" s="52"/>
+      <c r="H102" s="54" t="s">
         <v>262</v>
       </c>
-      <c r="I102" s="56" t="s">
+      <c r="I102" s="54" t="s">
         <v>263</v>
       </c>
-      <c r="J102" s="54">
+      <c r="J102" s="52">
         <v>11</v>
       </c>
-      <c r="K102" s="56" t="s">
+      <c r="K102" s="54" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="103" spans="2:11">
-      <c r="B103" s="54"/>
-      <c r="C103" s="54"/>
-      <c r="D103" s="54"/>
-      <c r="E103" s="54"/>
-      <c r="F103" s="54"/>
-      <c r="G103" s="54"/>
-      <c r="H103" s="56" t="s">
+      <c r="B103" s="52"/>
+      <c r="C103" s="52"/>
+      <c r="D103" s="52"/>
+      <c r="E103" s="52"/>
+      <c r="F103" s="52"/>
+      <c r="G103" s="52"/>
+      <c r="H103" s="54" t="s">
         <v>264</v>
       </c>
-      <c r="I103" s="56" t="s">
+      <c r="I103" s="54" t="s">
         <v>265</v>
       </c>
-      <c r="J103" s="54">
+      <c r="J103" s="52">
         <v>12</v>
       </c>
-      <c r="K103" s="56" t="s">
+      <c r="K103" s="54" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="104" spans="2:11">
-      <c r="B104" s="54"/>
-      <c r="C104" s="54"/>
-      <c r="D104" s="54"/>
-      <c r="E104" s="54"/>
-      <c r="F104" s="54"/>
-      <c r="G104" s="54"/>
-      <c r="H104" s="56" t="s">
+      <c r="B104" s="52"/>
+      <c r="C104" s="52"/>
+      <c r="D104" s="52"/>
+      <c r="E104" s="52"/>
+      <c r="F104" s="52"/>
+      <c r="G104" s="52"/>
+      <c r="H104" s="54" t="s">
         <v>266</v>
       </c>
-      <c r="I104" s="56" t="s">
+      <c r="I104" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="J104" s="54">
+      <c r="J104" s="52">
         <v>13</v>
       </c>
-      <c r="K104" s="56" t="s">
+      <c r="K104" s="54" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="105" spans="2:11">
-      <c r="B105" s="54"/>
-      <c r="C105" s="54"/>
-      <c r="D105" s="54"/>
-      <c r="E105" s="54"/>
-      <c r="F105" s="54"/>
-      <c r="G105" s="54"/>
-      <c r="H105" s="56" t="s">
+      <c r="B105" s="52"/>
+      <c r="C105" s="52"/>
+      <c r="D105" s="52"/>
+      <c r="E105" s="52"/>
+      <c r="F105" s="52"/>
+      <c r="G105" s="52"/>
+      <c r="H105" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="I105" s="56" t="s">
+      <c r="I105" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="J105" s="54">
+      <c r="J105" s="52">
         <v>14</v>
       </c>
-      <c r="K105" s="56" t="s">
+      <c r="K105" s="54" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="106" spans="2:11">
-      <c r="B106" s="54"/>
-      <c r="C106" s="54"/>
-      <c r="D106" s="54"/>
-      <c r="E106" s="54"/>
-      <c r="F106" s="54"/>
-      <c r="G106" s="54"/>
-      <c r="H106" s="56" t="s">
+      <c r="B106" s="52"/>
+      <c r="C106" s="52"/>
+      <c r="D106" s="52"/>
+      <c r="E106" s="52"/>
+      <c r="F106" s="52"/>
+      <c r="G106" s="52"/>
+      <c r="H106" s="54" t="s">
         <v>270</v>
       </c>
-      <c r="I106" s="56" t="s">
+      <c r="I106" s="54" t="s">
         <v>271</v>
       </c>
-      <c r="J106" s="54">
+      <c r="J106" s="52">
         <v>15</v>
       </c>
-      <c r="K106" s="56" t="s">
+      <c r="K106" s="54" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="107" spans="2:11">
-      <c r="B107" s="54"/>
-      <c r="C107" s="54"/>
-      <c r="D107" s="54"/>
-      <c r="E107" s="54"/>
-      <c r="F107" s="54"/>
-      <c r="G107" s="54"/>
-      <c r="H107" s="56" t="s">
+      <c r="B107" s="52"/>
+      <c r="C107" s="52"/>
+      <c r="D107" s="52"/>
+      <c r="E107" s="52"/>
+      <c r="F107" s="52"/>
+      <c r="G107" s="52"/>
+      <c r="H107" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="I107" s="56" t="s">
+      <c r="I107" s="54" t="s">
         <v>273</v>
       </c>
-      <c r="J107" s="54">
+      <c r="J107" s="52">
         <v>16</v>
       </c>
-      <c r="K107" s="56" t="s">
+      <c r="K107" s="54" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="108" spans="2:11">
-      <c r="B108" s="54"/>
-      <c r="C108" s="54"/>
-      <c r="D108" s="54"/>
-      <c r="E108" s="54"/>
-      <c r="F108" s="54"/>
-      <c r="G108" s="54"/>
-      <c r="H108" s="56" t="s">
+      <c r="B108" s="52"/>
+      <c r="C108" s="52"/>
+      <c r="D108" s="52"/>
+      <c r="E108" s="52"/>
+      <c r="F108" s="52"/>
+      <c r="G108" s="52"/>
+      <c r="H108" s="54" t="s">
         <v>274</v>
       </c>
-      <c r="I108" s="56" t="s">
+      <c r="I108" s="54" t="s">
         <v>275</v>
       </c>
-      <c r="J108" s="54">
+      <c r="J108" s="52">
         <v>17</v>
       </c>
-      <c r="K108" s="56" t="s">
+      <c r="K108" s="54" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="109" spans="2:11">
-      <c r="B109" s="54"/>
-      <c r="C109" s="54"/>
-      <c r="D109" s="54"/>
-      <c r="E109" s="54"/>
-      <c r="F109" s="54"/>
-      <c r="G109" s="54"/>
-      <c r="H109" s="56" t="s">
+      <c r="B109" s="52"/>
+      <c r="C109" s="52"/>
+      <c r="D109" s="52"/>
+      <c r="E109" s="52"/>
+      <c r="F109" s="52"/>
+      <c r="G109" s="52"/>
+      <c r="H109" s="54" t="s">
         <v>276</v>
       </c>
-      <c r="I109" s="56" t="s">
+      <c r="I109" s="54" t="s">
         <v>277</v>
       </c>
-      <c r="J109" s="54">
+      <c r="J109" s="52">
         <v>18</v>
       </c>
-      <c r="K109" s="56" t="s">
+      <c r="K109" s="54" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="110" spans="2:11">
-      <c r="B110" s="53" t="s">
+      <c r="B110" s="56" t="s">
         <v>278</v>
       </c>
-      <c r="C110" s="58" t="b">
+      <c r="C110" s="57" t="b">
         <v>0</v>
       </c>
-      <c r="D110" s="58" t="b">
+      <c r="D110" s="57" t="b">
         <v>1</v>
       </c>
-      <c r="E110" s="53"/>
-      <c r="F110" s="53"/>
-      <c r="G110" s="53"/>
-      <c r="H110" s="57" t="s">
+      <c r="E110" s="56"/>
+      <c r="F110" s="56"/>
+      <c r="G110" s="56"/>
+      <c r="H110" s="58" t="s">
         <v>279</v>
       </c>
-      <c r="I110" s="53" t="s">
+      <c r="I110" s="56" t="s">
         <v>284</v>
       </c>
-      <c r="J110" s="53">
+      <c r="J110" s="56">
         <v>1</v>
       </c>
-      <c r="K110" s="53" t="s">
+      <c r="K110" s="56" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="111" spans="2:11">
-      <c r="B111" s="53"/>
-      <c r="C111" s="53"/>
-      <c r="D111" s="53"/>
-      <c r="E111" s="53"/>
-      <c r="F111" s="53"/>
-      <c r="G111" s="53"/>
-      <c r="H111" s="57" t="s">
+      <c r="B111" s="56"/>
+      <c r="C111" s="56"/>
+      <c r="D111" s="56"/>
+      <c r="E111" s="56"/>
+      <c r="F111" s="56"/>
+      <c r="G111" s="56"/>
+      <c r="H111" s="58" t="s">
         <v>280</v>
       </c>
-      <c r="I111" s="53" t="s">
+      <c r="I111" s="56" t="s">
         <v>285</v>
       </c>
-      <c r="J111" s="53">
+      <c r="J111" s="56">
         <v>2</v>
       </c>
-      <c r="K111" s="53" t="s">
+      <c r="K111" s="56" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="112" spans="2:11">
-      <c r="B112" s="53"/>
-      <c r="C112" s="53"/>
-      <c r="D112" s="53"/>
-      <c r="E112" s="53"/>
-      <c r="F112" s="53"/>
-      <c r="G112" s="53"/>
-      <c r="H112" s="57" t="s">
+      <c r="B112" s="56"/>
+      <c r="C112" s="56"/>
+      <c r="D112" s="56"/>
+      <c r="E112" s="56"/>
+      <c r="F112" s="56"/>
+      <c r="G112" s="56"/>
+      <c r="H112" s="58" t="s">
         <v>281</v>
       </c>
-      <c r="I112" s="53" t="s">
+      <c r="I112" s="56" t="s">
         <v>286</v>
       </c>
-      <c r="J112" s="53">
+      <c r="J112" s="56">
         <v>3</v>
       </c>
-      <c r="K112" s="53" t="s">
+      <c r="K112" s="56" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="113" spans="2:11">
-      <c r="B113" s="53"/>
-      <c r="C113" s="53"/>
-      <c r="D113" s="53"/>
-      <c r="E113" s="53"/>
-      <c r="F113" s="53"/>
-      <c r="G113" s="53"/>
-      <c r="H113" s="57" t="s">
+      <c r="B113" s="56"/>
+      <c r="C113" s="56"/>
+      <c r="D113" s="56"/>
+      <c r="E113" s="56"/>
+      <c r="F113" s="56"/>
+      <c r="G113" s="56"/>
+      <c r="H113" s="58" t="s">
         <v>282</v>
       </c>
-      <c r="I113" s="53" t="s">
+      <c r="I113" s="56" t="s">
         <v>287</v>
       </c>
-      <c r="J113" s="53">
+      <c r="J113" s="56">
         <v>4</v>
       </c>
-      <c r="K113" s="53" t="s">
+      <c r="K113" s="56" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="114" spans="2:11">
-      <c r="B114" s="53"/>
-      <c r="C114" s="53"/>
-      <c r="D114" s="53"/>
-      <c r="E114" s="53"/>
-      <c r="F114" s="53"/>
-      <c r="G114" s="53"/>
-      <c r="H114" s="57" t="s">
+      <c r="B114" s="56"/>
+      <c r="C114" s="56"/>
+      <c r="D114" s="56"/>
+      <c r="E114" s="56"/>
+      <c r="F114" s="56"/>
+      <c r="G114" s="56"/>
+      <c r="H114" s="58" t="s">
         <v>283</v>
       </c>
-      <c r="I114" s="53" t="s">
+      <c r="I114" s="56" t="s">
         <v>288</v>
       </c>
-      <c r="J114" s="53">
+      <c r="J114" s="56">
         <v>5</v>
       </c>
-      <c r="K114" s="53" t="s">
+      <c r="K114" s="56" t="s">
         <v>288</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4600DA6-9676-4C30-922E-123B3D4C9EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5644F5D2-6466-49EB-9D73-787A111002FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="2940" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6040" yWindow="1690" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="256">
   <si>
     <t>##var</t>
   </si>
@@ -759,134 +759,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>无</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Affection</t>
-  </si>
-  <si>
-    <t>好感道具</t>
-  </si>
-  <si>
-    <t>Inspiration</t>
-  </si>
-  <si>
-    <t>灵感道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stress</t>
-  </si>
-  <si>
-    <t>压力道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Stamina</t>
-  </si>
-  <si>
-    <t>体力道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Story</t>
-  </si>
-  <si>
-    <t>剧情道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ingredient</t>
-  </si>
-  <si>
-    <t>食材道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Recipe</t>
-  </si>
-  <si>
-    <t>配方道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>食物道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>FigureModel</t>
-  </si>
-  <si>
-    <t>手办模型</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Painting</t>
-  </si>
-  <si>
-    <t>绘画道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>FactoryProductionMaterials</t>
-  </si>
-  <si>
-    <t>工厂生产材料</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cloth</t>
-  </si>
-  <si>
-    <t>布料</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Merchandise</t>
-  </si>
-  <si>
-    <t>周边货物</t>
-  </si>
-  <si>
-    <t>ShopItem</t>
-  </si>
-  <si>
-    <t>商店道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>FishBait</t>
-  </si>
-  <si>
-    <t>鱼饵店</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>FishRod</t>
-  </si>
-  <si>
-    <t>鱼竿</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>AdultToy</t>
-  </si>
-  <si>
-    <t>情趣道具</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ClawMachineDoll</t>
-  </si>
-  <si>
-    <t>娃娃机</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>ItemQuality</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -928,6 +800,20 @@
   </si>
   <si>
     <t>史诗</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Consumables</t>
+  </si>
+  <si>
+    <t>材料</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗品</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1709,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -3682,16 +3568,14 @@
       <c r="F91" s="52"/>
       <c r="G91" s="52"/>
       <c r="H91" s="54" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="I91" s="54" t="s">
-        <v>241</v>
-      </c>
-      <c r="J91" s="52">
+        <v>254</v>
+      </c>
+      <c r="J91" s="52"/>
+      <c r="K91" s="54">
         <v>0</v>
-      </c>
-      <c r="K91" s="54" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="92" spans="2:11">
@@ -3702,462 +3586,120 @@
       <c r="F92" s="52"/>
       <c r="G92" s="52"/>
       <c r="H92" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="I92" s="54" t="s">
+        <v>255</v>
+      </c>
+      <c r="J92" s="52"/>
+      <c r="K92" s="54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" s="56" t="s">
+        <v>241</v>
+      </c>
+      <c r="C93" s="57" t="b">
+        <v>0</v>
+      </c>
+      <c r="D93" s="57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="56"/>
+      <c r="F93" s="56"/>
+      <c r="G93" s="56"/>
+      <c r="H93" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="I92" s="54" t="s">
+      <c r="I93" s="56" t="s">
+        <v>247</v>
+      </c>
+      <c r="J93" s="56">
+        <v>1</v>
+      </c>
+      <c r="K93" s="56" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="56"/>
+      <c r="C94" s="56"/>
+      <c r="D94" s="56"/>
+      <c r="E94" s="56"/>
+      <c r="F94" s="56"/>
+      <c r="G94" s="56"/>
+      <c r="H94" s="58" t="s">
         <v>243</v>
       </c>
-      <c r="J92" s="52">
-        <v>1</v>
-      </c>
-      <c r="K92" s="54" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
-      <c r="B93" s="52"/>
-      <c r="C93" s="52"/>
-      <c r="D93" s="52"/>
-      <c r="E93" s="52"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="54" t="s">
+      <c r="I94" s="56" t="s">
+        <v>248</v>
+      </c>
+      <c r="J94" s="56">
+        <v>2</v>
+      </c>
+      <c r="K94" s="56" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="B95" s="56"/>
+      <c r="C95" s="56"/>
+      <c r="D95" s="56"/>
+      <c r="E95" s="56"/>
+      <c r="F95" s="56"/>
+      <c r="G95" s="56"/>
+      <c r="H95" s="58" t="s">
         <v>244</v>
       </c>
-      <c r="I93" s="54" t="s">
+      <c r="I95" s="56" t="s">
+        <v>249</v>
+      </c>
+      <c r="J95" s="56">
+        <v>3</v>
+      </c>
+      <c r="K95" s="56" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="B96" s="56"/>
+      <c r="C96" s="56"/>
+      <c r="D96" s="56"/>
+      <c r="E96" s="56"/>
+      <c r="F96" s="56"/>
+      <c r="G96" s="56"/>
+      <c r="H96" s="58" t="s">
         <v>245</v>
       </c>
-      <c r="J93" s="52">
-        <v>2</v>
-      </c>
-      <c r="K93" s="54" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11">
-      <c r="B94" s="52"/>
-      <c r="C94" s="52"/>
-      <c r="D94" s="52"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="52"/>
-      <c r="G94" s="52"/>
-      <c r="H94" s="54" t="s">
+      <c r="I96" s="56" t="s">
+        <v>250</v>
+      </c>
+      <c r="J96" s="56">
+        <v>4</v>
+      </c>
+      <c r="K96" s="56" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11">
+      <c r="B97" s="56"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="56"/>
+      <c r="E97" s="56"/>
+      <c r="F97" s="56"/>
+      <c r="G97" s="56"/>
+      <c r="H97" s="58" t="s">
         <v>246</v>
       </c>
-      <c r="I94" s="54" t="s">
-        <v>247</v>
-      </c>
-      <c r="J94" s="52">
-        <v>3</v>
-      </c>
-      <c r="K94" s="54" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11">
-      <c r="B95" s="52"/>
-      <c r="C95" s="52"/>
-      <c r="D95" s="52"/>
-      <c r="E95" s="52"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="52"/>
-      <c r="H95" s="54" t="s">
-        <v>248</v>
-      </c>
-      <c r="I95" s="54" t="s">
-        <v>249</v>
-      </c>
-      <c r="J95" s="52">
-        <v>4</v>
-      </c>
-      <c r="K95" s="54" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11">
-      <c r="B96" s="52"/>
-      <c r="C96" s="52"/>
-      <c r="D96" s="52"/>
-      <c r="E96" s="52"/>
-      <c r="F96" s="52"/>
-      <c r="G96" s="52"/>
-      <c r="H96" s="54" t="s">
-        <v>250</v>
-      </c>
-      <c r="I96" s="54" t="s">
+      <c r="I97" s="56" t="s">
         <v>251</v>
       </c>
-      <c r="J96" s="52">
+      <c r="J97" s="56">
         <v>5</v>
       </c>
-      <c r="K96" s="54" t="s">
+      <c r="K97" s="56" t="s">
         <v>251</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11">
-      <c r="B97" s="52"/>
-      <c r="C97" s="52"/>
-      <c r="D97" s="52"/>
-      <c r="E97" s="52"/>
-      <c r="F97" s="52"/>
-      <c r="G97" s="52"/>
-      <c r="H97" s="54" t="s">
-        <v>252</v>
-      </c>
-      <c r="I97" s="54" t="s">
-        <v>253</v>
-      </c>
-      <c r="J97" s="52">
-        <v>6</v>
-      </c>
-      <c r="K97" s="54" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11">
-      <c r="B98" s="52"/>
-      <c r="C98" s="52"/>
-      <c r="D98" s="52"/>
-      <c r="E98" s="52"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="52"/>
-      <c r="H98" s="54" t="s">
-        <v>254</v>
-      </c>
-      <c r="I98" s="54" t="s">
-        <v>255</v>
-      </c>
-      <c r="J98" s="52">
-        <v>7</v>
-      </c>
-      <c r="K98" s="54" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11">
-      <c r="B99" s="52"/>
-      <c r="C99" s="52"/>
-      <c r="D99" s="52"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="52"/>
-      <c r="G99" s="52"/>
-      <c r="H99" s="54" t="s">
-        <v>256</v>
-      </c>
-      <c r="I99" s="54" t="s">
-        <v>257</v>
-      </c>
-      <c r="J99" s="52">
-        <v>8</v>
-      </c>
-      <c r="K99" s="54" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11">
-      <c r="B100" s="52"/>
-      <c r="C100" s="52"/>
-      <c r="D100" s="52"/>
-      <c r="E100" s="52"/>
-      <c r="F100" s="52"/>
-      <c r="G100" s="52"/>
-      <c r="H100" s="54" t="s">
-        <v>258</v>
-      </c>
-      <c r="I100" s="54" t="s">
-        <v>259</v>
-      </c>
-      <c r="J100" s="52">
-        <v>9</v>
-      </c>
-      <c r="K100" s="54" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11">
-      <c r="B101" s="52"/>
-      <c r="C101" s="52"/>
-      <c r="D101" s="52"/>
-      <c r="E101" s="52"/>
-      <c r="F101" s="52"/>
-      <c r="G101" s="52"/>
-      <c r="H101" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="I101" s="54" t="s">
-        <v>261</v>
-      </c>
-      <c r="J101" s="52">
-        <v>10</v>
-      </c>
-      <c r="K101" s="54" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11">
-      <c r="B102" s="52"/>
-      <c r="C102" s="52"/>
-      <c r="D102" s="52"/>
-      <c r="E102" s="52"/>
-      <c r="F102" s="52"/>
-      <c r="G102" s="52"/>
-      <c r="H102" s="54" t="s">
-        <v>262</v>
-      </c>
-      <c r="I102" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="J102" s="52">
-        <v>11</v>
-      </c>
-      <c r="K102" s="54" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11">
-      <c r="B103" s="52"/>
-      <c r="C103" s="52"/>
-      <c r="D103" s="52"/>
-      <c r="E103" s="52"/>
-      <c r="F103" s="52"/>
-      <c r="G103" s="52"/>
-      <c r="H103" s="54" t="s">
-        <v>264</v>
-      </c>
-      <c r="I103" s="54" t="s">
-        <v>265</v>
-      </c>
-      <c r="J103" s="52">
-        <v>12</v>
-      </c>
-      <c r="K103" s="54" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="104" spans="2:11">
-      <c r="B104" s="52"/>
-      <c r="C104" s="52"/>
-      <c r="D104" s="52"/>
-      <c r="E104" s="52"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="52"/>
-      <c r="H104" s="54" t="s">
-        <v>266</v>
-      </c>
-      <c r="I104" s="54" t="s">
-        <v>267</v>
-      </c>
-      <c r="J104" s="52">
-        <v>13</v>
-      </c>
-      <c r="K104" s="54" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="105" spans="2:11">
-      <c r="B105" s="52"/>
-      <c r="C105" s="52"/>
-      <c r="D105" s="52"/>
-      <c r="E105" s="52"/>
-      <c r="F105" s="52"/>
-      <c r="G105" s="52"/>
-      <c r="H105" s="54" t="s">
-        <v>268</v>
-      </c>
-      <c r="I105" s="54" t="s">
-        <v>269</v>
-      </c>
-      <c r="J105" s="52">
-        <v>14</v>
-      </c>
-      <c r="K105" s="54" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11">
-      <c r="B106" s="52"/>
-      <c r="C106" s="52"/>
-      <c r="D106" s="52"/>
-      <c r="E106" s="52"/>
-      <c r="F106" s="52"/>
-      <c r="G106" s="52"/>
-      <c r="H106" s="54" t="s">
-        <v>270</v>
-      </c>
-      <c r="I106" s="54" t="s">
-        <v>271</v>
-      </c>
-      <c r="J106" s="52">
-        <v>15</v>
-      </c>
-      <c r="K106" s="54" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11">
-      <c r="B107" s="52"/>
-      <c r="C107" s="52"/>
-      <c r="D107" s="52"/>
-      <c r="E107" s="52"/>
-      <c r="F107" s="52"/>
-      <c r="G107" s="52"/>
-      <c r="H107" s="54" t="s">
-        <v>272</v>
-      </c>
-      <c r="I107" s="54" t="s">
-        <v>273</v>
-      </c>
-      <c r="J107" s="52">
-        <v>16</v>
-      </c>
-      <c r="K107" s="54" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11">
-      <c r="B108" s="52"/>
-      <c r="C108" s="52"/>
-      <c r="D108" s="52"/>
-      <c r="E108" s="52"/>
-      <c r="F108" s="52"/>
-      <c r="G108" s="52"/>
-      <c r="H108" s="54" t="s">
-        <v>274</v>
-      </c>
-      <c r="I108" s="54" t="s">
-        <v>275</v>
-      </c>
-      <c r="J108" s="52">
-        <v>17</v>
-      </c>
-      <c r="K108" s="54" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="109" spans="2:11">
-      <c r="B109" s="52"/>
-      <c r="C109" s="52"/>
-      <c r="D109" s="52"/>
-      <c r="E109" s="52"/>
-      <c r="F109" s="52"/>
-      <c r="G109" s="52"/>
-      <c r="H109" s="54" t="s">
-        <v>276</v>
-      </c>
-      <c r="I109" s="54" t="s">
-        <v>277</v>
-      </c>
-      <c r="J109" s="52">
-        <v>18</v>
-      </c>
-      <c r="K109" s="54" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="110" spans="2:11">
-      <c r="B110" s="56" t="s">
-        <v>278</v>
-      </c>
-      <c r="C110" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="D110" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="E110" s="56"/>
-      <c r="F110" s="56"/>
-      <c r="G110" s="56"/>
-      <c r="H110" s="58" t="s">
-        <v>279</v>
-      </c>
-      <c r="I110" s="56" t="s">
-        <v>284</v>
-      </c>
-      <c r="J110" s="56">
-        <v>1</v>
-      </c>
-      <c r="K110" s="56" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11">
-      <c r="B111" s="56"/>
-      <c r="C111" s="56"/>
-      <c r="D111" s="56"/>
-      <c r="E111" s="56"/>
-      <c r="F111" s="56"/>
-      <c r="G111" s="56"/>
-      <c r="H111" s="58" t="s">
-        <v>280</v>
-      </c>
-      <c r="I111" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="J111" s="56">
-        <v>2</v>
-      </c>
-      <c r="K111" s="56" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="112" spans="2:11">
-      <c r="B112" s="56"/>
-      <c r="C112" s="56"/>
-      <c r="D112" s="56"/>
-      <c r="E112" s="56"/>
-      <c r="F112" s="56"/>
-      <c r="G112" s="56"/>
-      <c r="H112" s="58" t="s">
-        <v>281</v>
-      </c>
-      <c r="I112" s="56" t="s">
-        <v>286</v>
-      </c>
-      <c r="J112" s="56">
-        <v>3</v>
-      </c>
-      <c r="K112" s="56" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="113" spans="2:11">
-      <c r="B113" s="56"/>
-      <c r="C113" s="56"/>
-      <c r="D113" s="56"/>
-      <c r="E113" s="56"/>
-      <c r="F113" s="56"/>
-      <c r="G113" s="56"/>
-      <c r="H113" s="58" t="s">
-        <v>282</v>
-      </c>
-      <c r="I113" s="56" t="s">
-        <v>287</v>
-      </c>
-      <c r="J113" s="56">
-        <v>4</v>
-      </c>
-      <c r="K113" s="56" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="114" spans="2:11">
-      <c r="B114" s="56"/>
-      <c r="C114" s="56"/>
-      <c r="D114" s="56"/>
-      <c r="E114" s="56"/>
-      <c r="F114" s="56"/>
-      <c r="G114" s="56"/>
-      <c r="H114" s="58" t="s">
-        <v>283</v>
-      </c>
-      <c r="I114" s="56" t="s">
-        <v>288</v>
-      </c>
-      <c r="J114" s="56">
-        <v>5</v>
-      </c>
-      <c r="K114" s="56" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,39 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5644F5D2-6466-49EB-9D73-787A111002FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6040" yWindow="1690" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30220" windowHeight="18660" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="smNativeData">
+      <pm:revision xmlns:pm="smNativeData" day="1783500644" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783500644" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783500644" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783500644"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="240">
   <si>
     <t>##var</t>
   </si>
@@ -753,112 +743,86 @@
   </si>
   <si>
     <t>每次</t>
-  </si>
-  <si>
-    <t>ItemType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemQuality</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>S</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SSR</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>高级</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>稀有</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>神器</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>史诗</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>Consumables</t>
-  </si>
-  <si>
-    <t>材料</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗品</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783500644" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783500644" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783500644" ulstyle="none" kern="1">
+            <pm:latin face="微软雅黑" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783500644" ulstyle="none" kern="1">
+            <pm:latin face="Arial Unicode MS" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="47">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -867,236 +831,1032 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79985961485641044"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFE1EFD8"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00E1EFD8" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="0000B0F0" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="0070AD47" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFACB9CA"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39988402966399123"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4AF82"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00F4AF82" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4AF82"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00F4AF82" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5DFB3"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00C5DFB3" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5DFB3"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00C5DFB3" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6E0B4"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00C6E0B4" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFB4C6E7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00B4C6E7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39988402966399123"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFA8D08C"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00A8D08C" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFA8D08C"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00A8D08C" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF70AD47"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="0070AD47" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.499984740745262"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CAAB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00F8CAAB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CAAB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="00F8CAAB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EA9DB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EA9DB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7E7E7E"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="007E7E7E" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7E7E7E"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500644" type="1" fgLvl="100" fgClr="007E7E7E" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="46">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
-      <right/>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
-      <left/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
-      <top/>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color rgb="FFDEE0E3"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -1111,7 +1871,250 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -1126,219 +2129,396 @@
       <bottom style="thin">
         <color rgb="FF1F2329"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500644">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="22" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="30" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="32" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="33" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="34" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="40" borderId="39" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="23" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="39" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="40" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="42" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="41" borderId="40" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="42" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="42" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="44" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="44" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFC6E0B4"/>
-      <color rgb="FF70AD47"/>
-      <color rgb="FFACB9CA"/>
-      <color rgb="FF4472C4"/>
-    </mruColors>
-  </colors>
+  <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="smNativeData">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783500644" count="1">
+        <pm:charStyle name="普通" fontId="0" Id="1"/>
+      </pm:charStyles>
+      <pm:colors xmlns:pm="smNativeData" id="1783500644" count="19">
+        <pm:color name="颜色 24" rgb="E1EFD8"/>
+        <pm:color name="20% 灰色" rgb="000000"/>
+        <pm:color name="颜色 26" rgb="FFE697"/>
+        <pm:color name="颜色 27" rgb="BDD7EE"/>
+        <pm:color name="颜色 28" rgb="00B0F0"/>
+        <pm:color name="颜色 29" rgb="70AD47"/>
+        <pm:color name="颜色 30" rgb="ACB9CA"/>
+        <pm:color name="颜色 31" rgb="4472C4"/>
+        <pm:color name="颜色 32" rgb="F4AF82"/>
+        <pm:color name="颜色 33" rgb="C5DFB3"/>
+        <pm:color name="颜色 34" rgb="C6E0B4"/>
+        <pm:color name="颜色 35" rgb="B4C6E7"/>
+        <pm:color name="颜色 36" rgb="A8D08C"/>
+        <pm:color name="颜色 37" rgb="A5A5A5"/>
+        <pm:color name="颜色 38" rgb="F8CAAB"/>
+        <pm:color name="颜色 39" rgb="8EA9DB"/>
+        <pm:color name="颜色 40" rgb="7E7E7E"/>
+        <pm:color name="颜色 41" rgb="DEE0E3"/>
+        <pm:color name="颜色 42" rgb="1F2329"/>
+      </pm:colors>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1348,106 +2528,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="EEECE1"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="1F497D"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="等线"/>
+        <a:ea typeface="SimSun"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1459,157 +2579,215 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr>
+        <a:prstTxWarp prst="textNoShape">
+          <a:avLst/>
+        </a:prstTxWarp>
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr>
+          <a:defRPr/>
+        </a:defPPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:L97"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.55"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9.000000" style="1"/>
+    <col min="2" max="2" width="27.077586" customWidth="1" style="1"/>
+    <col min="3" max="3" width="20.827586" customWidth="1" style="1"/>
+    <col min="4" max="4" width="19.000000" customWidth="1" style="1"/>
+    <col min="5" max="5" width="14.077586" customWidth="1" style="1"/>
+    <col min="6" max="6" width="9.327586" customWidth="1" style="1"/>
+    <col min="7" max="7" width="5.000000" customWidth="1" style="1"/>
+    <col min="8" max="8" width="38.663793" customWidth="1" style="1"/>
+    <col min="9" max="9" width="22.327586" customWidth="1" style="1"/>
+    <col min="10" max="10" width="12.077586" customWidth="1" style="1"/>
+    <col min="11" max="11" width="55.250000" customWidth="1" style="1"/>
+    <col min="12" max="16384" width="9.000000" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1634,13 +2812,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1698,7 +2876,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="2:11">
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
@@ -1717,14 +2895,14 @@
       <c r="I4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="2:11">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -1737,14 +2915,14 @@
       <c r="I5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="8" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="2:11">
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -1757,14 +2935,14 @@
       <c r="I6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="8" t="n">
         <v>3</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="2:11">
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -1777,14 +2955,14 @@
       <c r="I7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="8" t="n">
         <v>4</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="2:11">
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -1797,14 +2975,14 @@
       <c r="I8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="8" t="n">
         <v>5</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="2:11">
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -1817,14 +2995,14 @@
       <c r="I9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="2:11">
       <c r="B10" s="13" t="s">
         <v>32</v>
       </c>
@@ -1843,14 +3021,14 @@
       <c r="I10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="2:11">
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -1863,14 +3041,14 @@
       <c r="I11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="2:11">
       <c r="B12" s="14" t="s">
         <v>39</v>
       </c>
@@ -1885,14 +3063,14 @@
       <c r="I12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="2:11">
       <c r="B13" s="17"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -1905,14 +3083,14 @@
       <c r="I13" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="18" t="n">
         <v>2</v>
       </c>
       <c r="K13" s="19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="2:11">
       <c r="B14" s="20"/>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -1925,14 +3103,14 @@
       <c r="I14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="21" t="n">
         <v>3</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="2:11">
       <c r="B15" s="23" t="s">
         <v>48</v>
       </c>
@@ -1951,14 +3129,14 @@
       <c r="I15" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="23" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="2:11">
       <c r="B16" s="23"/>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
@@ -1971,7 +3149,7 @@
       <c r="I16" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="23" t="n">
         <v>2</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -1991,7 +3169,7 @@
       <c r="I17" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -2017,7 +3195,7 @@
       <c r="I18" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="J18" s="24">
+      <c r="J18" s="24" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="24" t="s">
@@ -2037,7 +3215,7 @@
       <c r="I19" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="24">
+      <c r="J19" s="24" t="n">
         <v>2</v>
       </c>
       <c r="K19" s="24" t="s">
@@ -2045,1669 +3223,1629 @@
       </c>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25" t="s">
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="I20" s="25" t="s">
+      <c r="I20" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="K20" s="25" t="s">
+      <c r="K20" s="24" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="24"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25" t="s">
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="I21" s="25" t="s">
+      <c r="I21" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="25" t="s">
+      <c r="K21" s="24" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:11">
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25" t="s">
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="I22" s="25" t="s">
+      <c r="I22" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="24" t="n">
         <v>5</v>
       </c>
-      <c r="K22" s="25" t="s">
+      <c r="K22" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="23" spans="2:11">
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25" t="s">
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="I23" s="25" t="s">
+      <c r="I23" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="K23" s="25" t="s">
+      <c r="K23" s="24" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25" t="s">
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I24" s="25" t="s">
+      <c r="I24" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="K24" s="25" t="s">
+      <c r="K24" s="24" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="25" spans="2:11">
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25" t="s">
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="I25" s="25" t="s">
+      <c r="I25" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="J25" s="25">
+      <c r="J25" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="K25" s="25" t="s">
+      <c r="K25" s="24" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="27" t="b">
+      <c r="C26" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D26" s="27" t="b">
+      <c r="D26" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26" t="s">
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="I26" s="26" t="s">
+      <c r="I26" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="J26" s="26">
+      <c r="J26" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="25" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="2:11">
-      <c r="B27" s="26"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-      <c r="H27" s="26" t="s">
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="I27" s="26" t="s">
+      <c r="I27" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="J27" s="26">
+      <c r="J27" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="K27" s="26" t="s">
+      <c r="K27" s="25" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="28" spans="2:11">
-      <c r="B28" s="28"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-      <c r="H28" s="26" t="s">
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="I28" s="26" t="s">
+      <c r="I28" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="J28" s="26">
+      <c r="J28" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="K28" s="26" t="s">
+      <c r="K28" s="25" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="29" spans="2:11">
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26" t="s">
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="I29" s="26" t="s">
+      <c r="I29" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="J29" s="26">
+      <c r="J29" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K29" s="26" t="s">
+      <c r="K29" s="25" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="30" spans="2:11">
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="30" t="b">
+      <c r="C30" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="D30" s="30" t="b">
+      <c r="D30" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31" t="s">
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="I30" s="31" t="s">
+      <c r="I30" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="31" t="s">
+      <c r="K30" s="29" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="32"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31" t="s">
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="I31" s="31" t="s">
+      <c r="I31" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="J31" s="31">
+      <c r="J31" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="K31" s="31" t="s">
+      <c r="K31" s="29" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="32" spans="2:11">
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31" t="s">
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="I32" s="31" t="s">
+      <c r="I32" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="J32" s="31">
+      <c r="J32" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="31" t="s">
+      <c r="K32" s="29" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="33" spans="2:11">
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31" t="s">
+      <c r="B33" s="29"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="I33" s="31" t="s">
+      <c r="I33" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="J33" s="31">
+      <c r="J33" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="K33" s="31" t="s">
+      <c r="K33" s="29" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="34" spans="2:11">
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="34" t="b">
+      <c r="C34" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="D34" s="34" t="b">
+      <c r="D34" s="31" t="b">
         <v>1</v>
       </c>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33" t="s">
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="I34" s="33" t="s">
+      <c r="I34" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="J34" s="33">
+      <c r="J34" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="K34" s="33" t="s">
+      <c r="K34" s="30" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="35" spans="2:11">
-      <c r="B35" s="33"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="33"/>
-      <c r="H35" s="33" t="s">
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="I35" s="33" t="s">
+      <c r="I35" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="J35" s="33">
+      <c r="J35" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="K35" s="33" t="s">
+      <c r="K35" s="30" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="2:11">
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33" t="s">
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="I36" s="33" t="s">
+      <c r="I36" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="J36" s="33">
+      <c r="J36" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="K36" s="33" t="s">
+      <c r="K36" s="30" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="37" spans="2:11">
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="36" t="b">
+      <c r="C37" s="33" t="b">
         <v>1</v>
       </c>
-      <c r="D37" s="36" t="b">
+      <c r="D37" s="33" t="b">
         <v>1</v>
       </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35" t="s">
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="I37" s="35" t="s">
+      <c r="I37" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="35">
+      <c r="J37" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="35" t="s">
+      <c r="K37" s="32" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="38" spans="2:11">
-      <c r="B38" s="35"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35" t="s">
+      <c r="B38" s="32"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="I38" s="35" t="s">
+      <c r="I38" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="J38" s="35">
+      <c r="J38" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="K38" s="35" t="s">
+      <c r="K38" s="32" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="39" spans="2:11">
-      <c r="B39" s="35"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35" t="s">
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="I39" s="35" t="s">
+      <c r="I39" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="J39" s="35">
-        <f t="shared" ref="J39:J60" si="0">J38*2</f>
+      <c r="J39" s="32">
+        <f>J38*2</f>
         <v>2</v>
       </c>
-      <c r="K39" s="35" t="s">
+      <c r="K39" s="32" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="40" spans="2:11">
-      <c r="B40" s="35"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35" t="s">
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="I40" s="35" t="s">
+      <c r="I40" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="J40" s="35">
-        <f t="shared" si="0"/>
+      <c r="J40" s="32">
+        <f>J39*2</f>
         <v>4</v>
       </c>
-      <c r="K40" s="35" t="s">
+      <c r="K40" s="32" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="41" spans="2:11">
-      <c r="B41" s="35"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35" t="s">
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="I41" s="35" t="s">
+      <c r="I41" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="J41" s="35">
-        <f t="shared" si="0"/>
+      <c r="J41" s="32">
+        <f>J40*2</f>
         <v>8</v>
       </c>
-      <c r="K41" s="35" t="s">
+      <c r="K41" s="32" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="42" spans="2:11">
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35" t="s">
+      <c r="B42" s="32"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="I42" s="35" t="s">
+      <c r="I42" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="J42" s="35">
-        <f t="shared" si="0"/>
+      <c r="J42" s="32">
+        <f>J41*2</f>
         <v>16</v>
       </c>
-      <c r="K42" s="35" t="s">
+      <c r="K42" s="32" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="43" spans="2:11">
-      <c r="B43" s="35"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35" t="s">
+      <c r="B43" s="32"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="I43" s="35" t="s">
+      <c r="I43" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="J43" s="35">
-        <f t="shared" si="0"/>
+      <c r="J43" s="32">
+        <f>J42*2</f>
         <v>32</v>
       </c>
-      <c r="K43" s="35" t="s">
+      <c r="K43" s="32" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="44" spans="2:11">
-      <c r="B44" s="35"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35" t="s">
+      <c r="B44" s="32"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="I44" s="35" t="s">
+      <c r="I44" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="J44" s="35">
-        <f t="shared" si="0"/>
+      <c r="J44" s="32">
+        <f>J43*2</f>
         <v>64</v>
       </c>
-      <c r="K44" s="35" t="s">
+      <c r="K44" s="32" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="45" spans="2:11">
-      <c r="B45" s="35"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35" t="s">
+      <c r="B45" s="32"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="I45" s="35" t="s">
+      <c r="I45" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="J45" s="35">
-        <f t="shared" si="0"/>
+      <c r="J45" s="32">
+        <f>J44*2</f>
         <v>128</v>
       </c>
-      <c r="K45" s="35" t="s">
+      <c r="K45" s="32" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="46" spans="2:11">
-      <c r="B46" s="35"/>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35" t="s">
+      <c r="B46" s="32"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="I46" s="35" t="s">
+      <c r="I46" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="J46" s="35">
-        <f t="shared" si="0"/>
+      <c r="J46" s="32">
+        <f>J45*2</f>
         <v>256</v>
       </c>
-      <c r="K46" s="35" t="s">
+      <c r="K46" s="32" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="47" spans="2:11">
-      <c r="B47" s="35"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35" t="s">
+      <c r="B47" s="32"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="I47" s="35" t="s">
+      <c r="I47" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="J47" s="35">
-        <f t="shared" si="0"/>
+      <c r="J47" s="32">
+        <f>J46*2</f>
         <v>512</v>
       </c>
-      <c r="K47" s="35" t="s">
+      <c r="K47" s="32" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="48" spans="2:11">
-      <c r="B48" s="35"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="35" t="s">
+      <c r="B48" s="32"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="I48" s="35" t="s">
+      <c r="I48" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="J48" s="35">
-        <f t="shared" si="0"/>
+      <c r="J48" s="32">
+        <f>J47*2</f>
         <v>1024</v>
       </c>
-      <c r="K48" s="35" t="s">
+      <c r="K48" s="32" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="49" spans="2:11">
-      <c r="B49" s="35"/>
-      <c r="C49" s="35"/>
-      <c r="D49" s="35"/>
-      <c r="E49" s="35"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="35" t="s">
+      <c r="B49" s="32"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="I49" s="35" t="s">
+      <c r="I49" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="J49" s="35">
-        <f t="shared" si="0"/>
+      <c r="J49" s="32">
+        <f>J48*2</f>
         <v>2048</v>
       </c>
-      <c r="K49" s="35" t="s">
+      <c r="K49" s="32" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="50" spans="2:11">
-      <c r="B50" s="35"/>
-      <c r="C50" s="35"/>
-      <c r="D50" s="35"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="35" t="s">
+      <c r="B50" s="32"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="I50" s="35" t="s">
+      <c r="I50" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="J50" s="35">
-        <f t="shared" si="0"/>
+      <c r="J50" s="32">
+        <f>J49*2</f>
         <v>4096</v>
       </c>
-      <c r="K50" s="35" t="s">
+      <c r="K50" s="32" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="51" spans="2:11">
-      <c r="B51" s="35"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="35" t="s">
+      <c r="B51" s="32"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="I51" s="35" t="s">
+      <c r="I51" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="J51" s="35">
-        <f t="shared" si="0"/>
+      <c r="J51" s="32">
+        <f>J50*2</f>
         <v>8192</v>
       </c>
-      <c r="K51" s="35" t="s">
+      <c r="K51" s="32" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="52" spans="2:11">
-      <c r="B52" s="35"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35" t="s">
+      <c r="B52" s="32"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32" t="s">
         <v>144</v>
       </c>
-      <c r="I52" s="35" t="s">
+      <c r="I52" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="J52" s="35">
-        <f t="shared" si="0"/>
+      <c r="J52" s="32">
+        <f>J51*2</f>
         <v>16384</v>
       </c>
-      <c r="K52" s="35" t="s">
+      <c r="K52" s="32" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="53" spans="2:11">
-      <c r="B53" s="35"/>
-      <c r="C53" s="35"/>
-      <c r="D53" s="35"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35" t="s">
+      <c r="B53" s="32"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="I53" s="35" t="s">
+      <c r="I53" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="J53" s="35">
-        <f t="shared" si="0"/>
+      <c r="J53" s="32">
+        <f>J52*2</f>
         <v>32768</v>
       </c>
-      <c r="K53" s="35" t="s">
+      <c r="K53" s="32" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="54" spans="2:11">
-      <c r="B54" s="35"/>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35" t="s">
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="I54" s="35" t="s">
+      <c r="I54" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="J54" s="35">
-        <f t="shared" si="0"/>
+      <c r="J54" s="32">
+        <f>J53*2</f>
         <v>65536</v>
       </c>
-      <c r="K54" s="35" t="s">
+      <c r="K54" s="32" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="55" spans="2:11">
-      <c r="B55" s="35"/>
-      <c r="C55" s="35"/>
-      <c r="D55" s="35"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35" t="s">
+      <c r="B55" s="32"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32" t="s">
         <v>153</v>
       </c>
-      <c r="I55" s="35" t="s">
+      <c r="I55" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="J55" s="35">
-        <f t="shared" si="0"/>
+      <c r="J55" s="32">
+        <f>J54*2</f>
         <v>131072</v>
       </c>
-      <c r="K55" s="35" t="s">
+      <c r="K55" s="32" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="56" spans="2:11">
-      <c r="B56" s="35"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="35"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35" t="s">
+      <c r="B56" s="32"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="I56" s="35" t="s">
+      <c r="I56" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="J56" s="35">
-        <f t="shared" si="0"/>
+      <c r="J56" s="32">
+        <f>J55*2</f>
         <v>262144</v>
       </c>
-      <c r="K56" s="35" t="s">
+      <c r="K56" s="32" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="57" spans="2:11">
-      <c r="B57" s="37"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="37" t="s">
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="I57" s="37" t="s">
+      <c r="I57" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="J57" s="37">
-        <f t="shared" si="0"/>
+      <c r="J57" s="34">
+        <f>J56*2</f>
         <v>524288</v>
       </c>
-      <c r="K57" s="37" t="s">
+      <c r="K57" s="34" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="58" spans="2:11">
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37" t="s">
+      <c r="B58" s="34"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="I58" s="37" t="s">
+      <c r="I58" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="J58" s="37">
-        <f t="shared" si="0"/>
+      <c r="J58" s="34">
+        <f>J57*2</f>
         <v>1048576</v>
       </c>
-      <c r="K58" s="37" t="s">
+      <c r="K58" s="34" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="59" spans="2:11">
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="37" t="s">
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="I59" s="37" t="s">
+      <c r="I59" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="J59" s="37">
-        <f t="shared" si="0"/>
+      <c r="J59" s="34">
+        <f>J58*2</f>
         <v>2097152</v>
       </c>
-      <c r="K59" s="37" t="s">
+      <c r="K59" s="34" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="60" spans="2:11">
-      <c r="B60" s="37"/>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="37"/>
-      <c r="G60" s="37"/>
-      <c r="H60" s="37" t="s">
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="I60" s="37" t="s">
+      <c r="I60" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="J60" s="37">
-        <f t="shared" si="0"/>
+      <c r="J60" s="34">
+        <f>J59*2</f>
         <v>4194304</v>
       </c>
-      <c r="K60" s="37" t="s">
+      <c r="K60" s="34" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="61" spans="2:11">
-      <c r="B61" s="38" t="s">
+      <c r="B61" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="C61" s="36" t="b">
+      <c r="C61" s="33" t="b">
         <v>1</v>
       </c>
-      <c r="D61" s="36" t="b">
+      <c r="D61" s="33" t="b">
         <v>1</v>
       </c>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38"/>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38" t="s">
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="I61" s="38" t="s">
+      <c r="I61" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="J61" s="35">
+      <c r="J61" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="K61" s="38" t="s">
+      <c r="K61" s="35" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="62" spans="2:11">
-      <c r="B62" s="38"/>
-      <c r="C62" s="38"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38" t="s">
+      <c r="B62" s="35"/>
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35" t="s">
         <v>174</v>
       </c>
-      <c r="I62" s="38" t="s">
+      <c r="I62" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="J62" s="35">
+      <c r="J62" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="K62" s="38" t="s">
+      <c r="K62" s="35" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="63" spans="2:11">
-      <c r="B63" s="38"/>
-      <c r="C63" s="38"/>
-      <c r="D63" s="38"/>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38" t="s">
+      <c r="B63" s="35"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="I63" s="38" t="s">
+      <c r="I63" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="J63" s="35">
+      <c r="J63" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="K63" s="38" t="s">
+      <c r="K63" s="35" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="64" spans="2:11">
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38" t="s">
+      <c r="B64" s="35"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="I64" s="38" t="s">
+      <c r="I64" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="J64" s="35">
+      <c r="J64" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="K64" s="38" t="s">
+      <c r="K64" s="35" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="65" spans="2:11">
-      <c r="B65" s="38"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="38"/>
-      <c r="E65" s="38"/>
-      <c r="F65" s="38"/>
-      <c r="G65" s="38"/>
-      <c r="H65" s="38" t="s">
+      <c r="B65" s="35"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="I65" s="38" t="s">
+      <c r="I65" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="J65" s="35">
+      <c r="J65" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="K65" s="38" t="s">
+      <c r="K65" s="35" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="66" spans="2:11">
-      <c r="B66" s="39" t="s">
+      <c r="B66" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="C66" s="40" t="b">
+      <c r="C66" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="D66" s="40" t="b">
+      <c r="D66" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E66" s="39"/>
-      <c r="F66" s="39"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="39" t="s">
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="36"/>
+      <c r="H66" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="I66" s="39" t="s">
+      <c r="I66" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="J66" s="39">
+      <c r="J66" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="K66" s="39" t="s">
+      <c r="K66" s="36" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="67" spans="2:11">
-      <c r="B67" s="39"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="39"/>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
-      <c r="H67" s="39" t="s">
+      <c r="B67" s="36"/>
+      <c r="C67" s="36"/>
+      <c r="D67" s="36"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="36"/>
+      <c r="G67" s="36"/>
+      <c r="H67" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="I67" s="39" t="s">
+      <c r="I67" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="J67" s="39">
+      <c r="J67" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="K67" s="39" t="s">
+      <c r="K67" s="36" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="68" spans="2:11">
-      <c r="B68" s="39"/>
-      <c r="C68" s="39"/>
-      <c r="D68" s="39"/>
-      <c r="E68" s="39"/>
-      <c r="F68" s="39"/>
-      <c r="G68" s="39"/>
-      <c r="H68" s="39" t="s">
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="I68" s="39" t="s">
+      <c r="I68" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="J68" s="39">
+      <c r="J68" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="K68" s="39" t="s">
+      <c r="K68" s="36" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="69" spans="2:11">
-      <c r="B69" s="39"/>
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="39"/>
-      <c r="F69" s="39"/>
-      <c r="G69" s="39"/>
-      <c r="H69" s="39" t="s">
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="36"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="I69" s="39" t="s">
+      <c r="I69" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="J69" s="39">
+      <c r="J69" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="K69" s="39" t="s">
+      <c r="K69" s="36" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="70" spans="2:11">
-      <c r="B70" s="39"/>
-      <c r="C70" s="39"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="39"/>
-      <c r="G70" s="39"/>
-      <c r="H70" s="39" t="s">
+      <c r="B70" s="36"/>
+      <c r="C70" s="36"/>
+      <c r="D70" s="36"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="36"/>
+      <c r="G70" s="36"/>
+      <c r="H70" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="I70" s="39" t="s">
+      <c r="I70" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="J70" s="39">
+      <c r="J70" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="K70" s="39" t="s">
+      <c r="K70" s="36" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="71" spans="2:11">
-      <c r="B71" s="39"/>
-      <c r="C71" s="39"/>
-      <c r="D71" s="39"/>
-      <c r="E71" s="39"/>
-      <c r="F71" s="39"/>
-      <c r="G71" s="39"/>
-      <c r="H71" s="39" t="s">
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="I71" s="39" t="s">
+      <c r="I71" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="J71" s="39">
+      <c r="J71" s="36" t="n">
         <v>32</v>
       </c>
-      <c r="K71" s="39" t="s">
+      <c r="K71" s="36" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="72" spans="2:11">
-      <c r="B72" s="39"/>
-      <c r="C72" s="39"/>
-      <c r="D72" s="39"/>
-      <c r="E72" s="39"/>
-      <c r="F72" s="39"/>
-      <c r="G72" s="39"/>
-      <c r="H72" s="39" t="s">
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="36"/>
+      <c r="H72" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="I72" s="39" t="s">
+      <c r="I72" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="J72" s="39">
+      <c r="J72" s="36" t="n">
         <v>64</v>
       </c>
-      <c r="K72" s="39" t="s">
+      <c r="K72" s="36" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="73" spans="2:11">
-      <c r="B73" s="39"/>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39"/>
-      <c r="H73" s="39" t="s">
+      <c r="B73" s="36"/>
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="36"/>
+      <c r="G73" s="36"/>
+      <c r="H73" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="I73" s="39" t="s">
+      <c r="I73" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="J73" s="39">
+      <c r="J73" s="36" t="n">
         <v>127</v>
       </c>
-      <c r="K73" s="39" t="s">
+      <c r="K73" s="36" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="74" spans="2:11">
-      <c r="B74" s="25" t="s">
+      <c r="B74" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="C74" s="41" t="b">
+      <c r="C74" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="D74" s="41" t="b">
+      <c r="D74" s="38" t="b">
         <v>1</v>
       </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="25" t="s">
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="I74" s="25" t="s">
+      <c r="I74" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="J74" s="25">
+      <c r="J74" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="K74" s="25"/>
+      <c r="K74" s="24"/>
     </row>
     <row r="75" spans="2:11">
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25"/>
-      <c r="G75" s="25"/>
-      <c r="H75" s="25" t="s">
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="I75" s="25" t="s">
+      <c r="I75" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="J75" s="25">
+      <c r="J75" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="K75" s="25"/>
+      <c r="K75" s="24"/>
     </row>
     <row r="76" spans="2:11">
-      <c r="B76" s="42" t="s">
+      <c r="B76" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C76" s="43" t="b">
+      <c r="C76" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="D76" s="43" t="b">
+      <c r="D76" s="40" t="b">
         <v>1</v>
       </c>
-      <c r="E76" s="44"/>
-      <c r="F76" s="44"/>
-      <c r="G76" s="44"/>
-      <c r="H76" s="44" t="s">
+      <c r="E76" s="41"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="I76" s="44" t="s">
+      <c r="I76" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="J76" s="44">
+      <c r="J76" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="K76" s="44" t="s">
+      <c r="K76" s="41" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="77" spans="2:11">
-      <c r="B77" s="44"/>
-      <c r="C77" s="44"/>
-      <c r="D77" s="44"/>
-      <c r="E77" s="44"/>
-      <c r="F77" s="44"/>
-      <c r="G77" s="44"/>
-      <c r="H77" s="44" t="s">
+      <c r="B77" s="41"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="41"/>
+      <c r="E77" s="41"/>
+      <c r="F77" s="41"/>
+      <c r="G77" s="41"/>
+      <c r="H77" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="I77" s="44" t="s">
+      <c r="I77" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="J77" s="44">
+      <c r="J77" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="K77" s="44" t="s">
+      <c r="K77" s="41" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="78" spans="2:11">
-      <c r="B78" s="45" t="s">
+      <c r="B78" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="C78" s="46" t="b">
+      <c r="C78" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="D78" s="46" t="b">
+      <c r="D78" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E78" s="26"/>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26" t="s">
+      <c r="E78" s="25"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="25"/>
+      <c r="H78" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="I78" s="26" t="s">
+      <c r="I78" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="J78" s="39">
+      <c r="J78" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="K78" s="26" t="s">
+      <c r="K78" s="25" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="79" spans="2:11">
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
-      <c r="D79" s="26"/>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="26"/>
-      <c r="H79" s="26" t="s">
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="I79" s="26" t="s">
+      <c r="I79" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="J79" s="39">
+      <c r="J79" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="K79" s="26" t="s">
+      <c r="K79" s="25" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="80" spans="2:11">
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
-      <c r="D80" s="26"/>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26" t="s">
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="25"/>
+      <c r="E80" s="25"/>
+      <c r="F80" s="25"/>
+      <c r="G80" s="25"/>
+      <c r="H80" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="I80" s="26" t="s">
+      <c r="I80" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="J80" s="39">
+      <c r="J80" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="K80" s="26" t="s">
+      <c r="K80" s="25" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="81" spans="2:11">
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
-      <c r="D81" s="26"/>
-      <c r="E81" s="26"/>
-      <c r="F81" s="26"/>
-      <c r="G81" s="26"/>
-      <c r="H81" s="26" t="s">
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="25"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
+      <c r="H81" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="I81" s="26" t="s">
+      <c r="I81" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="J81" s="39">
+      <c r="J81" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="K81" s="26" t="s">
+      <c r="K81" s="25" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="82" spans="2:11">
-      <c r="B82" s="26"/>
-      <c r="C82" s="26"/>
-      <c r="D82" s="26"/>
-      <c r="E82" s="26"/>
-      <c r="F82" s="26"/>
-      <c r="G82" s="26"/>
-      <c r="H82" s="26" t="s">
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
+      <c r="H82" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="I82" s="26" t="s">
+      <c r="I82" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="J82" s="39">
+      <c r="J82" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="K82" s="26" t="s">
+      <c r="K82" s="25" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="83" spans="2:11">
-      <c r="B83" s="47" t="s">
+      <c r="B83" s="43" t="s">
         <v>224</v>
       </c>
-      <c r="C83" s="43" t="b">
+      <c r="C83" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="D83" s="46" t="b">
+      <c r="D83" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E83" s="44"/>
-      <c r="F83" s="44"/>
-      <c r="G83" s="44"/>
-      <c r="H83" s="44" t="s">
+      <c r="E83" s="41"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="I83" s="44" t="s">
+      <c r="I83" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="J83" s="44">
+      <c r="J83" s="41" t="n">
         <v>1</v>
       </c>
-      <c r="K83" s="44" t="s">
+      <c r="K83" s="41" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="84" spans="2:11">
-      <c r="B84" s="44"/>
-      <c r="C84" s="44"/>
-      <c r="D84" s="44"/>
-      <c r="E84" s="44"/>
-      <c r="F84" s="44"/>
-      <c r="G84" s="44"/>
-      <c r="H84" s="44" t="s">
+      <c r="B84" s="41"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="41"/>
+      <c r="E84" s="41"/>
+      <c r="F84" s="41"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="I84" s="44" t="s">
+      <c r="I84" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="J84" s="44">
+      <c r="J84" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="K84" s="44" t="s">
+      <c r="K84" s="41" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="85" spans="2:11">
-      <c r="B85" s="26" t="s">
+      <c r="B85" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="C85" s="46" t="b">
+      <c r="C85" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D85" s="46" t="b">
+      <c r="D85" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E85" s="26"/>
-      <c r="F85" s="26"/>
-      <c r="G85" s="26"/>
-      <c r="H85" s="48" t="s">
+      <c r="E85" s="25"/>
+      <c r="F85" s="25"/>
+      <c r="G85" s="25"/>
+      <c r="H85" s="44" t="s">
         <v>183</v>
       </c>
-      <c r="I85" s="26" t="s">
+      <c r="I85" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="J85" s="26">
+      <c r="J85" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="K85" s="26" t="s">
+      <c r="K85" s="25" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="86" spans="2:11">
-      <c r="B86" s="26"/>
-      <c r="C86" s="26"/>
-      <c r="D86" s="26"/>
-      <c r="E86" s="26"/>
-      <c r="F86" s="26"/>
-      <c r="G86" s="26"/>
-      <c r="H86" s="48" t="s">
+      <c r="B86" s="25"/>
+      <c r="C86" s="25"/>
+      <c r="D86" s="25"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="25"/>
+      <c r="H86" s="44" t="s">
         <v>230</v>
       </c>
-      <c r="I86" s="26" t="s">
+      <c r="I86" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="J86" s="26">
+      <c r="J86" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="K86" s="26" t="s">
+      <c r="K86" s="25" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="87" spans="2:11">
-      <c r="B87" s="26"/>
-      <c r="C87" s="26"/>
-      <c r="D87" s="26"/>
-      <c r="E87" s="26"/>
-      <c r="F87" s="26"/>
-      <c r="G87" s="26"/>
-      <c r="H87" s="48" t="s">
+      <c r="B87" s="25"/>
+      <c r="C87" s="25"/>
+      <c r="D87" s="25"/>
+      <c r="E87" s="25"/>
+      <c r="F87" s="25"/>
+      <c r="G87" s="25"/>
+      <c r="H87" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="I87" s="26" t="s">
+      <c r="I87" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="J87" s="26">
+      <c r="J87" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K87" s="26" t="s">
+      <c r="K87" s="25" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="88" spans="2:11">
-      <c r="B88" s="49" t="s">
+      <c r="B88" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="C88" s="50" t="b">
+      <c r="C88" s="46" t="b">
         <v>0</v>
       </c>
-      <c r="D88" s="50" t="b">
+      <c r="D88" s="46" t="b">
         <v>1</v>
       </c>
-      <c r="E88" s="49"/>
-      <c r="F88" s="49"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="51" t="s">
+      <c r="E88" s="45"/>
+      <c r="F88" s="45"/>
+      <c r="G88" s="45"/>
+      <c r="H88" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="I88" s="49" t="s">
+      <c r="I88" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="J88" s="49">
+      <c r="J88" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="K88" s="49" t="s">
+      <c r="K88" s="45" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="89" spans="2:11">
-      <c r="B89" s="49"/>
-      <c r="C89" s="49"/>
-      <c r="D89" s="49"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="49"/>
-      <c r="G89" s="49"/>
-      <c r="H89" s="51" t="s">
+      <c r="B89" s="45"/>
+      <c r="C89" s="45"/>
+      <c r="D89" s="45"/>
+      <c r="E89" s="45"/>
+      <c r="F89" s="45"/>
+      <c r="G89" s="45"/>
+      <c r="H89" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="I89" s="49" t="s">
+      <c r="I89" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="J89" s="49">
+      <c r="J89" s="45" t="n">
         <v>2</v>
       </c>
-      <c r="K89" s="49" t="s">
+      <c r="K89" s="45" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="90" spans="2:11">
-      <c r="B90" s="49"/>
-      <c r="C90" s="49"/>
-      <c r="D90" s="49"/>
-      <c r="E90" s="49"/>
-      <c r="F90" s="49"/>
-      <c r="G90" s="49"/>
-      <c r="H90" s="51" t="s">
+      <c r="B90" s="45"/>
+      <c r="C90" s="45"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="45"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="45"/>
+      <c r="H90" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="I90" s="49" t="s">
+      <c r="I90" s="45" t="s">
         <v>239</v>
       </c>
-      <c r="J90" s="49">
+      <c r="J90" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="K90" s="49" t="s">
+      <c r="K90" s="45" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="91" spans="2:11">
-      <c r="B91" s="52" t="s">
-        <v>240</v>
-      </c>
-      <c r="C91" s="53" t="b">
-        <v>0</v>
-      </c>
-      <c r="D91" s="53" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="52"/>
-      <c r="F91" s="52"/>
-      <c r="G91" s="52"/>
-      <c r="H91" s="54" t="s">
-        <v>252</v>
-      </c>
-      <c r="I91" s="54" t="s">
-        <v>254</v>
-      </c>
-      <c r="J91" s="52"/>
-      <c r="K91" s="54">
-        <v>0</v>
-      </c>
+      <c r="B91" s="48"/>
+      <c r="C91" s="49"/>
+      <c r="D91" s="49"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="48"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="50"/>
+      <c r="I91" s="50"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="50"/>
     </row>
     <row r="92" spans="2:11">
-      <c r="B92" s="52"/>
-      <c r="C92" s="52"/>
-      <c r="D92" s="52"/>
-      <c r="E92" s="52"/>
-      <c r="F92" s="52"/>
-      <c r="G92" s="52"/>
-      <c r="H92" s="54" t="s">
-        <v>253</v>
-      </c>
-      <c r="I92" s="54" t="s">
-        <v>255</v>
-      </c>
-      <c r="J92" s="52"/>
-      <c r="K92" s="54">
-        <v>1</v>
-      </c>
+      <c r="B92" s="48"/>
+      <c r="C92" s="48"/>
+      <c r="D92" s="48"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="50"/>
+      <c r="I92" s="50"/>
+      <c r="J92" s="48"/>
+      <c r="K92" s="50"/>
     </row>
     <row r="93" spans="2:11">
-      <c r="B93" s="56" t="s">
-        <v>241</v>
-      </c>
-      <c r="C93" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="D93" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="56"/>
-      <c r="F93" s="56"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="58" t="s">
-        <v>242</v>
-      </c>
-      <c r="I93" s="56" t="s">
-        <v>247</v>
-      </c>
-      <c r="J93" s="56">
-        <v>1</v>
-      </c>
-      <c r="K93" s="56" t="s">
-        <v>247</v>
-      </c>
+      <c r="B93" s="51"/>
+      <c r="C93" s="52"/>
+      <c r="D93" s="52"/>
+      <c r="E93" s="51"/>
+      <c r="F93" s="51"/>
+      <c r="G93" s="51"/>
+      <c r="H93" s="53"/>
+      <c r="I93" s="51"/>
+      <c r="J93" s="51"/>
+      <c r="K93" s="51"/>
     </row>
     <row r="94" spans="2:11">
-      <c r="B94" s="56"/>
-      <c r="C94" s="56"/>
-      <c r="D94" s="56"/>
-      <c r="E94" s="56"/>
-      <c r="F94" s="56"/>
-      <c r="G94" s="56"/>
-      <c r="H94" s="58" t="s">
-        <v>243</v>
-      </c>
-      <c r="I94" s="56" t="s">
-        <v>248</v>
-      </c>
-      <c r="J94" s="56">
-        <v>2</v>
-      </c>
-      <c r="K94" s="56" t="s">
-        <v>248</v>
-      </c>
+      <c r="B94" s="51"/>
+      <c r="C94" s="51"/>
+      <c r="D94" s="51"/>
+      <c r="E94" s="51"/>
+      <c r="F94" s="51"/>
+      <c r="G94" s="51"/>
+      <c r="H94" s="53"/>
+      <c r="I94" s="51"/>
+      <c r="J94" s="51"/>
+      <c r="K94" s="51"/>
     </row>
     <row r="95" spans="2:11">
-      <c r="B95" s="56"/>
-      <c r="C95" s="56"/>
-      <c r="D95" s="56"/>
-      <c r="E95" s="56"/>
-      <c r="F95" s="56"/>
-      <c r="G95" s="56"/>
-      <c r="H95" s="58" t="s">
-        <v>244</v>
-      </c>
-      <c r="I95" s="56" t="s">
-        <v>249</v>
-      </c>
-      <c r="J95" s="56">
-        <v>3</v>
-      </c>
-      <c r="K95" s="56" t="s">
-        <v>249</v>
-      </c>
+      <c r="B95" s="51"/>
+      <c r="C95" s="51"/>
+      <c r="D95" s="51"/>
+      <c r="E95" s="51"/>
+      <c r="F95" s="51"/>
+      <c r="G95" s="51"/>
+      <c r="H95" s="53"/>
+      <c r="I95" s="51"/>
+      <c r="J95" s="51"/>
+      <c r="K95" s="51"/>
     </row>
     <row r="96" spans="2:11">
-      <c r="B96" s="56"/>
-      <c r="C96" s="56"/>
-      <c r="D96" s="56"/>
-      <c r="E96" s="56"/>
-      <c r="F96" s="56"/>
-      <c r="G96" s="56"/>
-      <c r="H96" s="58" t="s">
-        <v>245</v>
-      </c>
-      <c r="I96" s="56" t="s">
-        <v>250</v>
-      </c>
-      <c r="J96" s="56">
-        <v>4</v>
-      </c>
-      <c r="K96" s="56" t="s">
-        <v>250</v>
-      </c>
+      <c r="B96" s="51"/>
+      <c r="C96" s="51"/>
+      <c r="D96" s="51"/>
+      <c r="E96" s="51"/>
+      <c r="F96" s="51"/>
+      <c r="G96" s="51"/>
+      <c r="H96" s="53"/>
+      <c r="I96" s="51"/>
+      <c r="J96" s="51"/>
+      <c r="K96" s="51"/>
     </row>
     <row r="97" spans="2:11">
-      <c r="B97" s="56"/>
-      <c r="C97" s="56"/>
-      <c r="D97" s="56"/>
-      <c r="E97" s="56"/>
-      <c r="F97" s="56"/>
-      <c r="G97" s="56"/>
-      <c r="H97" s="58" t="s">
-        <v>246</v>
-      </c>
-      <c r="I97" s="56" t="s">
-        <v>251</v>
-      </c>
-      <c r="J97" s="56">
-        <v>5</v>
-      </c>
-      <c r="K97" s="56" t="s">
-        <v>251</v>
-      </c>
+      <c r="B97" s="51"/>
+      <c r="C97" s="51"/>
+      <c r="D97" s="51"/>
+      <c r="E97" s="51"/>
+      <c r="F97" s="51"/>
+      <c r="G97" s="51"/>
+      <c r="H97" s="53"/>
+      <c r="I97" s="51"/>
+      <c r="J97" s="51"/>
+      <c r="K97" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783500644" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783500644" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783500644" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783500644" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783500644" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783500644" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5644F5D2-6466-49EB-9D73-787A111002FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1AF98B-8BFD-4636-8762-8D4B034B7DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6040" yWindow="1690" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5060" yWindow="1980" windowWidth="30580" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -209,16 +209,10 @@
     <t>PropertyType</t>
   </si>
   <si>
-    <t>Gold</t>
-  </si>
-  <si>
     <t>金币</t>
   </si>
   <si>
     <t>通用游戏货币</t>
-  </si>
-  <si>
-    <t>GameGold</t>
   </si>
   <si>
     <t>游戏币</t>
@@ -814,6 +808,14 @@
   </si>
   <si>
     <t>消耗品</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Coin</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameCoin</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1300,9 +1302,6 @@
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1311,6 +1310,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1634,13 +1636,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -2012,16 +2014,16 @@
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="I18" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="I18" s="24" t="s">
+      <c r="J18" s="24">
+        <v>1</v>
+      </c>
+      <c r="K18" s="24" t="s">
         <v>59</v>
-      </c>
-      <c r="J18" s="24">
-        <v>1</v>
-      </c>
-      <c r="K18" s="24" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="19" spans="2:11">
@@ -2032,16 +2034,16 @@
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
       <c r="H19" s="24" t="s">
-        <v>61</v>
+        <v>255</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J19" s="24">
         <v>2</v>
       </c>
       <c r="K19" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="2:11">
@@ -2052,16 +2054,16 @@
       <c r="F20" s="25"/>
       <c r="G20" s="25"/>
       <c r="H20" s="25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J20" s="25">
         <v>3</v>
       </c>
       <c r="K20" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="2:11">
@@ -2072,16 +2074,16 @@
       <c r="F21" s="25"/>
       <c r="G21" s="25"/>
       <c r="H21" s="25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J21" s="25">
         <v>4</v>
       </c>
       <c r="K21" s="25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:11">
@@ -2092,16 +2094,16 @@
       <c r="F22" s="25"/>
       <c r="G22" s="25"/>
       <c r="H22" s="25" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J22" s="25">
         <v>5</v>
       </c>
       <c r="K22" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="2:11">
@@ -2112,16 +2114,16 @@
       <c r="F23" s="25"/>
       <c r="G23" s="25"/>
       <c r="H23" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J23" s="25">
         <v>6</v>
       </c>
       <c r="K23" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="2:11">
@@ -2132,16 +2134,16 @@
       <c r="F24" s="25"/>
       <c r="G24" s="25"/>
       <c r="H24" s="25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J24" s="25">
         <v>7</v>
       </c>
       <c r="K24" s="25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:11">
@@ -2152,21 +2154,21 @@
       <c r="F25" s="25"/>
       <c r="G25" s="25"/>
       <c r="H25" s="25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J25" s="25">
         <v>8</v>
       </c>
       <c r="K25" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="2:11">
       <c r="B26" s="26" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C26" s="27" t="b">
         <v>0</v>
@@ -2178,16 +2180,16 @@
       <c r="F26" s="26"/>
       <c r="G26" s="26"/>
       <c r="H26" s="26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J26" s="26">
         <v>0</v>
       </c>
       <c r="K26" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="2:11">
@@ -2198,16 +2200,16 @@
       <c r="F27" s="26"/>
       <c r="G27" s="26"/>
       <c r="H27" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J27" s="26">
         <v>1</v>
       </c>
       <c r="K27" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="2:11">
@@ -2218,16 +2220,16 @@
       <c r="F28" s="26"/>
       <c r="G28" s="26"/>
       <c r="H28" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J28" s="26">
         <v>2</v>
       </c>
       <c r="K28" s="26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="2:11">
@@ -2238,21 +2240,21 @@
       <c r="F29" s="26"/>
       <c r="G29" s="26"/>
       <c r="H29" s="26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I29" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J29" s="26">
         <v>3</v>
       </c>
       <c r="K29" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="2:11">
       <c r="B30" s="29" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" s="30" t="b">
         <v>0</v>
@@ -2264,16 +2266,16 @@
       <c r="F30" s="31"/>
       <c r="G30" s="31"/>
       <c r="H30" s="31" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I30" s="31" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J30" s="31">
         <v>0</v>
       </c>
       <c r="K30" s="31" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="2:11">
@@ -2284,16 +2286,16 @@
       <c r="F31" s="31"/>
       <c r="G31" s="31"/>
       <c r="H31" s="31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I31" s="31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J31" s="31">
         <v>1</v>
       </c>
       <c r="K31" s="31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="2:11">
@@ -2304,16 +2306,16 @@
       <c r="F32" s="31"/>
       <c r="G32" s="31"/>
       <c r="H32" s="31" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I32" s="31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J32" s="31">
         <v>2</v>
       </c>
       <c r="K32" s="31" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -2324,21 +2326,21 @@
       <c r="F33" s="31"/>
       <c r="G33" s="31"/>
       <c r="H33" s="31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I33" s="31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J33" s="31">
         <v>3</v>
       </c>
       <c r="K33" s="31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="2:11">
       <c r="B34" s="33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C34" s="34" t="b">
         <v>0</v>
@@ -2350,16 +2352,16 @@
       <c r="F34" s="33"/>
       <c r="G34" s="33"/>
       <c r="H34" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="J34" s="33">
+        <v>1</v>
+      </c>
+      <c r="K34" s="33" t="s">
         <v>89</v>
-      </c>
-      <c r="I34" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="J34" s="33">
-        <v>1</v>
-      </c>
-      <c r="K34" s="33" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -2370,16 +2372,16 @@
       <c r="F35" s="33"/>
       <c r="G35" s="33"/>
       <c r="H35" s="33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I35" s="33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J35" s="33">
         <v>2</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -2390,21 +2392,21 @@
       <c r="F36" s="33"/>
       <c r="G36" s="33"/>
       <c r="H36" s="33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J36" s="33">
         <v>3</v>
       </c>
       <c r="K36" s="33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="2:11">
       <c r="B37" s="35" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C37" s="36" t="b">
         <v>1</v>
@@ -2416,16 +2418,16 @@
       <c r="F37" s="35"/>
       <c r="G37" s="35"/>
       <c r="H37" s="35" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J37" s="35">
         <v>0</v>
       </c>
       <c r="K37" s="35" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="2:11">
@@ -2436,16 +2438,16 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
       <c r="H38" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="I38" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="J38" s="35">
+        <v>1</v>
+      </c>
+      <c r="K38" s="35" t="s">
         <v>102</v>
-      </c>
-      <c r="I38" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="J38" s="35">
-        <v>1</v>
-      </c>
-      <c r="K38" s="35" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="39" spans="2:11">
@@ -2456,17 +2458,17 @@
       <c r="F39" s="35"/>
       <c r="G39" s="35"/>
       <c r="H39" s="35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I39" s="35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J39" s="35">
         <f t="shared" ref="J39:J60" si="0">J38*2</f>
         <v>2</v>
       </c>
       <c r="K39" s="35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -2477,17 +2479,17 @@
       <c r="F40" s="35"/>
       <c r="G40" s="35"/>
       <c r="H40" s="35" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I40" s="35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J40" s="35">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="K40" s="35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="2:11">
@@ -2498,17 +2500,17 @@
       <c r="F41" s="35"/>
       <c r="G41" s="35"/>
       <c r="H41" s="35" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I41" s="35" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="J41" s="35">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="K41" s="35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="2:11">
@@ -2519,17 +2521,17 @@
       <c r="F42" s="35"/>
       <c r="G42" s="35"/>
       <c r="H42" s="35" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I42" s="35" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J42" s="35">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="K42" s="35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="2:11">
@@ -2540,17 +2542,17 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
       <c r="H43" s="35" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I43" s="35" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J43" s="35">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="K43" s="35" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="2:11">
@@ -2561,17 +2563,17 @@
       <c r="F44" s="35"/>
       <c r="G44" s="35"/>
       <c r="H44" s="35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I44" s="35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J44" s="35">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="K44" s="35" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="2:11">
@@ -2582,17 +2584,17 @@
       <c r="F45" s="35"/>
       <c r="G45" s="35"/>
       <c r="H45" s="35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I45" s="35" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J45" s="35">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
       <c r="K45" s="35" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="2:11">
@@ -2603,17 +2605,17 @@
       <c r="F46" s="35"/>
       <c r="G46" s="35"/>
       <c r="H46" s="35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I46" s="35" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J46" s="35">
         <f t="shared" si="0"/>
         <v>256</v>
       </c>
       <c r="K46" s="35" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="2:11">
@@ -2624,17 +2626,17 @@
       <c r="F47" s="35"/>
       <c r="G47" s="35"/>
       <c r="H47" s="35" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I47" s="35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J47" s="35">
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
       <c r="K47" s="35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="2:11">
@@ -2645,17 +2647,17 @@
       <c r="F48" s="35"/>
       <c r="G48" s="35"/>
       <c r="H48" s="35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I48" s="35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J48" s="35">
         <f t="shared" si="0"/>
         <v>1024</v>
       </c>
       <c r="K48" s="35" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="2:11">
@@ -2666,17 +2668,17 @@
       <c r="F49" s="35"/>
       <c r="G49" s="35"/>
       <c r="H49" s="35" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I49" s="35" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J49" s="35">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
       <c r="K49" s="35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="2:11">
@@ -2687,17 +2689,17 @@
       <c r="F50" s="35"/>
       <c r="G50" s="35"/>
       <c r="H50" s="35" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I50" s="35" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J50" s="35">
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
       <c r="K50" s="35" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="2:11">
@@ -2708,17 +2710,17 @@
       <c r="F51" s="35"/>
       <c r="G51" s="35"/>
       <c r="H51" s="35" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I51" s="35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J51" s="35">
         <f t="shared" si="0"/>
         <v>8192</v>
       </c>
       <c r="K51" s="35" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="2:11">
@@ -2729,17 +2731,17 @@
       <c r="F52" s="35"/>
       <c r="G52" s="35"/>
       <c r="H52" s="35" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I52" s="35" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J52" s="35">
         <f t="shared" si="0"/>
         <v>16384</v>
       </c>
       <c r="K52" s="35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="2:11">
@@ -2750,17 +2752,17 @@
       <c r="F53" s="35"/>
       <c r="G53" s="35"/>
       <c r="H53" s="35" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I53" s="35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J53" s="35">
         <f t="shared" si="0"/>
         <v>32768</v>
       </c>
       <c r="K53" s="35" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="2:11">
@@ -2771,17 +2773,17 @@
       <c r="F54" s="35"/>
       <c r="G54" s="35"/>
       <c r="H54" s="35" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I54" s="35" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J54" s="35">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
       <c r="K54" s="35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="2:11">
@@ -2792,17 +2794,17 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
       <c r="H55" s="35" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="I55" s="35" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J55" s="35">
         <f t="shared" si="0"/>
         <v>131072</v>
       </c>
       <c r="K55" s="35" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="2:11">
@@ -2813,17 +2815,17 @@
       <c r="F56" s="35"/>
       <c r="G56" s="35"/>
       <c r="H56" s="35" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I56" s="35" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J56" s="35">
         <f t="shared" si="0"/>
         <v>262144</v>
       </c>
       <c r="K56" s="35" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="2:11">
@@ -2834,17 +2836,17 @@
       <c r="F57" s="37"/>
       <c r="G57" s="37"/>
       <c r="H57" s="37" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I57" s="37" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J57" s="37">
         <f t="shared" si="0"/>
         <v>524288</v>
       </c>
       <c r="K57" s="37" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="2:11">
@@ -2855,17 +2857,17 @@
       <c r="F58" s="37"/>
       <c r="G58" s="37"/>
       <c r="H58" s="37" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I58" s="37" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="J58" s="37">
         <f t="shared" si="0"/>
         <v>1048576</v>
       </c>
       <c r="K58" s="37" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="2:11">
@@ -2876,17 +2878,17 @@
       <c r="F59" s="37"/>
       <c r="G59" s="37"/>
       <c r="H59" s="37" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="I59" s="37" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="J59" s="37">
         <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
       <c r="K59" s="37" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="2:11">
@@ -2897,22 +2899,22 @@
       <c r="F60" s="37"/>
       <c r="G60" s="37"/>
       <c r="H60" s="37" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I60" s="37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="J60" s="37">
         <f t="shared" si="0"/>
         <v>4194304</v>
       </c>
       <c r="K60" s="37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="2:11">
       <c r="B61" s="38" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C61" s="36" t="b">
         <v>1</v>
@@ -2924,16 +2926,16 @@
       <c r="F61" s="38"/>
       <c r="G61" s="38"/>
       <c r="H61" s="38" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I61" s="38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="J61" s="35">
         <v>1</v>
       </c>
       <c r="K61" s="38" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="2:11">
@@ -2944,16 +2946,16 @@
       <c r="F62" s="38"/>
       <c r="G62" s="38"/>
       <c r="H62" s="38" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I62" s="38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J62" s="35">
         <v>2</v>
       </c>
       <c r="K62" s="38" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="2:11">
@@ -2964,16 +2966,16 @@
       <c r="F63" s="38"/>
       <c r="G63" s="38"/>
       <c r="H63" s="38" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I63" s="38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J63" s="35">
         <v>4</v>
       </c>
       <c r="K63" s="38" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="2:11">
@@ -2984,16 +2986,16 @@
       <c r="F64" s="38"/>
       <c r="G64" s="38"/>
       <c r="H64" s="38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I64" s="38" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J64" s="35">
         <v>8</v>
       </c>
       <c r="K64" s="38" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="2:11">
@@ -3004,21 +3006,21 @@
       <c r="F65" s="38"/>
       <c r="G65" s="38"/>
       <c r="H65" s="38" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I65" s="38" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J65" s="35">
         <v>15</v>
       </c>
       <c r="K65" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="2:11">
       <c r="B66" s="39" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C66" s="40" t="b">
         <v>1</v>
@@ -3030,16 +3032,16 @@
       <c r="F66" s="39"/>
       <c r="G66" s="39"/>
       <c r="H66" s="39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I66" s="39" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J66" s="39">
         <v>1</v>
       </c>
       <c r="K66" s="39" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="2:11">
@@ -3050,16 +3052,16 @@
       <c r="F67" s="39"/>
       <c r="G67" s="39"/>
       <c r="H67" s="39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I67" s="39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J67" s="39">
         <v>2</v>
       </c>
       <c r="K67" s="39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="68" spans="2:11">
@@ -3070,16 +3072,16 @@
       <c r="F68" s="39"/>
       <c r="G68" s="39"/>
       <c r="H68" s="39" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I68" s="39" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J68" s="39">
         <v>4</v>
       </c>
       <c r="K68" s="39" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="2:11">
@@ -3090,16 +3092,16 @@
       <c r="F69" s="39"/>
       <c r="G69" s="39"/>
       <c r="H69" s="39" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I69" s="39" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J69" s="39">
         <v>8</v>
       </c>
       <c r="K69" s="39" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="2:11">
@@ -3110,16 +3112,16 @@
       <c r="F70" s="39"/>
       <c r="G70" s="39"/>
       <c r="H70" s="39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I70" s="39" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J70" s="39">
         <v>16</v>
       </c>
       <c r="K70" s="39" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="2:11">
@@ -3130,16 +3132,16 @@
       <c r="F71" s="39"/>
       <c r="G71" s="39"/>
       <c r="H71" s="39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I71" s="39" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J71" s="39">
         <v>32</v>
       </c>
       <c r="K71" s="39" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="2:11">
@@ -3150,16 +3152,16 @@
       <c r="F72" s="39"/>
       <c r="G72" s="39"/>
       <c r="H72" s="39" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I72" s="39" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J72" s="39">
         <v>64</v>
       </c>
       <c r="K72" s="39" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="2:11">
@@ -3170,21 +3172,21 @@
       <c r="F73" s="39"/>
       <c r="G73" s="39"/>
       <c r="H73" s="39" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I73" s="39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J73" s="39">
         <v>127</v>
       </c>
       <c r="K73" s="39" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="2:11">
       <c r="B74" s="25" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C74" s="41" t="b">
         <v>0</v>
@@ -3196,10 +3198,10 @@
       <c r="F74" s="25"/>
       <c r="G74" s="25"/>
       <c r="H74" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I74" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J74" s="25">
         <v>0</v>
@@ -3214,10 +3216,10 @@
       <c r="F75" s="25"/>
       <c r="G75" s="25"/>
       <c r="H75" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I75" s="25" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J75" s="25">
         <v>1</v>
@@ -3226,7 +3228,7 @@
     </row>
     <row r="76" spans="2:11">
       <c r="B76" s="42" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C76" s="43" t="b">
         <v>0</v>
@@ -3241,13 +3243,13 @@
         <v>55</v>
       </c>
       <c r="I76" s="44" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J76" s="44">
         <v>0</v>
       </c>
       <c r="K76" s="44" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="2:11">
@@ -3258,21 +3260,21 @@
       <c r="F77" s="44"/>
       <c r="G77" s="44"/>
       <c r="H77" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="I77" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="J77" s="44">
+        <v>1</v>
+      </c>
+      <c r="K77" s="44" t="s">
         <v>207</v>
-      </c>
-      <c r="I77" s="44" t="s">
-        <v>208</v>
-      </c>
-      <c r="J77" s="44">
-        <v>1</v>
-      </c>
-      <c r="K77" s="44" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="78" spans="2:11">
       <c r="B78" s="45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C78" s="46" t="b">
         <v>1</v>
@@ -3284,16 +3286,16 @@
       <c r="F78" s="26"/>
       <c r="G78" s="26"/>
       <c r="H78" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="I78" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="J78" s="39">
+        <v>1</v>
+      </c>
+      <c r="K78" s="26" t="s">
         <v>211</v>
-      </c>
-      <c r="I78" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="J78" s="39">
-        <v>1</v>
-      </c>
-      <c r="K78" s="26" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="79" spans="2:11">
@@ -3304,16 +3306,16 @@
       <c r="F79" s="26"/>
       <c r="G79" s="26"/>
       <c r="H79" s="26" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I79" s="26" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="J79" s="39">
         <v>2</v>
       </c>
       <c r="K79" s="26" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="2:11">
@@ -3324,16 +3326,16 @@
       <c r="F80" s="26"/>
       <c r="G80" s="26"/>
       <c r="H80" s="26" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I80" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J80" s="39">
         <v>4</v>
       </c>
       <c r="K80" s="26" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" spans="2:11">
@@ -3344,16 +3346,16 @@
       <c r="F81" s="26"/>
       <c r="G81" s="26"/>
       <c r="H81" s="26" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I81" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J81" s="39">
         <v>8</v>
       </c>
       <c r="K81" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="2:11">
@@ -3364,21 +3366,21 @@
       <c r="F82" s="26"/>
       <c r="G82" s="26"/>
       <c r="H82" s="26" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I82" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J82" s="39">
         <v>16</v>
       </c>
       <c r="K82" s="26" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="83" spans="2:11">
       <c r="B83" s="47" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C83" s="43" t="b">
         <v>0</v>
@@ -3390,16 +3392,16 @@
       <c r="F83" s="44"/>
       <c r="G83" s="44"/>
       <c r="H83" s="44" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I83" s="44" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J83" s="44">
         <v>1</v>
       </c>
       <c r="K83" s="44" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" spans="2:11">
@@ -3410,21 +3412,21 @@
       <c r="F84" s="44"/>
       <c r="G84" s="44"/>
       <c r="H84" s="44" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I84" s="44" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="J84" s="44">
         <v>2</v>
       </c>
       <c r="K84" s="44" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="26" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C85" s="46" t="b">
         <v>0</v>
@@ -3436,16 +3438,16 @@
       <c r="F85" s="26"/>
       <c r="G85" s="26"/>
       <c r="H85" s="48" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I85" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J85" s="26">
         <v>1</v>
       </c>
       <c r="K85" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="86" spans="2:11">
@@ -3456,16 +3458,16 @@
       <c r="F86" s="26"/>
       <c r="G86" s="26"/>
       <c r="H86" s="48" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I86" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="J86" s="26">
         <v>2</v>
       </c>
       <c r="K86" s="26" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="87" spans="2:11">
@@ -3476,21 +3478,21 @@
       <c r="F87" s="26"/>
       <c r="G87" s="26"/>
       <c r="H87" s="48" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I87" s="26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J87" s="26">
         <v>3</v>
       </c>
       <c r="K87" s="26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" spans="2:11">
       <c r="B88" s="49" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C88" s="50" t="b">
         <v>0</v>
@@ -3502,16 +3504,16 @@
       <c r="F88" s="49"/>
       <c r="G88" s="49"/>
       <c r="H88" s="51" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I88" s="49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J88" s="49">
         <v>1</v>
       </c>
       <c r="K88" s="49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="2:11">
@@ -3522,7 +3524,7 @@
       <c r="F89" s="49"/>
       <c r="G89" s="49"/>
       <c r="H89" s="51" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I89" s="49" t="s">
         <v>50</v>
@@ -3542,21 +3544,21 @@
       <c r="F90" s="49"/>
       <c r="G90" s="49"/>
       <c r="H90" s="51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I90" s="49" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J90" s="49">
         <v>3</v>
       </c>
       <c r="K90" s="49" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91" spans="2:11">
       <c r="B91" s="52" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C91" s="53" t="b">
         <v>0</v>
@@ -3568,10 +3570,10 @@
       <c r="F91" s="52"/>
       <c r="G91" s="52"/>
       <c r="H91" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="I91" s="54" t="s">
         <v>252</v>
-      </c>
-      <c r="I91" s="54" t="s">
-        <v>254</v>
       </c>
       <c r="J91" s="52"/>
       <c r="K91" s="54">
@@ -3586,10 +3588,10 @@
       <c r="F92" s="52"/>
       <c r="G92" s="52"/>
       <c r="H92" s="54" t="s">
+        <v>251</v>
+      </c>
+      <c r="I92" s="54" t="s">
         <v>253</v>
-      </c>
-      <c r="I92" s="54" t="s">
-        <v>255</v>
       </c>
       <c r="J92" s="52"/>
       <c r="K92" s="54">
@@ -3597,109 +3599,109 @@
       </c>
     </row>
     <row r="93" spans="2:11">
-      <c r="B93" s="56" t="s">
+      <c r="B93" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="C93" s="56" t="b">
+        <v>0</v>
+      </c>
+      <c r="D93" s="56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="55"/>
+      <c r="F93" s="55"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="57" t="s">
+        <v>240</v>
+      </c>
+      <c r="I93" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="J93" s="55">
+        <v>1</v>
+      </c>
+      <c r="K93" s="55" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="55"/>
+      <c r="C94" s="55"/>
+      <c r="D94" s="55"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="55"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="C93" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="D93" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="56"/>
-      <c r="F93" s="56"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="58" t="s">
+      <c r="I94" s="55" t="s">
+        <v>246</v>
+      </c>
+      <c r="J94" s="55">
+        <v>2</v>
+      </c>
+      <c r="K94" s="55" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="B95" s="55"/>
+      <c r="C95" s="55"/>
+      <c r="D95" s="55"/>
+      <c r="E95" s="55"/>
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="I93" s="56" t="s">
+      <c r="I95" s="55" t="s">
         <v>247</v>
       </c>
-      <c r="J93" s="56">
-        <v>1</v>
-      </c>
-      <c r="K93" s="56" t="s">
+      <c r="J95" s="55">
+        <v>3</v>
+      </c>
+      <c r="K95" s="55" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="94" spans="2:11">
-      <c r="B94" s="56"/>
-      <c r="C94" s="56"/>
-      <c r="D94" s="56"/>
-      <c r="E94" s="56"/>
-      <c r="F94" s="56"/>
-      <c r="G94" s="56"/>
-      <c r="H94" s="58" t="s">
+    <row r="96" spans="2:11">
+      <c r="B96" s="55"/>
+      <c r="C96" s="55"/>
+      <c r="D96" s="55"/>
+      <c r="E96" s="55"/>
+      <c r="F96" s="55"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="57" t="s">
         <v>243</v>
       </c>
-      <c r="I94" s="56" t="s">
+      <c r="I96" s="55" t="s">
         <v>248</v>
       </c>
-      <c r="J94" s="56">
-        <v>2</v>
-      </c>
-      <c r="K94" s="56" t="s">
+      <c r="J96" s="55">
+        <v>4</v>
+      </c>
+      <c r="K96" s="55" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="95" spans="2:11">
-      <c r="B95" s="56"/>
-      <c r="C95" s="56"/>
-      <c r="D95" s="56"/>
-      <c r="E95" s="56"/>
-      <c r="F95" s="56"/>
-      <c r="G95" s="56"/>
-      <c r="H95" s="58" t="s">
+    <row r="97" spans="2:11">
+      <c r="B97" s="55"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
+      <c r="E97" s="55"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="57" t="s">
         <v>244</v>
       </c>
-      <c r="I95" s="56" t="s">
+      <c r="I97" s="55" t="s">
         <v>249</v>
       </c>
-      <c r="J95" s="56">
-        <v>3</v>
-      </c>
-      <c r="K95" s="56" t="s">
+      <c r="J97" s="55">
+        <v>5</v>
+      </c>
+      <c r="K97" s="55" t="s">
         <v>249</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11">
-      <c r="B96" s="56"/>
-      <c r="C96" s="56"/>
-      <c r="D96" s="56"/>
-      <c r="E96" s="56"/>
-      <c r="F96" s="56"/>
-      <c r="G96" s="56"/>
-      <c r="H96" s="58" t="s">
-        <v>245</v>
-      </c>
-      <c r="I96" s="56" t="s">
-        <v>250</v>
-      </c>
-      <c r="J96" s="56">
-        <v>4</v>
-      </c>
-      <c r="K96" s="56" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11">
-      <c r="B97" s="56"/>
-      <c r="C97" s="56"/>
-      <c r="D97" s="56"/>
-      <c r="E97" s="56"/>
-      <c r="F97" s="56"/>
-      <c r="G97" s="56"/>
-      <c r="H97" s="58" t="s">
-        <v>246</v>
-      </c>
-      <c r="I97" s="56" t="s">
-        <v>251</v>
-      </c>
-      <c r="J97" s="56">
-        <v>5</v>
-      </c>
-      <c r="K97" s="56" t="s">
-        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,29 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30580" windowHeight="18810" tabRatio="500"/>
+    <workbookView windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783652431" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783652431" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783652431" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783652431"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="274">
   <si>
     <t>##var</t>
   </si>
@@ -839,86 +843,196 @@
   </si>
   <si>
     <t>周边货物</t>
+  </si>
+  <si>
+    <t>Doll</t>
+  </si>
+  <si>
+    <t>娃娃</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="23">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652431" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652431" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652431" ulstyle="none" kern="1">
-            <pm:latin face="微软雅黑" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652431" ulstyle="none" kern="1">
-            <pm:latin face="Arial Unicode MS" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="48">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -929,528 +1043,292 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE1EFD8"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00E1EFD8" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE697"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE697"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="0000B0F0" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="0070AD47" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACB9CA"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4AF82"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00F4AF82" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4AF82"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00F4AF82" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC5DFB3"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00C5DFB3" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5DFB3"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00C5DFB3" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6E0B4"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00C6E0B4" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB4C6E7"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00B4C6E7" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA8D08C"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00A8D08C" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8D08C"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00A8D08C" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70AD47"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="0070AD47" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8CAAB"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00F8CAAB" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8CAAB"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00F8CAAB" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8EA9DB"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8EA9DB"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7E7E7E"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="007E7E7E" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7E7E7E"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="007E7E7E" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652431" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="47">
+  <borders count="21">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1465,207 +1343,87 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1680,290 +1438,7 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1978,250 +1453,7 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -2236,211 +1468,253 @@
       <bottom style="thin">
         <color rgb="FF1F2329"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="none">
-        <color rgb="FF000000"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="none">
-        <color rgb="FF000000"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431">
-            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
-          </pm:border>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652431"/>
-        </ext>
-      </extLst>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2448,199 +1722,224 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="22" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="28" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="30" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="32" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="33" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="34" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="39" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="23" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="39" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="23" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="40" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="41" borderId="40" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="42" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="42" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="44" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="45" borderId="44" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0"/>
   <extLst>
-    <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783652431" count="1">
-        <pm:charStyle name="普通" fontId="0" Id="1"/>
-      </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783652431" count="19">
-        <pm:color name="颜色 24" rgb="E1EFD8"/>
-        <pm:color name="20% 灰色" rgb="000000"/>
-        <pm:color name="颜色 26" rgb="FFE697"/>
-        <pm:color name="颜色 27" rgb="BDD7EE"/>
-        <pm:color name="颜色 28" rgb="00B0F0"/>
-        <pm:color name="颜色 29" rgb="70AD47"/>
-        <pm:color name="颜色 30" rgb="ACB9CA"/>
-        <pm:color name="颜色 31" rgb="4472C4"/>
-        <pm:color name="颜色 32" rgb="F4AF82"/>
-        <pm:color name="颜色 33" rgb="C5DFB3"/>
-        <pm:color name="颜色 34" rgb="C6E0B4"/>
-        <pm:color name="颜色 35" rgb="B4C6E7"/>
-        <pm:color name="颜色 36" rgb="A8D08C"/>
-        <pm:color name="颜色 37" rgb="A5A5A5"/>
-        <pm:color name="颜色 38" rgb="F8CAAB"/>
-        <pm:color name="颜色 39" rgb="8EA9DB"/>
-        <pm:color name="颜色 40" rgb="7E7E7E"/>
-        <pm:color name="颜色 41" rgb="DEE0E3"/>
-        <pm:color name="颜色 42" rgb="1F2329"/>
-      </pm:colors>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2870,9 +2169,6 @@
     <a:spDef>
       <a:spPr/>
       <a:bodyPr>
-        <a:prstTxWarp prst="textNoShape">
-          <a:avLst/>
-        </a:prstTxWarp>
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2896,27 +2192,27 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:L104"/>
-  <sheetFormatPr defaultRowHeight="16.55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L106"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.000000" style="1"/>
-    <col min="2" max="2" width="27.077586" customWidth="1" style="1"/>
-    <col min="3" max="3" width="20.827586" customWidth="1" style="1"/>
-    <col min="4" max="4" width="19.000000" customWidth="1" style="1"/>
-    <col min="5" max="5" width="14.077586" customWidth="1" style="1"/>
-    <col min="6" max="6" width="9.327586" customWidth="1" style="1"/>
-    <col min="7" max="7" width="5.000000" customWidth="1" style="1"/>
-    <col min="8" max="8" width="38.663793" customWidth="1" style="1"/>
-    <col min="9" max="9" width="22.327586" customWidth="1" style="1"/>
-    <col min="10" max="10" width="12.077586" customWidth="1" style="1"/>
-    <col min="11" max="11" width="55.250000" customWidth="1" style="1"/>
-    <col min="12" max="16384" width="9.000000" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="27.075" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.825" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.075" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.325" style="1" customWidth="1"/>
+    <col min="7" max="7" width="5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.325" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.075" style="1" customWidth="1"/>
+    <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -2975,7 +2271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -3005,7 +2301,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="1:12">
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
@@ -3024,14 +2320,14 @@
       <c r="I4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="5">
         <v>1</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:11">
+    <row r="5" spans="1:12">
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -3044,14 +2340,14 @@
       <c r="I5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="8">
         <v>2</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="1:12">
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -3064,14 +2360,14 @@
       <c r="I6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="J6" s="8">
         <v>3</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="1:12">
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -3084,14 +2380,14 @@
       <c r="I7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="8">
         <v>4</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="1:12">
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -3104,14 +2400,14 @@
       <c r="I8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="8">
         <v>5</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="1:12">
       <c r="B9" s="10"/>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -3124,14 +2420,14 @@
       <c r="I9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="11">
         <v>6</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="1:12">
       <c r="B10" s="13" t="s">
         <v>32</v>
       </c>
@@ -3150,14 +2446,14 @@
       <c r="I10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="5">
         <v>1</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="1:12">
       <c r="B11" s="10"/>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -3170,14 +2466,14 @@
       <c r="I11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="11">
         <v>2</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="2:11">
+    <row r="12" spans="1:12">
       <c r="B12" s="14" t="s">
         <v>39</v>
       </c>
@@ -3192,14 +2488,14 @@
       <c r="I12" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="15">
         <v>1</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="2:11">
+    <row r="13" spans="1:12">
       <c r="B13" s="17"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -3212,14 +2508,14 @@
       <c r="I13" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="18">
         <v>2</v>
       </c>
       <c r="K13" s="19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="1:12">
       <c r="B14" s="20"/>
       <c r="C14" s="21"/>
       <c r="D14" s="21"/>
@@ -3232,14 +2528,14 @@
       <c r="I14" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="21">
         <v>3</v>
       </c>
       <c r="K14" s="22" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="1:12">
       <c r="B15" s="23" t="s">
         <v>48</v>
       </c>
@@ -3258,14 +2554,14 @@
       <c r="I15" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="23" t="n">
+      <c r="J15" s="23">
         <v>1</v>
       </c>
       <c r="K15" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="2:11">
+    <row r="16" spans="1:12">
       <c r="B16" s="23"/>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
@@ -3278,7 +2574,7 @@
       <c r="I16" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="23" t="n">
+      <c r="J16" s="23">
         <v>2</v>
       </c>
       <c r="K16" s="23" t="s">
@@ -3298,7 +2594,7 @@
       <c r="I17" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="J17" s="23" t="n">
+      <c r="J17" s="23">
         <v>0</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -3324,7 +2620,7 @@
       <c r="I18" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="J18" s="24" t="n">
+      <c r="J18" s="24">
         <v>1</v>
       </c>
       <c r="K18" s="24" t="s">
@@ -3344,7 +2640,7 @@
       <c r="I19" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="24" t="n">
+      <c r="J19" s="24">
         <v>2</v>
       </c>
       <c r="K19" s="24" t="s">
@@ -3364,7 +2660,7 @@
       <c r="I20" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="J20" s="24" t="n">
+      <c r="J20" s="24">
         <v>3</v>
       </c>
       <c r="K20" s="24" t="s">
@@ -3384,7 +2680,7 @@
       <c r="I21" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="J21" s="24" t="n">
+      <c r="J21" s="24">
         <v>4</v>
       </c>
       <c r="K21" s="24" t="s">
@@ -3404,7 +2700,7 @@
       <c r="I22" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="24" t="n">
+      <c r="J22" s="24">
         <v>5</v>
       </c>
       <c r="K22" s="24" t="s">
@@ -3424,7 +2720,7 @@
       <c r="I23" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="J23" s="24" t="n">
+      <c r="J23" s="24">
         <v>6</v>
       </c>
       <c r="K23" s="24" t="s">
@@ -3444,7 +2740,7 @@
       <c r="I24" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="J24" s="24" t="n">
+      <c r="J24" s="24">
         <v>7</v>
       </c>
       <c r="K24" s="24" t="s">
@@ -3464,7 +2760,7 @@
       <c r="I25" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="J25" s="24" t="n">
+      <c r="J25" s="24">
         <v>8</v>
       </c>
       <c r="K25" s="24" t="s">
@@ -3490,7 +2786,7 @@
       <c r="I26" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="J26" s="25" t="n">
+      <c r="J26" s="25">
         <v>0</v>
       </c>
       <c r="K26" s="25" t="s">
@@ -3510,7 +2806,7 @@
       <c r="I27" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="J27" s="25" t="n">
+      <c r="J27" s="25">
         <v>1</v>
       </c>
       <c r="K27" s="25" t="s">
@@ -3530,7 +2826,7 @@
       <c r="I28" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="J28" s="25" t="n">
+      <c r="J28" s="25">
         <v>2</v>
       </c>
       <c r="K28" s="25" t="s">
@@ -3550,7 +2846,7 @@
       <c r="I29" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="J29" s="25" t="n">
+      <c r="J29" s="25">
         <v>3</v>
       </c>
       <c r="K29" s="25" t="s">
@@ -3576,7 +2872,7 @@
       <c r="I30" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="J30" s="29" t="n">
+      <c r="J30" s="29">
         <v>0</v>
       </c>
       <c r="K30" s="29" t="s">
@@ -3596,7 +2892,7 @@
       <c r="I31" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="J31" s="29" t="n">
+      <c r="J31" s="29">
         <v>1</v>
       </c>
       <c r="K31" s="29" t="s">
@@ -3616,7 +2912,7 @@
       <c r="I32" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="J32" s="29" t="n">
+      <c r="J32" s="29">
         <v>2</v>
       </c>
       <c r="K32" s="29" t="s">
@@ -3636,7 +2932,7 @@
       <c r="I33" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="J33" s="29" t="n">
+      <c r="J33" s="29">
         <v>3</v>
       </c>
       <c r="K33" s="29" t="s">
@@ -3662,7 +2958,7 @@
       <c r="I34" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="J34" s="30" t="n">
+      <c r="J34" s="30">
         <v>1</v>
       </c>
       <c r="K34" s="30" t="s">
@@ -3682,7 +2978,7 @@
       <c r="I35" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="J35" s="30" t="n">
+      <c r="J35" s="30">
         <v>2</v>
       </c>
       <c r="K35" s="30" t="s">
@@ -3702,7 +2998,7 @@
       <c r="I36" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="J36" s="30" t="n">
+      <c r="J36" s="30">
         <v>3</v>
       </c>
       <c r="K36" s="30" t="s">
@@ -3728,7 +3024,7 @@
       <c r="I37" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="J37" s="32" t="n">
+      <c r="J37" s="32">
         <v>0</v>
       </c>
       <c r="K37" s="32" t="s">
@@ -3748,7 +3044,7 @@
       <c r="I38" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="J38" s="32" t="n">
+      <c r="J38" s="32">
         <v>1</v>
       </c>
       <c r="K38" s="32" t="s">
@@ -3769,7 +3065,7 @@
         <v>106</v>
       </c>
       <c r="J39" s="32">
-        <f>J38*2</f>
+        <f t="shared" ref="J39:J60" si="0">J38*2</f>
         <v>2</v>
       </c>
       <c r="K39" s="32" t="s">
@@ -3790,7 +3086,7 @@
         <v>109</v>
       </c>
       <c r="J40" s="32">
-        <f>J39*2</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="K40" s="32" t="s">
@@ -3811,7 +3107,7 @@
         <v>112</v>
       </c>
       <c r="J41" s="32">
-        <f>J40*2</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="K41" s="32" t="s">
@@ -3832,7 +3128,7 @@
         <v>115</v>
       </c>
       <c r="J42" s="32">
-        <f>J41*2</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="K42" s="32" t="s">
@@ -3853,7 +3149,7 @@
         <v>118</v>
       </c>
       <c r="J43" s="32">
-        <f>J42*2</f>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="K43" s="32" t="s">
@@ -3874,7 +3170,7 @@
         <v>121</v>
       </c>
       <c r="J44" s="32">
-        <f>J43*2</f>
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="K44" s="32" t="s">
@@ -3895,7 +3191,7 @@
         <v>124</v>
       </c>
       <c r="J45" s="32">
-        <f>J44*2</f>
+        <f t="shared" si="0"/>
         <v>128</v>
       </c>
       <c r="K45" s="32" t="s">
@@ -3916,7 +3212,7 @@
         <v>127</v>
       </c>
       <c r="J46" s="32">
-        <f>J45*2</f>
+        <f t="shared" si="0"/>
         <v>256</v>
       </c>
       <c r="K46" s="32" t="s">
@@ -3937,7 +3233,7 @@
         <v>130</v>
       </c>
       <c r="J47" s="32">
-        <f>J46*2</f>
+        <f t="shared" si="0"/>
         <v>512</v>
       </c>
       <c r="K47" s="32" t="s">
@@ -3958,7 +3254,7 @@
         <v>133</v>
       </c>
       <c r="J48" s="32">
-        <f>J47*2</f>
+        <f t="shared" si="0"/>
         <v>1024</v>
       </c>
       <c r="K48" s="32" t="s">
@@ -3979,7 +3275,7 @@
         <v>136</v>
       </c>
       <c r="J49" s="32">
-        <f>J48*2</f>
+        <f t="shared" si="0"/>
         <v>2048</v>
       </c>
       <c r="K49" s="32" t="s">
@@ -4000,7 +3296,7 @@
         <v>139</v>
       </c>
       <c r="J50" s="32">
-        <f>J49*2</f>
+        <f t="shared" si="0"/>
         <v>4096</v>
       </c>
       <c r="K50" s="32" t="s">
@@ -4021,7 +3317,7 @@
         <v>142</v>
       </c>
       <c r="J51" s="32">
-        <f>J50*2</f>
+        <f t="shared" si="0"/>
         <v>8192</v>
       </c>
       <c r="K51" s="32" t="s">
@@ -4042,7 +3338,7 @@
         <v>145</v>
       </c>
       <c r="J52" s="32">
-        <f>J51*2</f>
+        <f t="shared" si="0"/>
         <v>16384</v>
       </c>
       <c r="K52" s="32" t="s">
@@ -4063,7 +3359,7 @@
         <v>148</v>
       </c>
       <c r="J53" s="32">
-        <f>J52*2</f>
+        <f t="shared" si="0"/>
         <v>32768</v>
       </c>
       <c r="K53" s="32" t="s">
@@ -4084,7 +3380,7 @@
         <v>151</v>
       </c>
       <c r="J54" s="32">
-        <f>J53*2</f>
+        <f t="shared" si="0"/>
         <v>65536</v>
       </c>
       <c r="K54" s="32" t="s">
@@ -4105,7 +3401,7 @@
         <v>154</v>
       </c>
       <c r="J55" s="32">
-        <f>J54*2</f>
+        <f t="shared" si="0"/>
         <v>131072</v>
       </c>
       <c r="K55" s="32" t="s">
@@ -4126,7 +3422,7 @@
         <v>157</v>
       </c>
       <c r="J56" s="32">
-        <f>J55*2</f>
+        <f t="shared" si="0"/>
         <v>262144</v>
       </c>
       <c r="K56" s="32" t="s">
@@ -4147,7 +3443,7 @@
         <v>160</v>
       </c>
       <c r="J57" s="34">
-        <f>J56*2</f>
+        <f t="shared" si="0"/>
         <v>524288</v>
       </c>
       <c r="K57" s="34" t="s">
@@ -4168,7 +3464,7 @@
         <v>163</v>
       </c>
       <c r="J58" s="34">
-        <f>J57*2</f>
+        <f t="shared" si="0"/>
         <v>1048576</v>
       </c>
       <c r="K58" s="34" t="s">
@@ -4189,7 +3485,7 @@
         <v>166</v>
       </c>
       <c r="J59" s="34">
-        <f>J58*2</f>
+        <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
       <c r="K59" s="34" t="s">
@@ -4210,7 +3506,7 @@
         <v>169</v>
       </c>
       <c r="J60" s="34">
-        <f>J59*2</f>
+        <f t="shared" si="0"/>
         <v>4194304</v>
       </c>
       <c r="K60" s="34" t="s">
@@ -4236,7 +3532,7 @@
       <c r="I61" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="J61" s="32" t="n">
+      <c r="J61" s="32">
         <v>1</v>
       </c>
       <c r="K61" s="35" t="s">
@@ -4256,7 +3552,7 @@
       <c r="I62" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="J62" s="32" t="n">
+      <c r="J62" s="32">
         <v>2</v>
       </c>
       <c r="K62" s="35" t="s">
@@ -4276,7 +3572,7 @@
       <c r="I63" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="J63" s="32" t="n">
+      <c r="J63" s="32">
         <v>4</v>
       </c>
       <c r="K63" s="35" t="s">
@@ -4296,7 +3592,7 @@
       <c r="I64" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="J64" s="32" t="n">
+      <c r="J64" s="32">
         <v>8</v>
       </c>
       <c r="K64" s="35" t="s">
@@ -4316,7 +3612,7 @@
       <c r="I65" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="J65" s="32" t="n">
+      <c r="J65" s="32">
         <v>15</v>
       </c>
       <c r="K65" s="35" t="s">
@@ -4342,7 +3638,7 @@
       <c r="I66" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="J66" s="36" t="n">
+      <c r="J66" s="36">
         <v>1</v>
       </c>
       <c r="K66" s="36" t="s">
@@ -4362,7 +3658,7 @@
       <c r="I67" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="J67" s="36" t="n">
+      <c r="J67" s="36">
         <v>2</v>
       </c>
       <c r="K67" s="36" t="s">
@@ -4382,7 +3678,7 @@
       <c r="I68" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="J68" s="36" t="n">
+      <c r="J68" s="36">
         <v>4</v>
       </c>
       <c r="K68" s="36" t="s">
@@ -4402,7 +3698,7 @@
       <c r="I69" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="J69" s="36" t="n">
+      <c r="J69" s="36">
         <v>8</v>
       </c>
       <c r="K69" s="36" t="s">
@@ -4422,7 +3718,7 @@
       <c r="I70" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="J70" s="36" t="n">
+      <c r="J70" s="36">
         <v>16</v>
       </c>
       <c r="K70" s="36" t="s">
@@ -4442,7 +3738,7 @@
       <c r="I71" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="J71" s="36" t="n">
+      <c r="J71" s="36">
         <v>32</v>
       </c>
       <c r="K71" s="36" t="s">
@@ -4462,7 +3758,7 @@
       <c r="I72" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="J72" s="36" t="n">
+      <c r="J72" s="36">
         <v>64</v>
       </c>
       <c r="K72" s="36" t="s">
@@ -4482,7 +3778,7 @@
       <c r="I73" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="J73" s="36" t="n">
+      <c r="J73" s="36">
         <v>127</v>
       </c>
       <c r="K73" s="36" t="s">
@@ -4508,7 +3804,7 @@
       <c r="I74" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="J74" s="24" t="n">
+      <c r="J74" s="24">
         <v>0</v>
       </c>
       <c r="K74" s="24"/>
@@ -4526,7 +3822,7 @@
       <c r="I75" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="J75" s="24" t="n">
+      <c r="J75" s="24">
         <v>1</v>
       </c>
       <c r="K75" s="24"/>
@@ -4550,7 +3846,7 @@
       <c r="I76" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="J76" s="41" t="n">
+      <c r="J76" s="41">
         <v>0</v>
       </c>
       <c r="K76" s="41" t="s">
@@ -4570,7 +3866,7 @@
       <c r="I77" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="J77" s="41" t="n">
+      <c r="J77" s="41">
         <v>1</v>
       </c>
       <c r="K77" s="41" t="s">
@@ -4596,7 +3892,7 @@
       <c r="I78" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="J78" s="36" t="n">
+      <c r="J78" s="36">
         <v>1</v>
       </c>
       <c r="K78" s="25" t="s">
@@ -4616,7 +3912,7 @@
       <c r="I79" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="J79" s="36" t="n">
+      <c r="J79" s="36">
         <v>2</v>
       </c>
       <c r="K79" s="25" t="s">
@@ -4636,7 +3932,7 @@
       <c r="I80" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="J80" s="36" t="n">
+      <c r="J80" s="36">
         <v>4</v>
       </c>
       <c r="K80" s="25" t="s">
@@ -4656,7 +3952,7 @@
       <c r="I81" s="25" t="s">
         <v>221</v>
       </c>
-      <c r="J81" s="36" t="n">
+      <c r="J81" s="36">
         <v>8</v>
       </c>
       <c r="K81" s="25" t="s">
@@ -4676,7 +3972,7 @@
       <c r="I82" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="J82" s="36" t="n">
+      <c r="J82" s="36">
         <v>16</v>
       </c>
       <c r="K82" s="25" t="s">
@@ -4702,7 +3998,7 @@
       <c r="I83" s="41" t="s">
         <v>226</v>
       </c>
-      <c r="J83" s="41" t="n">
+      <c r="J83" s="41">
         <v>1</v>
       </c>
       <c r="K83" s="41" t="s">
@@ -4722,7 +4018,7 @@
       <c r="I84" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="J84" s="41" t="n">
+      <c r="J84" s="41">
         <v>2</v>
       </c>
       <c r="K84" s="41" t="s">
@@ -4748,7 +4044,7 @@
       <c r="I85" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="J85" s="25" t="n">
+      <c r="J85" s="25">
         <v>1</v>
       </c>
       <c r="K85" s="25" t="s">
@@ -4768,7 +4064,7 @@
       <c r="I86" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="J86" s="25" t="n">
+      <c r="J86" s="25">
         <v>2</v>
       </c>
       <c r="K86" s="25" t="s">
@@ -4788,7 +4084,7 @@
       <c r="I87" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="J87" s="25" t="n">
+      <c r="J87" s="25">
         <v>3</v>
       </c>
       <c r="K87" s="25" t="s">
@@ -4814,7 +4110,7 @@
       <c r="I88" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="J88" s="45" t="n">
+      <c r="J88" s="45">
         <v>1</v>
       </c>
       <c r="K88" s="45" t="s">
@@ -4834,7 +4130,7 @@
       <c r="I89" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="J89" s="45" t="n">
+      <c r="J89" s="45">
         <v>2</v>
       </c>
       <c r="K89" s="45" t="s">
@@ -4854,7 +4150,7 @@
       <c r="I90" s="45" t="s">
         <v>239</v>
       </c>
-      <c r="J90" s="45" t="n">
+      <c r="J90" s="45">
         <v>3</v>
       </c>
       <c r="K90" s="45" t="s">
@@ -4881,7 +4177,7 @@
         <v>242</v>
       </c>
       <c r="J91" s="48"/>
-      <c r="K91" s="50" t="n">
+      <c r="K91" s="50">
         <v>0</v>
       </c>
     </row>
@@ -4899,7 +4195,7 @@
         <v>244</v>
       </c>
       <c r="J92" s="48"/>
-      <c r="K92" s="50" t="n">
+      <c r="K92" s="50">
         <v>1</v>
       </c>
     </row>
@@ -4922,7 +4218,7 @@
       <c r="I93" s="51" t="s">
         <v>247</v>
       </c>
-      <c r="J93" s="51" t="n">
+      <c r="J93" s="51">
         <v>1</v>
       </c>
       <c r="K93" s="51" t="s">
@@ -4942,7 +4238,7 @@
       <c r="I94" s="51" t="s">
         <v>249</v>
       </c>
-      <c r="J94" s="51" t="n">
+      <c r="J94" s="51">
         <v>2</v>
       </c>
       <c r="K94" s="51" t="s">
@@ -4962,7 +4258,7 @@
       <c r="I95" s="51" t="s">
         <v>251</v>
       </c>
-      <c r="J95" s="51" t="n">
+      <c r="J95" s="51">
         <v>3</v>
       </c>
       <c r="K95" s="51" t="s">
@@ -4982,7 +4278,7 @@
       <c r="I96" s="51" t="s">
         <v>253</v>
       </c>
-      <c r="J96" s="51" t="n">
+      <c r="J96" s="51">
         <v>4</v>
       </c>
       <c r="K96" s="51" t="s">
@@ -5002,7 +4298,7 @@
       <c r="I97" s="51" t="s">
         <v>255</v>
       </c>
-      <c r="J97" s="51" t="n">
+      <c r="J97" s="51">
         <v>5</v>
       </c>
       <c r="K97" s="51" t="s">
@@ -5025,21 +4321,21 @@
       <c r="I98" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="J98" s="1" t="n">
+      <c r="J98" s="1">
         <v>1</v>
       </c>
       <c r="K98" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="99" spans="8:11">
+    <row r="99" spans="2:11">
       <c r="H99" s="1" t="s">
         <v>259</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="J99" s="1" t="n">
+      <c r="J99" s="1">
         <v>2</v>
       </c>
       <c r="K99" s="1" t="s">
@@ -5062,35 +4358,35 @@
       <c r="I100" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="J100" s="1" t="n">
+      <c r="J100" s="1">
         <v>1</v>
       </c>
       <c r="K100" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="101" spans="8:11">
+    <row r="101" spans="2:11">
       <c r="H101" s="1" t="s">
         <v>264</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="J101" s="1" t="n">
+      <c r="J101" s="1">
         <v>2</v>
       </c>
       <c r="K101" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="102" spans="8:11">
+    <row r="102" spans="2:11">
       <c r="H102" s="54" t="s">
         <v>266</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="J102" s="1" t="n">
+      <c r="J102" s="1">
         <v>3</v>
       </c>
       <c r="K102" s="1" t="s">
@@ -5110,57 +4406,61 @@
       <c r="I103" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J103" s="1" t="n">
+      <c r="J103" s="1">
         <v>4</v>
       </c>
       <c r="K103" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="104" spans="8:11">
+    <row r="104" spans="2:11">
       <c r="H104" s="1" t="s">
         <v>270</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="J104" s="1" t="n">
+      <c r="J104" s="1">
         <v>5</v>
       </c>
       <c r="K104" s="1" t="s">
         <v>271</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11">
+      <c r="H105" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J105" s="1">
+        <v>6</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
+      <c r="H106" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J106" s="1">
+        <v>7</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>258</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783652431" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783652431" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783652431" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783652431" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783652431" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
-  <extLst>
-    <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783652431" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
-        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
-        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
-      </pm:sheetPrefs>
-    </ext>
-  </extLst>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE115C2C-F51D-42E2-BC7F-69623933CEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="278">
   <si>
     <t>##var</t>
   </si>
@@ -849,19 +855,29 @@
   </si>
   <si>
     <t>娃娃</t>
+  </si>
+  <si>
+    <t>食材</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认材料</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认材料类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -872,167 +888,22 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="49">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1135,194 +1006,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1470,255 +1155,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1743,7 +1186,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1773,7 +1216,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1788,13 +1231,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1806,28 +1249,28 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1842,104 +1285,63 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2192,25 +1594,25 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L106"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.075" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.825" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.075" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.325" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.325" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.075" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -2237,13 +1639,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -2271,7 +1673,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -4353,44 +3755,44 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="J100" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="2:11">
       <c r="H101" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J101" s="1">
+        <v>1</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11">
+      <c r="H102" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I102" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="J101" s="1">
+      <c r="J102" s="1">
         <v>2</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="K102" s="1" t="s">
         <v>265</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11">
-      <c r="H102" s="54" t="s">
-        <v>266</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="J102" s="1">
-        <v>3</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="103" spans="2:11">
@@ -4401,66 +3803,80 @@
       <c r="F103"/>
       <c r="G103"/>
       <c r="H103" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J103" s="1">
+        <v>3</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="H104" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="I104" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J103" s="1">
+      <c r="J104" s="1">
         <v>4</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="K104" s="1" t="s">
         <v>269</v>
-      </c>
-    </row>
-    <row r="104" spans="2:11">
-      <c r="H104" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="J104" s="1">
-        <v>5</v>
-      </c>
-      <c r="K104" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="105" spans="2:11">
       <c r="H105" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J105" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="106" spans="2:11">
       <c r="H106" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J106" s="1">
+        <v>6</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11">
+      <c r="H107" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="I106" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="J106" s="1">
+      <c r="I107" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J107" s="1">
         <v>7</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>258</v>
+      <c r="K107" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE115C2C-F51D-42E2-BC7F-69623933CEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="287">
   <si>
     <t>##var</t>
   </si>
@@ -821,6 +815,12 @@
     <t>ItemMaterialType</t>
   </si>
   <si>
+    <t>默认材料</t>
+  </si>
+  <si>
+    <t>默认材料类型</t>
+  </si>
+  <si>
     <t>Recipe</t>
   </si>
   <si>
@@ -858,26 +858,49 @@
   </si>
   <si>
     <t>食材</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>默认材料</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>默认材料类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cloth</t>
+  </si>
+  <si>
+    <t>布料</t>
+  </si>
+  <si>
+    <t>FishingGear</t>
+  </si>
+  <si>
+    <t>渔具</t>
+  </si>
+  <si>
+    <t>FishingBait</t>
+  </si>
+  <si>
+    <t>鱼饵</t>
+  </si>
+  <si>
+    <t>AdultProduct</t>
+  </si>
+  <si>
+    <t>情趣用品</t>
+  </si>
+  <si>
+    <t>ShopSpecialItem</t>
+  </si>
+  <si>
+    <t>商店特殊道具</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -888,22 +911,167 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1006,8 +1174,194 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1155,13 +1509,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1327,21 +1923,62 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1594,25 +2231,25 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L107"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.0833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -1639,13 +2276,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1673,7 +2310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -3755,44 +4392,44 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="J100" s="1">
         <v>0</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
     </row>
     <row r="101" spans="2:11">
       <c r="H101" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J101" s="1">
         <v>1</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="102" spans="2:11">
       <c r="H102" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J102" s="1">
         <v>2</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="103" spans="2:11">
@@ -3803,58 +4440,58 @@
       <c r="F103"/>
       <c r="G103"/>
       <c r="H103" s="54" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J103" s="1">
         <v>3</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="2:11">
       <c r="H104" s="54" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J104" s="1">
         <v>4</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="2:11">
       <c r="H105" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J105" s="1">
         <v>5</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="106" spans="2:11">
       <c r="H106" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J106" s="1">
         <v>6</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107" spans="2:11">
@@ -3862,21 +4499,91 @@
         <v>257</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="J107" s="1">
         <v>7</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11">
+      <c r="H108" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J108" s="1">
+        <v>8</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11">
+      <c r="H109" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J109" s="1">
+        <v>9</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11">
+      <c r="H110" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J110" s="1">
+        <v>10</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11">
+      <c r="H111" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J111" s="1">
+        <v>11</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11">
+      <c r="H112" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J112" s="1">
+        <v>12</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868674FD-D686-427B-BC30-AB34DCF766CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500"/>
+    <workbookView xWindow="3200" yWindow="630" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="291">
   <si>
     <t>##var</t>
   </si>
@@ -752,155 +758,166 @@
     <t>ItemType</t>
   </si>
   <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t>Consumables</t>
+  </si>
+  <si>
+    <t>消耗品</t>
+  </si>
+  <si>
+    <t>ItemQuality</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>高级</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>稀有</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>神器</t>
+  </si>
+  <si>
+    <t>SSR</t>
+  </si>
+  <si>
+    <t>史诗</t>
+  </si>
+  <si>
+    <t>ItemConsumType</t>
+  </si>
+  <si>
+    <t>Ingredient</t>
+  </si>
+  <si>
+    <t>食材道具</t>
+  </si>
+  <si>
+    <t>Food</t>
+  </si>
+  <si>
+    <t>食物道具</t>
+  </si>
+  <si>
+    <t>ItemMaterialType</t>
+  </si>
+  <si>
+    <t>默认材料</t>
+  </si>
+  <si>
+    <t>默认材料类型</t>
+  </si>
+  <si>
+    <t>Recipe</t>
+  </si>
+  <si>
+    <t>配方道具</t>
+  </si>
+  <si>
+    <t>FigureModel</t>
+  </si>
+  <si>
+    <t>手办模型/模具框架</t>
+  </si>
+  <si>
+    <t>Painting</t>
+  </si>
+  <si>
+    <t>绘画贴纸（女主产出）</t>
+  </si>
+  <si>
+    <t>FactoryProductionMaterials</t>
+  </si>
+  <si>
+    <t>工厂生产资料（框架+贴纸合成产物）</t>
+  </si>
+  <si>
+    <t>Merchandise</t>
+  </si>
+  <si>
+    <t>周边货物</t>
+  </si>
+  <si>
+    <t>Doll</t>
+  </si>
+  <si>
+    <t>娃娃</t>
+  </si>
+  <si>
+    <t>食材</t>
+  </si>
+  <si>
+    <t>Cloth</t>
+  </si>
+  <si>
+    <t>布料</t>
+  </si>
+  <si>
+    <t>FishingGear</t>
+  </si>
+  <si>
+    <t>渔具</t>
+  </si>
+  <si>
+    <t>FishingBait</t>
+  </si>
+  <si>
+    <t>鱼饵</t>
+  </si>
+  <si>
+    <t>AdultProduct</t>
+  </si>
+  <si>
+    <t>情趣用品</t>
+  </si>
+  <si>
+    <t>ShopSpecialItem</t>
+  </si>
+  <si>
+    <t>商店特殊道具</t>
+  </si>
+  <si>
     <t>Material</t>
-  </si>
-  <si>
-    <t>材料</t>
-  </si>
-  <si>
-    <t>Consumables</t>
-  </si>
-  <si>
-    <t>消耗品</t>
-  </si>
-  <si>
-    <t>ItemQuality</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>高级</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>稀有</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>神器</t>
-  </si>
-  <si>
-    <t>SSR</t>
-  </si>
-  <si>
-    <t>史诗</t>
-  </si>
-  <si>
-    <t>ItemConsumType</t>
-  </si>
-  <si>
-    <t>Ingredient</t>
-  </si>
-  <si>
-    <t>食材道具</t>
-  </si>
-  <si>
-    <t>Food</t>
-  </si>
-  <si>
-    <t>食物道具</t>
-  </si>
-  <si>
-    <t>ItemMaterialType</t>
-  </si>
-  <si>
-    <t>默认材料</t>
-  </si>
-  <si>
-    <t>默认材料类型</t>
-  </si>
-  <si>
-    <t>Recipe</t>
-  </si>
-  <si>
-    <t>配方道具</t>
-  </si>
-  <si>
-    <t>FigureModel</t>
-  </si>
-  <si>
-    <t>手办模型/模具框架</t>
-  </si>
-  <si>
-    <t>Painting</t>
-  </si>
-  <si>
-    <t>绘画贴纸（女主产出）</t>
-  </si>
-  <si>
-    <t>FactoryProductionMaterials</t>
-  </si>
-  <si>
-    <t>工厂生产资料（框架+贴纸合成产物）</t>
-  </si>
-  <si>
-    <t>Merchandise</t>
-  </si>
-  <si>
-    <t>周边货物</t>
-  </si>
-  <si>
-    <t>Doll</t>
-  </si>
-  <si>
-    <t>娃娃</t>
-  </si>
-  <si>
-    <t>食材</t>
-  </si>
-  <si>
-    <t>Cloth</t>
-  </si>
-  <si>
-    <t>布料</t>
-  </si>
-  <si>
-    <t>FishingGear</t>
-  </si>
-  <si>
-    <t>渔具</t>
-  </si>
-  <si>
-    <t>FishingBait</t>
-  </si>
-  <si>
-    <t>鱼饵</t>
-  </si>
-  <si>
-    <t>AdultProduct</t>
-  </si>
-  <si>
-    <t>情趣用品</t>
-  </si>
-  <si>
-    <t>ShopSpecialItem</t>
-  </si>
-  <si>
-    <t>商店特殊道具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定无变化材料</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定可以使用的道具</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Runtime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>动态材料</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -911,167 +928,22 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="49">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1174,194 +1046,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1509,255 +1195,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1923,62 +1367,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2231,25 +1634,25 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L112"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.0833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -2276,13 +1679,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -2310,7 +1713,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -4210,14 +3613,16 @@
       <c r="F91" s="48"/>
       <c r="G91" s="48"/>
       <c r="H91" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="I91" s="50" t="s">
         <v>241</v>
       </c>
-      <c r="I91" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="J91" s="48"/>
-      <c r="K91" s="50">
+      <c r="J91" s="50">
         <v>0</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="92" spans="2:11">
@@ -4228,60 +3633,62 @@
       <c r="F92" s="48"/>
       <c r="G92" s="48"/>
       <c r="H92" s="50" t="s">
+        <v>242</v>
+      </c>
+      <c r="I92" s="50" t="s">
         <v>243</v>
       </c>
-      <c r="I92" s="50" t="s">
+      <c r="J92" s="50">
+        <v>1</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" s="48"/>
+      <c r="C93" s="48"/>
+      <c r="D93" s="48"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="48"/>
+      <c r="G93" s="48"/>
+      <c r="H93" s="50" t="s">
+        <v>289</v>
+      </c>
+      <c r="I93" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="J93" s="50">
+        <v>2</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="51" t="s">
         <v>244</v>
       </c>
-      <c r="J92" s="48"/>
-      <c r="K92" s="50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
-      <c r="B93" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="C93" s="52" t="b">
+      <c r="C94" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="D93" s="52" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="51"/>
-      <c r="F93" s="51"/>
-      <c r="G93" s="51"/>
-      <c r="H93" s="53" t="s">
-        <v>246</v>
-      </c>
-      <c r="I93" s="51" t="s">
-        <v>247</v>
-      </c>
-      <c r="J93" s="51">
-        <v>1</v>
-      </c>
-      <c r="K93" s="51" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11">
-      <c r="B94" s="51"/>
-      <c r="C94" s="51"/>
-      <c r="D94" s="51"/>
+      <c r="D94" s="52" t="b">
+        <v>1</v>
+      </c>
       <c r="E94" s="51"/>
       <c r="F94" s="51"/>
       <c r="G94" s="51"/>
       <c r="H94" s="53" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I94" s="51" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J94" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" s="51" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="95" spans="2:11">
@@ -4292,16 +3699,16 @@
       <c r="F95" s="51"/>
       <c r="G95" s="51"/>
       <c r="H95" s="53" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I95" s="51" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="J95" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K95" s="51" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="96" spans="2:11">
@@ -4312,16 +3719,16 @@
       <c r="F96" s="51"/>
       <c r="G96" s="51"/>
       <c r="H96" s="53" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="I96" s="51" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="J96" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K96" s="51" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="97" spans="2:11">
@@ -4332,258 +3739,278 @@
       <c r="F97" s="51"/>
       <c r="G97" s="51"/>
       <c r="H97" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="I97" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="J97" s="51">
+        <v>4</v>
+      </c>
+      <c r="K97" s="51" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11">
+      <c r="B98" s="51"/>
+      <c r="C98" s="51"/>
+      <c r="D98" s="51"/>
+      <c r="E98" s="51"/>
+      <c r="F98" s="51"/>
+      <c r="G98" s="51"/>
+      <c r="H98" s="53" t="s">
+        <v>253</v>
+      </c>
+      <c r="I98" s="51" t="s">
         <v>254</v>
       </c>
-      <c r="I97" s="51" t="s">
+      <c r="J98" s="51">
+        <v>5</v>
+      </c>
+      <c r="K98" s="51" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
+      <c r="B99" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="J97" s="51">
-        <v>5</v>
-      </c>
-      <c r="K97" s="51" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11">
-      <c r="B98" s="1" t="s">
+      <c r="C99" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="D99" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H99" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C98" s="49" t="b">
+      <c r="I99" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J99" s="1">
+        <v>1</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11">
+      <c r="H100" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="J100" s="1">
+        <v>2</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11">
+      <c r="B101" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C101" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D98" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="J98" s="1">
-        <v>1</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11">
-      <c r="H99" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J99" s="1">
-        <v>2</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11">
-      <c r="B100" s="1" t="s">
+      <c r="D101" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I101" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C100" s="49" t="b">
+      <c r="J101" s="1">
         <v>0</v>
       </c>
-      <c r="D100" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I100" s="1" t="s">
+      <c r="K101" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="J100" s="1">
-        <v>0</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11">
-      <c r="H101" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="J101" s="1">
-        <v>1</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="102" spans="2:11">
       <c r="H102" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J102" s="1">
+        <v>1</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="H103" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I103" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="J103" s="1">
+        <v>2</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="J102" s="1">
-        <v>2</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11">
-      <c r="B103"/>
-      <c r="C103"/>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103"/>
-      <c r="H103" s="54" t="s">
+      <c r="I104" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="J104" s="1">
+        <v>3</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11">
+      <c r="H105" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="J103" s="1">
-        <v>3</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="104" spans="2:11">
-      <c r="H104" s="54" t="s">
+      <c r="I105" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="I104" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="J104" s="1">
+      <c r="J105" s="1">
         <v>4</v>
       </c>
-      <c r="K104" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="105" spans="2:11">
-      <c r="H105" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="I105" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="J105" s="1">
-        <v>5</v>
-      </c>
       <c r="K105" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106" spans="2:11">
       <c r="H106" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="J106" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="107" spans="2:11">
       <c r="H107" s="1" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J107" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="108" spans="2:11">
       <c r="H108" s="1" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="J108" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="109" spans="2:11">
       <c r="H109" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J109" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="110" spans="2:11">
       <c r="H110" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="J110" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="111" spans="2:11">
       <c r="H111" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J111" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="H112" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J112" s="1">
+        <v>11</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="113" spans="8:11">
+      <c r="H113" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="I113" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="I112" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="J112" s="1">
+      <c r="J113" s="1">
         <v>12</v>
       </c>
-      <c r="K112" s="1" t="s">
-        <v>286</v>
+      <c r="K113" s="1" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868674FD-D686-427B-BC30-AB34DCF766CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB71C82-39BB-424A-9D93-477B198EF326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3200" yWindow="630" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="293">
   <si>
     <t>##var</t>
   </si>
@@ -910,6 +910,14 @@
   </si>
   <si>
     <t>动态材料</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FenCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉丝数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1640,7 +1648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2210,49 +2218,43 @@
       </c>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="25" t="s">
+      <c r="H26" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J26" s="1">
+        <v>9</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="26" t="b">
+      <c r="C27" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D26" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="J26" s="25">
-        <v>0</v>
-      </c>
-      <c r="K26" s="25" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11">
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
+      <c r="D27" s="26" t="b">
+        <v>1</v>
+      </c>
       <c r="E27" s="25"/>
       <c r="F27" s="25"/>
       <c r="G27" s="25"/>
       <c r="H27" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J27" s="25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="2:11">
@@ -2263,16 +2265,16 @@
       <c r="F28" s="25"/>
       <c r="G28" s="25"/>
       <c r="H28" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J28" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="2:11">
@@ -2283,62 +2285,62 @@
       <c r="F29" s="25"/>
       <c r="G29" s="25"/>
       <c r="H29" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="25">
+        <v>2</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="I29" s="25" t="s">
+      <c r="I30" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="J29" s="25">
+      <c r="J30" s="25">
         <v>3</v>
       </c>
-      <c r="K29" s="25" t="s">
+      <c r="K30" s="25" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="27" t="s">
+    <row r="31" spans="2:11">
+      <c r="B31" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="28" t="b">
+      <c r="C31" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="D30" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="I30" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="J30" s="29">
-        <v>0</v>
-      </c>
-      <c r="K30" s="29" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
+      <c r="D31" s="28" t="b">
+        <v>1</v>
+      </c>
       <c r="E31" s="29"/>
       <c r="F31" s="29"/>
       <c r="G31" s="29"/>
       <c r="H31" s="29" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I31" s="29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J31" s="29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="2:11">
@@ -2349,16 +2351,16 @@
       <c r="F32" s="29"/>
       <c r="G32" s="29"/>
       <c r="H32" s="29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I32" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J32" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -2369,62 +2371,62 @@
       <c r="F33" s="29"/>
       <c r="G33" s="29"/>
       <c r="H33" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="J33" s="29">
+        <v>2</v>
+      </c>
+      <c r="K33" s="29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="I33" s="29" t="s">
+      <c r="I34" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="J33" s="29">
+      <c r="J34" s="29">
         <v>3</v>
       </c>
-      <c r="K33" s="29" t="s">
+      <c r="K34" s="29" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="30" t="s">
+    <row r="35" spans="2:11">
+      <c r="B35" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C34" s="31" t="b">
+      <c r="C35" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="D34" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="I34" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="J34" s="30">
-        <v>1</v>
-      </c>
-      <c r="K34" s="30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="31" t="b">
+        <v>1</v>
+      </c>
       <c r="E35" s="30"/>
       <c r="F35" s="30"/>
       <c r="G35" s="30"/>
       <c r="H35" s="30" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I35" s="30" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J35" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K35" s="30" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -2435,62 +2437,62 @@
       <c r="F36" s="30"/>
       <c r="G36" s="30"/>
       <c r="H36" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="I36" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="J36" s="30">
+        <v>2</v>
+      </c>
+      <c r="K36" s="30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="I36" s="30" t="s">
+      <c r="I37" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="J36" s="30">
+      <c r="J37" s="30">
         <v>3</v>
       </c>
-      <c r="K36" s="30" t="s">
+      <c r="K37" s="30" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="37" spans="2:11">
-      <c r="B37" s="32" t="s">
+    <row r="38" spans="2:11">
+      <c r="B38" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="D37" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="I37" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="J37" s="32">
-        <v>0</v>
-      </c>
-      <c r="K37" s="32" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
+      <c r="C38" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" s="33" t="b">
+        <v>1</v>
+      </c>
       <c r="E38" s="32"/>
       <c r="F38" s="32"/>
       <c r="G38" s="32"/>
       <c r="H38" s="32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I38" s="32" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J38" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="32" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="2:11">
@@ -2501,17 +2503,16 @@
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
       <c r="H39" s="32" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I39" s="32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J39" s="32">
-        <f t="shared" ref="J39:J60" si="0">J38*2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K39" s="32" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -2522,17 +2523,17 @@
       <c r="F40" s="32"/>
       <c r="G40" s="32"/>
       <c r="H40" s="32" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J40" s="32">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" ref="J40:J61" si="0">J39*2</f>
+        <v>2</v>
       </c>
       <c r="K40" s="32" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="2:11">
@@ -2543,17 +2544,17 @@
       <c r="F41" s="32"/>
       <c r="G41" s="32"/>
       <c r="H41" s="32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I41" s="32" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J41" s="32">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K41" s="32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="2:11">
@@ -2564,17 +2565,17 @@
       <c r="F42" s="32"/>
       <c r="G42" s="32"/>
       <c r="H42" s="32" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I42" s="32" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J42" s="32">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K42" s="32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" spans="2:11">
@@ -2585,17 +2586,17 @@
       <c r="F43" s="32"/>
       <c r="G43" s="32"/>
       <c r="H43" s="32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I43" s="32" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J43" s="32">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K43" s="32" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="2:11">
@@ -2606,17 +2607,17 @@
       <c r="F44" s="32"/>
       <c r="G44" s="32"/>
       <c r="H44" s="32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I44" s="32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J44" s="32">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K44" s="32" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="2:11">
@@ -2627,17 +2628,17 @@
       <c r="F45" s="32"/>
       <c r="G45" s="32"/>
       <c r="H45" s="32" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I45" s="32" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="J45" s="32">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K45" s="32" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="2:11">
@@ -2648,17 +2649,17 @@
       <c r="F46" s="32"/>
       <c r="G46" s="32"/>
       <c r="H46" s="32" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I46" s="32" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J46" s="32">
         <f t="shared" si="0"/>
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="K46" s="32" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="2:11">
@@ -2669,17 +2670,17 @@
       <c r="F47" s="32"/>
       <c r="G47" s="32"/>
       <c r="H47" s="32" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I47" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J47" s="32">
         <f t="shared" si="0"/>
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="K47" s="32" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="2:11">
@@ -2690,17 +2691,17 @@
       <c r="F48" s="32"/>
       <c r="G48" s="32"/>
       <c r="H48" s="32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I48" s="32" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="0"/>
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="K48" s="32" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="2:11">
@@ -2711,17 +2712,17 @@
       <c r="F49" s="32"/>
       <c r="G49" s="32"/>
       <c r="H49" s="32" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I49" s="32" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J49" s="32">
         <f t="shared" si="0"/>
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="50" spans="2:11">
@@ -2732,17 +2733,17 @@
       <c r="F50" s="32"/>
       <c r="G50" s="32"/>
       <c r="H50" s="32" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I50" s="32" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J50" s="32">
         <f t="shared" si="0"/>
-        <v>4096</v>
+        <v>2048</v>
       </c>
       <c r="K50" s="32" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51" spans="2:11">
@@ -2753,59 +2754,59 @@
       <c r="F51" s="32"/>
       <c r="G51" s="32"/>
       <c r="H51" s="32" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I51" s="32" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J51" s="32">
         <f t="shared" si="0"/>
-        <v>8192</v>
+        <v>4096</v>
       </c>
       <c r="K51" s="32" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="2:11">
       <c r="B52" s="32"/>
       <c r="C52" s="32"/>
       <c r="D52" s="32"/>
-      <c r="E52" s="34"/>
+      <c r="E52" s="32"/>
       <c r="F52" s="32"/>
       <c r="G52" s="32"/>
       <c r="H52" s="32" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I52" s="32" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J52" s="32">
         <f t="shared" si="0"/>
-        <v>16384</v>
+        <v>8192</v>
       </c>
       <c r="K52" s="32" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="2:11">
       <c r="B53" s="32"/>
       <c r="C53" s="32"/>
       <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
+      <c r="E53" s="34"/>
       <c r="F53" s="32"/>
       <c r="G53" s="32"/>
       <c r="H53" s="32" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I53" s="32" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J53" s="32">
         <f t="shared" si="0"/>
-        <v>32768</v>
+        <v>16384</v>
       </c>
       <c r="K53" s="32" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="2:11">
@@ -2816,17 +2817,17 @@
       <c r="F54" s="32"/>
       <c r="G54" s="32"/>
       <c r="H54" s="32" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I54" s="32" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J54" s="32">
         <f t="shared" si="0"/>
-        <v>65536</v>
+        <v>32768</v>
       </c>
       <c r="K54" s="32" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="2:11">
@@ -2837,59 +2838,59 @@
       <c r="F55" s="32"/>
       <c r="G55" s="32"/>
       <c r="H55" s="32" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I55" s="32" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>131072</v>
+        <v>65536</v>
       </c>
       <c r="K55" s="32" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="2:11">
       <c r="B56" s="32"/>
-      <c r="C56" s="34"/>
+      <c r="C56" s="32"/>
       <c r="D56" s="32"/>
       <c r="E56" s="32"/>
       <c r="F56" s="32"/>
       <c r="G56" s="32"/>
       <c r="H56" s="32" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I56" s="32" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J56" s="32">
         <f t="shared" si="0"/>
+        <v>131072</v>
+      </c>
+      <c r="K56" s="32" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
+      <c r="B57" s="32"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="I57" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="J57" s="32">
+        <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K56" s="32" t="s">
+      <c r="K57" s="32" t="s">
         <v>158</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="34"/>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="34"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="I57" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="J57" s="34">
-        <f t="shared" si="0"/>
-        <v>524288</v>
-      </c>
-      <c r="K57" s="34" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="58" spans="2:11">
@@ -2900,17 +2901,17 @@
       <c r="F58" s="34"/>
       <c r="G58" s="34"/>
       <c r="H58" s="34" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I58" s="34" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J58" s="34">
         <f t="shared" si="0"/>
-        <v>1048576</v>
+        <v>524288</v>
       </c>
       <c r="K58" s="34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="2:11">
@@ -2921,17 +2922,17 @@
       <c r="F59" s="34"/>
       <c r="G59" s="34"/>
       <c r="H59" s="34" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I59" s="34" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J59" s="34">
         <f t="shared" si="0"/>
-        <v>2097152</v>
+        <v>1048576</v>
       </c>
       <c r="K59" s="34" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="2:11">
@@ -2942,63 +2943,64 @@
       <c r="F60" s="34"/>
       <c r="G60" s="34"/>
       <c r="H60" s="34" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I60" s="34" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J60" s="34">
         <f t="shared" si="0"/>
+        <v>2097152</v>
+      </c>
+      <c r="K60" s="34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="I61" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="J61" s="34">
+        <f t="shared" si="0"/>
         <v>4194304</v>
       </c>
-      <c r="K60" s="34" t="s">
+      <c r="K61" s="34" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="35" t="s">
+    <row r="62" spans="2:11">
+      <c r="B62" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="C61" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="D61" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="I61" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="J61" s="32">
-        <v>1</v>
-      </c>
-      <c r="K61" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="35"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
+      <c r="C62" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D62" s="33" t="b">
+        <v>1</v>
+      </c>
       <c r="E62" s="35"/>
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
       <c r="H62" s="35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I62" s="35" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J62" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K62" s="35" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="2:11">
@@ -3009,16 +3011,16 @@
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
       <c r="H63" s="35" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I63" s="35" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J63" s="32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K63" s="35" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="2:11">
@@ -3029,16 +3031,16 @@
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
       <c r="H64" s="35" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I64" s="35" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J64" s="32">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K64" s="35" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="2:11">
@@ -3049,62 +3051,62 @@
       <c r="F65" s="35"/>
       <c r="G65" s="35"/>
       <c r="H65" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="I65" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="J65" s="32">
+        <v>8</v>
+      </c>
+      <c r="K65" s="35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" s="35"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="I65" s="35" t="s">
+      <c r="I66" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J66" s="32">
         <v>15</v>
       </c>
-      <c r="K65" s="35" t="s">
+      <c r="K66" s="35" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="36" t="s">
+    <row r="67" spans="2:11">
+      <c r="B67" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="C66" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="D66" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-      <c r="G66" s="36"/>
-      <c r="H66" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="I66" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="J66" s="36">
-        <v>1</v>
-      </c>
-      <c r="K66" s="36" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="36"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
+      <c r="C67" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" s="37" t="b">
+        <v>1</v>
+      </c>
       <c r="E67" s="36"/>
       <c r="F67" s="36"/>
       <c r="G67" s="36"/>
       <c r="H67" s="36" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J67" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" s="36" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="68" spans="2:11">
@@ -3115,16 +3117,16 @@
       <c r="F68" s="36"/>
       <c r="G68" s="36"/>
       <c r="H68" s="36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J68" s="36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K68" s="36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="69" spans="2:11">
@@ -3135,16 +3137,16 @@
       <c r="F69" s="36"/>
       <c r="G69" s="36"/>
       <c r="H69" s="36" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J69" s="36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K69" s="36" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="2:11">
@@ -3155,16 +3157,16 @@
       <c r="F70" s="36"/>
       <c r="G70" s="36"/>
       <c r="H70" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J70" s="36">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K70" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="2:11">
@@ -3175,16 +3177,16 @@
       <c r="F71" s="36"/>
       <c r="G71" s="36"/>
       <c r="H71" s="36" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I71" s="36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J71" s="36">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K71" s="36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="2:11">
@@ -3195,16 +3197,16 @@
       <c r="F72" s="36"/>
       <c r="G72" s="36"/>
       <c r="H72" s="36" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I72" s="36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J72" s="36">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K72" s="36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="2:11">
@@ -3215,150 +3217,150 @@
       <c r="F73" s="36"/>
       <c r="G73" s="36"/>
       <c r="H73" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="I73" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="J73" s="36">
+        <v>64</v>
+      </c>
+      <c r="K73" s="36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="I73" s="36" t="s">
+      <c r="I74" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="J73" s="36">
+      <c r="J74" s="36">
         <v>127</v>
       </c>
-      <c r="K73" s="36" t="s">
+      <c r="K74" s="36" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="2:11">
-      <c r="B74" s="24" t="s">
+    <row r="75" spans="2:11">
+      <c r="B75" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="C74" s="38" t="b">
+      <c r="C75" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="D74" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="I74" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="J74" s="24">
-        <v>0</v>
-      </c>
-      <c r="K74" s="24"/>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
+      <c r="D75" s="38" t="b">
+        <v>1</v>
+      </c>
       <c r="E75" s="24"/>
       <c r="F75" s="24"/>
       <c r="G75" s="24"/>
       <c r="H75" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="I75" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="J75" s="24">
+        <v>0</v>
+      </c>
+      <c r="K75" s="24"/>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" s="24"/>
+      <c r="C76" s="24"/>
+      <c r="D76" s="24"/>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="I75" s="24" t="s">
+      <c r="I76" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="J75" s="24">
-        <v>1</v>
-      </c>
-      <c r="K75" s="24"/>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="39" t="s">
+      <c r="J76" s="24">
+        <v>1</v>
+      </c>
+      <c r="K76" s="24"/>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C76" s="40" t="b">
+      <c r="C77" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="D76" s="40" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" s="41"/>
-      <c r="F76" s="41"/>
-      <c r="G76" s="41"/>
-      <c r="H76" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="I76" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="J76" s="41">
-        <v>0</v>
-      </c>
-      <c r="K76" s="41" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77" s="41"/>
-      <c r="C77" s="41"/>
-      <c r="D77" s="41"/>
+      <c r="D77" s="40" t="b">
+        <v>1</v>
+      </c>
       <c r="E77" s="41"/>
       <c r="F77" s="41"/>
       <c r="G77" s="41"/>
       <c r="H77" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I77" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="J77" s="41">
+        <v>0</v>
+      </c>
+      <c r="K77" s="41" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" s="41"/>
+      <c r="C78" s="41"/>
+      <c r="D78" s="41"/>
+      <c r="E78" s="41"/>
+      <c r="F78" s="41"/>
+      <c r="G78" s="41"/>
+      <c r="H78" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="I77" s="41" t="s">
+      <c r="I78" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="J77" s="41">
-        <v>1</v>
-      </c>
-      <c r="K77" s="41" t="s">
+      <c r="J78" s="41">
+        <v>1</v>
+      </c>
+      <c r="K78" s="41" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="42" t="s">
+    <row r="79" spans="2:11">
+      <c r="B79" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="C78" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D78" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
-      <c r="G78" s="25"/>
-      <c r="H78" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="I78" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="J78" s="36">
-        <v>1</v>
-      </c>
-      <c r="K78" s="25" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="25"/>
+      <c r="C79" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" s="26" t="b">
+        <v>1</v>
+      </c>
       <c r="E79" s="25"/>
       <c r="F79" s="25"/>
       <c r="G79" s="25"/>
       <c r="H79" s="25" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I79" s="25" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J79" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79" s="25" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="2:11">
@@ -3369,16 +3371,16 @@
       <c r="F80" s="25"/>
       <c r="G80" s="25"/>
       <c r="H80" s="25" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I80" s="25" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J80" s="36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K80" s="25" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" spans="2:11">
@@ -3389,16 +3391,16 @@
       <c r="F81" s="25"/>
       <c r="G81" s="25"/>
       <c r="H81" s="25" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I81" s="25" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J81" s="36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K81" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="2:11">
@@ -3409,108 +3411,108 @@
       <c r="F82" s="25"/>
       <c r="G82" s="25"/>
       <c r="H82" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="I82" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="J82" s="36">
+        <v>8</v>
+      </c>
+      <c r="K82" s="25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="25"/>
+      <c r="G83" s="25"/>
+      <c r="H83" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="I82" s="25" t="s">
+      <c r="I83" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="J82" s="36">
+      <c r="J83" s="36">
         <v>16</v>
       </c>
-      <c r="K82" s="25" t="s">
+      <c r="K83" s="25" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="83" spans="2:11">
-      <c r="B83" s="43" t="s">
+    <row r="84" spans="2:11">
+      <c r="B84" s="43" t="s">
         <v>224</v>
       </c>
-      <c r="C83" s="40" t="b">
+      <c r="C84" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="D83" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="41"/>
-      <c r="F83" s="41"/>
-      <c r="G83" s="41"/>
-      <c r="H83" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="I83" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="J83" s="41">
-        <v>1</v>
-      </c>
-      <c r="K83" s="41" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84" s="41"/>
-      <c r="C84" s="41"/>
-      <c r="D84" s="41"/>
+      <c r="D84" s="26" t="b">
+        <v>1</v>
+      </c>
       <c r="E84" s="41"/>
       <c r="F84" s="41"/>
       <c r="G84" s="41"/>
       <c r="H84" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="I84" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J84" s="41">
+        <v>1</v>
+      </c>
+      <c r="K84" s="41" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" s="41"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="41"/>
+      <c r="E85" s="41"/>
+      <c r="F85" s="41"/>
+      <c r="G85" s="41"/>
+      <c r="H85" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="I84" s="41" t="s">
+      <c r="I85" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="J84" s="41">
+      <c r="J85" s="41">
         <v>2</v>
       </c>
-      <c r="K84" s="41" t="s">
+      <c r="K85" s="41" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="85" spans="2:11">
-      <c r="B85" s="25" t="s">
+    <row r="86" spans="2:11">
+      <c r="B86" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="C85" s="26" t="b">
+      <c r="C86" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D85" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="25"/>
-      <c r="F85" s="25"/>
-      <c r="G85" s="25"/>
-      <c r="H85" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="I85" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="J85" s="25">
-        <v>1</v>
-      </c>
-      <c r="K85" s="25" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="25"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="25"/>
+      <c r="D86" s="26" t="b">
+        <v>1</v>
+      </c>
       <c r="E86" s="25"/>
       <c r="F86" s="25"/>
       <c r="G86" s="25"/>
       <c r="H86" s="44" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="I86" s="25" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="J86" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K86" s="25" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
     </row>
     <row r="87" spans="2:11">
@@ -3521,62 +3523,62 @@
       <c r="F87" s="25"/>
       <c r="G87" s="25"/>
       <c r="H87" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="I87" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="J87" s="25">
+        <v>2</v>
+      </c>
+      <c r="K87" s="25" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="I87" s="25" t="s">
+      <c r="I88" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="J87" s="25">
+      <c r="J88" s="25">
         <v>3</v>
       </c>
-      <c r="K87" s="25" t="s">
+      <c r="K88" s="25" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="88" spans="2:11">
-      <c r="B88" s="45" t="s">
+    <row r="89" spans="2:11">
+      <c r="B89" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="C88" s="46" t="b">
+      <c r="C89" s="46" t="b">
         <v>0</v>
       </c>
-      <c r="D88" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="45"/>
-      <c r="F88" s="45"/>
-      <c r="G88" s="45"/>
-      <c r="H88" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="I88" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="J88" s="45">
-        <v>1</v>
-      </c>
-      <c r="K88" s="45" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
-      <c r="B89" s="45"/>
-      <c r="C89" s="45"/>
-      <c r="D89" s="45"/>
+      <c r="D89" s="46" t="b">
+        <v>1</v>
+      </c>
       <c r="E89" s="45"/>
       <c r="F89" s="45"/>
       <c r="G89" s="45"/>
       <c r="H89" s="47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I89" s="45" t="s">
-        <v>50</v>
+        <v>236</v>
       </c>
       <c r="J89" s="45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K89" s="45" t="s">
-        <v>50</v>
+        <v>236</v>
       </c>
     </row>
     <row r="90" spans="2:11">
@@ -3587,62 +3589,62 @@
       <c r="F90" s="45"/>
       <c r="G90" s="45"/>
       <c r="H90" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="I90" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="J90" s="45">
+        <v>2</v>
+      </c>
+      <c r="K90" s="45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="B91" s="45"/>
+      <c r="C91" s="45"/>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="45"/>
+      <c r="G91" s="45"/>
+      <c r="H91" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="I90" s="45" t="s">
+      <c r="I91" s="45" t="s">
         <v>239</v>
       </c>
-      <c r="J90" s="45">
+      <c r="J91" s="45">
         <v>3</v>
       </c>
-      <c r="K90" s="45" t="s">
+      <c r="K91" s="45" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="91" spans="2:11">
-      <c r="B91" s="48" t="s">
+    <row r="92" spans="2:11">
+      <c r="B92" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="C91" s="49" t="b">
+      <c r="C92" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D91" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="48"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="48"/>
-      <c r="H91" s="50" t="s">
-        <v>286</v>
-      </c>
-      <c r="I91" s="50" t="s">
-        <v>241</v>
-      </c>
-      <c r="J91" s="50">
-        <v>0</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11">
-      <c r="B92" s="48"/>
-      <c r="C92" s="48"/>
-      <c r="D92" s="48"/>
+      <c r="D92" s="49" t="b">
+        <v>1</v>
+      </c>
       <c r="E92" s="48"/>
       <c r="F92" s="48"/>
       <c r="G92" s="48"/>
       <c r="H92" s="50" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="I92" s="50" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J92" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="93" spans="2:11">
@@ -3653,62 +3655,62 @@
       <c r="F93" s="48"/>
       <c r="G93" s="48"/>
       <c r="H93" s="50" t="s">
+        <v>242</v>
+      </c>
+      <c r="I93" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="J93" s="50">
+        <v>1</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="48"/>
+      <c r="C94" s="48"/>
+      <c r="D94" s="48"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+      <c r="H94" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="I93" s="50" t="s">
+      <c r="I94" s="50" t="s">
         <v>290</v>
       </c>
-      <c r="J93" s="50">
+      <c r="J94" s="50">
         <v>2</v>
       </c>
-      <c r="K93" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="94" spans="2:11">
-      <c r="B94" s="51" t="s">
+    <row r="95" spans="2:11">
+      <c r="B95" s="51" t="s">
         <v>244</v>
       </c>
-      <c r="C94" s="52" t="b">
+      <c r="C95" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="D94" s="52" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" s="51"/>
-      <c r="F94" s="51"/>
-      <c r="G94" s="51"/>
-      <c r="H94" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="I94" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="J94" s="51">
-        <v>1</v>
-      </c>
-      <c r="K94" s="51" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11">
-      <c r="B95" s="51"/>
-      <c r="C95" s="51"/>
-      <c r="D95" s="51"/>
+      <c r="D95" s="52" t="b">
+        <v>1</v>
+      </c>
       <c r="E95" s="51"/>
       <c r="F95" s="51"/>
       <c r="G95" s="51"/>
       <c r="H95" s="53" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I95" s="51" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J95" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" s="51" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="96" spans="2:11">
@@ -3719,16 +3721,16 @@
       <c r="F96" s="51"/>
       <c r="G96" s="51"/>
       <c r="H96" s="53" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I96" s="51" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J96" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K96" s="51" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="97" spans="2:11">
@@ -3739,16 +3741,16 @@
       <c r="F97" s="51"/>
       <c r="G97" s="51"/>
       <c r="H97" s="53" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I97" s="51" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J97" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K97" s="51" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="98" spans="2:11">
@@ -3759,252 +3761,273 @@
       <c r="F98" s="51"/>
       <c r="G98" s="51"/>
       <c r="H98" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="I98" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="J98" s="51">
+        <v>4</v>
+      </c>
+      <c r="K98" s="51" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
+      <c r="B99" s="51"/>
+      <c r="C99" s="51"/>
+      <c r="D99" s="51"/>
+      <c r="E99" s="51"/>
+      <c r="F99" s="51"/>
+      <c r="G99" s="51"/>
+      <c r="H99" s="53" t="s">
         <v>253</v>
       </c>
-      <c r="I98" s="51" t="s">
+      <c r="I99" s="51" t="s">
         <v>254</v>
       </c>
-      <c r="J98" s="51">
+      <c r="J99" s="51">
         <v>5</v>
       </c>
-      <c r="K98" s="51" t="s">
+      <c r="K99" s="51" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="99" spans="2:11">
-      <c r="B99" s="1" t="s">
+    <row r="100" spans="2:11">
+      <c r="B100" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C99" s="49" t="b">
+      <c r="C100" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D99" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H99" s="1" t="s">
+      <c r="D100" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I99" s="1" t="s">
+      <c r="I100" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="J99" s="1">
-        <v>1</v>
-      </c>
-      <c r="K99" s="1" t="s">
+      <c r="J100" s="1">
+        <v>1</v>
+      </c>
+      <c r="K100" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="100" spans="2:11">
-      <c r="H100" s="1" t="s">
+    <row r="101" spans="2:11">
+      <c r="H101" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="I101" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="J100" s="1">
+      <c r="J101" s="1">
         <v>2</v>
       </c>
-      <c r="K100" s="1" t="s">
+      <c r="K101" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="101" spans="2:11">
-      <c r="B101" s="1" t="s">
+    <row r="102" spans="2:11">
+      <c r="B102" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C101" s="49" t="b">
+      <c r="C102" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D101" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H101" s="1" t="s">
+      <c r="D102" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H102" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I102" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J101" s="1">
+      <c r="J102" s="1">
         <v>0</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="K102" s="1" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11">
-      <c r="H102" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="J102" s="1">
-        <v>1</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="103" spans="2:11">
       <c r="H103" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J103" s="1">
+        <v>1</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="H104" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="I104" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="J103" s="1">
+      <c r="J104" s="1">
         <v>2</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="K104" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="104" spans="2:11">
-      <c r="B104"/>
-      <c r="C104"/>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104" s="54" t="s">
+    <row r="105" spans="2:11">
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="I104" s="1" t="s">
+      <c r="I105" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J104" s="1">
+      <c r="J105" s="1">
         <v>3</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="K105" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="105" spans="2:11">
-      <c r="H105" s="54" t="s">
+    <row r="106" spans="2:11">
+      <c r="H106" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="I105" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J105" s="1">
+      <c r="J106" s="1">
         <v>4</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="K106" s="1" t="s">
         <v>270</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11">
-      <c r="H106" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="J106" s="1">
-        <v>5</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="107" spans="2:11">
       <c r="H107" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J107" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="108" spans="2:11">
       <c r="H108" s="1" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J108" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="109" spans="2:11">
       <c r="H109" s="1" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J109" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="110" spans="2:11">
       <c r="H110" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J110" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="111" spans="2:11">
       <c r="H111" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J111" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="H112" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J112" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="113" spans="8:11">
       <c r="H113" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J113" s="1">
+        <v>11</v>
+      </c>
+      <c r="K113" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="114" spans="8:11">
+      <c r="H114" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I113" s="1" t="s">
+      <c r="I114" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="J113" s="1">
+      <c r="J114" s="1">
         <v>12</v>
       </c>
-      <c r="K113" s="1" t="s">
+      <c r="K114" s="1" t="s">
         <v>285</v>
       </c>
     </row>
+    <row r="129" s="1" customFormat="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB71C82-39BB-424A-9D93-477B198EF326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5931D23D-324B-4F62-AA59-C3AE5A963E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6740" yWindow="2280" windowWidth="30580" windowHeight="17170" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="295">
   <si>
     <t>##var</t>
   </si>
@@ -918,6 +918,14 @@
   </si>
   <si>
     <t>粉丝数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FanGrowthRate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>粉丝增长系数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1648,7 +1656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2232,49 +2240,43 @@
       </c>
     </row>
     <row r="27" spans="2:11">
-      <c r="B27" s="25" t="s">
+      <c r="H27" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="J27" s="1">
+        <v>10</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="26" t="b">
+      <c r="C28" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D27" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="I27" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="J27" s="25">
-        <v>0</v>
-      </c>
-      <c r="K27" s="25" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11">
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
+      <c r="D28" s="26" t="b">
+        <v>1</v>
+      </c>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
       <c r="G28" s="25"/>
       <c r="H28" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J28" s="25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" s="25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="2:11">
@@ -2285,16 +2287,16 @@
       <c r="F29" s="25"/>
       <c r="G29" s="25"/>
       <c r="H29" s="25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J29" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -2305,62 +2307,62 @@
       <c r="F30" s="25"/>
       <c r="G30" s="25"/>
       <c r="H30" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="J30" s="25">
+        <v>2</v>
+      </c>
+      <c r="K30" s="25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="I30" s="25" t="s">
+      <c r="I31" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="J30" s="25">
+      <c r="J31" s="25">
         <v>3</v>
       </c>
-      <c r="K30" s="25" t="s">
+      <c r="K31" s="25" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="27" t="s">
+    <row r="32" spans="2:11">
+      <c r="B32" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="C31" s="28" t="b">
+      <c r="C32" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="D31" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29" t="s">
-        <v>80</v>
-      </c>
-      <c r="I31" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="J31" s="29">
-        <v>0</v>
-      </c>
-      <c r="K31" s="29" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
+      <c r="D32" s="28" t="b">
+        <v>1</v>
+      </c>
       <c r="E32" s="29"/>
       <c r="F32" s="29"/>
       <c r="G32" s="29"/>
       <c r="H32" s="29" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I32" s="29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J32" s="29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -2371,16 +2373,16 @@
       <c r="F33" s="29"/>
       <c r="G33" s="29"/>
       <c r="H33" s="29" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J33" s="29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" s="29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -2391,62 +2393,62 @@
       <c r="F34" s="29"/>
       <c r="G34" s="29"/>
       <c r="H34" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="I34" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="J34" s="29">
+        <v>2</v>
+      </c>
+      <c r="K34" s="29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I35" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="J34" s="29">
+      <c r="J35" s="29">
         <v>3</v>
       </c>
-      <c r="K34" s="29" t="s">
+      <c r="K35" s="29" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="30" t="s">
+    <row r="36" spans="2:11">
+      <c r="B36" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="31" t="b">
+      <c r="C36" s="31" t="b">
         <v>0</v>
       </c>
-      <c r="D35" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="I35" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="J35" s="30">
-        <v>1</v>
-      </c>
-      <c r="K35" s="30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
+      <c r="D36" s="31" t="b">
+        <v>1</v>
+      </c>
       <c r="E36" s="30"/>
       <c r="F36" s="30"/>
       <c r="G36" s="30"/>
       <c r="H36" s="30" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I36" s="30" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="J36" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" s="30" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -2457,62 +2459,62 @@
       <c r="F37" s="30"/>
       <c r="G37" s="30"/>
       <c r="H37" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="I37" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="J37" s="30">
+        <v>2</v>
+      </c>
+      <c r="K37" s="30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="I37" s="30" t="s">
+      <c r="I38" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="J37" s="30">
+      <c r="J38" s="30">
         <v>3</v>
       </c>
-      <c r="K37" s="30" t="s">
+      <c r="K38" s="30" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="32" t="s">
+    <row r="39" spans="2:11">
+      <c r="B39" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="D38" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="I38" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="J38" s="32">
-        <v>0</v>
-      </c>
-      <c r="K38" s="32" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
+      <c r="C39" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" s="33" t="b">
+        <v>1</v>
+      </c>
       <c r="E39" s="32"/>
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
       <c r="H39" s="32" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I39" s="32" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J39" s="32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" s="32" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -2523,17 +2525,16 @@
       <c r="F40" s="32"/>
       <c r="G40" s="32"/>
       <c r="H40" s="32" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="J40" s="32">
-        <f t="shared" ref="J40:J61" si="0">J39*2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="32" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="2:11">
@@ -2544,17 +2545,17 @@
       <c r="F41" s="32"/>
       <c r="G41" s="32"/>
       <c r="H41" s="32" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I41" s="32" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J41" s="32">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" ref="J41:J62" si="0">J40*2</f>
+        <v>2</v>
       </c>
       <c r="K41" s="32" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="2:11">
@@ -2565,17 +2566,17 @@
       <c r="F42" s="32"/>
       <c r="G42" s="32"/>
       <c r="H42" s="32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I42" s="32" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J42" s="32">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K42" s="32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="2:11">
@@ -2586,17 +2587,17 @@
       <c r="F43" s="32"/>
       <c r="G43" s="32"/>
       <c r="H43" s="32" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I43" s="32" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="J43" s="32">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K43" s="32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="2:11">
@@ -2607,17 +2608,17 @@
       <c r="F44" s="32"/>
       <c r="G44" s="32"/>
       <c r="H44" s="32" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I44" s="32" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="J44" s="32">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K44" s="32" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="2:11">
@@ -2628,17 +2629,17 @@
       <c r="F45" s="32"/>
       <c r="G45" s="32"/>
       <c r="H45" s="32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I45" s="32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="J45" s="32">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K45" s="32" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="2:11">
@@ -2649,17 +2650,17 @@
       <c r="F46" s="32"/>
       <c r="G46" s="32"/>
       <c r="H46" s="32" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I46" s="32" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="J46" s="32">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K46" s="32" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="2:11">
@@ -2670,17 +2671,17 @@
       <c r="F47" s="32"/>
       <c r="G47" s="32"/>
       <c r="H47" s="32" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I47" s="32" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J47" s="32">
         <f t="shared" si="0"/>
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="K47" s="32" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="2:11">
@@ -2691,17 +2692,17 @@
       <c r="F48" s="32"/>
       <c r="G48" s="32"/>
       <c r="H48" s="32" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I48" s="32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="0"/>
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="K48" s="32" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="2:11">
@@ -2712,17 +2713,17 @@
       <c r="F49" s="32"/>
       <c r="G49" s="32"/>
       <c r="H49" s="32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I49" s="32" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="J49" s="32">
         <f t="shared" si="0"/>
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="2:11">
@@ -2733,17 +2734,17 @@
       <c r="F50" s="32"/>
       <c r="G50" s="32"/>
       <c r="H50" s="32" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I50" s="32" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J50" s="32">
         <f t="shared" si="0"/>
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="K50" s="32" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="2:11">
@@ -2754,17 +2755,17 @@
       <c r="F51" s="32"/>
       <c r="G51" s="32"/>
       <c r="H51" s="32" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I51" s="32" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J51" s="32">
         <f t="shared" si="0"/>
-        <v>4096</v>
+        <v>2048</v>
       </c>
       <c r="K51" s="32" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="52" spans="2:11">
@@ -2775,59 +2776,59 @@
       <c r="F52" s="32"/>
       <c r="G52" s="32"/>
       <c r="H52" s="32" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I52" s="32" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J52" s="32">
         <f t="shared" si="0"/>
-        <v>8192</v>
+        <v>4096</v>
       </c>
       <c r="K52" s="32" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="2:11">
       <c r="B53" s="32"/>
       <c r="C53" s="32"/>
       <c r="D53" s="32"/>
-      <c r="E53" s="34"/>
+      <c r="E53" s="32"/>
       <c r="F53" s="32"/>
       <c r="G53" s="32"/>
       <c r="H53" s="32" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I53" s="32" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J53" s="32">
         <f t="shared" si="0"/>
-        <v>16384</v>
+        <v>8192</v>
       </c>
       <c r="K53" s="32" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="54" spans="2:11">
       <c r="B54" s="32"/>
       <c r="C54" s="32"/>
       <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
+      <c r="E54" s="34"/>
       <c r="F54" s="32"/>
       <c r="G54" s="32"/>
       <c r="H54" s="32" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I54" s="32" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J54" s="32">
         <f t="shared" si="0"/>
-        <v>32768</v>
+        <v>16384</v>
       </c>
       <c r="K54" s="32" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="2:11">
@@ -2838,17 +2839,17 @@
       <c r="F55" s="32"/>
       <c r="G55" s="32"/>
       <c r="H55" s="32" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="I55" s="32" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
-        <v>65536</v>
+        <v>32768</v>
       </c>
       <c r="K55" s="32" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="2:11">
@@ -2859,59 +2860,59 @@
       <c r="F56" s="32"/>
       <c r="G56" s="32"/>
       <c r="H56" s="32" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I56" s="32" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J56" s="32">
         <f t="shared" si="0"/>
-        <v>131072</v>
+        <v>65536</v>
       </c>
       <c r="K56" s="32" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="2:11">
       <c r="B57" s="32"/>
-      <c r="C57" s="34"/>
+      <c r="C57" s="32"/>
       <c r="D57" s="32"/>
       <c r="E57" s="32"/>
       <c r="F57" s="32"/>
       <c r="G57" s="32"/>
       <c r="H57" s="32" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I57" s="32" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J57" s="32">
         <f t="shared" si="0"/>
+        <v>131072</v>
+      </c>
+      <c r="K57" s="32" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" s="32"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="I58" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="J58" s="32">
+        <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K57" s="32" t="s">
+      <c r="K58" s="32" t="s">
         <v>158</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="34"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="34"/>
-      <c r="F58" s="34"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="I58" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="J58" s="34">
-        <f t="shared" si="0"/>
-        <v>524288</v>
-      </c>
-      <c r="K58" s="34" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="59" spans="2:11">
@@ -2922,17 +2923,17 @@
       <c r="F59" s="34"/>
       <c r="G59" s="34"/>
       <c r="H59" s="34" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I59" s="34" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J59" s="34">
         <f t="shared" si="0"/>
-        <v>1048576</v>
+        <v>524288</v>
       </c>
       <c r="K59" s="34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="2:11">
@@ -2943,17 +2944,17 @@
       <c r="F60" s="34"/>
       <c r="G60" s="34"/>
       <c r="H60" s="34" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="I60" s="34" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="J60" s="34">
         <f t="shared" si="0"/>
-        <v>2097152</v>
+        <v>1048576</v>
       </c>
       <c r="K60" s="34" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="2:11">
@@ -2964,63 +2965,64 @@
       <c r="F61" s="34"/>
       <c r="G61" s="34"/>
       <c r="H61" s="34" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I61" s="34" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J61" s="34">
         <f t="shared" si="0"/>
+        <v>2097152</v>
+      </c>
+      <c r="K61" s="34" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
+      <c r="B62" s="34"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="I62" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="J62" s="34">
+        <f t="shared" si="0"/>
         <v>4194304</v>
       </c>
-      <c r="K61" s="34" t="s">
+      <c r="K62" s="34" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="35" t="s">
+    <row r="63" spans="2:11">
+      <c r="B63" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="C62" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="D62" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="I62" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="J62" s="32">
-        <v>1</v>
-      </c>
-      <c r="K62" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="35"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
+      <c r="C63" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D63" s="33" t="b">
+        <v>1</v>
+      </c>
       <c r="E63" s="35"/>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
       <c r="H63" s="35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="I63" s="35" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="J63" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K63" s="35" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" spans="2:11">
@@ -3031,16 +3033,16 @@
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
       <c r="H64" s="35" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I64" s="35" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J64" s="32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K64" s="35" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65" spans="2:11">
@@ -3051,16 +3053,16 @@
       <c r="F65" s="35"/>
       <c r="G65" s="35"/>
       <c r="H65" s="35" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I65" s="35" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="J65" s="32">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K65" s="35" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="2:11">
@@ -3071,62 +3073,62 @@
       <c r="F66" s="35"/>
       <c r="G66" s="35"/>
       <c r="H66" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="I66" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="J66" s="32">
+        <v>8</v>
+      </c>
+      <c r="K66" s="35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" s="35"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="35"/>
+      <c r="E67" s="35"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="I66" s="35" t="s">
+      <c r="I67" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J67" s="32">
         <v>15</v>
       </c>
-      <c r="K66" s="35" t="s">
+      <c r="K67" s="35" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="36" t="s">
+    <row r="68" spans="2:11">
+      <c r="B68" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="C67" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="D67" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="36"/>
-      <c r="F67" s="36"/>
-      <c r="G67" s="36"/>
-      <c r="H67" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="I67" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="J67" s="36">
-        <v>1</v>
-      </c>
-      <c r="K67" s="36" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
+      <c r="C68" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="D68" s="37" t="b">
+        <v>1</v>
+      </c>
       <c r="E68" s="36"/>
       <c r="F68" s="36"/>
       <c r="G68" s="36"/>
       <c r="H68" s="36" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J68" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K68" s="36" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="69" spans="2:11">
@@ -3137,16 +3139,16 @@
       <c r="F69" s="36"/>
       <c r="G69" s="36"/>
       <c r="H69" s="36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J69" s="36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K69" s="36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="2:11">
@@ -3157,16 +3159,16 @@
       <c r="F70" s="36"/>
       <c r="G70" s="36"/>
       <c r="H70" s="36" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J70" s="36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K70" s="36" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="2:11">
@@ -3177,16 +3179,16 @@
       <c r="F71" s="36"/>
       <c r="G71" s="36"/>
       <c r="H71" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I71" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J71" s="36">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K71" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="72" spans="2:11">
@@ -3197,16 +3199,16 @@
       <c r="F72" s="36"/>
       <c r="G72" s="36"/>
       <c r="H72" s="36" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I72" s="36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J72" s="36">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K72" s="36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="2:11">
@@ -3217,16 +3219,16 @@
       <c r="F73" s="36"/>
       <c r="G73" s="36"/>
       <c r="H73" s="36" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I73" s="36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J73" s="36">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K73" s="36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="2:11">
@@ -3237,150 +3239,150 @@
       <c r="F74" s="36"/>
       <c r="G74" s="36"/>
       <c r="H74" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="I74" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="J74" s="36">
+        <v>64</v>
+      </c>
+      <c r="K74" s="36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="B75" s="36"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="36"/>
+      <c r="G75" s="36"/>
+      <c r="H75" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="I74" s="36" t="s">
+      <c r="I75" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="J74" s="36">
+      <c r="J75" s="36">
         <v>127</v>
       </c>
-      <c r="K74" s="36" t="s">
+      <c r="K75" s="36" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="2:11">
-      <c r="B75" s="24" t="s">
+    <row r="76" spans="2:11">
+      <c r="B76" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="C75" s="38" t="b">
+      <c r="C76" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="D75" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="24"/>
-      <c r="H75" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="I75" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="J75" s="24">
-        <v>0</v>
-      </c>
-      <c r="K75" s="24"/>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
+      <c r="D76" s="38" t="b">
+        <v>1</v>
+      </c>
       <c r="E76" s="24"/>
       <c r="F76" s="24"/>
       <c r="G76" s="24"/>
       <c r="H76" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="I76" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="J76" s="24">
+        <v>0</v>
+      </c>
+      <c r="K76" s="24"/>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" s="24"/>
+      <c r="C77" s="24"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="I76" s="24" t="s">
+      <c r="I77" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="J76" s="24">
-        <v>1</v>
-      </c>
-      <c r="K76" s="24"/>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77" s="39" t="s">
+      <c r="J77" s="24">
+        <v>1</v>
+      </c>
+      <c r="K77" s="24"/>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="C77" s="40" t="b">
+      <c r="C78" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="D77" s="40" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" s="41"/>
-      <c r="F77" s="41"/>
-      <c r="G77" s="41"/>
-      <c r="H77" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="I77" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="J77" s="41">
-        <v>0</v>
-      </c>
-      <c r="K77" s="41" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="41"/>
-      <c r="C78" s="41"/>
-      <c r="D78" s="41"/>
+      <c r="D78" s="40" t="b">
+        <v>1</v>
+      </c>
       <c r="E78" s="41"/>
       <c r="F78" s="41"/>
       <c r="G78" s="41"/>
       <c r="H78" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="I78" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="J78" s="41">
+        <v>0</v>
+      </c>
+      <c r="K78" s="41" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="I78" s="41" t="s">
+      <c r="I79" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="J78" s="41">
-        <v>1</v>
-      </c>
-      <c r="K78" s="41" t="s">
+      <c r="J79" s="41">
+        <v>1</v>
+      </c>
+      <c r="K79" s="41" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="42" t="s">
+    <row r="80" spans="2:11">
+      <c r="B80" s="42" t="s">
         <v>210</v>
       </c>
-      <c r="C79" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D79" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="25"/>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="I79" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="J79" s="36">
-        <v>1</v>
-      </c>
-      <c r="K79" s="25" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
+      <c r="C80" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="D80" s="26" t="b">
+        <v>1</v>
+      </c>
       <c r="E80" s="25"/>
       <c r="F80" s="25"/>
       <c r="G80" s="25"/>
       <c r="H80" s="25" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I80" s="25" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J80" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K80" s="25" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="81" spans="2:11">
@@ -3391,16 +3393,16 @@
       <c r="F81" s="25"/>
       <c r="G81" s="25"/>
       <c r="H81" s="25" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I81" s="25" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J81" s="36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K81" s="25" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="82" spans="2:11">
@@ -3411,16 +3413,16 @@
       <c r="F82" s="25"/>
       <c r="G82" s="25"/>
       <c r="H82" s="25" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I82" s="25" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J82" s="36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K82" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="83" spans="2:11">
@@ -3431,108 +3433,108 @@
       <c r="F83" s="25"/>
       <c r="G83" s="25"/>
       <c r="H83" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="I83" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="J83" s="36">
+        <v>8</v>
+      </c>
+      <c r="K83" s="25" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" s="25"/>
+      <c r="C84" s="25"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="25"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="25"/>
+      <c r="H84" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="I83" s="25" t="s">
+      <c r="I84" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="J83" s="36">
+      <c r="J84" s="36">
         <v>16</v>
       </c>
-      <c r="K83" s="25" t="s">
+      <c r="K84" s="25" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="84" spans="2:11">
-      <c r="B84" s="43" t="s">
+    <row r="85" spans="2:11">
+      <c r="B85" s="43" t="s">
         <v>224</v>
       </c>
-      <c r="C84" s="40" t="b">
+      <c r="C85" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="D84" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="41"/>
-      <c r="F84" s="41"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="I84" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="J84" s="41">
-        <v>1</v>
-      </c>
-      <c r="K84" s="41" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="B85" s="41"/>
-      <c r="C85" s="41"/>
-      <c r="D85" s="41"/>
+      <c r="D85" s="26" t="b">
+        <v>1</v>
+      </c>
       <c r="E85" s="41"/>
       <c r="F85" s="41"/>
       <c r="G85" s="41"/>
       <c r="H85" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="I85" s="41" t="s">
+        <v>226</v>
+      </c>
+      <c r="J85" s="41">
+        <v>1</v>
+      </c>
+      <c r="K85" s="41" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="41"/>
+      <c r="C86" s="41"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="41"/>
+      <c r="F86" s="41"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="41" t="s">
         <v>227</v>
       </c>
-      <c r="I85" s="41" t="s">
+      <c r="I86" s="41" t="s">
         <v>228</v>
       </c>
-      <c r="J85" s="41">
+      <c r="J86" s="41">
         <v>2</v>
       </c>
-      <c r="K85" s="41" t="s">
+      <c r="K86" s="41" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="25" t="s">
+    <row r="87" spans="2:11">
+      <c r="B87" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="C86" s="26" t="b">
+      <c r="C87" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D86" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="25"/>
-      <c r="F86" s="25"/>
-      <c r="G86" s="25"/>
-      <c r="H86" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="I86" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="J86" s="25">
-        <v>1</v>
-      </c>
-      <c r="K86" s="25" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="B87" s="25"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="25"/>
+      <c r="D87" s="26" t="b">
+        <v>1</v>
+      </c>
       <c r="E87" s="25"/>
       <c r="F87" s="25"/>
       <c r="G87" s="25"/>
       <c r="H87" s="44" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="I87" s="25" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="J87" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K87" s="25" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="2:11">
@@ -3543,62 +3545,62 @@
       <c r="F88" s="25"/>
       <c r="G88" s="25"/>
       <c r="H88" s="44" t="s">
+        <v>230</v>
+      </c>
+      <c r="I88" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="J88" s="25">
+        <v>2</v>
+      </c>
+      <c r="K88" s="25" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" s="25"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="25"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="25"/>
+      <c r="H89" s="44" t="s">
         <v>232</v>
       </c>
-      <c r="I88" s="25" t="s">
+      <c r="I89" s="25" t="s">
         <v>233</v>
       </c>
-      <c r="J88" s="25">
+      <c r="J89" s="25">
         <v>3</v>
       </c>
-      <c r="K88" s="25" t="s">
+      <c r="K89" s="25" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="89" spans="2:11">
-      <c r="B89" s="45" t="s">
+    <row r="90" spans="2:11">
+      <c r="B90" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="C89" s="46" t="b">
+      <c r="C90" s="46" t="b">
         <v>0</v>
       </c>
-      <c r="D89" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="45"/>
-      <c r="F89" s="45"/>
-      <c r="G89" s="45"/>
-      <c r="H89" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="I89" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="J89" s="45">
-        <v>1</v>
-      </c>
-      <c r="K89" s="45" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11">
-      <c r="B90" s="45"/>
-      <c r="C90" s="45"/>
-      <c r="D90" s="45"/>
+      <c r="D90" s="46" t="b">
+        <v>1</v>
+      </c>
       <c r="E90" s="45"/>
       <c r="F90" s="45"/>
       <c r="G90" s="45"/>
       <c r="H90" s="47" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="I90" s="45" t="s">
-        <v>50</v>
+        <v>236</v>
       </c>
       <c r="J90" s="45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K90" s="45" t="s">
-        <v>50</v>
+        <v>236</v>
       </c>
     </row>
     <row r="91" spans="2:11">
@@ -3609,62 +3611,62 @@
       <c r="F91" s="45"/>
       <c r="G91" s="45"/>
       <c r="H91" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="I91" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="J91" s="45">
+        <v>2</v>
+      </c>
+      <c r="K91" s="45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="B92" s="45"/>
+      <c r="C92" s="45"/>
+      <c r="D92" s="45"/>
+      <c r="E92" s="45"/>
+      <c r="F92" s="45"/>
+      <c r="G92" s="45"/>
+      <c r="H92" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="I91" s="45" t="s">
+      <c r="I92" s="45" t="s">
         <v>239</v>
       </c>
-      <c r="J91" s="45">
+      <c r="J92" s="45">
         <v>3</v>
       </c>
-      <c r="K91" s="45" t="s">
+      <c r="K92" s="45" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="92" spans="2:11">
-      <c r="B92" s="48" t="s">
+    <row r="93" spans="2:11">
+      <c r="B93" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="C92" s="49" t="b">
+      <c r="C93" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D92" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
-      <c r="H92" s="50" t="s">
-        <v>286</v>
-      </c>
-      <c r="I92" s="50" t="s">
-        <v>241</v>
-      </c>
-      <c r="J92" s="50">
-        <v>0</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
-      <c r="B93" s="48"/>
-      <c r="C93" s="48"/>
-      <c r="D93" s="48"/>
+      <c r="D93" s="49" t="b">
+        <v>1</v>
+      </c>
       <c r="E93" s="48"/>
       <c r="F93" s="48"/>
       <c r="G93" s="48"/>
       <c r="H93" s="50" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="I93" s="50" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J93" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="94" spans="2:11">
@@ -3675,62 +3677,62 @@
       <c r="F94" s="48"/>
       <c r="G94" s="48"/>
       <c r="H94" s="50" t="s">
+        <v>242</v>
+      </c>
+      <c r="I94" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="J94" s="50">
+        <v>1</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="B95" s="48"/>
+      <c r="C95" s="48"/>
+      <c r="D95" s="48"/>
+      <c r="E95" s="48"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="48"/>
+      <c r="H95" s="50" t="s">
         <v>289</v>
       </c>
-      <c r="I94" s="50" t="s">
+      <c r="I95" s="50" t="s">
         <v>290</v>
       </c>
-      <c r="J94" s="50">
+      <c r="J95" s="50">
         <v>2</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="K95" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="95" spans="2:11">
-      <c r="B95" s="51" t="s">
+    <row r="96" spans="2:11">
+      <c r="B96" s="51" t="s">
         <v>244</v>
       </c>
-      <c r="C95" s="52" t="b">
+      <c r="C96" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="D95" s="52" t="b">
-        <v>1</v>
-      </c>
-      <c r="E95" s="51"/>
-      <c r="F95" s="51"/>
-      <c r="G95" s="51"/>
-      <c r="H95" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="I95" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="J95" s="51">
-        <v>1</v>
-      </c>
-      <c r="K95" s="51" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11">
-      <c r="B96" s="51"/>
-      <c r="C96" s="51"/>
-      <c r="D96" s="51"/>
+      <c r="D96" s="52" t="b">
+        <v>1</v>
+      </c>
       <c r="E96" s="51"/>
       <c r="F96" s="51"/>
       <c r="G96" s="51"/>
       <c r="H96" s="53" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I96" s="51" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J96" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K96" s="51" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="2:11">
@@ -3741,16 +3743,16 @@
       <c r="F97" s="51"/>
       <c r="G97" s="51"/>
       <c r="H97" s="53" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I97" s="51" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J97" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K97" s="51" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="98" spans="2:11">
@@ -3761,16 +3763,16 @@
       <c r="F98" s="51"/>
       <c r="G98" s="51"/>
       <c r="H98" s="53" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I98" s="51" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="J98" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K98" s="51" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="99" spans="2:11">
@@ -3781,253 +3783,272 @@
       <c r="F99" s="51"/>
       <c r="G99" s="51"/>
       <c r="H99" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="I99" s="51" t="s">
+        <v>252</v>
+      </c>
+      <c r="J99" s="51">
+        <v>4</v>
+      </c>
+      <c r="K99" s="51" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="100" spans="2:11">
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
+      <c r="F100" s="51"/>
+      <c r="G100" s="51"/>
+      <c r="H100" s="53" t="s">
         <v>253</v>
       </c>
-      <c r="I99" s="51" t="s">
+      <c r="I100" s="51" t="s">
         <v>254</v>
       </c>
-      <c r="J99" s="51">
+      <c r="J100" s="51">
         <v>5</v>
       </c>
-      <c r="K99" s="51" t="s">
+      <c r="K100" s="51" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="100" spans="2:11">
-      <c r="B100" s="1" t="s">
+    <row r="101" spans="2:11">
+      <c r="B101" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C100" s="49" t="b">
+      <c r="C101" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D100" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H100" s="1" t="s">
+      <c r="D101" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="I101" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="J100" s="1">
-        <v>1</v>
-      </c>
-      <c r="K100" s="1" t="s">
+      <c r="J101" s="1">
+        <v>1</v>
+      </c>
+      <c r="K101" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="101" spans="2:11">
-      <c r="H101" s="1" t="s">
+    <row r="102" spans="2:11">
+      <c r="H102" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I102" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="J101" s="1">
+      <c r="J102" s="1">
         <v>2</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="K102" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="102" spans="2:11">
-      <c r="B102" s="1" t="s">
+    <row r="103" spans="2:11">
+      <c r="B103" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C102" s="49" t="b">
+      <c r="C103" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D102" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H102" s="1" t="s">
+      <c r="D103" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H103" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="I103" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="J102" s="1">
+      <c r="J103" s="1">
         <v>0</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K103" s="1" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11">
-      <c r="H103" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="J103" s="1">
-        <v>1</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="104" spans="2:11">
       <c r="H104" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J104" s="1">
+        <v>1</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11">
+      <c r="H105" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="I104" s="1" t="s">
+      <c r="I105" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="J104" s="1">
+      <c r="J105" s="1">
         <v>2</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="K105" s="1" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="105" spans="2:11">
-      <c r="B105"/>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105" s="54" t="s">
+    <row r="106" spans="2:11">
+      <c r="B106"/>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="I105" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J105" s="1">
+      <c r="J106" s="1">
         <v>3</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="K106" s="1" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="106" spans="2:11">
-      <c r="H106" s="54" t="s">
+    <row r="107" spans="2:11">
+      <c r="H107" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="I106" s="1" t="s">
+      <c r="I107" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J106" s="1">
+      <c r="J107" s="1">
         <v>4</v>
       </c>
-      <c r="K106" s="1" t="s">
+      <c r="K107" s="1" t="s">
         <v>270</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11">
-      <c r="H107" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="J107" s="1">
-        <v>5</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="108" spans="2:11">
       <c r="H108" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J108" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="109" spans="2:11">
       <c r="H109" s="1" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J109" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="110" spans="2:11">
       <c r="H110" s="1" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J110" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="111" spans="2:11">
       <c r="H111" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J111" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="H112" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J112" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="113" spans="8:11">
       <c r="H113" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J113" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="114" spans="8:11">
       <c r="H114" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="J114" s="1">
+        <v>11</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="115" spans="8:11">
+      <c r="H115" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="I114" s="1" t="s">
+      <c r="I115" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="J114" s="1">
+      <c r="J115" s="1">
         <v>12</v>
       </c>
-      <c r="K114" s="1" t="s">
+      <c r="K115" s="1" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="129" s="1" customFormat="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5931D23D-324B-4F62-AA59-C3AE5A963E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6740" yWindow="2280" windowWidth="30580" windowHeight="17170" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="298">
   <si>
     <t>##var</t>
   </si>
@@ -266,6 +260,18 @@
     <t>爱心币</t>
   </si>
   <si>
+    <t>FenCount</t>
+  </si>
+  <si>
+    <t>粉丝数</t>
+  </si>
+  <si>
+    <t>FanGrowthRate</t>
+  </si>
+  <si>
+    <t>粉丝增长系数</t>
+  </si>
+  <si>
     <t>UICanvasLayer</t>
   </si>
   <si>
@@ -548,6 +554,15 @@
     <t>23=工厂制作</t>
   </si>
   <si>
+    <t>ShopHelp</t>
+  </si>
+  <si>
+    <t>商店帮忙</t>
+  </si>
+  <si>
+    <t>24=工厂制作</t>
+  </si>
+  <si>
     <t>ShowRuleTimeType</t>
   </si>
   <si>
@@ -758,15 +773,30 @@
     <t>ItemType</t>
   </si>
   <si>
+    <t>Material</t>
+  </si>
+  <si>
     <t>材料</t>
   </si>
   <si>
+    <t>固定无变化材料</t>
+  </si>
+  <si>
     <t>Consumables</t>
   </si>
   <si>
     <t>消耗品</t>
   </si>
   <si>
+    <t>固定可以使用的道具</t>
+  </si>
+  <si>
+    <t>Runtime</t>
+  </si>
+  <si>
+    <t>动态材料</t>
+  </si>
+  <si>
     <t>ItemQuality</t>
   </si>
   <si>
@@ -891,49 +921,19 @@
   </si>
   <si>
     <t>商店特殊道具</t>
-  </si>
-  <si>
-    <t>Material</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>固定无变化材料</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>固定可以使用的道具</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Runtime</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>动态材料</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FenCount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>粉丝数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>FanGrowthRate</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>粉丝增长系数</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -944,22 +944,167 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1062,8 +1207,194 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1211,13 +1542,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1383,21 +1956,62 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1650,25 +2264,25 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L115"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.0833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -1695,13 +2309,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1729,7 +2343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2227,35 +2841,35 @@
     </row>
     <row r="26" spans="2:11">
       <c r="H26" s="1" t="s">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>292</v>
+        <v>78</v>
       </c>
       <c r="J26" s="1">
         <v>9</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>292</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="2:11">
       <c r="H27" s="1" t="s">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>294</v>
+        <v>80</v>
       </c>
       <c r="J27" s="1">
         <v>10</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>294</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="2:11">
       <c r="B28" s="25" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C28" s="26" t="b">
         <v>0</v>
@@ -2267,16 +2881,16 @@
       <c r="F28" s="25"/>
       <c r="G28" s="25"/>
       <c r="H28" s="25" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J28" s="25">
         <v>0</v>
       </c>
       <c r="K28" s="25" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="2:11">
@@ -2287,16 +2901,16 @@
       <c r="F29" s="25"/>
       <c r="G29" s="25"/>
       <c r="H29" s="25" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J29" s="25">
         <v>1</v>
       </c>
       <c r="K29" s="25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="2:11">
@@ -2307,16 +2921,16 @@
       <c r="F30" s="25"/>
       <c r="G30" s="25"/>
       <c r="H30" s="25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J30" s="25">
         <v>2</v>
       </c>
       <c r="K30" s="25" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="2:11">
@@ -2327,21 +2941,21 @@
       <c r="F31" s="25"/>
       <c r="G31" s="25"/>
       <c r="H31" s="25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J31" s="25">
         <v>3</v>
       </c>
       <c r="K31" s="25" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="2:11">
       <c r="B32" s="27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C32" s="28" t="b">
         <v>0</v>
@@ -2353,16 +2967,16 @@
       <c r="F32" s="29"/>
       <c r="G32" s="29"/>
       <c r="H32" s="29" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I32" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J32" s="29">
         <v>0</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -2373,16 +2987,16 @@
       <c r="F33" s="29"/>
       <c r="G33" s="29"/>
       <c r="H33" s="29" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I33" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J33" s="29">
         <v>1</v>
       </c>
       <c r="K33" s="29" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="2:11">
@@ -2393,16 +3007,16 @@
       <c r="F34" s="29"/>
       <c r="G34" s="29"/>
       <c r="H34" s="29" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I34" s="29" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J34" s="29">
         <v>2</v>
       </c>
       <c r="K34" s="29" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="2:11">
@@ -2413,21 +3027,21 @@
       <c r="F35" s="29"/>
       <c r="G35" s="29"/>
       <c r="H35" s="29" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I35" s="29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J35" s="29">
         <v>3</v>
       </c>
       <c r="K35" s="29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="B36" s="30" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C36" s="31" t="b">
         <v>0</v>
@@ -2439,16 +3053,16 @@
       <c r="F36" s="30"/>
       <c r="G36" s="30"/>
       <c r="H36" s="30" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I36" s="30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="J36" s="30">
         <v>1</v>
       </c>
       <c r="K36" s="30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -2459,16 +3073,16 @@
       <c r="F37" s="30"/>
       <c r="G37" s="30"/>
       <c r="H37" s="30" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I37" s="30" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J37" s="30">
         <v>2</v>
       </c>
       <c r="K37" s="30" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="2:11">
@@ -2479,21 +3093,21 @@
       <c r="F38" s="30"/>
       <c r="G38" s="30"/>
       <c r="H38" s="30" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I38" s="30" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J38" s="30">
         <v>3</v>
       </c>
       <c r="K38" s="30" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="2:11">
       <c r="B39" s="32" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C39" s="33" t="b">
         <v>1</v>
@@ -2505,16 +3119,16 @@
       <c r="F39" s="32"/>
       <c r="G39" s="32"/>
       <c r="H39" s="32" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I39" s="32" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J39" s="32">
         <v>0</v>
       </c>
       <c r="K39" s="32" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -2525,16 +3139,16 @@
       <c r="F40" s="32"/>
       <c r="G40" s="32"/>
       <c r="H40" s="32" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I40" s="32" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J40" s="32">
         <v>1</v>
       </c>
       <c r="K40" s="32" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="2:11">
@@ -2545,17 +3159,17 @@
       <c r="F41" s="32"/>
       <c r="G41" s="32"/>
       <c r="H41" s="32" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I41" s="32" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J41" s="32">
-        <f t="shared" ref="J41:J62" si="0">J40*2</f>
+        <f t="shared" ref="J41:J63" si="0">J40*2</f>
         <v>2</v>
       </c>
       <c r="K41" s="32" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="2:11">
@@ -2566,17 +3180,17 @@
       <c r="F42" s="32"/>
       <c r="G42" s="32"/>
       <c r="H42" s="32" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I42" s="32" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="J42" s="32">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="K42" s="32" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="2:11">
@@ -2587,17 +3201,17 @@
       <c r="F43" s="32"/>
       <c r="G43" s="32"/>
       <c r="H43" s="32" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I43" s="32" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J43" s="32">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="K43" s="32" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="2:11">
@@ -2608,17 +3222,17 @@
       <c r="F44" s="32"/>
       <c r="G44" s="32"/>
       <c r="H44" s="32" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="I44" s="32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="J44" s="32">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="K44" s="32" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="2:11">
@@ -2629,17 +3243,17 @@
       <c r="F45" s="32"/>
       <c r="G45" s="32"/>
       <c r="H45" s="32" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I45" s="32" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J45" s="32">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="K45" s="32" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="2:11">
@@ -2650,17 +3264,17 @@
       <c r="F46" s="32"/>
       <c r="G46" s="32"/>
       <c r="H46" s="32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I46" s="32" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J46" s="32">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="K46" s="32" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="2:11">
@@ -2671,17 +3285,17 @@
       <c r="F47" s="32"/>
       <c r="G47" s="32"/>
       <c r="H47" s="32" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I47" s="32" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J47" s="32">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
       <c r="K47" s="32" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="2:11">
@@ -2692,17 +3306,17 @@
       <c r="F48" s="32"/>
       <c r="G48" s="32"/>
       <c r="H48" s="32" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I48" s="32" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="0"/>
         <v>256</v>
       </c>
       <c r="K48" s="32" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="2:11">
@@ -2713,17 +3327,17 @@
       <c r="F49" s="32"/>
       <c r="G49" s="32"/>
       <c r="H49" s="32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I49" s="32" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J49" s="32">
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
       <c r="K49" s="32" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" spans="2:11">
@@ -2734,17 +3348,17 @@
       <c r="F50" s="32"/>
       <c r="G50" s="32"/>
       <c r="H50" s="32" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I50" s="32" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J50" s="32">
         <f t="shared" si="0"/>
         <v>1024</v>
       </c>
       <c r="K50" s="32" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="2:11">
@@ -2755,17 +3369,17 @@
       <c r="F51" s="32"/>
       <c r="G51" s="32"/>
       <c r="H51" s="32" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I51" s="32" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J51" s="32">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
       <c r="K51" s="32" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="2:11">
@@ -2776,17 +3390,17 @@
       <c r="F52" s="32"/>
       <c r="G52" s="32"/>
       <c r="H52" s="32" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="I52" s="32" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J52" s="32">
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
       <c r="K52" s="32" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="2:11">
@@ -2797,17 +3411,17 @@
       <c r="F53" s="32"/>
       <c r="G53" s="32"/>
       <c r="H53" s="32" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="I53" s="32" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J53" s="32">
         <f t="shared" si="0"/>
         <v>8192</v>
       </c>
       <c r="K53" s="32" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="2:11">
@@ -2818,17 +3432,17 @@
       <c r="F54" s="32"/>
       <c r="G54" s="32"/>
       <c r="H54" s="32" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I54" s="32" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="J54" s="32">
         <f t="shared" si="0"/>
         <v>16384</v>
       </c>
       <c r="K54" s="32" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="2:11">
@@ -2839,17 +3453,17 @@
       <c r="F55" s="32"/>
       <c r="G55" s="32"/>
       <c r="H55" s="32" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I55" s="32" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J55" s="32">
         <f t="shared" si="0"/>
         <v>32768</v>
       </c>
       <c r="K55" s="32" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="2:11">
@@ -2860,17 +3474,17 @@
       <c r="F56" s="32"/>
       <c r="G56" s="32"/>
       <c r="H56" s="32" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I56" s="32" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J56" s="32">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
       <c r="K56" s="32" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="2:11">
@@ -2881,17 +3495,17 @@
       <c r="F57" s="32"/>
       <c r="G57" s="32"/>
       <c r="H57" s="32" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="I57" s="32" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J57" s="32">
         <f t="shared" si="0"/>
         <v>131072</v>
       </c>
       <c r="K57" s="32" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="2:11">
@@ -2902,17 +3516,17 @@
       <c r="F58" s="32"/>
       <c r="G58" s="32"/>
       <c r="H58" s="32" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I58" s="32" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="0"/>
         <v>262144</v>
       </c>
       <c r="K58" s="32" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="2:11">
@@ -2923,17 +3537,17 @@
       <c r="F59" s="34"/>
       <c r="G59" s="34"/>
       <c r="H59" s="34" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I59" s="34" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J59" s="34">
         <f t="shared" si="0"/>
         <v>524288</v>
       </c>
       <c r="K59" s="34" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="2:11">
@@ -2944,17 +3558,17 @@
       <c r="F60" s="34"/>
       <c r="G60" s="34"/>
       <c r="H60" s="34" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I60" s="34" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J60" s="34">
         <f t="shared" si="0"/>
         <v>1048576</v>
       </c>
       <c r="K60" s="34" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="2:11">
@@ -2965,17 +3579,17 @@
       <c r="F61" s="34"/>
       <c r="G61" s="34"/>
       <c r="H61" s="34" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I61" s="34" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J61" s="34">
         <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
       <c r="K61" s="34" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="2:11">
@@ -2986,63 +3600,64 @@
       <c r="F62" s="34"/>
       <c r="G62" s="34"/>
       <c r="H62" s="34" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I62" s="34" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J62" s="34">
         <f t="shared" si="0"/>
         <v>4194304</v>
       </c>
       <c r="K62" s="34" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" spans="2:11">
-      <c r="B63" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="C63" s="33" t="b">
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="I63" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="J63" s="34">
+        <f t="shared" si="0"/>
+        <v>8388608</v>
+      </c>
+      <c r="K63" s="34" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11">
+      <c r="B64" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="33" t="b">
         <v>1</v>
       </c>
-      <c r="D63" s="33" t="b">
+      <c r="D64" s="33" t="b">
         <v>1</v>
       </c>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="I63" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="J63" s="32">
-        <v>1</v>
-      </c>
-      <c r="K63" s="35" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="64" spans="2:11">
-      <c r="B64" s="35"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
       <c r="E64" s="35"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
       <c r="H64" s="35" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I64" s="35" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J64" s="32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K64" s="35" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="2:11">
@@ -3053,16 +3668,16 @@
       <c r="F65" s="35"/>
       <c r="G65" s="35"/>
       <c r="H65" s="35" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="I65" s="35" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="J65" s="32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K65" s="35" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="66" spans="2:11">
@@ -3073,16 +3688,16 @@
       <c r="F66" s="35"/>
       <c r="G66" s="35"/>
       <c r="H66" s="35" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I66" s="35" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J66" s="32">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K66" s="35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="2:11">
@@ -3093,62 +3708,62 @@
       <c r="F67" s="35"/>
       <c r="G67" s="35"/>
       <c r="H67" s="35" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I67" s="35" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J67" s="32">
+        <v>8</v>
+      </c>
+      <c r="K67" s="35" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="I68" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="J68" s="32">
         <v>15</v>
       </c>
-      <c r="K67" s="35" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="C68" s="37" t="b">
+      <c r="K68" s="35" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11">
+      <c r="B69" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C69" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="D68" s="37" t="b">
+      <c r="D69" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="I68" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="J68" s="36">
-        <v>1</v>
-      </c>
-      <c r="K68" s="36" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="69" spans="2:11">
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
       <c r="E69" s="36"/>
       <c r="F69" s="36"/>
       <c r="G69" s="36"/>
       <c r="H69" s="36" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J69" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K69" s="36" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="2:11">
@@ -3159,16 +3774,16 @@
       <c r="F70" s="36"/>
       <c r="G70" s="36"/>
       <c r="H70" s="36" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J70" s="36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K70" s="36" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="71" spans="2:11">
@@ -3179,16 +3794,16 @@
       <c r="F71" s="36"/>
       <c r="G71" s="36"/>
       <c r="H71" s="36" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="I71" s="36" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J71" s="36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K71" s="36" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72" spans="2:11">
@@ -3199,16 +3814,16 @@
       <c r="F72" s="36"/>
       <c r="G72" s="36"/>
       <c r="H72" s="36" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I72" s="36" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J72" s="36">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K72" s="36" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="73" spans="2:11">
@@ -3219,16 +3834,16 @@
       <c r="F73" s="36"/>
       <c r="G73" s="36"/>
       <c r="H73" s="36" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I73" s="36" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J73" s="36">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K73" s="36" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="74" spans="2:11">
@@ -3239,16 +3854,16 @@
       <c r="F74" s="36"/>
       <c r="G74" s="36"/>
       <c r="H74" s="36" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="I74" s="36" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="J74" s="36">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K74" s="36" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="75" spans="2:11">
@@ -3259,150 +3874,150 @@
       <c r="F75" s="36"/>
       <c r="G75" s="36"/>
       <c r="H75" s="36" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="I75" s="36" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="J75" s="36">
+        <v>64</v>
+      </c>
+      <c r="K75" s="36" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="I76" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="J76" s="36">
         <v>127</v>
       </c>
-      <c r="K75" s="36" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="C76" s="38" t="b">
+      <c r="K76" s="36" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="C77" s="38" t="b">
         <v>0</v>
       </c>
-      <c r="D76" s="38" t="b">
+      <c r="D77" s="38" t="b">
         <v>1</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="I76" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="J76" s="24">
-        <v>0</v>
-      </c>
-      <c r="K76" s="24"/>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
-      <c r="D77" s="24"/>
       <c r="E77" s="24"/>
       <c r="F77" s="24"/>
       <c r="G77" s="24"/>
       <c r="H77" s="24" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I77" s="24" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J77" s="24">
+        <v>0</v>
+      </c>
+      <c r="K77" s="24"/>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" s="24"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="24"/>
+      <c r="E78" s="24"/>
+      <c r="F78" s="24"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="I78" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="J78" s="24">
         <v>1</v>
       </c>
-      <c r="K77" s="24"/>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="C78" s="40" t="b">
+      <c r="K78" s="24"/>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="C79" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="D78" s="40" t="b">
+      <c r="D79" s="40" t="b">
         <v>1</v>
       </c>
-      <c r="E78" s="41"/>
-      <c r="F78" s="41"/>
-      <c r="G78" s="41"/>
-      <c r="H78" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="I78" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="J78" s="41">
-        <v>0</v>
-      </c>
-      <c r="K78" s="41" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="41"/>
-      <c r="C79" s="41"/>
-      <c r="D79" s="41"/>
       <c r="E79" s="41"/>
       <c r="F79" s="41"/>
       <c r="G79" s="41"/>
       <c r="H79" s="41" t="s">
-        <v>207</v>
+        <v>55</v>
       </c>
       <c r="I79" s="41" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="J79" s="41">
+        <v>0</v>
+      </c>
+      <c r="K79" s="41" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" s="41"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="41"/>
+      <c r="E80" s="41"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="I80" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="J80" s="41">
         <v>1</v>
       </c>
-      <c r="K79" s="41" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="B80" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="C80" s="26" t="b">
+      <c r="K80" s="41" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="C81" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="D80" s="26" t="b">
+      <c r="D81" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="I80" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="J80" s="36">
-        <v>1</v>
-      </c>
-      <c r="K80" s="25" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="B81" s="25"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="25"/>
       <c r="E81" s="25"/>
       <c r="F81" s="25"/>
       <c r="G81" s="25"/>
       <c r="H81" s="25" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="I81" s="25" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="J81" s="36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="25" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="82" spans="2:11">
@@ -3413,16 +4028,16 @@
       <c r="F82" s="25"/>
       <c r="G82" s="25"/>
       <c r="H82" s="25" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I82" s="25" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="J82" s="36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K82" s="25" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" spans="2:11">
@@ -3433,16 +4048,16 @@
       <c r="F83" s="25"/>
       <c r="G83" s="25"/>
       <c r="H83" s="25" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="I83" s="25" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J83" s="36">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K83" s="25" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="2:11">
@@ -3453,108 +4068,108 @@
       <c r="F84" s="25"/>
       <c r="G84" s="25"/>
       <c r="H84" s="25" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I84" s="25" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="J84" s="36">
+        <v>8</v>
+      </c>
+      <c r="K84" s="25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" s="25"/>
+      <c r="C85" s="25"/>
+      <c r="D85" s="25"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="25"/>
+      <c r="G85" s="25"/>
+      <c r="H85" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="I85" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="J85" s="36">
         <v>16</v>
       </c>
-      <c r="K84" s="25" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="B85" s="43" t="s">
-        <v>224</v>
-      </c>
-      <c r="C85" s="40" t="b">
+      <c r="K85" s="25" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="C86" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="D85" s="26" t="b">
+      <c r="D86" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E85" s="41"/>
-      <c r="F85" s="41"/>
-      <c r="G85" s="41"/>
-      <c r="H85" s="41" t="s">
-        <v>225</v>
-      </c>
-      <c r="I85" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="J85" s="41">
-        <v>1</v>
-      </c>
-      <c r="K85" s="41" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="41"/>
-      <c r="C86" s="41"/>
-      <c r="D86" s="41"/>
       <c r="E86" s="41"/>
       <c r="F86" s="41"/>
       <c r="G86" s="41"/>
       <c r="H86" s="41" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I86" s="41" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="J86" s="41">
+        <v>1</v>
+      </c>
+      <c r="K86" s="41" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" s="41"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="41"/>
+      <c r="G87" s="41"/>
+      <c r="H87" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="I87" s="41" t="s">
+        <v>235</v>
+      </c>
+      <c r="J87" s="41">
         <v>2</v>
       </c>
-      <c r="K86" s="41" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="B87" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="C87" s="26" t="b">
+      <c r="K87" s="41" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="C88" s="26" t="b">
         <v>0</v>
       </c>
-      <c r="D87" s="26" t="b">
+      <c r="D88" s="26" t="b">
         <v>1</v>
       </c>
-      <c r="E87" s="25"/>
-      <c r="F87" s="25"/>
-      <c r="G87" s="25"/>
-      <c r="H87" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="I87" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="J87" s="25">
-        <v>1</v>
-      </c>
-      <c r="K87" s="25" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11">
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
       <c r="E88" s="25"/>
       <c r="F88" s="25"/>
       <c r="G88" s="25"/>
       <c r="H88" s="44" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="I88" s="25" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="J88" s="25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K88" s="25" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
     </row>
     <row r="89" spans="2:11">
@@ -3565,62 +4180,62 @@
       <c r="F89" s="25"/>
       <c r="G89" s="25"/>
       <c r="H89" s="44" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I89" s="25" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="J89" s="25">
+        <v>2</v>
+      </c>
+      <c r="K89" s="25" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
+      <c r="H90" s="44" t="s">
+        <v>239</v>
+      </c>
+      <c r="I90" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="J90" s="25">
         <v>3</v>
       </c>
-      <c r="K89" s="25" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11">
-      <c r="B90" s="45" t="s">
-        <v>234</v>
-      </c>
-      <c r="C90" s="46" t="b">
+      <c r="K90" s="25" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="B91" s="45" t="s">
+        <v>241</v>
+      </c>
+      <c r="C91" s="46" t="b">
         <v>0</v>
       </c>
-      <c r="D90" s="46" t="b">
+      <c r="D91" s="46" t="b">
         <v>1</v>
       </c>
-      <c r="E90" s="45"/>
-      <c r="F90" s="45"/>
-      <c r="G90" s="45"/>
-      <c r="H90" s="47" t="s">
-        <v>235</v>
-      </c>
-      <c r="I90" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="J90" s="45">
-        <v>1</v>
-      </c>
-      <c r="K90" s="45" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
-      <c r="B91" s="45"/>
-      <c r="C91" s="45"/>
-      <c r="D91" s="45"/>
       <c r="E91" s="45"/>
       <c r="F91" s="45"/>
       <c r="G91" s="45"/>
       <c r="H91" s="47" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I91" s="45" t="s">
-        <v>50</v>
+        <v>243</v>
       </c>
       <c r="J91" s="45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K91" s="45" t="s">
-        <v>50</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" spans="2:11">
@@ -3631,62 +4246,62 @@
       <c r="F92" s="45"/>
       <c r="G92" s="45"/>
       <c r="H92" s="47" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="I92" s="45" t="s">
-        <v>239</v>
+        <v>50</v>
       </c>
       <c r="J92" s="45">
+        <v>2</v>
+      </c>
+      <c r="K92" s="45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" s="45"/>
+      <c r="C93" s="45"/>
+      <c r="D93" s="45"/>
+      <c r="E93" s="45"/>
+      <c r="F93" s="45"/>
+      <c r="G93" s="45"/>
+      <c r="H93" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="I93" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="J93" s="45">
         <v>3</v>
       </c>
-      <c r="K92" s="45" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
-      <c r="B93" s="48" t="s">
-        <v>240</v>
-      </c>
-      <c r="C93" s="49" t="b">
+      <c r="K93" s="45" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="48" t="s">
+        <v>247</v>
+      </c>
+      <c r="C94" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D93" s="49" t="b">
+      <c r="D94" s="49" t="b">
         <v>1</v>
       </c>
-      <c r="E93" s="48"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="48"/>
-      <c r="H93" s="50" t="s">
-        <v>286</v>
-      </c>
-      <c r="I93" s="50" t="s">
-        <v>241</v>
-      </c>
-      <c r="J93" s="50">
-        <v>0</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11">
-      <c r="B94" s="48"/>
-      <c r="C94" s="48"/>
-      <c r="D94" s="48"/>
       <c r="E94" s="48"/>
       <c r="F94" s="48"/>
       <c r="G94" s="48"/>
       <c r="H94" s="50" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="I94" s="50" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="J94" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>288</v>
+        <v>250</v>
       </c>
     </row>
     <row r="95" spans="2:11">
@@ -3697,62 +4312,62 @@
       <c r="F95" s="48"/>
       <c r="G95" s="48"/>
       <c r="H95" s="50" t="s">
-        <v>289</v>
+        <v>251</v>
       </c>
       <c r="I95" s="50" t="s">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="J95" s="50">
+        <v>1</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="B96" s="48"/>
+      <c r="C96" s="48"/>
+      <c r="D96" s="48"/>
+      <c r="E96" s="48"/>
+      <c r="F96" s="48"/>
+      <c r="G96" s="48"/>
+      <c r="H96" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="I96" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="J96" s="50">
         <v>2</v>
       </c>
-      <c r="K95" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11">
-      <c r="B96" s="51" t="s">
-        <v>244</v>
-      </c>
-      <c r="C96" s="52" t="b">
+      <c r="K96" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11">
+      <c r="B97" s="51" t="s">
+        <v>256</v>
+      </c>
+      <c r="C97" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="D96" s="52" t="b">
+      <c r="D97" s="52" t="b">
         <v>1</v>
       </c>
-      <c r="E96" s="51"/>
-      <c r="F96" s="51"/>
-      <c r="G96" s="51"/>
-      <c r="H96" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="I96" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="J96" s="51">
-        <v>1</v>
-      </c>
-      <c r="K96" s="51" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11">
-      <c r="B97" s="51"/>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51"/>
       <c r="E97" s="51"/>
       <c r="F97" s="51"/>
       <c r="G97" s="51"/>
       <c r="H97" s="53" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="I97" s="51" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="J97" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" s="51" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="98" spans="2:11">
@@ -3763,16 +4378,16 @@
       <c r="F98" s="51"/>
       <c r="G98" s="51"/>
       <c r="H98" s="53" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="I98" s="51" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="J98" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K98" s="51" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="99" spans="2:11">
@@ -3783,16 +4398,16 @@
       <c r="F99" s="51"/>
       <c r="G99" s="51"/>
       <c r="H99" s="53" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="I99" s="51" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="J99" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K99" s="51" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="100" spans="2:11">
@@ -3803,258 +4418,278 @@
       <c r="F100" s="51"/>
       <c r="G100" s="51"/>
       <c r="H100" s="53" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="I100" s="51" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="J100" s="51">
+        <v>4</v>
+      </c>
+      <c r="K100" s="51" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="101" spans="2:11">
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="I101" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="J101" s="51">
         <v>5</v>
       </c>
-      <c r="K100" s="51" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="101" spans="2:11">
-      <c r="B101" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C101" s="49" t="b">
+      <c r="K101" s="51" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11">
+      <c r="B102" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C102" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D101" s="49" t="b">
+      <c r="D102" s="49" t="b">
         <v>1</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="J101" s="1">
+      <c r="H102" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="J102" s="1">
         <v>1</v>
       </c>
-      <c r="K101" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="102" spans="2:11">
-      <c r="H102" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="J102" s="1">
+      <c r="K102" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="H103" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="J103" s="1">
         <v>2</v>
       </c>
-      <c r="K102" s="1" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11">
-      <c r="B103" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C103" s="49" t="b">
+      <c r="K103" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="B104" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C104" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D103" s="49" t="b">
+      <c r="D104" s="49" t="b">
         <v>1</v>
       </c>
-      <c r="H103" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="J103" s="1">
+      <c r="H104" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J104" s="1">
         <v>0</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="104" spans="2:11">
-      <c r="H104" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="I104" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="J104" s="1">
-        <v>1</v>
-      </c>
       <c r="K104" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="105" spans="2:11">
       <c r="H105" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="J105" s="1">
+        <v>1</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
+      <c r="H106" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J106" s="1">
         <v>2</v>
       </c>
-      <c r="K105" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11">
-      <c r="B106"/>
-      <c r="C106"/>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106" s="54" t="s">
-        <v>267</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="J106" s="1">
+      <c r="K106" s="1" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11">
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J107" s="1">
         <v>3</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11">
-      <c r="H107" s="54" t="s">
-        <v>269</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="J107" s="1">
+      <c r="K107" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11">
+      <c r="H108" s="54" t="s">
+        <v>281</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J108" s="1">
         <v>4</v>
       </c>
-      <c r="K107" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="108" spans="2:11">
-      <c r="H108" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="I108" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="J108" s="1">
-        <v>5</v>
-      </c>
       <c r="K108" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="109" spans="2:11">
       <c r="H109" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="J109" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" spans="2:11">
       <c r="H110" s="1" t="s">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="J110" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111" spans="2:11">
       <c r="H111" s="1" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="J111" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="H112" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="J112" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="113" spans="8:11">
       <c r="H113" s="1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="J113" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
     </row>
     <row r="114" spans="8:11">
       <c r="H114" s="1" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="J114" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="115" spans="8:11">
       <c r="H115" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="J115" s="1">
+        <v>11</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="116" spans="8:11">
+      <c r="H116" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J116" s="1">
         <v>12</v>
       </c>
-      <c r="K115" s="1" t="s">
-        <v>285</v>
+      <c r="K116" s="1" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="302">
   <si>
     <t>##var</t>
   </si>
@@ -270,6 +270,18 @@
   </si>
   <si>
     <t>粉丝增长系数</t>
+  </si>
+  <si>
+    <t>StaminaPercent</t>
+  </si>
+  <si>
+    <t>体力百分比</t>
+  </si>
+  <si>
+    <t>StaminaMax</t>
+  </si>
+  <si>
+    <t>体力上限</t>
   </si>
   <si>
     <t>UICanvasLayer</t>
@@ -949,7 +961,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial Unicode MS"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1790,7 +1802,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1866,6 +1878,9 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1917,11 +1932,8 @@
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1948,9 +1960,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2270,7 +2279,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2868,201 +2877,183 @@
       </c>
     </row>
     <row r="28" spans="2:11">
-      <c r="B28" s="25" t="s">
+      <c r="H28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="26" t="b">
+      <c r="I28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J28" s="1">
+        <v>11</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="H29" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J29" s="1">
+        <v>12</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="26" t="b">
+      <c r="D30" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="I28" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="J28" s="25">
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="J30" s="26">
         <v>0</v>
       </c>
-      <c r="K28" s="25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11">
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="I29" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="J29" s="25">
+      <c r="K30" s="26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="I31" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="J31" s="26">
         <v>1</v>
       </c>
-      <c r="K29" s="25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11">
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="I30" s="25" t="s">
+      <c r="K31" s="26" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="J32" s="26">
+        <v>2</v>
+      </c>
+      <c r="K32" s="26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="J33" s="26">
+        <v>3</v>
+      </c>
+      <c r="K33" s="26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I34" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="J30" s="25">
-        <v>2</v>
-      </c>
-      <c r="K30" s="25" t="s">
+      <c r="J34" s="30">
+        <v>0</v>
+      </c>
+      <c r="K34" s="30" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" s="25" t="s">
+    <row r="35" spans="2:11">
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="J31" s="25">
-        <v>3</v>
-      </c>
-      <c r="K31" s="25" t="s">
+      <c r="J35" s="30">
+        <v>1</v>
+      </c>
+      <c r="K35" s="30" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="2:11">
-      <c r="B32" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C32" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="J32" s="29">
-        <v>0</v>
-      </c>
-      <c r="K32" s="29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="I33" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="J33" s="29">
-        <v>1</v>
-      </c>
-      <c r="K33" s="29" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="I34" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="J34" s="29">
-        <v>2</v>
-      </c>
-      <c r="K34" s="29" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="I35" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="J35" s="29">
-        <v>3</v>
-      </c>
-      <c r="K35" s="29" t="s">
-        <v>89</v>
-      </c>
-    </row>
     <row r="36" spans="2:11">
-      <c r="B36" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" s="31" t="b">
-        <v>1</v>
-      </c>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="30"/>
       <c r="F36" s="30"/>
       <c r="G36" s="30"/>
       <c r="H36" s="30" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="I36" s="30" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J36" s="30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" s="30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -3073,591 +3064,590 @@
       <c r="F37" s="30"/>
       <c r="G37" s="30"/>
       <c r="H37" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="I37" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="J37" s="30">
+        <v>3</v>
+      </c>
+      <c r="K37" s="30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="I37" s="30" t="s">
+      <c r="C38" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" s="32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="J37" s="30">
+      <c r="I38" s="31" t="s">
+        <v>98</v>
+      </c>
+      <c r="J38" s="31">
+        <v>1</v>
+      </c>
+      <c r="K38" s="31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="I39" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="J39" s="31">
         <v>2</v>
       </c>
-      <c r="K37" s="30" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="I38" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="J38" s="30">
+      <c r="K39" s="31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="I40" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="J40" s="31">
         <v>3</v>
       </c>
-      <c r="K38" s="30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" s="33" t="b">
+      <c r="K40" s="31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41" s="33" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="34" t="b">
         <v>1</v>
       </c>
-      <c r="D39" s="33" t="b">
+      <c r="D41" s="34" t="b">
         <v>1</v>
       </c>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="I39" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="J39" s="32">
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="I41" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="J41" s="33">
         <v>0</v>
       </c>
-      <c r="K39" s="32" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="I40" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="J40" s="32">
+      <c r="K41" s="33" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="I42" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="J42" s="33">
         <v>1</v>
       </c>
-      <c r="K40" s="32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11">
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="I41" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="J41" s="32">
-        <f t="shared" ref="J41:J63" si="0">J40*2</f>
+      <c r="K42" s="33" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="J43" s="33">
+        <f t="shared" ref="J43:J65" si="0">J42*2</f>
         <v>2</v>
       </c>
-      <c r="K41" s="32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="I42" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="J42" s="32">
+      <c r="K43" s="33" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11">
+      <c r="B44" s="33"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="I44" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="J44" s="33">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K42" s="32" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
-      <c r="B43" s="32"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="I43" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="J43" s="32">
+      <c r="K44" s="33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11">
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="33"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="I45" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="J45" s="33">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K43" s="32" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
-      <c r="B44" s="32"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="I44" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="J44" s="32">
+      <c r="K45" s="33" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="B46" s="33"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="33"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="I46" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="J46" s="33">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="K44" s="32" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11">
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="I45" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="J45" s="32">
+      <c r="K46" s="33" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11">
+      <c r="B47" s="33"/>
+      <c r="C47" s="33"/>
+      <c r="D47" s="33"/>
+      <c r="E47" s="33"/>
+      <c r="F47" s="33"/>
+      <c r="G47" s="33"/>
+      <c r="H47" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="I47" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="J47" s="33">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="K45" s="32" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11">
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="I46" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="J46" s="32">
+      <c r="K47" s="33" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11">
+      <c r="B48" s="33"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="33"/>
+      <c r="H48" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="I48" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="J48" s="33">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="K46" s="32" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11">
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="I47" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="J47" s="32">
+      <c r="K48" s="33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11">
+      <c r="B49" s="33"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
+      <c r="H49" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="I49" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="J49" s="33">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="K47" s="32" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="I48" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="J48" s="32">
+      <c r="K49" s="33" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
+      <c r="H50" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="I50" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="J50" s="33">
         <f t="shared" si="0"/>
         <v>256</v>
       </c>
-      <c r="K48" s="32" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="49" spans="2:11">
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="I49" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="J49" s="32">
+      <c r="K50" s="33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="33"/>
+      <c r="C51" s="33"/>
+      <c r="D51" s="33"/>
+      <c r="E51" s="33"/>
+      <c r="F51" s="33"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="I51" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="J51" s="33">
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
-      <c r="K49" s="32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" spans="2:11">
-      <c r="B50" s="32"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="I50" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="J50" s="32">
+      <c r="K51" s="33" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="33"/>
+      <c r="H52" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="I52" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="J52" s="33">
         <f t="shared" si="0"/>
         <v>1024</v>
       </c>
-      <c r="K50" s="32" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11">
-      <c r="B51" s="32"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="I51" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="J51" s="32">
+      <c r="K52" s="33" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="33"/>
+      <c r="E53" s="33"/>
+      <c r="F53" s="33"/>
+      <c r="G53" s="33"/>
+      <c r="H53" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="I53" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="J53" s="33">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
-      <c r="K51" s="32" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="52" spans="2:11">
-      <c r="B52" s="32"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="I52" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="J52" s="32">
+      <c r="K53" s="33" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
+      <c r="B54" s="33"/>
+      <c r="C54" s="33"/>
+      <c r="D54" s="33"/>
+      <c r="E54" s="33"/>
+      <c r="F54" s="33"/>
+      <c r="G54" s="33"/>
+      <c r="H54" s="33" t="s">
+        <v>146</v>
+      </c>
+      <c r="I54" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="J54" s="33">
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
-      <c r="K52" s="32" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11">
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="I53" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="J53" s="32">
+      <c r="K54" s="33" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11">
+      <c r="B55" s="33"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="33"/>
+      <c r="E55" s="33"/>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33"/>
+      <c r="H55" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="I55" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="J55" s="33">
         <f t="shared" si="0"/>
         <v>8192</v>
       </c>
-      <c r="K53" s="32" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="54" spans="2:11">
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="I54" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="J54" s="32">
+      <c r="K55" s="33" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11">
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="J56" s="33">
         <f t="shared" si="0"/>
         <v>16384</v>
       </c>
-      <c r="K54" s="32" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11">
-      <c r="B55" s="32"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="I55" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="J55" s="32">
+      <c r="K56" s="33" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11">
+      <c r="B57" s="33"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="I57" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="J57" s="33">
         <f t="shared" si="0"/>
         <v>32768</v>
       </c>
-      <c r="K55" s="32" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11">
-      <c r="B56" s="32"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="I56" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="J56" s="32">
+      <c r="K57" s="33" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11">
+      <c r="B58" s="33"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="33"/>
+      <c r="E58" s="33"/>
+      <c r="F58" s="33"/>
+      <c r="G58" s="33"/>
+      <c r="H58" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="I58" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="J58" s="33">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
-      <c r="K56" s="32" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11">
-      <c r="B57" s="32"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="I57" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="J57" s="32">
+      <c r="K58" s="33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11">
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
+      <c r="H59" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="I59" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="J59" s="33">
         <f t="shared" si="0"/>
         <v>131072</v>
       </c>
-      <c r="K57" s="32" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11">
-      <c r="B58" s="32"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="I58" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="J58" s="32">
+      <c r="K59" s="33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11">
+      <c r="B60" s="33"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="I60" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="J60" s="33">
         <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K58" s="32" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11">
-      <c r="B59" s="34"/>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="34"/>
-      <c r="H59" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="I59" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="J59" s="34">
+      <c r="K60" s="33" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="I61" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="J61" s="35">
         <f t="shared" si="0"/>
         <v>524288</v>
       </c>
-      <c r="K59" s="34" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="60" spans="2:11">
-      <c r="B60" s="34"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="I60" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="J60" s="34">
+      <c r="K61" s="35" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11">
+      <c r="B62" s="35"/>
+      <c r="C62" s="35"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="I62" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="J62" s="35">
         <f t="shared" si="0"/>
         <v>1048576</v>
       </c>
-      <c r="K60" s="34" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="34"/>
-      <c r="C61" s="34"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="34"/>
-      <c r="F61" s="34"/>
-      <c r="G61" s="34"/>
-      <c r="H61" s="34" t="s">
-        <v>169</v>
-      </c>
-      <c r="I61" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="J61" s="34">
+      <c r="K62" s="35" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11">
+      <c r="B63" s="35"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="I63" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="J63" s="35">
         <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
-      <c r="K61" s="34" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="2:11">
-      <c r="B62" s="34"/>
-      <c r="C62" s="34"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="34"/>
-      <c r="H62" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="I62" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J62" s="34">
-        <f t="shared" si="0"/>
-        <v>4194304</v>
-      </c>
-      <c r="K62" s="34" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11">
-      <c r="B63" s="34"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="34" t="s">
+      <c r="K63" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="I63" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="J63" s="34">
-        <f t="shared" si="0"/>
-        <v>8388608</v>
-      </c>
-      <c r="K63" s="34" t="s">
-        <v>177</v>
-      </c>
     </row>
     <row r="64" spans="2:11">
-      <c r="B64" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C64" s="33" t="b">
-        <v>1</v>
-      </c>
-      <c r="D64" s="33" t="b">
-        <v>1</v>
-      </c>
+      <c r="B64" s="35"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
       <c r="E64" s="35"/>
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
       <c r="H64" s="35" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I64" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="J64" s="32">
-        <v>1</v>
+        <v>177</v>
+      </c>
+      <c r="J64" s="35">
+        <f t="shared" si="0"/>
+        <v>4194304</v>
       </c>
       <c r="K64" s="35" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="2:11">
@@ -3668,102 +3658,103 @@
       <c r="F65" s="35"/>
       <c r="G65" s="35"/>
       <c r="H65" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="I65" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="J65" s="35">
+        <f t="shared" si="0"/>
+        <v>8388608</v>
+      </c>
+      <c r="K65" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="I65" s="35" t="s">
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="J65" s="32">
+      <c r="C66" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="D66" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="36"/>
+      <c r="H66" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="I66" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="J66" s="33">
+        <v>1</v>
+      </c>
+      <c r="K66" s="36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11">
+      <c r="B67" s="36"/>
+      <c r="C67" s="36"/>
+      <c r="D67" s="36"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="36"/>
+      <c r="G67" s="36"/>
+      <c r="H67" s="36" t="s">
+        <v>185</v>
+      </c>
+      <c r="I67" s="36" t="s">
+        <v>186</v>
+      </c>
+      <c r="J67" s="33">
         <v>2</v>
       </c>
-      <c r="K65" s="35" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="35"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="I66" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="J66" s="32">
+      <c r="K67" s="36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11">
+      <c r="B68" s="36"/>
+      <c r="C68" s="36"/>
+      <c r="D68" s="36"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="36"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="I68" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="J68" s="33">
         <v>4</v>
       </c>
-      <c r="K66" s="35" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="35"/>
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="I67" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="J67" s="32">
-        <v>8</v>
-      </c>
-      <c r="K67" s="35" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11">
-      <c r="B68" s="35"/>
-      <c r="C68" s="35"/>
-      <c r="D68" s="35"/>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="35" t="s">
+      <c r="K68" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="I68" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="J68" s="32">
-        <v>15</v>
-      </c>
-      <c r="K68" s="35" t="s">
-        <v>192</v>
-      </c>
     </row>
     <row r="69" spans="2:11">
-      <c r="B69" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="C69" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="D69" s="37" t="b">
-        <v>1</v>
-      </c>
+      <c r="B69" s="36"/>
+      <c r="C69" s="36"/>
+      <c r="D69" s="36"/>
       <c r="E69" s="36"/>
       <c r="F69" s="36"/>
       <c r="G69" s="36"/>
       <c r="H69" s="36" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="J69" s="36">
-        <v>1</v>
+        <v>192</v>
+      </c>
+      <c r="J69" s="33">
+        <v>8</v>
       </c>
       <c r="K69" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="2:11">
@@ -3774,637 +3765,643 @@
       <c r="F70" s="36"/>
       <c r="G70" s="36"/>
       <c r="H70" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="I70" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="J70" s="33">
+        <v>15</v>
+      </c>
+      <c r="K70" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="I70" s="36" t="s">
+    </row>
+    <row r="71" spans="2:11">
+      <c r="B71" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="J70" s="36">
+      <c r="C71" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="D71" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="I71" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="J71" s="37">
+        <v>1</v>
+      </c>
+      <c r="K71" s="37" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="B72" s="37"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="37"/>
+      <c r="H72" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="I72" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="J72" s="37">
         <v>2</v>
       </c>
-      <c r="K70" s="36" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="71" spans="2:11">
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="I71" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="J71" s="36">
+      <c r="K72" s="37" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
+      <c r="B73" s="37"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="37"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="37"/>
+      <c r="H73" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="I73" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="J73" s="37">
         <v>4</v>
       </c>
-      <c r="K71" s="36" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="36"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="36"/>
-      <c r="E72" s="36"/>
-      <c r="F72" s="36"/>
-      <c r="G72" s="36"/>
-      <c r="H72" s="36" t="s">
-        <v>200</v>
-      </c>
-      <c r="I72" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="J72" s="36">
+      <c r="K73" s="37" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="I74" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="J74" s="37">
         <v>8</v>
       </c>
-      <c r="K72" s="36" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11">
-      <c r="B73" s="36"/>
-      <c r="C73" s="36"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="36"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="36"/>
-      <c r="H73" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="I73" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="J73" s="36">
+      <c r="K74" s="37" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="B75" s="37"/>
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
+      <c r="E75" s="37"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="37"/>
+      <c r="H75" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="I75" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="J75" s="37">
         <v>16</v>
       </c>
-      <c r="K73" s="36" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="B74" s="36"/>
-      <c r="C74" s="36"/>
-      <c r="D74" s="36"/>
-      <c r="E74" s="36"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="36" t="s">
-        <v>204</v>
-      </c>
-      <c r="I74" s="36" t="s">
-        <v>205</v>
-      </c>
-      <c r="J74" s="36">
+      <c r="K75" s="37" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" s="37"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="37"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="H76" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="I76" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="J76" s="37">
         <v>32</v>
       </c>
-      <c r="K74" s="36" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="B75" s="36"/>
-      <c r="C75" s="36"/>
-      <c r="D75" s="36"/>
-      <c r="E75" s="36"/>
-      <c r="F75" s="36"/>
-      <c r="G75" s="36"/>
-      <c r="H75" s="36" t="s">
-        <v>206</v>
-      </c>
-      <c r="I75" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="J75" s="36">
+      <c r="K76" s="37" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" s="37"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="37"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="I77" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="J77" s="37">
         <v>64</v>
       </c>
-      <c r="K75" s="36" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="36"/>
-      <c r="C76" s="36"/>
-      <c r="D76" s="36"/>
-      <c r="E76" s="36"/>
-      <c r="F76" s="36"/>
-      <c r="G76" s="36"/>
-      <c r="H76" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="I76" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="J76" s="36">
+      <c r="K77" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="I78" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="J78" s="37">
         <v>127</v>
       </c>
-      <c r="K76" s="36" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="C77" s="38" t="b">
+      <c r="K78" s="37" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" s="39" t="b">
         <v>0</v>
       </c>
-      <c r="D77" s="38" t="b">
+      <c r="D79" s="39" t="b">
         <v>1</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="I77" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="J77" s="24">
+      <c r="E79" s="24"/>
+      <c r="F79" s="24"/>
+      <c r="G79" s="24"/>
+      <c r="H79" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="I79" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="J79" s="24">
         <v>0</v>
       </c>
-      <c r="K77" s="24"/>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="24"/>
-      <c r="C78" s="24"/>
-      <c r="D78" s="24"/>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="I78" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="J78" s="24">
+      <c r="K79" s="24"/>
+    </row>
+    <row r="80" spans="2:11">
+      <c r="B80" s="24"/>
+      <c r="C80" s="24"/>
+      <c r="D80" s="24"/>
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="I80" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="J80" s="24">
         <v>1</v>
       </c>
-      <c r="K78" s="24"/>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="C79" s="40" t="b">
+      <c r="K80" s="24"/>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="D79" s="40" t="b">
+      <c r="D81" s="41" t="b">
         <v>1</v>
       </c>
-      <c r="E79" s="41"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="41"/>
-      <c r="H79" s="41" t="s">
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="I79" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="J79" s="41">
+      <c r="I81" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="J81" s="42">
         <v>0</v>
       </c>
-      <c r="K79" s="41" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="B80" s="41"/>
-      <c r="C80" s="41"/>
-      <c r="D80" s="41"/>
-      <c r="E80" s="41"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="41"/>
-      <c r="H80" s="41" t="s">
-        <v>214</v>
-      </c>
-      <c r="I80" s="41" t="s">
-        <v>215</v>
-      </c>
-      <c r="J80" s="41">
+      <c r="K81" s="42" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" s="42"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="I82" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="J82" s="42">
         <v>1</v>
       </c>
-      <c r="K80" s="41" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="B81" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="C81" s="26" t="b">
+      <c r="K82" s="42" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="C83" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="D81" s="26" t="b">
+      <c r="D83" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="E81" s="25"/>
-      <c r="F81" s="25"/>
-      <c r="G81" s="25"/>
-      <c r="H81" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="I81" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="J81" s="36">
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="I83" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="J83" s="37">
         <v>1</v>
       </c>
-      <c r="K81" s="25" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82" s="25"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="25"/>
-      <c r="E82" s="25"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="25"/>
-      <c r="H82" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="I82" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="J82" s="36">
+      <c r="K83" s="26" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11">
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="I84" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="J84" s="37">
         <v>2</v>
       </c>
-      <c r="K82" s="25" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11">
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="25"/>
-      <c r="E83" s="25"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25"/>
-      <c r="H83" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="I83" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="J83" s="36">
+      <c r="K84" s="26" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11">
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="I85" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="J85" s="37">
         <v>4</v>
       </c>
-      <c r="K83" s="25" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="25"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="I84" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="J84" s="36">
+      <c r="K85" s="26" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11">
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="I86" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="J86" s="37">
         <v>8</v>
       </c>
-      <c r="K84" s="25" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11">
-      <c r="B85" s="25"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="25"/>
-      <c r="E85" s="25"/>
-      <c r="F85" s="25"/>
-      <c r="G85" s="25"/>
-      <c r="H85" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="I85" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="J85" s="36">
+      <c r="K86" s="26" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11">
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+      <c r="G87" s="26"/>
+      <c r="H87" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="I87" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="J87" s="37">
         <v>16</v>
       </c>
-      <c r="K85" s="25" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="43" t="s">
-        <v>231</v>
-      </c>
-      <c r="C86" s="40" t="b">
+      <c r="K87" s="26" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" s="42" t="s">
+        <v>235</v>
+      </c>
+      <c r="C88" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="D86" s="26" t="b">
+      <c r="D88" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="E86" s="41"/>
-      <c r="F86" s="41"/>
-      <c r="G86" s="41"/>
-      <c r="H86" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="I86" s="41" t="s">
-        <v>233</v>
-      </c>
-      <c r="J86" s="41">
+      <c r="E88" s="42"/>
+      <c r="F88" s="42"/>
+      <c r="G88" s="42"/>
+      <c r="H88" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="I88" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="J88" s="42">
         <v>1</v>
       </c>
-      <c r="K86" s="41" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11">
-      <c r="B87" s="41"/>
-      <c r="C87" s="41"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="41"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="41" t="s">
-        <v>234</v>
-      </c>
-      <c r="I87" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="J87" s="41">
+      <c r="K88" s="42" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" s="42"/>
+      <c r="C89" s="42"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+      <c r="G89" s="42"/>
+      <c r="H89" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="I89" s="42" t="s">
+        <v>239</v>
+      </c>
+      <c r="J89" s="42">
         <v>2</v>
       </c>
-      <c r="K87" s="41" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11">
-      <c r="B88" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="C88" s="26" t="b">
+      <c r="K89" s="42" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="C90" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D88" s="26" t="b">
+      <c r="D90" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="44" t="s">
-        <v>190</v>
-      </c>
-      <c r="I88" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="J88" s="25">
+      <c r="E90" s="26"/>
+      <c r="F90" s="26"/>
+      <c r="G90" s="26"/>
+      <c r="H90" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="I90" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="J90" s="26">
         <v>1</v>
       </c>
-      <c r="K88" s="25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
-      <c r="B89" s="25"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="25"/>
-      <c r="G89" s="25"/>
-      <c r="H89" s="44" t="s">
-        <v>237</v>
-      </c>
-      <c r="I89" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="J89" s="25">
+      <c r="K90" s="26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11">
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="26"/>
+      <c r="E91" s="26"/>
+      <c r="F91" s="26"/>
+      <c r="G91" s="26"/>
+      <c r="H91" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="I91" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="J91" s="26">
         <v>2</v>
       </c>
-      <c r="K89" s="25" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11">
-      <c r="B90" s="25"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="25"/>
-      <c r="E90" s="25"/>
-      <c r="F90" s="25"/>
-      <c r="G90" s="25"/>
-      <c r="H90" s="44" t="s">
-        <v>239</v>
-      </c>
-      <c r="I90" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="J90" s="25">
+      <c r="K91" s="26" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11">
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+      <c r="G92" s="26"/>
+      <c r="H92" s="44" t="s">
+        <v>243</v>
+      </c>
+      <c r="I92" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="J92" s="26">
         <v>3</v>
       </c>
-      <c r="K90" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
-      <c r="B91" s="45" t="s">
-        <v>241</v>
-      </c>
-      <c r="C91" s="46" t="b">
+      <c r="K92" s="26" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="C93" s="46" t="b">
         <v>0</v>
       </c>
-      <c r="D91" s="46" t="b">
+      <c r="D93" s="46" t="b">
         <v>1</v>
       </c>
-      <c r="E91" s="45"/>
-      <c r="F91" s="45"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="47" t="s">
-        <v>242</v>
-      </c>
-      <c r="I91" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="J91" s="45">
-        <v>1</v>
-      </c>
-      <c r="K91" s="45" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="92" spans="2:11">
-      <c r="B92" s="45"/>
-      <c r="C92" s="45"/>
-      <c r="D92" s="45"/>
-      <c r="E92" s="45"/>
-      <c r="F92" s="45"/>
-      <c r="G92" s="45"/>
-      <c r="H92" s="47" t="s">
-        <v>244</v>
-      </c>
-      <c r="I92" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="J92" s="45">
-        <v>2</v>
-      </c>
-      <c r="K92" s="45" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="93" spans="2:11">
-      <c r="B93" s="45"/>
-      <c r="C93" s="45"/>
-      <c r="D93" s="45"/>
       <c r="E93" s="45"/>
       <c r="F93" s="45"/>
       <c r="G93" s="45"/>
       <c r="H93" s="47" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I93" s="45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J93" s="45">
+        <v>1</v>
+      </c>
+      <c r="K93" s="45" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11">
+      <c r="B94" s="45"/>
+      <c r="C94" s="45"/>
+      <c r="D94" s="45"/>
+      <c r="E94" s="45"/>
+      <c r="F94" s="45"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="I94" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="J94" s="45">
+        <v>2</v>
+      </c>
+      <c r="K94" s="45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11">
+      <c r="B95" s="45"/>
+      <c r="C95" s="45"/>
+      <c r="D95" s="45"/>
+      <c r="E95" s="45"/>
+      <c r="F95" s="45"/>
+      <c r="G95" s="45"/>
+      <c r="H95" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="I95" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="J95" s="45">
         <v>3</v>
       </c>
-      <c r="K93" s="45" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11">
-      <c r="B94" s="48" t="s">
-        <v>247</v>
-      </c>
-      <c r="C94" s="49" t="b">
+      <c r="K95" s="45" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="B96" s="48" t="s">
+        <v>251</v>
+      </c>
+      <c r="C96" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D94" s="49" t="b">
+      <c r="D96" s="49" t="b">
         <v>1</v>
       </c>
-      <c r="E94" s="48"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="48"/>
-      <c r="H94" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="I94" s="50" t="s">
-        <v>249</v>
-      </c>
-      <c r="J94" s="50">
-        <v>0</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="95" spans="2:11">
-      <c r="B95" s="48"/>
-      <c r="C95" s="48"/>
-      <c r="D95" s="48"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="48"/>
-      <c r="H95" s="50" t="s">
-        <v>251</v>
-      </c>
-      <c r="I95" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="J95" s="50">
-        <v>1</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="96" spans="2:11">
-      <c r="B96" s="48"/>
-      <c r="C96" s="48"/>
-      <c r="D96" s="48"/>
       <c r="E96" s="48"/>
       <c r="F96" s="48"/>
       <c r="G96" s="48"/>
       <c r="H96" s="50" t="s">
+        <v>252</v>
+      </c>
+      <c r="I96" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="J96" s="50">
+        <v>0</v>
+      </c>
+      <c r="K96" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="I96" s="50" t="s">
+    </row>
+    <row r="97" spans="2:11">
+      <c r="B97" s="48"/>
+      <c r="C97" s="48"/>
+      <c r="D97" s="48"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="48"/>
+      <c r="G97" s="48"/>
+      <c r="H97" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="J96" s="50">
+      <c r="I97" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="J97" s="50">
+        <v>1</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11">
+      <c r="B98" s="48"/>
+      <c r="C98" s="48"/>
+      <c r="D98" s="48"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="I98" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="J98" s="50">
         <v>2</v>
       </c>
-      <c r="K96" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11">
-      <c r="B97" s="51" t="s">
-        <v>256</v>
-      </c>
-      <c r="C97" s="52" t="b">
+      <c r="K98" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
+      <c r="B99" s="51" t="s">
+        <v>260</v>
+      </c>
+      <c r="C99" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="D97" s="52" t="b">
+      <c r="D99" s="52" t="b">
         <v>1</v>
       </c>
-      <c r="E97" s="51"/>
-      <c r="F97" s="51"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="53" t="s">
-        <v>257</v>
-      </c>
-      <c r="I97" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="J97" s="51">
-        <v>1</v>
-      </c>
-      <c r="K97" s="51" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="98" spans="2:11">
-      <c r="B98" s="51"/>
-      <c r="C98" s="51"/>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
-      <c r="F98" s="51"/>
-      <c r="G98" s="51"/>
-      <c r="H98" s="53" t="s">
-        <v>259</v>
-      </c>
-      <c r="I98" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="J98" s="51">
-        <v>2</v>
-      </c>
-      <c r="K98" s="51" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="99" spans="2:11">
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
       <c r="E99" s="51"/>
       <c r="F99" s="51"/>
       <c r="G99" s="51"/>
-      <c r="H99" s="53" t="s">
+      <c r="H99" s="51" t="s">
         <v>261</v>
       </c>
       <c r="I99" s="51" t="s">
         <v>262</v>
       </c>
       <c r="J99" s="51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K99" s="51" t="s">
         <v>262</v>
@@ -4417,14 +4414,14 @@
       <c r="E100" s="51"/>
       <c r="F100" s="51"/>
       <c r="G100" s="51"/>
-      <c r="H100" s="53" t="s">
+      <c r="H100" s="51" t="s">
         <v>263</v>
       </c>
       <c r="I100" s="51" t="s">
         <v>264</v>
       </c>
       <c r="J100" s="51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K100" s="51" t="s">
         <v>264</v>
@@ -4437,59 +4434,62 @@
       <c r="E101" s="51"/>
       <c r="F101" s="51"/>
       <c r="G101" s="51"/>
-      <c r="H101" s="53" t="s">
+      <c r="H101" s="51" t="s">
         <v>265</v>
       </c>
       <c r="I101" s="51" t="s">
         <v>266</v>
       </c>
       <c r="J101" s="51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K101" s="51" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="102" spans="2:11">
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="51"/>
+      <c r="C102" s="51"/>
+      <c r="D102" s="51"/>
+      <c r="E102" s="51"/>
+      <c r="F102" s="51"/>
+      <c r="G102" s="51"/>
+      <c r="H102" s="51" t="s">
         <v>267</v>
       </c>
-      <c r="C102" s="49" t="b">
-        <v>0</v>
-      </c>
-      <c r="D102" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H102" s="1" t="s">
+      <c r="I102" s="51" t="s">
         <v>268</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="J102" s="51">
+        <v>4</v>
+      </c>
+      <c r="K102" s="51" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="B103" s="51"/>
+      <c r="C103" s="51"/>
+      <c r="D103" s="51"/>
+      <c r="E103" s="51"/>
+      <c r="F103" s="51"/>
+      <c r="G103" s="51"/>
+      <c r="H103" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="J102" s="1">
-        <v>1</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="103" spans="2:11">
-      <c r="H103" s="1" t="s">
+      <c r="I103" s="51" t="s">
         <v>270</v>
       </c>
-      <c r="I103" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="J103" s="1">
-        <v>2</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>271</v>
+      <c r="J103" s="51">
+        <v>5</v>
+      </c>
+      <c r="K103" s="51" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="2:11">
       <c r="B104" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C104" s="49" t="b">
         <v>0</v>
@@ -4498,103 +4498,112 @@
         <v>1</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>273</v>
       </c>
       <c r="J104" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="2:11">
       <c r="H105" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I105" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="I105" s="1" t="s">
+      <c r="J105" s="1">
+        <v>2</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11">
+      <c r="B106" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="J105" s="1">
+      <c r="C106" s="49" t="b">
+        <v>0</v>
+      </c>
+      <c r="D106" s="49" t="b">
         <v>1</v>
       </c>
-      <c r="K105" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="106" spans="2:11">
       <c r="H106" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I106" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I106" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="J106" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K106" s="1" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="107" spans="2:11">
-      <c r="B107"/>
-      <c r="C107"/>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107" s="54" t="s">
+      <c r="H107" s="1" t="s">
         <v>279</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>280</v>
       </c>
       <c r="J107" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K107" s="1" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="108" spans="2:11">
-      <c r="H108" s="54" t="s">
+      <c r="H108" s="1" t="s">
         <v>281</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>282</v>
       </c>
       <c r="J108" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K108" s="1" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="109" spans="2:11">
-      <c r="H109" s="1" t="s">
+      <c r="B109" s="53"/>
+      <c r="C109" s="53"/>
+      <c r="D109" s="53"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="53"/>
+      <c r="G109" s="53"/>
+      <c r="H109" s="25" t="s">
         <v>283</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>284</v>
       </c>
       <c r="J109" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K109" s="1" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="110" spans="2:11">
-      <c r="H110" s="1" t="s">
+      <c r="H110" s="25" t="s">
         <v>285</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>286</v>
       </c>
       <c r="J110" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K110" s="1" t="s">
         <v>286</v>
@@ -4602,41 +4611,41 @@
     </row>
     <row r="111" spans="2:11">
       <c r="H111" s="1" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J111" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="H112" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J112" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="113" spans="8:11">
       <c r="H113" s="1" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>291</v>
       </c>
       <c r="J113" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K113" s="1" t="s">
         <v>291</v>
@@ -4650,7 +4659,7 @@
         <v>293</v>
       </c>
       <c r="J114" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K114" s="1" t="s">
         <v>293</v>
@@ -4664,7 +4673,7 @@
         <v>295</v>
       </c>
       <c r="J115" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K115" s="1" t="s">
         <v>295</v>
@@ -4678,10 +4687,38 @@
         <v>297</v>
       </c>
       <c r="J116" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K116" s="1" t="s">
         <v>297</v>
+      </c>
+    </row>
+    <row r="117" spans="8:11">
+      <c r="H117" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J117" s="1">
+        <v>11</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="118" spans="8:11">
+      <c r="H118" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J118" s="1">
+        <v>12</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64716C02-36BC-48B0-BEB8-844BB495369A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500"/>
+    <workbookView xWindow="4560" yWindow="3220" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="305">
   <si>
     <t>##var</t>
   </si>
@@ -933,19 +939,25 @@
   </si>
   <si>
     <t>商店特殊道具</t>
+  </si>
+  <si>
+    <t>Popularity</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>人气值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>人气数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -956,167 +968,37 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="SimSun"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="49">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1221,192 +1103,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1554,255 +1256,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1962,65 +1422,24 @@
     <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2273,25 +1692,25 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L118"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L119"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.0833333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.0833333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -2318,13 +1737,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -2352,7 +1771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
+    <row r="3" spans="1:12" ht="99" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2905,49 +2324,43 @@
       </c>
     </row>
     <row r="30" spans="2:11">
-      <c r="B30" s="26" t="s">
+      <c r="H30" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="I30" s="54" t="s">
+        <v>304</v>
+      </c>
+      <c r="J30" s="1">
+        <v>13</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="27" t="b">
+      <c r="C31" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D30" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="I30" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="J30" s="26">
-        <v>0</v>
-      </c>
-      <c r="K30" s="26" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11">
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
+      <c r="D31" s="27" t="b">
+        <v>1</v>
+      </c>
       <c r="E31" s="26"/>
       <c r="F31" s="26"/>
       <c r="G31" s="26"/>
       <c r="H31" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I31" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J31" s="26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="2:11">
@@ -2958,16 +2371,16 @@
       <c r="F32" s="26"/>
       <c r="G32" s="26"/>
       <c r="H32" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I32" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J32" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="2:11">
@@ -2978,62 +2391,62 @@
       <c r="F33" s="26"/>
       <c r="G33" s="26"/>
       <c r="H33" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="I33" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="J33" s="26">
+        <v>2</v>
+      </c>
+      <c r="K33" s="26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="I33" s="26" t="s">
+      <c r="I34" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="J33" s="26">
+      <c r="J34" s="26">
         <v>3</v>
       </c>
-      <c r="K33" s="26" t="s">
+      <c r="K34" s="26" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="28" t="s">
+    <row r="35" spans="2:11">
+      <c r="B35" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C34" s="29" t="b">
+      <c r="C35" s="29" t="b">
         <v>0</v>
       </c>
-      <c r="D34" s="29" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="I34" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="J34" s="30">
-        <v>0</v>
-      </c>
-      <c r="K34" s="30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="D35" s="29" t="b">
+        <v>1</v>
+      </c>
       <c r="E35" s="30"/>
       <c r="F35" s="30"/>
       <c r="G35" s="30"/>
       <c r="H35" s="30" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I35" s="30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J35" s="30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="2:11">
@@ -3044,16 +2457,16 @@
       <c r="F36" s="30"/>
       <c r="G36" s="30"/>
       <c r="H36" s="30" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I36" s="30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J36" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36" s="30" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="2:11">
@@ -3064,62 +2477,62 @@
       <c r="F37" s="30"/>
       <c r="G37" s="30"/>
       <c r="H37" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="I37" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="J37" s="30">
+        <v>2</v>
+      </c>
+      <c r="K37" s="30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="I37" s="30" t="s">
+      <c r="I38" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="J37" s="30">
+      <c r="J38" s="30">
         <v>3</v>
       </c>
-      <c r="K37" s="30" t="s">
+      <c r="K38" s="30" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="31" t="s">
+    <row r="39" spans="2:11">
+      <c r="B39" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="32" t="b">
+      <c r="C39" s="32" t="b">
         <v>0</v>
       </c>
-      <c r="D38" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="I38" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="J38" s="31">
-        <v>1</v>
-      </c>
-      <c r="K38" s="31" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
+      <c r="D39" s="32" t="b">
+        <v>1</v>
+      </c>
       <c r="E39" s="31"/>
       <c r="F39" s="31"/>
       <c r="G39" s="31"/>
       <c r="H39" s="31" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I39" s="31" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J39" s="31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K39" s="31" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="2:11">
@@ -3130,62 +2543,62 @@
       <c r="F40" s="31"/>
       <c r="G40" s="31"/>
       <c r="H40" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="I40" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="J40" s="31">
+        <v>2</v>
+      </c>
+      <c r="K40" s="31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="I40" s="31" t="s">
+      <c r="I41" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="J40" s="31">
+      <c r="J41" s="31">
         <v>3</v>
       </c>
-      <c r="K40" s="31" t="s">
+      <c r="K41" s="31" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="2:11">
-      <c r="B41" s="33" t="s">
+    <row r="42" spans="2:11">
+      <c r="B42" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="D41" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="I41" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="J41" s="33">
-        <v>0</v>
-      </c>
-      <c r="K41" s="33" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="B42" s="33"/>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
+      <c r="C42" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" s="34" t="b">
+        <v>1</v>
+      </c>
       <c r="E42" s="33"/>
       <c r="F42" s="33"/>
       <c r="G42" s="33"/>
       <c r="H42" s="33" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="I42" s="33" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J42" s="33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="33" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="2:11">
@@ -3196,17 +2609,16 @@
       <c r="F43" s="33"/>
       <c r="G43" s="33"/>
       <c r="H43" s="33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I43" s="33" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J43" s="33">
-        <f t="shared" ref="J43:J65" si="0">J42*2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K43" s="33" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="2:11">
@@ -3217,17 +2629,17 @@
       <c r="F44" s="33"/>
       <c r="G44" s="33"/>
       <c r="H44" s="33" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I44" s="33" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J44" s="33">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" ref="J44:J66" si="0">J43*2</f>
+        <v>2</v>
       </c>
       <c r="K44" s="33" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="2:11">
@@ -3238,17 +2650,17 @@
       <c r="F45" s="33"/>
       <c r="G45" s="33"/>
       <c r="H45" s="33" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I45" s="33" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J45" s="33">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K45" s="33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="2:11">
@@ -3259,17 +2671,17 @@
       <c r="F46" s="33"/>
       <c r="G46" s="33"/>
       <c r="H46" s="33" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I46" s="33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J46" s="33">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K46" s="33" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="2:11">
@@ -3280,17 +2692,17 @@
       <c r="F47" s="33"/>
       <c r="G47" s="33"/>
       <c r="H47" s="33" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I47" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J47" s="33">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K47" s="33" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="2:11">
@@ -3301,17 +2713,17 @@
       <c r="F48" s="33"/>
       <c r="G48" s="33"/>
       <c r="H48" s="33" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I48" s="33" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="J48" s="33">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K48" s="33" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="2:11">
@@ -3322,17 +2734,17 @@
       <c r="F49" s="33"/>
       <c r="G49" s="33"/>
       <c r="H49" s="33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="I49" s="33" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J49" s="33">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>64</v>
       </c>
       <c r="K49" s="33" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="2:11">
@@ -3343,17 +2755,17 @@
       <c r="F50" s="33"/>
       <c r="G50" s="33"/>
       <c r="H50" s="33" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I50" s="33" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J50" s="33">
         <f t="shared" si="0"/>
-        <v>256</v>
+        <v>128</v>
       </c>
       <c r="K50" s="33" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="51" spans="2:11">
@@ -3364,17 +2776,17 @@
       <c r="F51" s="33"/>
       <c r="G51" s="33"/>
       <c r="H51" s="33" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I51" s="33" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="J51" s="33">
         <f t="shared" si="0"/>
-        <v>512</v>
+        <v>256</v>
       </c>
       <c r="K51" s="33" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="2:11">
@@ -3385,17 +2797,17 @@
       <c r="F52" s="33"/>
       <c r="G52" s="33"/>
       <c r="H52" s="33" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I52" s="33" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J52" s="33">
         <f t="shared" si="0"/>
-        <v>1024</v>
+        <v>512</v>
       </c>
       <c r="K52" s="33" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="53" spans="2:11">
@@ -3406,17 +2818,17 @@
       <c r="F53" s="33"/>
       <c r="G53" s="33"/>
       <c r="H53" s="33" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I53" s="33" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J53" s="33">
         <f t="shared" si="0"/>
-        <v>2048</v>
+        <v>1024</v>
       </c>
       <c r="K53" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="2:11">
@@ -3427,17 +2839,17 @@
       <c r="F54" s="33"/>
       <c r="G54" s="33"/>
       <c r="H54" s="33" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="I54" s="33" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J54" s="33">
         <f t="shared" si="0"/>
-        <v>4096</v>
+        <v>2048</v>
       </c>
       <c r="K54" s="33" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="2:11">
@@ -3448,59 +2860,59 @@
       <c r="F55" s="33"/>
       <c r="G55" s="33"/>
       <c r="H55" s="33" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I55" s="33" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="J55" s="33">
         <f t="shared" si="0"/>
-        <v>8192</v>
+        <v>4096</v>
       </c>
       <c r="K55" s="33" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="2:11">
       <c r="B56" s="33"/>
       <c r="C56" s="33"/>
       <c r="D56" s="33"/>
-      <c r="E56" s="35"/>
+      <c r="E56" s="33"/>
       <c r="F56" s="33"/>
       <c r="G56" s="33"/>
       <c r="H56" s="33" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="I56" s="33" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J56" s="33">
         <f t="shared" si="0"/>
-        <v>16384</v>
+        <v>8192</v>
       </c>
       <c r="K56" s="33" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="2:11">
       <c r="B57" s="33"/>
       <c r="C57" s="33"/>
       <c r="D57" s="33"/>
-      <c r="E57" s="33"/>
+      <c r="E57" s="35"/>
       <c r="F57" s="33"/>
       <c r="G57" s="33"/>
       <c r="H57" s="33" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I57" s="33" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J57" s="33">
         <f t="shared" si="0"/>
-        <v>32768</v>
+        <v>16384</v>
       </c>
       <c r="K57" s="33" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="2:11">
@@ -3511,17 +2923,17 @@
       <c r="F58" s="33"/>
       <c r="G58" s="33"/>
       <c r="H58" s="33" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I58" s="33" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J58" s="33">
         <f t="shared" si="0"/>
-        <v>65536</v>
+        <v>32768</v>
       </c>
       <c r="K58" s="33" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" spans="2:11">
@@ -3532,59 +2944,59 @@
       <c r="F59" s="33"/>
       <c r="G59" s="33"/>
       <c r="H59" s="33" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I59" s="33" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J59" s="33">
         <f t="shared" si="0"/>
-        <v>131072</v>
+        <v>65536</v>
       </c>
       <c r="K59" s="33" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="2:11">
       <c r="B60" s="33"/>
-      <c r="C60" s="35"/>
+      <c r="C60" s="33"/>
       <c r="D60" s="33"/>
       <c r="E60" s="33"/>
       <c r="F60" s="33"/>
       <c r="G60" s="33"/>
       <c r="H60" s="33" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I60" s="33" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J60" s="33">
         <f t="shared" si="0"/>
+        <v>131072</v>
+      </c>
+      <c r="K60" s="33" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11">
+      <c r="B61" s="33"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="33"/>
+      <c r="E61" s="33"/>
+      <c r="F61" s="33"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="I61" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="J61" s="33">
+        <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K60" s="33" t="s">
+      <c r="K61" s="33" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="61" spans="2:11">
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="I61" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="J61" s="35">
-        <f t="shared" si="0"/>
-        <v>524288</v>
-      </c>
-      <c r="K61" s="35" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="62" spans="2:11">
@@ -3595,17 +3007,17 @@
       <c r="F62" s="35"/>
       <c r="G62" s="35"/>
       <c r="H62" s="35" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="I62" s="35" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J62" s="35">
         <f t="shared" si="0"/>
-        <v>1048576</v>
+        <v>524288</v>
       </c>
       <c r="K62" s="35" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="2:11">
@@ -3616,17 +3028,17 @@
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
       <c r="H63" s="35" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I63" s="35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J63" s="35">
         <f t="shared" si="0"/>
-        <v>2097152</v>
+        <v>1048576</v>
       </c>
       <c r="K63" s="35" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="64" spans="2:11">
@@ -3637,17 +3049,17 @@
       <c r="F64" s="35"/>
       <c r="G64" s="35"/>
       <c r="H64" s="35" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I64" s="35" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J64" s="35">
         <f t="shared" si="0"/>
-        <v>4194304</v>
+        <v>2097152</v>
       </c>
       <c r="K64" s="35" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="2:11">
@@ -3658,63 +3070,64 @@
       <c r="F65" s="35"/>
       <c r="G65" s="35"/>
       <c r="H65" s="35" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I65" s="35" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="J65" s="35">
         <f t="shared" si="0"/>
+        <v>4194304</v>
+      </c>
+      <c r="K65" s="35" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11">
+      <c r="B66" s="35"/>
+      <c r="C66" s="35"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="I66" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="J66" s="35">
+        <f t="shared" si="0"/>
         <v>8388608</v>
       </c>
-      <c r="K65" s="35" t="s">
+      <c r="K66" s="35" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="66" spans="2:11">
-      <c r="B66" s="36" t="s">
+    <row r="67" spans="2:11">
+      <c r="B67" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="C66" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="D66" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-      <c r="G66" s="36"/>
-      <c r="H66" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="I66" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="J66" s="33">
-        <v>1</v>
-      </c>
-      <c r="K66" s="36" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="67" spans="2:11">
-      <c r="B67" s="36"/>
-      <c r="C67" s="36"/>
-      <c r="D67" s="36"/>
+      <c r="C67" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" s="34" t="b">
+        <v>1</v>
+      </c>
       <c r="E67" s="36"/>
       <c r="F67" s="36"/>
       <c r="G67" s="36"/>
       <c r="H67" s="36" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J67" s="33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K67" s="36" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" spans="2:11">
@@ -3725,16 +3138,16 @@
       <c r="F68" s="36"/>
       <c r="G68" s="36"/>
       <c r="H68" s="36" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="J68" s="33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K68" s="36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="2:11">
@@ -3745,16 +3158,16 @@
       <c r="F69" s="36"/>
       <c r="G69" s="36"/>
       <c r="H69" s="36" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J69" s="33">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K69" s="36" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="70" spans="2:11">
@@ -3765,62 +3178,62 @@
       <c r="F70" s="36"/>
       <c r="G70" s="36"/>
       <c r="H70" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="I70" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="J70" s="33">
+        <v>8</v>
+      </c>
+      <c r="K70" s="36" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11">
+      <c r="B71" s="36"/>
+      <c r="C71" s="36"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="I70" s="36" t="s">
+      <c r="I71" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="J70" s="33">
+      <c r="J71" s="33">
         <v>15</v>
       </c>
-      <c r="K70" s="36" t="s">
+      <c r="K71" s="36" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="71" spans="2:11">
-      <c r="B71" s="37" t="s">
+    <row r="72" spans="2:11">
+      <c r="B72" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="C71" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="D71" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="37"/>
-      <c r="F71" s="37"/>
-      <c r="G71" s="37"/>
-      <c r="H71" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="I71" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="J71" s="37">
-        <v>1</v>
-      </c>
-      <c r="K71" s="37" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="37"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
+      <c r="C72" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="D72" s="38" t="b">
+        <v>1</v>
+      </c>
       <c r="E72" s="37"/>
       <c r="F72" s="37"/>
       <c r="G72" s="37"/>
       <c r="H72" s="37" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I72" s="37" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J72" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K72" s="37" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="2:11">
@@ -3831,16 +3244,16 @@
       <c r="F73" s="37"/>
       <c r="G73" s="37"/>
       <c r="H73" s="37" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I73" s="37" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J73" s="37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K73" s="37" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="2:11">
@@ -3851,16 +3264,16 @@
       <c r="F74" s="37"/>
       <c r="G74" s="37"/>
       <c r="H74" s="37" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I74" s="37" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J74" s="37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K74" s="37" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="2:11">
@@ -3871,16 +3284,16 @@
       <c r="F75" s="37"/>
       <c r="G75" s="37"/>
       <c r="H75" s="37" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I75" s="37" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="J75" s="37">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K75" s="37" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="2:11">
@@ -3891,16 +3304,16 @@
       <c r="F76" s="37"/>
       <c r="G76" s="37"/>
       <c r="H76" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I76" s="37" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="J76" s="37">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K76" s="37" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="2:11">
@@ -3911,16 +3324,16 @@
       <c r="F77" s="37"/>
       <c r="G77" s="37"/>
       <c r="H77" s="37" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I77" s="37" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J77" s="37">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K77" s="37" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="2:11">
@@ -3931,150 +3344,150 @@
       <c r="F78" s="37"/>
       <c r="G78" s="37"/>
       <c r="H78" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="I78" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="J78" s="37">
+        <v>64</v>
+      </c>
+      <c r="K78" s="37" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="37"/>
+      <c r="H79" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="I78" s="37" t="s">
+      <c r="I79" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="J78" s="37">
+      <c r="J79" s="37">
         <v>127</v>
       </c>
-      <c r="K78" s="37" t="s">
+      <c r="K79" s="37" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="24" t="s">
+    <row r="80" spans="2:11">
+      <c r="B80" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="C79" s="39" t="b">
+      <c r="C80" s="39" t="b">
         <v>0</v>
       </c>
-      <c r="D79" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="24"/>
-      <c r="F79" s="24"/>
-      <c r="G79" s="24"/>
-      <c r="H79" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="I79" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="J79" s="24">
-        <v>0</v>
-      </c>
-      <c r="K79" s="24"/>
-    </row>
-    <row r="80" spans="2:11">
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
+      <c r="D80" s="39" t="b">
+        <v>1</v>
+      </c>
       <c r="E80" s="24"/>
       <c r="F80" s="24"/>
       <c r="G80" s="24"/>
       <c r="H80" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="I80" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="J80" s="24">
+        <v>0</v>
+      </c>
+      <c r="K80" s="24"/>
+    </row>
+    <row r="81" spans="2:11">
+      <c r="B81" s="24"/>
+      <c r="C81" s="24"/>
+      <c r="D81" s="24"/>
+      <c r="E81" s="24"/>
+      <c r="F81" s="24"/>
+      <c r="G81" s="24"/>
+      <c r="H81" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="I80" s="24" t="s">
+      <c r="I81" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="J80" s="24">
-        <v>1</v>
-      </c>
-      <c r="K80" s="24"/>
-    </row>
-    <row r="81" spans="2:11">
-      <c r="B81" s="40" t="s">
+      <c r="J81" s="24">
+        <v>1</v>
+      </c>
+      <c r="K81" s="24"/>
+    </row>
+    <row r="82" spans="2:11">
+      <c r="B82" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="C81" s="41" t="b">
+      <c r="C82" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="D81" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" s="42"/>
-      <c r="F81" s="42"/>
-      <c r="G81" s="42"/>
-      <c r="H81" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="I81" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="J81" s="42">
-        <v>0</v>
-      </c>
-      <c r="K81" s="42" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="82" spans="2:11">
-      <c r="B82" s="42"/>
-      <c r="C82" s="42"/>
-      <c r="D82" s="42"/>
+      <c r="D82" s="41" t="b">
+        <v>1</v>
+      </c>
       <c r="E82" s="42"/>
       <c r="F82" s="42"/>
       <c r="G82" s="42"/>
       <c r="H82" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="I82" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="J82" s="42">
+        <v>0</v>
+      </c>
+      <c r="K82" s="42" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11">
+      <c r="B83" s="42"/>
+      <c r="C83" s="42"/>
+      <c r="D83" s="42"/>
+      <c r="E83" s="42"/>
+      <c r="F83" s="42"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="I82" s="42" t="s">
+      <c r="I83" s="42" t="s">
         <v>219</v>
       </c>
-      <c r="J82" s="42">
-        <v>1</v>
-      </c>
-      <c r="K82" s="42" t="s">
+      <c r="J83" s="42">
+        <v>1</v>
+      </c>
+      <c r="K83" s="42" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="83" spans="2:11">
-      <c r="B83" s="43" t="s">
+    <row r="84" spans="2:11">
+      <c r="B84" s="43" t="s">
         <v>221</v>
       </c>
-      <c r="C83" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="D83" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="26"/>
-      <c r="F83" s="26"/>
-      <c r="G83" s="26"/>
-      <c r="H83" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="I83" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="J83" s="37">
-        <v>1</v>
-      </c>
-      <c r="K83" s="26" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11">
-      <c r="B84" s="26"/>
-      <c r="C84" s="26"/>
-      <c r="D84" s="26"/>
+      <c r="C84" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D84" s="27" t="b">
+        <v>1</v>
+      </c>
       <c r="E84" s="26"/>
       <c r="F84" s="26"/>
       <c r="G84" s="26"/>
       <c r="H84" s="26" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J84" s="37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" s="26" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="85" spans="2:11">
@@ -4085,16 +3498,16 @@
       <c r="F85" s="26"/>
       <c r="G85" s="26"/>
       <c r="H85" s="26" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I85" s="26" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J85" s="37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K85" s="26" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="86" spans="2:11">
@@ -4105,16 +3518,16 @@
       <c r="F86" s="26"/>
       <c r="G86" s="26"/>
       <c r="H86" s="26" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I86" s="26" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J86" s="37">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K86" s="26" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87" spans="2:11">
@@ -4125,108 +3538,108 @@
       <c r="F87" s="26"/>
       <c r="G87" s="26"/>
       <c r="H87" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="I87" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="J87" s="37">
+        <v>8</v>
+      </c>
+      <c r="K87" s="26" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11">
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="26"/>
+      <c r="G88" s="26"/>
+      <c r="H88" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="I87" s="26" t="s">
+      <c r="I88" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="J87" s="37">
+      <c r="J88" s="37">
         <v>16</v>
       </c>
-      <c r="K87" s="26" t="s">
+      <c r="K88" s="26" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="88" spans="2:11">
-      <c r="B88" s="42" t="s">
+    <row r="89" spans="2:11">
+      <c r="B89" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="C88" s="41" t="b">
+      <c r="C89" s="41" t="b">
         <v>0</v>
       </c>
-      <c r="D88" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="42"/>
-      <c r="F88" s="42"/>
-      <c r="G88" s="42"/>
-      <c r="H88" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="I88" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="J88" s="42">
-        <v>1</v>
-      </c>
-      <c r="K88" s="42" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11">
-      <c r="B89" s="42"/>
-      <c r="C89" s="42"/>
-      <c r="D89" s="42"/>
+      <c r="D89" s="27" t="b">
+        <v>1</v>
+      </c>
       <c r="E89" s="42"/>
       <c r="F89" s="42"/>
       <c r="G89" s="42"/>
       <c r="H89" s="42" t="s">
+        <v>236</v>
+      </c>
+      <c r="I89" s="42" t="s">
+        <v>237</v>
+      </c>
+      <c r="J89" s="42">
+        <v>1</v>
+      </c>
+      <c r="K89" s="42" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11">
+      <c r="B90" s="42"/>
+      <c r="C90" s="42"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
+      <c r="G90" s="42"/>
+      <c r="H90" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="I89" s="42" t="s">
+      <c r="I90" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="J89" s="42">
+      <c r="J90" s="42">
         <v>2</v>
       </c>
-      <c r="K89" s="42" t="s">
+      <c r="K90" s="42" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="2:11">
-      <c r="B90" s="26" t="s">
+    <row r="91" spans="2:11">
+      <c r="B91" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C90" s="27" t="b">
+      <c r="C91" s="27" t="b">
         <v>0</v>
       </c>
-      <c r="D90" s="27" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" s="26"/>
-      <c r="F90" s="26"/>
-      <c r="G90" s="26"/>
-      <c r="H90" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="I90" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="J90" s="26">
-        <v>1</v>
-      </c>
-      <c r="K90" s="26" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11">
-      <c r="B91" s="26"/>
-      <c r="C91" s="26"/>
-      <c r="D91" s="26"/>
+      <c r="D91" s="27" t="b">
+        <v>1</v>
+      </c>
       <c r="E91" s="26"/>
       <c r="F91" s="26"/>
       <c r="G91" s="26"/>
       <c r="H91" s="44" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="I91" s="26" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="J91" s="26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K91" s="26" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
     </row>
     <row r="92" spans="2:11">
@@ -4237,62 +3650,62 @@
       <c r="F92" s="26"/>
       <c r="G92" s="26"/>
       <c r="H92" s="44" t="s">
+        <v>241</v>
+      </c>
+      <c r="I92" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="J92" s="26">
+        <v>2</v>
+      </c>
+      <c r="K92" s="26" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11">
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="26"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="26"/>
+      <c r="G93" s="26"/>
+      <c r="H93" s="44" t="s">
         <v>243</v>
       </c>
-      <c r="I92" s="26" t="s">
+      <c r="I93" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="J92" s="26">
+      <c r="J93" s="26">
         <v>3</v>
       </c>
-      <c r="K92" s="26" t="s">
+      <c r="K93" s="26" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="93" spans="2:11">
-      <c r="B93" s="45" t="s">
+    <row r="94" spans="2:11">
+      <c r="B94" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="C93" s="46" t="b">
+      <c r="C94" s="46" t="b">
         <v>0</v>
       </c>
-      <c r="D93" s="46" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="45"/>
-      <c r="F93" s="45"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="I93" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="J93" s="45">
-        <v>1</v>
-      </c>
-      <c r="K93" s="45" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="94" spans="2:11">
-      <c r="B94" s="45"/>
-      <c r="C94" s="45"/>
-      <c r="D94" s="45"/>
+      <c r="D94" s="46" t="b">
+        <v>1</v>
+      </c>
       <c r="E94" s="45"/>
       <c r="F94" s="45"/>
       <c r="G94" s="45"/>
       <c r="H94" s="47" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I94" s="45" t="s">
-        <v>50</v>
+        <v>247</v>
       </c>
       <c r="J94" s="45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K94" s="45" t="s">
-        <v>50</v>
+        <v>247</v>
       </c>
     </row>
     <row r="95" spans="2:11">
@@ -4303,62 +3716,62 @@
       <c r="F95" s="45"/>
       <c r="G95" s="45"/>
       <c r="H95" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="I95" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="J95" s="45">
+        <v>2</v>
+      </c>
+      <c r="K95" s="45" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11">
+      <c r="B96" s="45"/>
+      <c r="C96" s="45"/>
+      <c r="D96" s="45"/>
+      <c r="E96" s="45"/>
+      <c r="F96" s="45"/>
+      <c r="G96" s="45"/>
+      <c r="H96" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="I95" s="45" t="s">
+      <c r="I96" s="45" t="s">
         <v>250</v>
       </c>
-      <c r="J95" s="45">
+      <c r="J96" s="45">
         <v>3</v>
       </c>
-      <c r="K95" s="45" t="s">
+      <c r="K96" s="45" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="96" spans="2:11">
-      <c r="B96" s="48" t="s">
+    <row r="97" spans="2:11">
+      <c r="B97" s="48" t="s">
         <v>251</v>
       </c>
-      <c r="C96" s="49" t="b">
+      <c r="C97" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D96" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="E96" s="48"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="48"/>
-      <c r="H96" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="I96" s="50" t="s">
-        <v>253</v>
-      </c>
-      <c r="J96" s="50">
-        <v>0</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="97" spans="2:11">
-      <c r="B97" s="48"/>
-      <c r="C97" s="48"/>
-      <c r="D97" s="48"/>
+      <c r="D97" s="49" t="b">
+        <v>1</v>
+      </c>
       <c r="E97" s="48"/>
       <c r="F97" s="48"/>
       <c r="G97" s="48"/>
       <c r="H97" s="50" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="I97" s="50" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="J97" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="2:11">
@@ -4369,62 +3782,62 @@
       <c r="F98" s="48"/>
       <c r="G98" s="48"/>
       <c r="H98" s="50" t="s">
+        <v>255</v>
+      </c>
+      <c r="I98" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="J98" s="50">
+        <v>1</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11">
+      <c r="B99" s="48"/>
+      <c r="C99" s="48"/>
+      <c r="D99" s="48"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="50" t="s">
         <v>258</v>
       </c>
-      <c r="I98" s="50" t="s">
+      <c r="I99" s="50" t="s">
         <v>259</v>
       </c>
-      <c r="J98" s="50">
+      <c r="J99" s="50">
         <v>2</v>
       </c>
-      <c r="K98" s="1" t="s">
+      <c r="K99" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="99" spans="2:11">
-      <c r="B99" s="51" t="s">
+    <row r="100" spans="2:11">
+      <c r="B100" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="C99" s="52" t="b">
+      <c r="C100" s="52" t="b">
         <v>0</v>
       </c>
-      <c r="D99" s="52" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" s="51"/>
-      <c r="F99" s="51"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="51" t="s">
-        <v>261</v>
-      </c>
-      <c r="I99" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="J99" s="51">
-        <v>1</v>
-      </c>
-      <c r="K99" s="51" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11">
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
+      <c r="D100" s="52" t="b">
+        <v>1</v>
+      </c>
       <c r="E100" s="51"/>
       <c r="F100" s="51"/>
       <c r="G100" s="51"/>
       <c r="H100" s="51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I100" s="51" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="J100" s="51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K100" s="51" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="101" spans="2:11">
@@ -4435,16 +3848,16 @@
       <c r="F101" s="51"/>
       <c r="G101" s="51"/>
       <c r="H101" s="51" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I101" s="51" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="J101" s="51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K101" s="51" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="102" spans="2:11">
@@ -4455,16 +3868,16 @@
       <c r="F102" s="51"/>
       <c r="G102" s="51"/>
       <c r="H102" s="51" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I102" s="51" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="J102" s="51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K102" s="51" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="103" spans="2:11">
@@ -4475,249 +3888,269 @@
       <c r="F103" s="51"/>
       <c r="G103" s="51"/>
       <c r="H103" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="I103" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="J103" s="51">
+        <v>4</v>
+      </c>
+      <c r="K103" s="51" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11">
+      <c r="B104" s="51"/>
+      <c r="C104" s="51"/>
+      <c r="D104" s="51"/>
+      <c r="E104" s="51"/>
+      <c r="F104" s="51"/>
+      <c r="G104" s="51"/>
+      <c r="H104" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="I103" s="51" t="s">
+      <c r="I104" s="51" t="s">
         <v>270</v>
       </c>
-      <c r="J103" s="51">
+      <c r="J104" s="51">
         <v>5</v>
       </c>
-      <c r="K103" s="51" t="s">
+      <c r="K104" s="51" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="104" spans="2:11">
-      <c r="B104" s="1" t="s">
+    <row r="105" spans="2:11">
+      <c r="B105" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C104" s="49" t="b">
+      <c r="C105" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D104" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H104" s="1" t="s">
+      <c r="D105" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H105" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="I104" s="1" t="s">
+      <c r="I105" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J104" s="1">
-        <v>1</v>
-      </c>
-      <c r="K104" s="1" t="s">
+      <c r="J105" s="1">
+        <v>1</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="105" spans="2:11">
-      <c r="H105" s="1" t="s">
+    <row r="106" spans="2:11">
+      <c r="H106" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I105" s="1" t="s">
+      <c r="I106" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="J105" s="1">
+      <c r="J106" s="1">
         <v>2</v>
       </c>
-      <c r="K105" s="1" t="s">
+      <c r="K106" s="1" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="106" spans="2:11">
-      <c r="B106" s="1" t="s">
+    <row r="107" spans="2:11">
+      <c r="B107" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C106" s="49" t="b">
+      <c r="C107" s="49" t="b">
         <v>0</v>
       </c>
-      <c r="D106" s="49" t="b">
-        <v>1</v>
-      </c>
-      <c r="H106" s="1" t="s">
+      <c r="D107" s="49" t="b">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="I106" s="1" t="s">
+      <c r="I107" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="J106" s="1">
+      <c r="J107" s="1">
         <v>0</v>
       </c>
-      <c r="K106" s="1" t="s">
+      <c r="K107" s="1" t="s">
         <v>278</v>
-      </c>
-    </row>
-    <row r="107" spans="2:11">
-      <c r="H107" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="J107" s="1">
-        <v>1</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="108" spans="2:11">
       <c r="H108" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J108" s="1">
+        <v>1</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11">
+      <c r="H109" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="I108" s="1" t="s">
+      <c r="I109" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="J108" s="1">
+      <c r="J109" s="1">
         <v>2</v>
       </c>
-      <c r="K108" s="1" t="s">
+      <c r="K109" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="109" spans="2:11">
-      <c r="B109" s="53"/>
-      <c r="C109" s="53"/>
-      <c r="D109" s="53"/>
-      <c r="E109" s="53"/>
-      <c r="F109" s="53"/>
-      <c r="G109" s="53"/>
-      <c r="H109" s="25" t="s">
+    <row r="110" spans="2:11">
+      <c r="B110" s="25"/>
+      <c r="C110" s="25"/>
+      <c r="D110" s="25"/>
+      <c r="E110" s="25"/>
+      <c r="F110" s="25"/>
+      <c r="G110" s="25"/>
+      <c r="H110" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="I109" s="1" t="s">
+      <c r="I110" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="J109" s="1">
+      <c r="J110" s="1">
         <v>3</v>
       </c>
-      <c r="K109" s="1" t="s">
+      <c r="K110" s="1" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="110" spans="2:11">
-      <c r="H110" s="25" t="s">
+    <row r="111" spans="2:11">
+      <c r="H111" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="I110" s="1" t="s">
+      <c r="I111" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="J110" s="1">
+      <c r="J111" s="1">
         <v>4</v>
       </c>
-      <c r="K110" s="1" t="s">
+      <c r="K111" s="1" t="s">
         <v>286</v>
-      </c>
-    </row>
-    <row r="111" spans="2:11">
-      <c r="H111" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="J111" s="1">
-        <v>5</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="H112" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J112" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="113" spans="8:11">
       <c r="H113" s="1" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J113" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="114" spans="8:11">
       <c r="H114" s="1" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J114" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="115" spans="8:11">
       <c r="H115" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J115" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="116" spans="8:11">
       <c r="H116" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J116" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="117" spans="8:11">
       <c r="H117" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J117" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="118" spans="8:11">
       <c r="H118" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J118" s="1">
+        <v>11</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="119" spans="8:11">
+      <c r="H119" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="I118" s="1" t="s">
+      <c r="I119" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="J118" s="1">
+      <c r="J119" s="1">
         <v>12</v>
       </c>
-      <c r="K118" s="1" t="s">
+      <c r="K119" s="1" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4725,8 +4158,8 @@
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64716C02-36BC-48B0-BEB8-844BB495369A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9777B058-C1E1-4980-963D-9901CDFCA212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="3220" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4180" yWindow="3220" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -941,16 +941,16 @@
     <t>商店特殊道具</t>
   </si>
   <si>
-    <t>Popularity</t>
+    <t>ExposureValue</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>人气值</t>
+    <t>曝光值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>曝光值</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>人气数</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1422,11 +1422,11 @@
     <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1737,13 +1737,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -2327,14 +2327,14 @@
       <c r="H30" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="I30" s="54" t="s">
-        <v>304</v>
+      <c r="I30" s="53" t="s">
+        <v>303</v>
       </c>
       <c r="J30" s="1">
         <v>13</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="2:11">

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9777B058-C1E1-4980-963D-9901CDFCA212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4180" yWindow="3220" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="306">
   <si>
     <t>##var</t>
   </si>
@@ -290,6 +284,12 @@
     <t>体力上限</t>
   </si>
   <si>
+    <t>ExposureValue</t>
+  </si>
+  <si>
+    <t>曝光值</t>
+  </si>
+  <si>
     <t>UICanvasLayer</t>
   </si>
   <si>
@@ -941,23 +941,23 @@
     <t>商店特殊道具</t>
   </si>
   <si>
-    <t>ExposureValue</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>曝光值</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>曝光值</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>FishingProduct</t>
+  </si>
+  <si>
+    <t>钓鱼产品</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -968,37 +968,174 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="SimSun"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="SimSun"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1037,6 +1174,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
@@ -1103,12 +1246,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1256,13 +1579,255 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1341,27 +1906,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1371,40 +1933,37 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1413,33 +1972,80 @@
     <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1692,25 +2298,25 @@
       </a:style>
     </a:spDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L119"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L120"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="27.08203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.0833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.8333333333333" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.08203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.0833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="38.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.08203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="38.6666666666667" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.0833333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="55.25" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -1737,13 +2343,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1771,7 +2377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -2325,1075 +2931,1075 @@
     </row>
     <row r="30" spans="2:11">
       <c r="H30" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="I30" s="53" t="s">
-        <v>303</v>
+        <v>85</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>86</v>
       </c>
       <c r="J30" s="1">
         <v>13</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>304</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="27" t="b">
+      <c r="B31" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="D31" s="27" t="b">
+      <c r="D31" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="I31" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="J31" s="26">
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="I31" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="J31" s="27">
         <v>0</v>
       </c>
-      <c r="K31" s="26" t="s">
-        <v>87</v>
+      <c r="K31" s="27" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="2:11">
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="I32" s="26" t="s">
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="I32" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="J32" s="27">
+        <v>1</v>
+      </c>
+      <c r="K32" s="27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="I33" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="J33" s="27">
+        <v>2</v>
+      </c>
+      <c r="K33" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11">
+      <c r="B34" s="27"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="I34" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" s="27">
+        <v>3</v>
+      </c>
+      <c r="K34" s="27" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" s="29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="I35" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="J32" s="26">
+      <c r="J35" s="31">
+        <v>0</v>
+      </c>
+      <c r="K35" s="31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="I36" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="J36" s="31">
         <v>1</v>
       </c>
-      <c r="K32" s="26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="B33" s="26"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="I33" s="26" t="s">
+      <c r="K36" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="J33" s="26">
+    </row>
+    <row r="37" spans="2:11">
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="I37" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J37" s="31">
         <v>2</v>
       </c>
-      <c r="K33" s="26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="I34" s="26" t="s">
+      <c r="K37" s="31" t="s">
         <v>93</v>
       </c>
-      <c r="J34" s="26">
+    </row>
+    <row r="38" spans="2:11">
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="I38" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="J38" s="31">
         <v>3</v>
       </c>
-      <c r="K34" s="26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="29" t="b">
+      <c r="K38" s="31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="B39" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="33" t="b">
         <v>0</v>
       </c>
-      <c r="D35" s="29" t="b">
+      <c r="D39" s="33" t="b">
         <v>1</v>
       </c>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="I35" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="J35" s="30">
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="I39" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="J39" s="32">
+        <v>1</v>
+      </c>
+      <c r="K39" s="32" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11">
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="I40" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="J40" s="32">
+        <v>2</v>
+      </c>
+      <c r="K40" s="32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="I41" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="J41" s="32">
+        <v>3</v>
+      </c>
+      <c r="K41" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="B42" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" s="35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="I42" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="J42" s="34">
         <v>0</v>
       </c>
-      <c r="K35" s="30" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="I36" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="J36" s="30">
+      <c r="K42" s="34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="I43" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="J43" s="34">
         <v>1</v>
       </c>
-      <c r="K36" s="30" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="I37" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="J37" s="30">
-        <v>2</v>
-      </c>
-      <c r="K37" s="30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="I38" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="J38" s="30">
-        <v>3</v>
-      </c>
-      <c r="K38" s="30" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="B39" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" s="32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="I39" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="J39" s="31">
-        <v>1</v>
-      </c>
-      <c r="K39" s="31" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="I40" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="J40" s="31">
-        <v>2</v>
-      </c>
-      <c r="K40" s="31" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11">
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="I41" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="J41" s="31">
-        <v>3</v>
-      </c>
-      <c r="K41" s="31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="B42" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="D42" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="I42" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="J42" s="33">
-        <v>0</v>
-      </c>
-      <c r="K42" s="33" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="I43" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="J43" s="33">
-        <v>1</v>
-      </c>
-      <c r="K43" s="33" t="s">
-        <v>112</v>
+      <c r="K43" s="34" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="2:11">
-      <c r="B44" s="33"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33" t="s">
-        <v>113</v>
-      </c>
-      <c r="I44" s="33" t="s">
-        <v>114</v>
-      </c>
-      <c r="J44" s="33">
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="I44" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="J44" s="34">
         <f t="shared" ref="J44:J66" si="0">J43*2</f>
         <v>2</v>
       </c>
-      <c r="K44" s="33" t="s">
-        <v>115</v>
+      <c r="K44" s="34" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="2:11">
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="33"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33" t="s">
-        <v>116</v>
-      </c>
-      <c r="I45" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="J45" s="33">
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="I45" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="J45" s="34">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K45" s="33" t="s">
-        <v>118</v>
+      <c r="K45" s="34" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="2:11">
-      <c r="B46" s="33"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="33"/>
-      <c r="E46" s="33"/>
-      <c r="F46" s="33"/>
-      <c r="G46" s="33"/>
-      <c r="H46" s="33" t="s">
-        <v>119</v>
-      </c>
-      <c r="I46" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="J46" s="33">
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="I46" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="J46" s="34">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K46" s="33" t="s">
-        <v>121</v>
+      <c r="K46" s="34" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="2:11">
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="33"/>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="I47" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="J47" s="33">
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="I47" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="J47" s="34">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="K47" s="33" t="s">
-        <v>124</v>
+      <c r="K47" s="34" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="2:11">
-      <c r="B48" s="33"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33" t="s">
-        <v>125</v>
-      </c>
-      <c r="I48" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="J48" s="33">
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="I48" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="J48" s="34">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="K48" s="33" t="s">
-        <v>127</v>
+      <c r="K48" s="34" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="2:11">
-      <c r="B49" s="33"/>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="I49" s="33" t="s">
-        <v>129</v>
-      </c>
-      <c r="J49" s="33">
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="I49" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="J49" s="34">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="K49" s="33" t="s">
-        <v>130</v>
+      <c r="K49" s="34" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="2:11">
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
-      <c r="H50" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="I50" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="J50" s="33">
+      <c r="B50" s="34"/>
+      <c r="C50" s="34"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+      <c r="G50" s="34"/>
+      <c r="H50" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="J50" s="34">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="K50" s="33" t="s">
-        <v>133</v>
+      <c r="K50" s="34" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="51" spans="2:11">
-      <c r="B51" s="33"/>
-      <c r="C51" s="33"/>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="I51" s="33" t="s">
-        <v>135</v>
-      </c>
-      <c r="J51" s="33">
+      <c r="B51" s="34"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="I51" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="J51" s="34">
         <f t="shared" si="0"/>
         <v>256</v>
       </c>
-      <c r="K51" s="33" t="s">
-        <v>136</v>
+      <c r="K51" s="34" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="2:11">
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33"/>
-      <c r="H52" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="I52" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="J52" s="33">
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="I52" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="J52" s="34">
         <f t="shared" si="0"/>
         <v>512</v>
       </c>
-      <c r="K52" s="33" t="s">
-        <v>139</v>
+      <c r="K52" s="34" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="2:11">
-      <c r="B53" s="33"/>
-      <c r="C53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33" t="s">
-        <v>140</v>
-      </c>
-      <c r="I53" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="J53" s="33">
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="I53" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="J53" s="34">
         <f t="shared" si="0"/>
         <v>1024</v>
       </c>
-      <c r="K53" s="33" t="s">
-        <v>142</v>
+      <c r="K53" s="34" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="2:11">
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="I54" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="J54" s="33">
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="I54" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="J54" s="34">
         <f t="shared" si="0"/>
         <v>2048</v>
       </c>
-      <c r="K54" s="33" t="s">
-        <v>145</v>
+      <c r="K54" s="34" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="2:11">
-      <c r="B55" s="33"/>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="33"/>
-      <c r="F55" s="33"/>
-      <c r="G55" s="33"/>
-      <c r="H55" s="33" t="s">
-        <v>146</v>
-      </c>
-      <c r="I55" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="J55" s="33">
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="I55" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="J55" s="34">
         <f t="shared" si="0"/>
         <v>4096</v>
       </c>
-      <c r="K55" s="33" t="s">
-        <v>148</v>
+      <c r="K55" s="34" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="2:11">
-      <c r="B56" s="33"/>
-      <c r="C56" s="33"/>
-      <c r="D56" s="33"/>
-      <c r="E56" s="33"/>
-      <c r="F56" s="33"/>
-      <c r="G56" s="33"/>
-      <c r="H56" s="33" t="s">
-        <v>149</v>
-      </c>
-      <c r="I56" s="33" t="s">
-        <v>150</v>
-      </c>
-      <c r="J56" s="33">
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="I56" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="J56" s="34">
         <f t="shared" si="0"/>
         <v>8192</v>
       </c>
-      <c r="K56" s="33" t="s">
-        <v>151</v>
+      <c r="K56" s="34" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="2:11">
-      <c r="B57" s="33"/>
-      <c r="C57" s="33"/>
-      <c r="D57" s="33"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="33"/>
-      <c r="G57" s="33"/>
-      <c r="H57" s="33" t="s">
-        <v>152</v>
-      </c>
-      <c r="I57" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="J57" s="33">
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="I57" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="J57" s="34">
         <f t="shared" si="0"/>
         <v>16384</v>
       </c>
-      <c r="K57" s="33" t="s">
-        <v>154</v>
+      <c r="K57" s="34" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="2:11">
-      <c r="B58" s="33"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="33"/>
-      <c r="E58" s="33"/>
-      <c r="F58" s="33"/>
-      <c r="G58" s="33"/>
-      <c r="H58" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="I58" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="J58" s="33">
+      <c r="B58" s="34"/>
+      <c r="C58" s="34"/>
+      <c r="D58" s="34"/>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="I58" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="J58" s="34">
         <f t="shared" si="0"/>
         <v>32768</v>
       </c>
-      <c r="K58" s="33" t="s">
-        <v>157</v>
+      <c r="K58" s="34" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="2:11">
-      <c r="B59" s="33"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
-      <c r="H59" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="I59" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="J59" s="33">
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="I59" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="J59" s="34">
         <f t="shared" si="0"/>
         <v>65536</v>
       </c>
-      <c r="K59" s="33" t="s">
-        <v>160</v>
+      <c r="K59" s="34" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="60" spans="2:11">
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="I60" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="J60" s="33">
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="34"/>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="I60" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="J60" s="34">
         <f t="shared" si="0"/>
         <v>131072</v>
       </c>
-      <c r="K60" s="33" t="s">
-        <v>163</v>
+      <c r="K60" s="34" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="61" spans="2:11">
-      <c r="B61" s="33"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33"/>
-      <c r="F61" s="33"/>
-      <c r="G61" s="33"/>
-      <c r="H61" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="I61" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="J61" s="33">
+      <c r="B61" s="34"/>
+      <c r="C61" s="36"/>
+      <c r="D61" s="34"/>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="I61" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="J61" s="34">
         <f t="shared" si="0"/>
         <v>262144</v>
       </c>
-      <c r="K61" s="33" t="s">
-        <v>166</v>
+      <c r="K61" s="34" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="2:11">
-      <c r="B62" s="35"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="35"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="I62" s="35" t="s">
-        <v>168</v>
-      </c>
-      <c r="J62" s="35">
+      <c r="B62" s="36"/>
+      <c r="C62" s="36"/>
+      <c r="D62" s="36"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="36"/>
+      <c r="G62" s="36"/>
+      <c r="H62" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="I62" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="J62" s="36">
         <f t="shared" si="0"/>
         <v>524288</v>
       </c>
-      <c r="K62" s="35" t="s">
-        <v>169</v>
+      <c r="K62" s="36" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="2:11">
-      <c r="B63" s="35"/>
-      <c r="C63" s="35"/>
-      <c r="D63" s="35"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="I63" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="J63" s="35">
+      <c r="B63" s="36"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="36"/>
+      <c r="G63" s="36"/>
+      <c r="H63" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="I63" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="J63" s="36">
         <f t="shared" si="0"/>
         <v>1048576</v>
       </c>
-      <c r="K63" s="35" t="s">
-        <v>172</v>
+      <c r="K63" s="36" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="2:11">
-      <c r="B64" s="35"/>
-      <c r="C64" s="35"/>
-      <c r="D64" s="35"/>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="I64" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="J64" s="35">
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="36"/>
+      <c r="G64" s="36"/>
+      <c r="H64" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="I64" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="J64" s="36">
         <f t="shared" si="0"/>
         <v>2097152</v>
       </c>
-      <c r="K64" s="35" t="s">
-        <v>175</v>
+      <c r="K64" s="36" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="2:11">
-      <c r="B65" s="35"/>
-      <c r="C65" s="35"/>
-      <c r="D65" s="35"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="I65" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="J65" s="35">
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="I65" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="J65" s="36">
         <f t="shared" si="0"/>
         <v>4194304</v>
       </c>
-      <c r="K65" s="35" t="s">
-        <v>178</v>
+      <c r="K65" s="36" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="2:11">
-      <c r="B66" s="35"/>
-      <c r="C66" s="35"/>
-      <c r="D66" s="35"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="I66" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="J66" s="35">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+      <c r="G66" s="36"/>
+      <c r="H66" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="I66" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="J66" s="36">
         <f t="shared" si="0"/>
         <v>8388608</v>
       </c>
-      <c r="K66" s="35" t="s">
-        <v>181</v>
+      <c r="K66" s="36" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="67" spans="2:11">
-      <c r="B67" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="C67" s="34" t="b">
+      <c r="B67" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="C67" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="D67" s="34" t="b">
+      <c r="D67" s="35" t="b">
         <v>1</v>
       </c>
-      <c r="E67" s="36"/>
-      <c r="F67" s="36"/>
-      <c r="G67" s="36"/>
-      <c r="H67" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="I67" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="J67" s="33">
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="37"/>
+      <c r="H67" s="37" t="s">
+        <v>185</v>
+      </c>
+      <c r="I67" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="J67" s="34">
         <v>1</v>
       </c>
-      <c r="K67" s="36" t="s">
-        <v>184</v>
+      <c r="K67" s="37" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="2:11">
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="I68" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="J68" s="33">
+      <c r="B68" s="37"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="I68" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="J68" s="34">
         <v>2</v>
       </c>
-      <c r="K68" s="36" t="s">
-        <v>187</v>
+      <c r="K68" s="37" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="69" spans="2:11">
-      <c r="B69" s="36"/>
-      <c r="C69" s="36"/>
-      <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="I69" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="J69" s="33">
+      <c r="B69" s="37"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="37"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="37"/>
+      <c r="H69" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="I69" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="J69" s="34">
         <v>4</v>
       </c>
-      <c r="K69" s="36" t="s">
-        <v>190</v>
+      <c r="K69" s="37" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="2:11">
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="I70" s="36" t="s">
-        <v>192</v>
-      </c>
-      <c r="J70" s="33">
+      <c r="B70" s="37"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="I70" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="J70" s="34">
         <v>8</v>
       </c>
-      <c r="K70" s="36" t="s">
-        <v>193</v>
+      <c r="K70" s="37" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="2:11">
-      <c r="B71" s="36"/>
-      <c r="C71" s="36"/>
-      <c r="D71" s="36"/>
-      <c r="E71" s="36"/>
-      <c r="F71" s="36"/>
-      <c r="G71" s="36"/>
-      <c r="H71" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="I71" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="J71" s="33">
+      <c r="B71" s="37"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="37"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="I71" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="J71" s="34">
         <v>15</v>
       </c>
-      <c r="K71" s="36" t="s">
+      <c r="K71" s="37" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11">
+      <c r="B72" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="C72" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="D72" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="38"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="I72" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="J72" s="38">
+        <v>1</v>
+      </c>
+      <c r="K72" s="38" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11">
+      <c r="B73" s="38"/>
+      <c r="C73" s="38"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="38"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="I73" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="J73" s="38">
+        <v>2</v>
+      </c>
+      <c r="K73" s="38" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11">
+      <c r="B74" s="38"/>
+      <c r="C74" s="38"/>
+      <c r="D74" s="38"/>
+      <c r="E74" s="38"/>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="I74" s="38" t="s">
+        <v>205</v>
+      </c>
+      <c r="J74" s="38">
+        <v>4</v>
+      </c>
+      <c r="K74" s="38" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11">
+      <c r="B75" s="38"/>
+      <c r="C75" s="38"/>
+      <c r="D75" s="38"/>
+      <c r="E75" s="38"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="38"/>
+      <c r="H75" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="I75" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="J75" s="38">
+        <v>8</v>
+      </c>
+      <c r="K75" s="38" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11">
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="38"/>
+      <c r="H76" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="I76" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="J76" s="38">
+        <v>16</v>
+      </c>
+      <c r="K76" s="38" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11">
+      <c r="B77" s="38"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="38"/>
+      <c r="E77" s="38"/>
+      <c r="F77" s="38"/>
+      <c r="G77" s="38"/>
+      <c r="H77" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="I77" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="J77" s="38">
+        <v>32</v>
+      </c>
+      <c r="K77" s="38" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11">
+      <c r="B78" s="38"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="38"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="38"/>
+      <c r="H78" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="I78" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="J78" s="38">
+        <v>64</v>
+      </c>
+      <c r="K78" s="38" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11">
+      <c r="B79" s="38"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="38"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="38"/>
+      <c r="H79" s="38" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="72" spans="2:11">
-      <c r="B72" s="37" t="s">
+      <c r="I79" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="C72" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="D72" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="37"/>
-      <c r="F72" s="37"/>
-      <c r="G72" s="37"/>
-      <c r="H72" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="I72" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="J72" s="37">
-        <v>1</v>
-      </c>
-      <c r="K72" s="37" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="73" spans="2:11">
-      <c r="B73" s="37"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="I73" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="J73" s="37">
-        <v>2</v>
-      </c>
-      <c r="K73" s="37" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="74" spans="2:11">
-      <c r="B74" s="37"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="37"/>
-      <c r="G74" s="37"/>
-      <c r="H74" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="I74" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="J74" s="37">
-        <v>4</v>
-      </c>
-      <c r="K74" s="37" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="75" spans="2:11">
-      <c r="B75" s="37"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="37"/>
-      <c r="G75" s="37"/>
-      <c r="H75" s="37" t="s">
-        <v>204</v>
-      </c>
-      <c r="I75" s="37" t="s">
-        <v>205</v>
-      </c>
-      <c r="J75" s="37">
-        <v>8</v>
-      </c>
-      <c r="K75" s="37" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="76" spans="2:11">
-      <c r="B76" s="37"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="37"/>
-      <c r="G76" s="37"/>
-      <c r="H76" s="37" t="s">
-        <v>206</v>
-      </c>
-      <c r="I76" s="37" t="s">
-        <v>207</v>
-      </c>
-      <c r="J76" s="37">
-        <v>16</v>
-      </c>
-      <c r="K76" s="37" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="77" spans="2:11">
-      <c r="B77" s="37"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="37"/>
-      <c r="G77" s="37"/>
-      <c r="H77" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="I77" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="J77" s="37">
-        <v>32</v>
-      </c>
-      <c r="K77" s="37" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="78" spans="2:11">
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="37"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="I78" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="J78" s="37">
-        <v>64</v>
-      </c>
-      <c r="K78" s="37" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="79" spans="2:11">
-      <c r="B79" s="37"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="37"/>
-      <c r="G79" s="37"/>
-      <c r="H79" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="I79" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="J79" s="37">
+      <c r="J79" s="38">
         <v>127</v>
       </c>
-      <c r="K79" s="37" t="s">
-        <v>195</v>
+      <c r="K79" s="38" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="80" spans="2:11">
       <c r="B80" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="C80" s="39" t="b">
+        <v>214</v>
+      </c>
+      <c r="C80" s="40" t="b">
         <v>0</v>
       </c>
-      <c r="D80" s="39" t="b">
+      <c r="D80" s="40" t="b">
         <v>1</v>
       </c>
       <c r="E80" s="24"/>
       <c r="F80" s="24"/>
       <c r="G80" s="24"/>
       <c r="H80" s="24" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I80" s="24" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J80" s="24">
         <v>0</v>
@@ -3408,10 +4014,10 @@
       <c r="F81" s="24"/>
       <c r="G81" s="24"/>
       <c r="H81" s="24" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I81" s="24" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J81" s="24">
         <v>1</v>
@@ -3419,593 +4025,593 @@
       <c r="K81" s="24"/>
     </row>
     <row r="82" spans="2:11">
-      <c r="B82" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="C82" s="41" t="b">
+      <c r="B82" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="C82" s="42" t="b">
         <v>0</v>
       </c>
-      <c r="D82" s="41" t="b">
+      <c r="D82" s="42" t="b">
         <v>1</v>
       </c>
-      <c r="E82" s="42"/>
-      <c r="F82" s="42"/>
-      <c r="G82" s="42"/>
-      <c r="H82" s="42" t="s">
+      <c r="E82" s="43"/>
+      <c r="F82" s="43"/>
+      <c r="G82" s="43"/>
+      <c r="H82" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="I82" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="J82" s="42">
+      <c r="I82" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="J82" s="43">
         <v>0</v>
       </c>
-      <c r="K82" s="42" t="s">
-        <v>217</v>
+      <c r="K82" s="43" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="83" spans="2:11">
-      <c r="B83" s="42"/>
-      <c r="C83" s="42"/>
-      <c r="D83" s="42"/>
-      <c r="E83" s="42"/>
-      <c r="F83" s="42"/>
-      <c r="G83" s="42"/>
-      <c r="H83" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="I83" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="J83" s="42">
+      <c r="B83" s="43"/>
+      <c r="C83" s="43"/>
+      <c r="D83" s="43"/>
+      <c r="E83" s="43"/>
+      <c r="F83" s="43"/>
+      <c r="G83" s="43"/>
+      <c r="H83" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="I83" s="43" t="s">
+        <v>221</v>
+      </c>
+      <c r="J83" s="43">
         <v>1</v>
       </c>
-      <c r="K83" s="42" t="s">
-        <v>220</v>
+      <c r="K83" s="43" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="84" spans="2:11">
-      <c r="B84" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="C84" s="27" t="b">
+      <c r="B84" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="C84" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="D84" s="27" t="b">
+      <c r="D84" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="E84" s="26"/>
-      <c r="F84" s="26"/>
-      <c r="G84" s="26"/>
-      <c r="H84" s="26" t="s">
-        <v>222</v>
-      </c>
-      <c r="I84" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="J84" s="37">
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="I84" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="J84" s="38">
         <v>1</v>
       </c>
-      <c r="K84" s="26" t="s">
-        <v>224</v>
+      <c r="K84" s="27" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="85" spans="2:11">
-      <c r="B85" s="26"/>
-      <c r="C85" s="26"/>
-      <c r="D85" s="26"/>
-      <c r="E85" s="26"/>
-      <c r="F85" s="26"/>
-      <c r="G85" s="26"/>
-      <c r="H85" s="26" t="s">
-        <v>225</v>
-      </c>
-      <c r="I85" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="J85" s="37">
+      <c r="B85" s="27"/>
+      <c r="C85" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="I85" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="J85" s="38">
         <v>2</v>
       </c>
-      <c r="K85" s="26" t="s">
-        <v>227</v>
+      <c r="K85" s="27" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="86" spans="2:11">
-      <c r="B86" s="26"/>
-      <c r="C86" s="26"/>
-      <c r="D86" s="26"/>
-      <c r="E86" s="26"/>
-      <c r="F86" s="26"/>
-      <c r="G86" s="26"/>
-      <c r="H86" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="I86" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="J86" s="37">
+      <c r="B86" s="27"/>
+      <c r="C86" s="27"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
+      <c r="H86" s="27" t="s">
+        <v>230</v>
+      </c>
+      <c r="I86" s="27" t="s">
+        <v>231</v>
+      </c>
+      <c r="J86" s="38">
         <v>4</v>
       </c>
-      <c r="K86" s="26" t="s">
-        <v>230</v>
+      <c r="K86" s="27" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="87" spans="2:11">
-      <c r="B87" s="26"/>
-      <c r="C87" s="26"/>
-      <c r="D87" s="26"/>
-      <c r="E87" s="26"/>
-      <c r="F87" s="26"/>
-      <c r="G87" s="26"/>
-      <c r="H87" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="I87" s="26" t="s">
-        <v>232</v>
-      </c>
-      <c r="J87" s="37">
+      <c r="B87" s="27"/>
+      <c r="C87" s="27"/>
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="I87" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="J87" s="38">
         <v>8</v>
       </c>
-      <c r="K87" s="26" t="s">
-        <v>232</v>
+      <c r="K87" s="27" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="2:11">
-      <c r="B88" s="26"/>
-      <c r="C88" s="26"/>
-      <c r="D88" s="26"/>
-      <c r="E88" s="26"/>
-      <c r="F88" s="26"/>
-      <c r="G88" s="26"/>
-      <c r="H88" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="I88" s="26" t="s">
-        <v>234</v>
-      </c>
-      <c r="J88" s="37">
+      <c r="B88" s="27"/>
+      <c r="C88" s="27"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="27"/>
+      <c r="F88" s="27"/>
+      <c r="G88" s="27"/>
+      <c r="H88" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="I88" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="J88" s="38">
         <v>16</v>
       </c>
-      <c r="K88" s="26" t="s">
-        <v>234</v>
+      <c r="K88" s="27" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="89" spans="2:11">
-      <c r="B89" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="C89" s="41" t="b">
+      <c r="B89" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="C89" s="42" t="b">
         <v>0</v>
       </c>
-      <c r="D89" s="27" t="b">
+      <c r="D89" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="E89" s="42"/>
-      <c r="F89" s="42"/>
-      <c r="G89" s="42"/>
-      <c r="H89" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="I89" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="J89" s="42">
+      <c r="E89" s="43"/>
+      <c r="F89" s="43"/>
+      <c r="G89" s="43"/>
+      <c r="H89" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="I89" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="J89" s="43">
         <v>1</v>
       </c>
-      <c r="K89" s="42" t="s">
-        <v>237</v>
+      <c r="K89" s="43" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="2:11">
-      <c r="B90" s="42"/>
-      <c r="C90" s="42"/>
-      <c r="D90" s="42"/>
-      <c r="E90" s="42"/>
-      <c r="F90" s="42"/>
-      <c r="G90" s="42"/>
-      <c r="H90" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="I90" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="J90" s="42">
+      <c r="B90" s="43"/>
+      <c r="C90" s="43"/>
+      <c r="D90" s="43"/>
+      <c r="E90" s="43"/>
+      <c r="F90" s="43"/>
+      <c r="G90" s="43"/>
+      <c r="H90" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="I90" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="J90" s="43">
         <v>2</v>
       </c>
-      <c r="K90" s="42" t="s">
-        <v>239</v>
+      <c r="K90" s="43" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="91" spans="2:11">
-      <c r="B91" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="C91" s="27" t="b">
+      <c r="B91" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="C91" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="D91" s="27" t="b">
+      <c r="D91" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="E91" s="26"/>
-      <c r="F91" s="26"/>
-      <c r="G91" s="26"/>
-      <c r="H91" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="I91" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="J91" s="26">
+      <c r="E91" s="27"/>
+      <c r="F91" s="27"/>
+      <c r="G91" s="27"/>
+      <c r="H91" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="I91" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="J91" s="27">
         <v>1</v>
       </c>
-      <c r="K91" s="26" t="s">
-        <v>195</v>
+      <c r="K91" s="27" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="2:11">
-      <c r="B92" s="26"/>
-      <c r="C92" s="26"/>
-      <c r="D92" s="26"/>
-      <c r="E92" s="26"/>
-      <c r="F92" s="26"/>
-      <c r="G92" s="26"/>
-      <c r="H92" s="44" t="s">
-        <v>241</v>
-      </c>
-      <c r="I92" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="J92" s="26">
+      <c r="B92" s="27"/>
+      <c r="C92" s="27"/>
+      <c r="D92" s="27"/>
+      <c r="E92" s="27"/>
+      <c r="F92" s="27"/>
+      <c r="G92" s="27"/>
+      <c r="H92" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="I92" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="J92" s="27">
         <v>2</v>
       </c>
-      <c r="K92" s="26" t="s">
-        <v>242</v>
+      <c r="K92" s="27" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="93" spans="2:11">
-      <c r="B93" s="26"/>
-      <c r="C93" s="26"/>
-      <c r="D93" s="26"/>
-      <c r="E93" s="26"/>
-      <c r="F93" s="26"/>
-      <c r="G93" s="26"/>
-      <c r="H93" s="44" t="s">
-        <v>243</v>
-      </c>
-      <c r="I93" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="J93" s="26">
+      <c r="B93" s="27"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="27"/>
+      <c r="G93" s="27"/>
+      <c r="H93" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="I93" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="J93" s="27">
         <v>3</v>
       </c>
-      <c r="K93" s="26" t="s">
-        <v>244</v>
+      <c r="K93" s="27" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="94" spans="2:11">
-      <c r="B94" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="C94" s="46" t="b">
+      <c r="B94" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="C94" s="47" t="b">
         <v>0</v>
       </c>
-      <c r="D94" s="46" t="b">
+      <c r="D94" s="47" t="b">
         <v>1</v>
       </c>
-      <c r="E94" s="45"/>
-      <c r="F94" s="45"/>
-      <c r="G94" s="45"/>
-      <c r="H94" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="I94" s="45" t="s">
-        <v>247</v>
-      </c>
-      <c r="J94" s="45">
+      <c r="E94" s="46"/>
+      <c r="F94" s="46"/>
+      <c r="G94" s="46"/>
+      <c r="H94" s="48" t="s">
+        <v>248</v>
+      </c>
+      <c r="I94" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="J94" s="46">
         <v>1</v>
       </c>
-      <c r="K94" s="45" t="s">
-        <v>247</v>
+      <c r="K94" s="46" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="95" spans="2:11">
-      <c r="B95" s="45"/>
-      <c r="C95" s="45"/>
-      <c r="D95" s="45"/>
-      <c r="E95" s="45"/>
-      <c r="F95" s="45"/>
-      <c r="G95" s="45"/>
-      <c r="H95" s="47" t="s">
-        <v>248</v>
-      </c>
-      <c r="I95" s="45" t="s">
+      <c r="B95" s="46"/>
+      <c r="C95" s="46"/>
+      <c r="D95" s="46"/>
+      <c r="E95" s="46"/>
+      <c r="F95" s="46"/>
+      <c r="G95" s="46"/>
+      <c r="H95" s="48" t="s">
+        <v>250</v>
+      </c>
+      <c r="I95" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="J95" s="45">
+      <c r="J95" s="46">
         <v>2</v>
       </c>
-      <c r="K95" s="45" t="s">
+      <c r="K95" s="46" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="96" spans="2:11">
-      <c r="B96" s="45"/>
-      <c r="C96" s="45"/>
-      <c r="D96" s="45"/>
-      <c r="E96" s="45"/>
-      <c r="F96" s="45"/>
-      <c r="G96" s="45"/>
-      <c r="H96" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="I96" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="J96" s="45">
+      <c r="B96" s="46"/>
+      <c r="C96" s="46"/>
+      <c r="D96" s="46"/>
+      <c r="E96" s="46"/>
+      <c r="F96" s="46"/>
+      <c r="G96" s="46"/>
+      <c r="H96" s="48" t="s">
+        <v>251</v>
+      </c>
+      <c r="I96" s="46" t="s">
+        <v>252</v>
+      </c>
+      <c r="J96" s="46">
         <v>3</v>
       </c>
-      <c r="K96" s="45" t="s">
-        <v>250</v>
+      <c r="K96" s="46" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="97" spans="2:11">
-      <c r="B97" s="48" t="s">
-        <v>251</v>
-      </c>
-      <c r="C97" s="49" t="b">
+      <c r="B97" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="C97" s="50" t="b">
         <v>0</v>
       </c>
-      <c r="D97" s="49" t="b">
+      <c r="D97" s="50" t="b">
         <v>1</v>
       </c>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="48"/>
-      <c r="H97" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="I97" s="50" t="s">
-        <v>253</v>
-      </c>
-      <c r="J97" s="50">
+      <c r="E97" s="49"/>
+      <c r="F97" s="49"/>
+      <c r="G97" s="49"/>
+      <c r="H97" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="I97" s="51" t="s">
+        <v>255</v>
+      </c>
+      <c r="J97" s="51">
         <v>0</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="98" spans="2:11">
-      <c r="B98" s="48"/>
-      <c r="C98" s="48"/>
-      <c r="D98" s="48"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="50" t="s">
-        <v>255</v>
-      </c>
-      <c r="I98" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="J98" s="50">
+      <c r="B98" s="49"/>
+      <c r="C98" s="49"/>
+      <c r="D98" s="49"/>
+      <c r="E98" s="49"/>
+      <c r="F98" s="49"/>
+      <c r="G98" s="49"/>
+      <c r="H98" s="51" t="s">
+        <v>257</v>
+      </c>
+      <c r="I98" s="51" t="s">
+        <v>258</v>
+      </c>
+      <c r="J98" s="51">
         <v>1</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="99" spans="2:11">
-      <c r="B99" s="48"/>
-      <c r="C99" s="48"/>
-      <c r="D99" s="48"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="50" t="s">
-        <v>258</v>
-      </c>
-      <c r="I99" s="50" t="s">
-        <v>259</v>
-      </c>
-      <c r="J99" s="50">
+      <c r="B99" s="49"/>
+      <c r="C99" s="49"/>
+      <c r="D99" s="49"/>
+      <c r="E99" s="49"/>
+      <c r="F99" s="49"/>
+      <c r="G99" s="49"/>
+      <c r="H99" s="51" t="s">
+        <v>260</v>
+      </c>
+      <c r="I99" s="51" t="s">
+        <v>261</v>
+      </c>
+      <c r="J99" s="51">
         <v>2</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="2:11">
-      <c r="B100" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="C100" s="52" t="b">
+      <c r="B100" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="C100" s="53" t="b">
         <v>0</v>
       </c>
-      <c r="D100" s="52" t="b">
+      <c r="D100" s="53" t="b">
         <v>1</v>
       </c>
-      <c r="E100" s="51"/>
-      <c r="F100" s="51"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51" t="s">
-        <v>261</v>
-      </c>
-      <c r="I100" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="J100" s="51">
+      <c r="E100" s="52"/>
+      <c r="F100" s="52"/>
+      <c r="G100" s="52"/>
+      <c r="H100" s="52" t="s">
+        <v>263</v>
+      </c>
+      <c r="I100" s="52" t="s">
+        <v>264</v>
+      </c>
+      <c r="J100" s="52">
         <v>1</v>
       </c>
-      <c r="K100" s="51" t="s">
-        <v>262</v>
+      <c r="K100" s="52" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="2:11">
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="51"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51" t="s">
-        <v>263</v>
-      </c>
-      <c r="I101" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="J101" s="51">
+      <c r="B101" s="52"/>
+      <c r="C101" s="52"/>
+      <c r="D101" s="52"/>
+      <c r="E101" s="52"/>
+      <c r="F101" s="52"/>
+      <c r="G101" s="52"/>
+      <c r="H101" s="52" t="s">
+        <v>265</v>
+      </c>
+      <c r="I101" s="52" t="s">
+        <v>266</v>
+      </c>
+      <c r="J101" s="52">
         <v>2</v>
       </c>
-      <c r="K101" s="51" t="s">
-        <v>264</v>
+      <c r="K101" s="52" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="102" spans="2:11">
-      <c r="B102" s="51"/>
-      <c r="C102" s="51"/>
-      <c r="D102" s="51"/>
-      <c r="E102" s="51"/>
-      <c r="F102" s="51"/>
-      <c r="G102" s="51"/>
-      <c r="H102" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="I102" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="J102" s="51">
+      <c r="B102" s="52"/>
+      <c r="C102" s="52"/>
+      <c r="D102" s="52"/>
+      <c r="E102" s="52"/>
+      <c r="F102" s="52"/>
+      <c r="G102" s="52"/>
+      <c r="H102" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="I102" s="52" t="s">
+        <v>268</v>
+      </c>
+      <c r="J102" s="52">
         <v>3</v>
       </c>
-      <c r="K102" s="51" t="s">
-        <v>266</v>
+      <c r="K102" s="52" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="103" spans="2:11">
-      <c r="B103" s="51"/>
-      <c r="C103" s="51"/>
-      <c r="D103" s="51"/>
-      <c r="E103" s="51"/>
-      <c r="F103" s="51"/>
-      <c r="G103" s="51"/>
-      <c r="H103" s="51" t="s">
-        <v>267</v>
-      </c>
-      <c r="I103" s="51" t="s">
-        <v>268</v>
-      </c>
-      <c r="J103" s="51">
+      <c r="B103" s="52"/>
+      <c r="C103" s="52"/>
+      <c r="D103" s="52"/>
+      <c r="E103" s="52"/>
+      <c r="F103" s="52"/>
+      <c r="G103" s="52"/>
+      <c r="H103" s="52" t="s">
+        <v>269</v>
+      </c>
+      <c r="I103" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="J103" s="52">
         <v>4</v>
       </c>
-      <c r="K103" s="51" t="s">
-        <v>268</v>
+      <c r="K103" s="52" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="2:11">
-      <c r="B104" s="51"/>
-      <c r="C104" s="51"/>
-      <c r="D104" s="51"/>
-      <c r="E104" s="51"/>
-      <c r="F104" s="51"/>
-      <c r="G104" s="51"/>
-      <c r="H104" s="51" t="s">
-        <v>269</v>
-      </c>
-      <c r="I104" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="J104" s="51">
+      <c r="B104" s="52"/>
+      <c r="C104" s="52"/>
+      <c r="D104" s="52"/>
+      <c r="E104" s="52"/>
+      <c r="F104" s="52"/>
+      <c r="G104" s="52"/>
+      <c r="H104" s="52" t="s">
+        <v>271</v>
+      </c>
+      <c r="I104" s="52" t="s">
+        <v>272</v>
+      </c>
+      <c r="J104" s="52">
         <v>5</v>
       </c>
-      <c r="K104" s="51" t="s">
-        <v>270</v>
+      <c r="K104" s="52" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="105" spans="2:11">
       <c r="B105" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C105" s="49" t="b">
+        <v>273</v>
+      </c>
+      <c r="C105" s="50" t="b">
         <v>0</v>
       </c>
-      <c r="D105" s="49" t="b">
+      <c r="D105" s="50" t="b">
         <v>1</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J105" s="1">
         <v>1</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="106" spans="2:11">
       <c r="H106" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J106" s="1">
         <v>2</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="107" spans="2:11">
       <c r="B107" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C107" s="49" t="b">
+        <v>278</v>
+      </c>
+      <c r="C107" s="50" t="b">
         <v>0</v>
       </c>
-      <c r="D107" s="49" t="b">
+      <c r="D107" s="50" t="b">
         <v>1</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J107" s="1">
         <v>0</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="108" spans="2:11">
       <c r="H108" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J108" s="1">
         <v>1</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="109" spans="2:11">
       <c r="H109" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J109" s="1">
         <v>2</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="110" spans="2:11">
@@ -4016,150 +4622,164 @@
       <c r="F110" s="25"/>
       <c r="G110" s="25"/>
       <c r="H110" s="25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J110" s="1">
         <v>3</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="111" spans="2:11">
       <c r="H111" s="25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J111" s="1">
         <v>4</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="H112" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J112" s="1">
         <v>5</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="113" spans="8:11">
       <c r="H113" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J113" s="1">
         <v>6</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="114" spans="8:11">
       <c r="H114" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J114" s="1">
         <v>7</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="115" spans="8:11">
       <c r="H115" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J115" s="1">
         <v>8</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="116" spans="8:11">
       <c r="H116" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J116" s="1">
         <v>9</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="117" spans="8:11">
       <c r="H117" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J117" s="1">
         <v>10</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="118" spans="8:11">
       <c r="H118" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J118" s="1">
         <v>11</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="119" spans="8:11">
       <c r="H119" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J119" s="1">
         <v>12</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
+      </c>
+    </row>
+    <row r="120" spans="8:11">
+      <c r="H120" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="J120" s="1">
+        <v>13</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -497,7 +497,7 @@
     <t>鱼饵店</t>
   </si>
   <si>
-    <t>15=鱼饵购买</t>
+    <t>15=鱼饵店</t>
   </si>
   <si>
     <t>Photography</t>
@@ -578,7 +578,7 @@
     <t>商店帮忙</t>
   </si>
   <si>
-    <t>24=工厂制作</t>
+    <t>24=商店帮忙</t>
   </si>
   <si>
     <t>ShowRuleTimeType</t>

--- a/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__enums__.xlsx
@@ -1,26 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" tabRatio="500"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="0" windowHeight="17680" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="smNativeData">
+      <pm:revision xmlns:pm="smNativeData" day="1784543560" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1784543560" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1784543560" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1784543560"/>
     </ext>
   </extLst>
 </workbook>
@@ -236,16 +232,16 @@
     <t>行动值</t>
   </si>
   <si>
-    <t>BasicProductionVolume</t>
-  </si>
-  <si>
-    <t>基本生产量</t>
-  </si>
-  <si>
-    <t>BasicGoodProductRate</t>
-  </si>
-  <si>
-    <t>基础良品率</t>
+    <t>FishLevel</t>
+  </si>
+  <si>
+    <t>钓鱼等级</t>
+  </si>
+  <si>
+    <t>FishExp</t>
+  </si>
+  <si>
+    <t>钓鱼经验</t>
   </si>
   <si>
     <t>ClawMachineValue</t>
@@ -950,192 +946,364 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="13">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="9" formatCode="0%"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
+    </font>
+    <font>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" ulstyle="none" kern="1">
+            <pm:latin face="微软雅黑" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" ulstyle="none" kern="1">
+            <pm:latin face="微软雅黑" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
+      <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="0000FF" ulstyle="single" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <u/>
+      <name val="SimSun"/>
+      <color rgb="FF800080"/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="800080" ulstyle="single" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <u/>
+      <name val="SimSun"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="FF0000" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FFEEECE1"/>
+      <sz val="18"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="EEECE1" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="360" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="360" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="360" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <i/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="7F7F7F" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default" i="1"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" i="1"/>
+            <pm:ea face="SimSun" sz="220" lang="default" i="1"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <b/>
+      <color rgb="FFEEECE1"/>
+      <sz val="15"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="EEECE1" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="300" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="300" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="300" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FFEEECE1"/>
+      <sz val="13"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="EEECE1" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="260" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="260" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="260" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FFEEECE1"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="EEECE1" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
+      <name val="SimSun"/>
+      <color rgb="FF3F3F76"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="3F3F76" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
+      <b/>
+      <color rgb="FF3F3F3F"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="3F3F3F" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
       <b/>
+      <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="FA7D00" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="FFFFFF" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
+      <name val="SimSun"/>
+      <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="FA7D00" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
+      <b/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default" weight="bold"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default" weight="bold"/>
+            <pm:ea face="SimSun" sz="220" lang="default" weight="bold"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <b/>
+      <name val="SimSun"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="006100" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="9C0006" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="9C6500" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="SimSun"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SimSun"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1784543560" fgClr="FFFFFF" ulstyle="none" kern="1">
+            <pm:latin face="SimSun" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="84">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1144,395 +1312,1827 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFFFCC" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFCC99" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00F2F2F2" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFC7CE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFEB9C" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="004F81BD" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00DCE6F1" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CCE4"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00B8CCE4" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95B3D7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="0095B3D7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0504D"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00C0504D" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00F2DCDB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6B8B7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00E6B8B7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA9694"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00DA9694" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBB59"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="009BBB59" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DC"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00EBF1DC" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7E3BB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00D7E3BB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2D69A"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00C2D69A" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8064A2"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="008064A2" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00E4DFEC" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCC0DA"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00CCC0DA" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1A0C7"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00B1A0C7" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BACC6"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="004BACC6" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEEF3"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00DAEEF3" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7DEE8"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00B7DEE8" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92CDDC"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="0092CDDC" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00F79646" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FDE9D9" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCD5B4"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FCD5B4" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFABF8F"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FABF8F" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE1EFD8"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00E1EFD8" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE697"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE697"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFE697" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00BDD7EE" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="0000B0F0" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="0070AD47" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFACB9CA"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACB9CA"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00ACB9CA" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="004472C4" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4AF82"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00F4AF82" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4AF82"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00F4AF82" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC5DFB3"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00C5DFB3" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5DFB3"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00C5DFB3" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6E0B4"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00C6E0B4" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB4C6E7"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00B4C6E7" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA8D08C"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00A8D08C" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8D08C"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00A8D08C" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="0070AD47" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00A5A5A5" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8CAAB"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00F8CAAB" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CAAB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00F8CAAB" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8EA9DB"/>
         <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8EA9DB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7E7E7E"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="007E7E7E" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7E7E7E"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="007E7E7E" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1784543560" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+  <borders count="83">
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="B2B2B2"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4F81BD"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="4F81BD"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFA6BEDD"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="bottom" type="1" style="0" width="30" dist="20" width2="20" rgb="A6BEDD"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="7F7F7F"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="left" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+            <pm:line position="right" type="2" style="0" width="20" dist="20" width2="20" rgb="3F3F3F"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="FF8001"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4F81BD"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF4F81BD"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="4F81BD"/>
+            <pm:line position="bottom" type="2" style="0" width="20" dist="20" width2="20" rgb="4F81BD"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -1547,7 +3147,290 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -1562,7 +3445,250 @@
       <bottom style="thin">
         <color rgb="FFDEE0E3"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="DEE0E3"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
@@ -1577,475 +3703,785 @@
       <bottom style="thin">
         <color rgb="FF1F2329"/>
       </bottom>
-      <diagonal/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="1F2329"/>
+          </pm:border>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560">
+            <pm:line position="top" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="bottom" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="left" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+            <pm:line position="right" type="1" style="0" width="20" dist="20" width2="20" rgb="000000"/>
+          </pm:border>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1784543560"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="28" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="29" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="30" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="31" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="32" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="33" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="34" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="35" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="36" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="12">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="13">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="14">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="16">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" xfId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="10" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="11" xfId="23">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="12" xfId="24">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="13" xfId="25">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="14" xfId="26">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="15" xfId="27">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="16" xfId="28">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="17" xfId="29">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="18" xfId="30">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="19" xfId="31">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="20" xfId="32">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="21" xfId="33">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="22" xfId="34">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="23" xfId="35">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="24" xfId="36">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="25" xfId="37">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="26" xfId="38">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="27" xfId="39">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="28" xfId="40">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="29" xfId="41">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="30" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="31" xfId="43">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="32" xfId="44">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="33" xfId="45">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="34" xfId="46">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="35" xfId="47">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="36" xfId="48">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="40" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="42" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="42" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="50" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="51" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="52" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="53" borderId="52" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="54" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="55" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="56" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="57" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="58" borderId="57" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="59" borderId="58" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="33" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="60" borderId="59" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="61" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="62" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="63" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="64" borderId="63" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="65" borderId="64" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="66" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="67" borderId="66" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="68" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="69" borderId="68" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="70" borderId="69" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="71" borderId="70" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="72" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="73" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="74" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="75" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="76" borderId="75" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="60" borderId="59" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="60" borderId="59" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="77" borderId="76" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="78" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="77" borderId="76" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="79" borderId="78" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="80" borderId="79" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="79" borderId="78" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="81" borderId="80" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="82" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3" customBuiltin="1"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5" customBuiltin="1"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6" customBuiltin="1"